--- a/data/mainboard_ipos.xlsx
+++ b/data/mainboard_ipos.xlsx
@@ -2677,7 +2677,7 @@
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>2026-09-12 23:14:55</t>
+          <t>2026-09-13 13:49:32</t>
         </is>
       </c>
     </row>
@@ -2761,7 +2761,7 @@
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>2026-09-12 23:14:55</t>
+          <t>2026-09-13 13:49:32</t>
         </is>
       </c>
     </row>
@@ -2897,7 +2897,7 @@
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>2026-09-12 23:14:55</t>
+          <t>2026-09-13 13:49:32</t>
         </is>
       </c>
     </row>
@@ -3101,7 +3101,7 @@
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>2026-09-12 23:14:55</t>
+          <t>2026-09-13 13:49:32</t>
         </is>
       </c>
     </row>
@@ -3169,7 +3169,7 @@
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>2026-09-12 23:14:55</t>
+          <t>2026-09-13 13:49:32</t>
         </is>
       </c>
     </row>
@@ -3509,7 +3509,7 @@
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>2026-09-12 23:14:55</t>
+          <t>2026-09-13 13:49:32</t>
         </is>
       </c>
     </row>
@@ -3577,7 +3577,7 @@
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>2026-09-12 23:14:55</t>
+          <t>2026-09-13 13:49:32</t>
         </is>
       </c>
     </row>
@@ -3641,7 +3641,7 @@
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>2026-09-12 23:14:55</t>
+          <t>2026-09-13 13:49:32</t>
         </is>
       </c>
     </row>
@@ -3705,7 +3705,7 @@
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>2026-09-12 23:14:55</t>
+          <t>2026-09-13 13:49:32</t>
         </is>
       </c>
     </row>
@@ -3769,7 +3769,7 @@
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>2026-09-12 23:14:55</t>
+          <t>2026-09-13 13:49:32</t>
         </is>
       </c>
     </row>
@@ -3833,7 +3833,7 @@
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>2026-09-12 23:14:55</t>
+          <t>2026-09-13 13:49:32</t>
         </is>
       </c>
     </row>
@@ -3897,7 +3897,7 @@
       </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t>2026-09-12 23:14:55</t>
+          <t>2026-09-13 13:49:32</t>
         </is>
       </c>
     </row>

--- a/data/mainboard_ipos.xlsx
+++ b/data/mainboard_ipos.xlsx
@@ -2677,7 +2677,7 @@
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>2026-09-13 13:49:32</t>
+          <t>2026-09-13 23:42:35</t>
         </is>
       </c>
     </row>
@@ -2761,7 +2761,7 @@
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>2026-09-13 13:49:32</t>
+          <t>2026-09-13 23:42:35</t>
         </is>
       </c>
     </row>
@@ -2897,7 +2897,7 @@
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>2026-09-13 13:49:32</t>
+          <t>2026-09-13 23:42:35</t>
         </is>
       </c>
     </row>
@@ -3101,7 +3101,7 @@
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>2026-09-13 13:49:32</t>
+          <t>2026-09-13 23:42:35</t>
         </is>
       </c>
     </row>
@@ -3169,7 +3169,7 @@
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>2026-09-13 13:49:32</t>
+          <t>2026-09-13 23:42:35</t>
         </is>
       </c>
     </row>
@@ -3509,7 +3509,7 @@
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>2026-09-13 13:49:32</t>
+          <t>2026-09-13 23:42:35</t>
         </is>
       </c>
     </row>
@@ -3577,7 +3577,7 @@
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>2026-09-13 13:49:32</t>
+          <t>2026-09-13 23:42:35</t>
         </is>
       </c>
     </row>
@@ -3641,7 +3641,7 @@
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>2026-09-13 13:49:32</t>
+          <t>2026-09-13 23:42:35</t>
         </is>
       </c>
     </row>
@@ -3705,7 +3705,7 @@
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>2026-09-13 13:49:32</t>
+          <t>2026-09-13 23:42:35</t>
         </is>
       </c>
     </row>
@@ -3769,7 +3769,7 @@
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>2026-09-13 13:49:32</t>
+          <t>2026-09-13 23:42:35</t>
         </is>
       </c>
     </row>
@@ -3833,7 +3833,7 @@
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>2026-09-13 13:49:32</t>
+          <t>2026-09-13 23:42:35</t>
         </is>
       </c>
     </row>
@@ -3897,7 +3897,7 @@
       </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t>2026-09-13 13:49:32</t>
+          <t>2026-09-13 23:42:35</t>
         </is>
       </c>
     </row>

--- a/data/mainboard_ipos.xlsx
+++ b/data/mainboard_ipos.xlsx
@@ -2677,7 +2677,7 @@
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>2026-09-13 23:42:35</t>
+          <t>2026-09-14 14:26:13</t>
         </is>
       </c>
     </row>
@@ -2761,7 +2761,7 @@
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>2026-09-13 23:42:35</t>
+          <t>2026-09-14 14:26:13</t>
         </is>
       </c>
     </row>
@@ -2897,7 +2897,7 @@
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>2026-09-13 23:42:35</t>
+          <t>2026-09-14 14:26:13</t>
         </is>
       </c>
     </row>
@@ -3101,7 +3101,7 @@
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>2026-09-13 23:42:35</t>
+          <t>2026-09-14 14:26:13</t>
         </is>
       </c>
     </row>
@@ -3169,7 +3169,7 @@
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>2026-09-13 23:42:35</t>
+          <t>2026-09-14 14:26:13</t>
         </is>
       </c>
     </row>
@@ -3509,7 +3509,7 @@
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>2026-09-13 23:42:35</t>
+          <t>2026-09-14 14:26:13</t>
         </is>
       </c>
     </row>
@@ -3577,7 +3577,7 @@
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>2026-09-13 23:42:35</t>
+          <t>2026-09-14 14:26:13</t>
         </is>
       </c>
     </row>
@@ -3641,7 +3641,7 @@
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>2026-09-13 23:42:35</t>
+          <t>2026-09-14 14:26:13</t>
         </is>
       </c>
     </row>
@@ -3705,7 +3705,7 @@
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>2026-09-13 23:42:35</t>
+          <t>2026-09-14 14:26:13</t>
         </is>
       </c>
     </row>
@@ -3769,7 +3769,7 @@
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>2026-09-13 23:42:35</t>
+          <t>2026-09-14 14:26:13</t>
         </is>
       </c>
     </row>
@@ -3833,7 +3833,7 @@
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>2026-09-13 23:42:35</t>
+          <t>2026-09-14 14:26:13</t>
         </is>
       </c>
     </row>
@@ -3897,7 +3897,7 @@
       </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t>2026-09-13 23:42:35</t>
+          <t>2026-09-14 14:26:13</t>
         </is>
       </c>
     </row>

--- a/data/mainboard_ipos.xlsx
+++ b/data/mainboard_ipos.xlsx
@@ -2677,7 +2677,7 @@
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>2026-09-14 14:26:13</t>
+          <t>2026-09-15 14:11:37</t>
         </is>
       </c>
     </row>
@@ -2761,7 +2761,7 @@
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>2026-09-14 14:26:13</t>
+          <t>2026-09-15 14:11:37</t>
         </is>
       </c>
     </row>
@@ -2773,9 +2773,9 @@
       </c>
       <c r="B29" t="inlineStr"/>
       <c r="C29" t="inlineStr"/>
-      <c r="D29" s="3" t="inlineStr">
-        <is>
-          <t>Closed</t>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>Listed</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -2824,12 +2824,12 @@
       <c r="P29" t="inlineStr"/>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/pranavconstructions/PCL02</t>
+          <t>https://www.moneycontrol.com/ipo/construction-residentialcommercial-complexes/pranavconstructions/PCL02</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>2026-09-11 13:34:16</t>
+          <t>2026-09-15 14:11:37</t>
         </is>
       </c>
     </row>
@@ -2897,7 +2897,7 @@
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>2026-09-14 14:26:13</t>
+          <t>2026-09-15 14:11:37</t>
         </is>
       </c>
     </row>
@@ -2965,7 +2965,7 @@
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>2026-09-11 13:34:16</t>
+          <t>2026-09-15 14:11:37</t>
         </is>
       </c>
     </row>
@@ -3101,7 +3101,7 @@
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>2026-09-14 14:26:13</t>
+          <t>2026-09-15 14:11:37</t>
         </is>
       </c>
     </row>
@@ -3169,7 +3169,7 @@
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>2026-09-14 14:26:13</t>
+          <t>2026-09-15 14:11:37</t>
         </is>
       </c>
     </row>
@@ -3509,7 +3509,7 @@
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>2026-09-14 14:26:13</t>
+          <t>2026-09-15 14:11:37</t>
         </is>
       </c>
     </row>
@@ -3577,7 +3577,7 @@
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>2026-09-14 14:26:13</t>
+          <t>2026-09-15 14:11:37</t>
         </is>
       </c>
     </row>
@@ -3641,7 +3641,7 @@
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>2026-09-14 14:26:13</t>
+          <t>2026-09-15 14:11:37</t>
         </is>
       </c>
     </row>
@@ -3705,7 +3705,7 @@
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>2026-09-14 14:26:13</t>
+          <t>2026-09-15 14:11:37</t>
         </is>
       </c>
     </row>
@@ -3769,7 +3769,7 @@
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>2026-09-14 14:26:13</t>
+          <t>2026-09-15 14:11:37</t>
         </is>
       </c>
     </row>
@@ -3833,7 +3833,7 @@
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>2026-09-14 14:26:13</t>
+          <t>2026-09-15 14:11:37</t>
         </is>
       </c>
     </row>
@@ -3897,7 +3897,7 @@
       </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t>2026-09-14 14:26:13</t>
+          <t>2026-09-15 14:11:37</t>
         </is>
       </c>
     </row>

--- a/data/mainboard_ipos.xlsx
+++ b/data/mainboard_ipos.xlsx
@@ -2813,15 +2813,31 @@
           <t>14880</t>
         </is>
       </c>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr"/>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>165</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>19800</t>
+        </is>
+      </c>
       <c r="N29" t="inlineStr">
         <is>
           <t>121</t>
         </is>
       </c>
-      <c r="O29" t="inlineStr"/>
-      <c r="P29" t="inlineStr"/>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>4920</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
       <c r="Q29" t="inlineStr">
         <is>
           <t>https://www.moneycontrol.com/ipo/construction-residentialcommercial-complexes/pranavconstructions/PCL02</t>
@@ -2829,7 +2845,7 @@
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>2026-09-15 14:11:37</t>
+          <t>2026-09-16 14:06:13</t>
         </is>
       </c>
     </row>
@@ -2841,9 +2857,9 @@
       </c>
       <c r="B30" t="inlineStr"/>
       <c r="C30" t="inlineStr"/>
-      <c r="D30" s="3" t="inlineStr">
-        <is>
-          <t>Closed</t>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>Listed</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -2892,12 +2908,12 @@
       <c r="P30" t="inlineStr"/>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/glasswallsystemsindia/GWSIL</t>
+          <t>https://www.moneycontrol.com/ipo/glassglass-products/glasswallsystemsindia/GWSIL</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>2026-09-15 14:11:37</t>
+          <t>2026-09-16 14:06:13</t>
         </is>
       </c>
     </row>
@@ -2909,9 +2925,9 @@
       </c>
       <c r="B31" t="inlineStr"/>
       <c r="C31" t="inlineStr"/>
-      <c r="D31" s="3" t="inlineStr">
-        <is>
-          <t>Closed</t>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>Listed</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -2960,12 +2976,12 @@
       <c r="P31" t="inlineStr"/>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/kanoharelectricals/KEL09</t>
+          <t>https://www.moneycontrol.com/ipo/electric-equipment/kanoharelectricals/KEL09</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>2026-09-15 14:11:37</t>
+          <t>2026-09-16 14:06:13</t>
         </is>
       </c>
     </row>
@@ -2977,9 +2993,9 @@
       </c>
       <c r="B32" t="inlineStr"/>
       <c r="C32" t="inlineStr"/>
-      <c r="D32" s="3" t="inlineStr">
-        <is>
-          <t>Closed</t>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>Listed</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -3028,12 +3044,12 @@
       <c r="P32" t="inlineStr"/>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/prasolchemicals/PCL03</t>
+          <t>https://www.moneycontrol.com/ipo/speciality-chemicals/prasolchemicals/PCL03</t>
         </is>
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>2026-09-11 13:34:16</t>
+          <t>2026-09-16 14:06:13</t>
         </is>
       </c>
     </row>
@@ -3101,7 +3117,7 @@
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>2026-09-15 14:11:37</t>
+          <t>2026-09-16 14:06:13</t>
         </is>
       </c>
     </row>
@@ -3169,7 +3185,7 @@
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>2026-09-15 14:11:37</t>
+          <t>2026-09-16 14:06:13</t>
         </is>
       </c>
     </row>
@@ -3181,9 +3197,9 @@
       </c>
       <c r="B35" t="inlineStr"/>
       <c r="C35" t="inlineStr"/>
-      <c r="D35" s="4" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="D35" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -3225,7 +3241,7 @@
       <c r="M35" t="inlineStr"/>
       <c r="N35" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>49</t>
         </is>
       </c>
       <c r="O35" t="inlineStr"/>
@@ -3237,7 +3253,7 @@
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>2026-09-11 13:34:16</t>
+          <t>2026-09-16 14:06:13</t>
         </is>
       </c>
     </row>
@@ -3249,9 +3265,9 @@
       </c>
       <c r="B36" t="inlineStr"/>
       <c r="C36" t="inlineStr"/>
-      <c r="D36" s="4" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="D36" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -3293,7 +3309,7 @@
       <c r="M36" t="inlineStr"/>
       <c r="N36" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="O36" t="inlineStr"/>
@@ -3305,7 +3321,7 @@
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>2026-09-11 13:34:16</t>
+          <t>2026-09-16 14:06:13</t>
         </is>
       </c>
     </row>
@@ -3565,7 +3581,7 @@
       <c r="M40" t="inlineStr"/>
       <c r="N40" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="O40" t="inlineStr"/>
@@ -3577,7 +3593,7 @@
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>2026-09-15 14:11:37</t>
+          <t>2026-09-16 14:06:13</t>
         </is>
       </c>
     </row>
@@ -3589,9 +3605,9 @@
       </c>
       <c r="B41" t="inlineStr"/>
       <c r="C41" t="inlineStr"/>
-      <c r="D41" s="5" t="inlineStr">
-        <is>
-          <t>Upcoming</t>
+      <c r="D41" s="4" t="inlineStr">
+        <is>
+          <t>Open</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -3621,7 +3637,7 @@
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>79-84</t>
+          <t>84</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
@@ -3641,7 +3657,7 @@
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>2026-09-15 14:11:37</t>
+          <t>2026-09-16 14:06:13</t>
         </is>
       </c>
     </row>
@@ -3653,9 +3669,9 @@
       </c>
       <c r="B42" t="inlineStr"/>
       <c r="C42" t="inlineStr"/>
-      <c r="D42" s="5" t="inlineStr">
-        <is>
-          <t>Upcoming</t>
+      <c r="D42" s="4" t="inlineStr">
+        <is>
+          <t>Open</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -3685,7 +3701,7 @@
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>88-93</t>
+          <t>93</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
@@ -3705,7 +3721,7 @@
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>2026-09-15 14:11:37</t>
+          <t>2026-09-16 14:06:13</t>
         </is>
       </c>
     </row>
@@ -3717,9 +3733,9 @@
       </c>
       <c r="B43" t="inlineStr"/>
       <c r="C43" t="inlineStr"/>
-      <c r="D43" s="5" t="inlineStr">
-        <is>
-          <t>Upcoming</t>
+      <c r="D43" s="4" t="inlineStr">
+        <is>
+          <t>Open</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -3749,7 +3765,7 @@
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>403-424</t>
+          <t>424</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
@@ -3769,7 +3785,7 @@
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>2026-09-15 14:11:37</t>
+          <t>2026-09-16 14:06:13</t>
         </is>
       </c>
     </row>
@@ -3833,7 +3849,7 @@
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>2026-09-15 14:11:37</t>
+          <t>2026-09-16 14:06:13</t>
         </is>
       </c>
     </row>
@@ -3897,7 +3913,7 @@
       </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t>2026-09-15 14:11:37</t>
+          <t>2026-09-16 14:06:13</t>
         </is>
       </c>
     </row>

--- a/data/mainboard_ipos.xlsx
+++ b/data/mainboard_ipos.xlsx
@@ -3061,9 +3061,9 @@
       </c>
       <c r="B33" t="inlineStr"/>
       <c r="C33" t="inlineStr"/>
-      <c r="D33" s="3" t="inlineStr">
-        <is>
-          <t>Closed</t>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>Listed</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -3112,12 +3112,12 @@
       <c r="P33" t="inlineStr"/>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/assetreconstructioncompanyindia/ARCIL</t>
+          <t>https://www.moneycontrol.com/ipo/finance-others/assetreconstructioncompanyindia/ARCIL</t>
         </is>
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>2026-09-16 14:06:13</t>
+          <t>2026-09-17 14:10:12</t>
         </is>
       </c>
     </row>
@@ -3197,9 +3197,9 @@
       </c>
       <c r="B35" t="inlineStr"/>
       <c r="C35" t="inlineStr"/>
-      <c r="D35" s="3" t="inlineStr">
-        <is>
-          <t>Closed</t>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>Listed</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -3248,12 +3248,12 @@
       <c r="P35" t="inlineStr"/>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/lccprojects/LPL02</t>
+          <t>https://www.moneycontrol.com/ipo/construction-infrastructure/lccprojects/LPL02</t>
         </is>
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>2026-09-16 14:06:13</t>
+          <t>2026-09-17 14:10:12</t>
         </is>
       </c>
     </row>
@@ -3265,9 +3265,9 @@
       </c>
       <c r="B36" t="inlineStr"/>
       <c r="C36" t="inlineStr"/>
-      <c r="D36" s="3" t="inlineStr">
-        <is>
-          <t>Closed</t>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>Listed</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -3316,12 +3316,12 @@
       <c r="P36" t="inlineStr"/>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/manipalpaymentidentitysolutions/MPISL</t>
+          <t>https://www.moneycontrol.com/ipo/printingpublishing/manipalpaymentidentitysolutions/MPISL</t>
         </is>
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>2026-09-16 14:06:13</t>
+          <t>2026-09-17 14:10:12</t>
         </is>
       </c>
     </row>
@@ -3333,9 +3333,9 @@
       </c>
       <c r="B37" t="inlineStr"/>
       <c r="C37" t="inlineStr"/>
-      <c r="D37" s="4" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>Listed</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -3377,19 +3377,19 @@
       <c r="M37" t="inlineStr"/>
       <c r="N37" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>73</t>
         </is>
       </c>
       <c r="O37" t="inlineStr"/>
       <c r="P37" t="inlineStr"/>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/rentomojo/RL10</t>
+          <t>https://www.moneycontrol.com/ipo/miscellaneous/rentomojo/RL10</t>
         </is>
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>2026-09-11 13:34:16</t>
+          <t>2026-09-17 14:10:12</t>
         </is>
       </c>
     </row>
@@ -3537,9 +3537,9 @@
       </c>
       <c r="B40" t="inlineStr"/>
       <c r="C40" t="inlineStr"/>
-      <c r="D40" s="4" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="D40" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -3581,7 +3581,7 @@
       <c r="M40" t="inlineStr"/>
       <c r="N40" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>28</t>
         </is>
       </c>
       <c r="O40" t="inlineStr"/>
@@ -3593,7 +3593,7 @@
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>2026-09-16 14:06:13</t>
+          <t>2026-09-17 14:10:12</t>
         </is>
       </c>
     </row>
@@ -3647,7 +3647,11 @@
       </c>
       <c r="L41" t="inlineStr"/>
       <c r="M41" t="inlineStr"/>
-      <c r="N41" t="inlineStr"/>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="O41" t="inlineStr"/>
       <c r="P41" t="inlineStr"/>
       <c r="Q41" t="inlineStr">
@@ -3657,7 +3661,7 @@
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>2026-09-16 14:06:13</t>
+          <t>2026-09-17 14:10:12</t>
         </is>
       </c>
     </row>
@@ -3711,7 +3715,11 @@
       </c>
       <c r="L42" t="inlineStr"/>
       <c r="M42" t="inlineStr"/>
-      <c r="N42" t="inlineStr"/>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
       <c r="O42" t="inlineStr"/>
       <c r="P42" t="inlineStr"/>
       <c r="Q42" t="inlineStr">
@@ -3721,7 +3729,7 @@
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>2026-09-16 14:06:13</t>
+          <t>2026-09-17 14:10:12</t>
         </is>
       </c>
     </row>
@@ -3775,7 +3783,11 @@
       </c>
       <c r="L43" t="inlineStr"/>
       <c r="M43" t="inlineStr"/>
-      <c r="N43" t="inlineStr"/>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="O43" t="inlineStr"/>
       <c r="P43" t="inlineStr"/>
       <c r="Q43" t="inlineStr">
@@ -3785,7 +3797,7 @@
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>2026-09-16 14:06:13</t>
+          <t>2026-09-17 14:10:12</t>
         </is>
       </c>
     </row>
@@ -3797,9 +3809,9 @@
       </c>
       <c r="B44" t="inlineStr"/>
       <c r="C44" t="inlineStr"/>
-      <c r="D44" s="5" t="inlineStr">
-        <is>
-          <t>Upcoming</t>
+      <c r="D44" s="4" t="inlineStr">
+        <is>
+          <t>Open</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -3829,7 +3841,7 @@
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>1700-1785</t>
+          <t>1785</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
@@ -3849,7 +3861,7 @@
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>2026-09-16 14:06:13</t>
+          <t>2026-09-17 14:10:12</t>
         </is>
       </c>
     </row>
@@ -3861,9 +3873,9 @@
       </c>
       <c r="B45" t="inlineStr"/>
       <c r="C45" t="inlineStr"/>
-      <c r="D45" s="5" t="inlineStr">
-        <is>
-          <t>Upcoming</t>
+      <c r="D45" s="4" t="inlineStr">
+        <is>
+          <t>Open</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -3893,7 +3905,7 @@
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>94-99</t>
+          <t>99</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
@@ -3913,7 +3925,7 @@
       </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t>2026-09-16 14:06:13</t>
+          <t>2026-09-17 14:10:12</t>
         </is>
       </c>
     </row>

--- a/data/mainboard_ipos.xlsx
+++ b/data/mainboard_ipos.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Mainboard IPOs" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Mainboard IPOs'!$A$1:$R$56</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Mainboard IPOs'!$A$1:$R$62</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -449,7 +449,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R56"/>
+  <dimension ref="A1:R62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -3469,9 +3469,9 @@
       </c>
       <c r="B39" t="inlineStr"/>
       <c r="C39" t="inlineStr"/>
-      <c r="D39" s="4" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>Listed</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -3509,23 +3509,39 @@
           <t>14980</t>
         </is>
       </c>
-      <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr"/>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>154</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>16478</t>
+        </is>
+      </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="O39" t="inlineStr"/>
-      <c r="P39" t="inlineStr"/>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>1498</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/veegalanddevelopers/VDL02</t>
+          <t>https://www.moneycontrol.com/ipo/construction-residentialcommercial-complexes/veegalanddevelopers/VDL02</t>
         </is>
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>2026-09-15 14:11:37</t>
+          <t>2026-09-18 23:59:33</t>
         </is>
       </c>
     </row>
@@ -3593,7 +3609,7 @@
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>2026-09-17 14:10:12</t>
+          <t>2026-09-18 23:59:33</t>
         </is>
       </c>
     </row>
@@ -3649,19 +3665,19 @@
       <c r="M41" t="inlineStr"/>
       <c r="N41" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="O41" t="inlineStr"/>
       <c r="P41" t="inlineStr"/>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/heromotorsltd/HML02</t>
+          <t>https://www.moneycontrol.com/ipo/heromotors/HML02</t>
         </is>
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>2026-09-17 14:10:12</t>
+          <t>2026-09-18 23:59:33</t>
         </is>
       </c>
     </row>
@@ -3717,19 +3733,19 @@
       <c r="M42" t="inlineStr"/>
       <c r="N42" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>103</t>
         </is>
       </c>
       <c r="O42" t="inlineStr"/>
       <c r="P42" t="inlineStr"/>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/jindalsupremeindialtd/JSI01</t>
+          <t>https://www.moneycontrol.com/ipo/jindalsupremeindia/JSI01</t>
         </is>
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>2026-09-17 14:10:12</t>
+          <t>2026-09-18 23:59:33</t>
         </is>
       </c>
     </row>
@@ -3785,19 +3801,19 @@
       <c r="M43" t="inlineStr"/>
       <c r="N43" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>27</t>
         </is>
       </c>
       <c r="O43" t="inlineStr"/>
       <c r="P43" t="inlineStr"/>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/ssretailltd/SRL03</t>
+          <t>https://www.moneycontrol.com/ipo/ssretail/SRL03</t>
         </is>
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>2026-09-17 14:10:12</t>
+          <t>2026-09-18 23:59:33</t>
         </is>
       </c>
     </row>
@@ -3851,7 +3867,11 @@
       </c>
       <c r="L44" t="inlineStr"/>
       <c r="M44" t="inlineStr"/>
-      <c r="N44" t="inlineStr"/>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="O44" t="inlineStr"/>
       <c r="P44" t="inlineStr"/>
       <c r="Q44" t="inlineStr">
@@ -3861,7 +3881,7 @@
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>2026-09-17 14:10:12</t>
+          <t>2026-09-18 23:59:33</t>
         </is>
       </c>
     </row>
@@ -3915,24 +3935,28 @@
       </c>
       <c r="L45" t="inlineStr"/>
       <c r="M45" t="inlineStr"/>
-      <c r="N45" t="inlineStr"/>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="O45" t="inlineStr"/>
       <c r="P45" t="inlineStr"/>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/sonaselectionindialtd/SIL36</t>
+          <t>https://www.moneycontrol.com/ipo/sonaselectionindia/SIL36</t>
         </is>
       </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t>2026-09-17 14:10:12</t>
+          <t>2026-09-18 23:59:33</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Complete Sports and Management India Ltd</t>
+          <t>Varmora Granito Ltd</t>
         </is>
       </c>
       <c r="B46" t="inlineStr"/>
@@ -3944,33 +3968,37 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Aug 28, 2026</t>
+          <t>Sep 22, 2026</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Sep 01, 2026</t>
+          <t>Sep 24, 2026</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Sep 02, 2026</t>
-        </is>
-      </c>
-      <c r="H46" t="inlineStr"/>
+          <t>Sep 25, 2026</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Sep 29, 2026</t>
+        </is>
+      </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>101</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>128-135</t>
+          <t>140-148</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>135000</t>
+          <t>14948</t>
         </is>
       </c>
       <c r="L46" t="inlineStr"/>
@@ -3980,19 +4008,19 @@
       <c r="P46" t="inlineStr"/>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/completesportsmanagementindialtd/CSMIL</t>
+          <t>https://www.moneycontrol.com/ipo/varmoragranitoltd/VGL</t>
         </is>
       </c>
       <c r="R46" t="inlineStr">
         <is>
-          <t>2026-08-25 09:29:52</t>
+          <t>2026-09-18 23:59:33</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Credent Connect N Care Ltd</t>
+          <t>A-One Steels India Ltd</t>
         </is>
       </c>
       <c r="B47" t="inlineStr"/>
@@ -4004,33 +4032,37 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Aug 13, 2026</t>
+          <t>Sep 24, 2026</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Aug 17, 2026</t>
+          <t>Sep 28, 2026</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Aug 18, 2026</t>
-        </is>
-      </c>
-      <c r="H47" t="inlineStr"/>
+          <t>Sep 29, 2026</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Oct 01, 2026</t>
+        </is>
+      </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>600</t>
+          <t>37</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>179-189</t>
+          <t>385-405</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>113400</t>
+          <t>14985</t>
         </is>
       </c>
       <c r="L47" t="inlineStr"/>
@@ -4040,19 +4072,19 @@
       <c r="P47" t="inlineStr"/>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/credentconnectncareltd/CCC04</t>
+          <t>https://www.moneycontrol.com/ipo/a-onesteelsindialtd/ASIL</t>
         </is>
       </c>
       <c r="R47" t="inlineStr">
         <is>
-          <t>2026-08-10 22:43:12</t>
+          <t>2026-09-18 23:59:33</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Farm Peace Ltd</t>
+          <t>ArMee Infotech Ltd</t>
         </is>
       </c>
       <c r="B48" t="inlineStr"/>
@@ -4064,35 +4096,27 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Sep 01, 2026</t>
+          <t>Sep 23, 2026</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Sep 03, 2026</t>
+          <t>Sep 25, 2026</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Sep 04, 2026</t>
+          <t>Sep 28, 2026</t>
         </is>
       </c>
       <c r="H48" t="inlineStr"/>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>2000</t>
-        </is>
-      </c>
+      <c r="I48" t="inlineStr"/>
       <c r="J48" t="inlineStr">
         <is>
-          <t>59</t>
-        </is>
-      </c>
-      <c r="K48" t="inlineStr">
-        <is>
-          <t>118000</t>
-        </is>
-      </c>
+          <t>350-375</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr"/>
       <c r="L48" t="inlineStr"/>
       <c r="M48" t="inlineStr"/>
       <c r="N48" t="inlineStr"/>
@@ -4100,19 +4124,19 @@
       <c r="P48" t="inlineStr"/>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/farmpeaceltd/FPL02</t>
+          <t>https://www.moneycontrol.com/ipo/armeeinfotechltd/AIL12</t>
         </is>
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>2026-08-27 19:43:03</t>
+          <t>2026-09-18 23:59:33</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Kheria Autocomp Ltd</t>
+          <t>Complete Sports and Management India Ltd</t>
         </is>
       </c>
       <c r="B49" t="inlineStr"/>
@@ -4124,33 +4148,33 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Sep 17, 2026</t>
+          <t>Aug 28, 2026</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Sep 21, 2026</t>
+          <t>Sep 01, 2026</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Sep 22, 2026</t>
+          <t>Sep 02, 2026</t>
         </is>
       </c>
       <c r="H49" t="inlineStr"/>
       <c r="I49" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>96-101</t>
+          <t>128-135</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>121200</t>
+          <t>135000</t>
         </is>
       </c>
       <c r="L49" t="inlineStr"/>
@@ -4160,19 +4184,19 @@
       <c r="P49" t="inlineStr"/>
       <c r="Q49" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/kheriaautocompltd/KAL05</t>
+          <t>https://www.moneycontrol.com/ipo/completesportsmanagementindialtd/CSMIL</t>
         </is>
       </c>
       <c r="R49" t="inlineStr">
         <is>
-          <t>2026-09-11 13:34:16</t>
+          <t>2026-08-25 09:29:52</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Mopshop Distribution Ltd</t>
+          <t>Credent Connect N Care Ltd</t>
         </is>
       </c>
       <c r="B50" t="inlineStr"/>
@@ -4184,33 +4208,33 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Aug 19, 2026</t>
+          <t>Aug 13, 2026</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Aug 21, 2026</t>
+          <t>Aug 17, 2026</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Aug 24, 2026</t>
+          <t>Aug 18, 2026</t>
         </is>
       </c>
       <c r="H50" t="inlineStr"/>
       <c r="I50" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>600</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>138</t>
+          <t>179-189</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>138000</t>
+          <t>113400</t>
         </is>
       </c>
       <c r="L50" t="inlineStr"/>
@@ -4220,19 +4244,19 @@
       <c r="P50" t="inlineStr"/>
       <c r="Q50" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/mopshopdistributionltd/MDL03</t>
+          <t>https://www.moneycontrol.com/ipo/credentconnectncareltd/CCC04</t>
         </is>
       </c>
       <c r="R50" t="inlineStr">
         <is>
-          <t>2026-08-14 21:36:23</t>
+          <t>2026-08-10 22:43:12</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Paluck Technologies Ltd</t>
+          <t>Elevate Campuses Ltd</t>
         </is>
       </c>
       <c r="B51" t="inlineStr"/>
@@ -4244,35 +4268,27 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Aug 28, 2026</t>
+          <t>Sep 23, 2026</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Sep 01, 2026</t>
+          <t>Sep 25, 2026</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Sep 02, 2026</t>
+          <t>Sep 28, 2026</t>
         </is>
       </c>
       <c r="H51" t="inlineStr"/>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
+      <c r="I51" t="inlineStr"/>
       <c r="J51" t="inlineStr">
         <is>
-          <t>46-48</t>
-        </is>
-      </c>
-      <c r="K51" t="inlineStr">
-        <is>
-          <t>144000</t>
-        </is>
-      </c>
+          <t>343-362</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr"/>
       <c r="L51" t="inlineStr"/>
       <c r="M51" t="inlineStr"/>
       <c r="N51" t="inlineStr"/>
@@ -4280,75 +4296,79 @@
       <c r="P51" t="inlineStr"/>
       <c r="Q51" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/palucktechnologiesltd/PTL08</t>
+          <t>https://www.moneycontrol.com/ipo/elevatecampusesltd/ECL04</t>
         </is>
       </c>
       <c r="R51" t="inlineStr">
         <is>
-          <t>2026-08-25 09:29:52</t>
+          <t>2026-09-18 23:59:33</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Purple Style Labs Ltd</t>
+          <t>Farm Peace Ltd</t>
         </is>
       </c>
       <c r="B52" t="inlineStr"/>
       <c r="C52" t="inlineStr"/>
-      <c r="D52" s="4" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="D52" s="5" t="inlineStr">
+        <is>
+          <t>Upcoming</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Aug 31, 2026</t>
+          <t>Sep 01, 2026</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Sep 02, 2026</t>
+          <t>Sep 03, 2026</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Sep 03, 2026</t>
+          <t>Sep 04, 2026</t>
         </is>
       </c>
       <c r="H52" t="inlineStr"/>
-      <c r="I52" t="inlineStr"/>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>575</t>
-        </is>
-      </c>
-      <c r="K52" t="inlineStr"/>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>118000</t>
+        </is>
+      </c>
       <c r="L52" t="inlineStr"/>
       <c r="M52" t="inlineStr"/>
-      <c r="N52" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="N52" t="inlineStr"/>
       <c r="O52" t="inlineStr"/>
       <c r="P52" t="inlineStr"/>
       <c r="Q52" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/purplestylelabsltd/PSL05</t>
+          <t>https://www.moneycontrol.com/ipo/farmpeaceltd/FPL02</t>
         </is>
       </c>
       <c r="R52" t="inlineStr">
         <is>
-          <t>2026-09-02 13:25:30</t>
+          <t>2026-08-27 19:43:03</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Q&amp;T Foods Ltd</t>
+          <t>Kheria Autocomp Ltd</t>
         </is>
       </c>
       <c r="B53" t="inlineStr"/>
@@ -4360,17 +4380,17 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Aug 12, 2026</t>
+          <t>Sep 17, 2026</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Aug 14, 2026</t>
+          <t>Sep 21, 2026</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Aug 17, 2026</t>
+          <t>Sep 22, 2026</t>
         </is>
       </c>
       <c r="H53" t="inlineStr"/>
@@ -4381,12 +4401,12 @@
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>115</t>
+          <t>96-101</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>138000</t>
+          <t>121200</t>
         </is>
       </c>
       <c r="L53" t="inlineStr"/>
@@ -4396,19 +4416,19 @@
       <c r="P53" t="inlineStr"/>
       <c r="Q53" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/qtfoodsltd/QFL</t>
+          <t>https://www.moneycontrol.com/ipo/kheriaautocompltd/KAL05</t>
         </is>
       </c>
       <c r="R53" t="inlineStr">
         <is>
-          <t>2026-08-10 10:24:29</t>
+          <t>2026-09-11 13:34:16</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Shanti Inorganics Ltd</t>
+          <t>Mopshop Distribution Ltd</t>
         </is>
       </c>
       <c r="B54" t="inlineStr"/>
@@ -4420,33 +4440,33 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Aug 31, 2026</t>
+          <t>Aug 19, 2026</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Sep 02, 2026</t>
+          <t>Aug 21, 2026</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Sep 03, 2026</t>
+          <t>Aug 24, 2026</t>
         </is>
       </c>
       <c r="H54" t="inlineStr"/>
       <c r="I54" t="inlineStr">
         <is>
-          <t>1600</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>79-83</t>
+          <t>138</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>132800</t>
+          <t>138000</t>
         </is>
       </c>
       <c r="L54" t="inlineStr"/>
@@ -4456,19 +4476,19 @@
       <c r="P54" t="inlineStr"/>
       <c r="Q54" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/shantiinorganicsltd/SIL34</t>
+          <t>https://www.moneycontrol.com/ipo/mopshopdistributionltd/MDL03</t>
         </is>
       </c>
       <c r="R54" t="inlineStr">
         <is>
-          <t>2026-08-25 09:29:52</t>
+          <t>2026-08-14 21:36:23</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Technocrats Plasma Systems Ltd</t>
+          <t>Paluck Technologies Ltd</t>
         </is>
       </c>
       <c r="B55" t="inlineStr"/>
@@ -4480,33 +4500,33 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Aug 14, 2026</t>
+          <t>Aug 28, 2026</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Aug 18, 2026</t>
+          <t>Sep 01, 2026</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Aug 19, 2026</t>
+          <t>Sep 02, 2026</t>
         </is>
       </c>
       <c r="H55" t="inlineStr"/>
       <c r="I55" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>3000</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>125-132</t>
+          <t>46-48</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>132000</t>
+          <t>144000</t>
         </is>
       </c>
       <c r="L55" t="inlineStr"/>
@@ -4516,77 +4536,417 @@
       <c r="P55" t="inlineStr"/>
       <c r="Q55" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/technocratsplasmasystemsltd/TPSL</t>
+          <t>https://www.moneycontrol.com/ipo/palucktechnologiesltd/PTL08</t>
         </is>
       </c>
       <c r="R55" t="inlineStr">
         <is>
-          <t>2026-08-11 21:41:02</t>
+          <t>2026-08-25 09:29:52</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Vama Wovenfab Ltd</t>
+          <t>Purple Style Labs Ltd</t>
         </is>
       </c>
       <c r="B56" t="inlineStr"/>
       <c r="C56" t="inlineStr"/>
-      <c r="D56" s="5" t="inlineStr">
-        <is>
-          <t>Upcoming</t>
+      <c r="D56" s="4" t="inlineStr">
+        <is>
+          <t>Open</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Sep 15, 2026</t>
+          <t>Aug 31, 2026</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Sep 17, 2026</t>
+          <t>Sep 02, 2026</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Sep 18, 2026</t>
+          <t>Sep 03, 2026</t>
         </is>
       </c>
       <c r="H56" t="inlineStr"/>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>400</t>
-        </is>
-      </c>
+      <c r="I56" t="inlineStr"/>
       <c r="J56" t="inlineStr">
         <is>
-          <t>324-341</t>
-        </is>
-      </c>
-      <c r="K56" t="inlineStr">
-        <is>
-          <t>136400</t>
-        </is>
-      </c>
+          <t>575</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr"/>
       <c r="L56" t="inlineStr"/>
       <c r="M56" t="inlineStr"/>
-      <c r="N56" t="inlineStr"/>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="O56" t="inlineStr"/>
       <c r="P56" t="inlineStr"/>
       <c r="Q56" t="inlineStr">
         <is>
+          <t>https://www.moneycontrol.com/ipo/purplestylelabsltd/PSL05</t>
+        </is>
+      </c>
+      <c r="R56" t="inlineStr">
+        <is>
+          <t>2026-09-02 13:25:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Q&amp;T Foods Ltd</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr"/>
+      <c r="C57" t="inlineStr"/>
+      <c r="D57" s="5" t="inlineStr">
+        <is>
+          <t>Upcoming</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>Aug 12, 2026</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Aug 14, 2026</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Aug 17, 2026</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr"/>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>1200</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>115</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>138000</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr"/>
+      <c r="M57" t="inlineStr"/>
+      <c r="N57" t="inlineStr"/>
+      <c r="O57" t="inlineStr"/>
+      <c r="P57" t="inlineStr"/>
+      <c r="Q57" t="inlineStr">
+        <is>
+          <t>https://www.moneycontrol.com/ipo/qtfoodsltd/QFL</t>
+        </is>
+      </c>
+      <c r="R57" t="inlineStr">
+        <is>
+          <t>2026-08-10 10:24:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Shanti Inorganics Ltd</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr"/>
+      <c r="C58" t="inlineStr"/>
+      <c r="D58" s="5" t="inlineStr">
+        <is>
+          <t>Upcoming</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>Aug 31, 2026</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Sep 02, 2026</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Sep 03, 2026</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr"/>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>1600</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>79-83</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>132800</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr"/>
+      <c r="M58" t="inlineStr"/>
+      <c r="N58" t="inlineStr"/>
+      <c r="O58" t="inlineStr"/>
+      <c r="P58" t="inlineStr"/>
+      <c r="Q58" t="inlineStr">
+        <is>
+          <t>https://www.moneycontrol.com/ipo/shantiinorganicsltd/SIL34</t>
+        </is>
+      </c>
+      <c r="R58" t="inlineStr">
+        <is>
+          <t>2026-08-25 09:29:52</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Swastika Infra Ltd</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr"/>
+      <c r="C59" t="inlineStr"/>
+      <c r="D59" s="5" t="inlineStr">
+        <is>
+          <t>Upcoming</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>Sep 23, 2026</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Sep 25, 2026</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Sep 28, 2026</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr"/>
+      <c r="I59" t="inlineStr"/>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>175-185</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr"/>
+      <c r="M59" t="inlineStr"/>
+      <c r="N59" t="inlineStr"/>
+      <c r="O59" t="inlineStr"/>
+      <c r="P59" t="inlineStr"/>
+      <c r="Q59" t="inlineStr">
+        <is>
+          <t>https://www.moneycontrol.com/ipo/swastikainfraltd/SIL37</t>
+        </is>
+      </c>
+      <c r="R59" t="inlineStr">
+        <is>
+          <t>2026-09-18 23:59:33</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Technocrats Plasma Systems Ltd</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr"/>
+      <c r="C60" t="inlineStr"/>
+      <c r="D60" s="5" t="inlineStr">
+        <is>
+          <t>Upcoming</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>Aug 14, 2026</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Aug 18, 2026</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Aug 19, 2026</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr"/>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>125-132</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>132000</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr"/>
+      <c r="M60" t="inlineStr"/>
+      <c r="N60" t="inlineStr"/>
+      <c r="O60" t="inlineStr"/>
+      <c r="P60" t="inlineStr"/>
+      <c r="Q60" t="inlineStr">
+        <is>
+          <t>https://www.moneycontrol.com/ipo/technocratsplasmasystemsltd/TPSL</t>
+        </is>
+      </c>
+      <c r="R60" t="inlineStr">
+        <is>
+          <t>2026-08-11 21:41:02</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Unitec Fibres Ltd</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr"/>
+      <c r="C61" t="inlineStr"/>
+      <c r="D61" s="5" t="inlineStr">
+        <is>
+          <t>Upcoming</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>Sep 23, 2026</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Sep 25, 2026</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Sep 28, 2026</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr"/>
+      <c r="I61" t="inlineStr"/>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>83-88</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr"/>
+      <c r="M61" t="inlineStr"/>
+      <c r="N61" t="inlineStr"/>
+      <c r="O61" t="inlineStr"/>
+      <c r="P61" t="inlineStr"/>
+      <c r="Q61" t="inlineStr">
+        <is>
+          <t>https://www.moneycontrol.com/ipo/unitecfibresltd/UFL03</t>
+        </is>
+      </c>
+      <c r="R61" t="inlineStr">
+        <is>
+          <t>2026-09-18 23:59:33</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Vama Wovenfab Ltd</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr"/>
+      <c r="C62" t="inlineStr"/>
+      <c r="D62" s="5" t="inlineStr">
+        <is>
+          <t>Upcoming</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>Sep 15, 2026</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Sep 17, 2026</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Sep 18, 2026</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr"/>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>400</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>324-341</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>136400</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr"/>
+      <c r="M62" t="inlineStr"/>
+      <c r="N62" t="inlineStr"/>
+      <c r="O62" t="inlineStr"/>
+      <c r="P62" t="inlineStr"/>
+      <c r="Q62" t="inlineStr">
+        <is>
           <t>https://www.moneycontrol.com/ipo/vamawovenfabltd/VWL01</t>
         </is>
       </c>
-      <c r="R56" t="inlineStr">
+      <c r="R62" t="inlineStr">
         <is>
           <t>2026-09-11 13:34:16</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:R56"/>
+  <autoFilter ref="A1:R62"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/mainboard_ipos.xlsx
+++ b/data/mainboard_ipos.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Mainboard IPOs" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Mainboard IPOs'!$A$1:$R$62</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Mainboard IPOs'!$A$1:$R$63</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -449,7 +449,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R62"/>
+  <dimension ref="A1:R63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -3541,7 +3541,7 @@
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>2026-09-18 23:59:33</t>
+          <t>2026-09-19 13:33:35</t>
         </is>
       </c>
     </row>
@@ -3609,7 +3609,7 @@
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>2026-09-18 23:59:33</t>
+          <t>2026-09-19 13:33:35</t>
         </is>
       </c>
     </row>
@@ -3621,9 +3621,9 @@
       </c>
       <c r="B41" t="inlineStr"/>
       <c r="C41" t="inlineStr"/>
-      <c r="D41" s="4" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="D41" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -3665,7 +3665,7 @@
       <c r="M41" t="inlineStr"/>
       <c r="N41" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="O41" t="inlineStr"/>
@@ -3677,7 +3677,7 @@
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>2026-09-18 23:59:33</t>
+          <t>2026-09-19 13:33:35</t>
         </is>
       </c>
     </row>
@@ -3689,9 +3689,9 @@
       </c>
       <c r="B42" t="inlineStr"/>
       <c r="C42" t="inlineStr"/>
-      <c r="D42" s="4" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="D42" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -3733,7 +3733,7 @@
       <c r="M42" t="inlineStr"/>
       <c r="N42" t="inlineStr">
         <is>
-          <t>103</t>
+          <t>181</t>
         </is>
       </c>
       <c r="O42" t="inlineStr"/>
@@ -3745,7 +3745,7 @@
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>2026-09-18 23:59:33</t>
+          <t>2026-09-19 13:33:35</t>
         </is>
       </c>
     </row>
@@ -3881,7 +3881,7 @@
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>2026-09-18 23:59:33</t>
+          <t>2026-09-19 13:33:35</t>
         </is>
       </c>
     </row>
@@ -3949,7 +3949,7 @@
       </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t>2026-09-18 23:59:33</t>
+          <t>2026-09-19 13:33:35</t>
         </is>
       </c>
     </row>
@@ -4013,14 +4013,14 @@
       </c>
       <c r="R46" t="inlineStr">
         <is>
-          <t>2026-09-18 23:59:33</t>
+          <t>2026-09-19 13:33:35</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A-One Steels India Ltd</t>
+          <t>Adroit Industries India Ltd</t>
         </is>
       </c>
       <c r="B47" t="inlineStr"/>
@@ -4032,37 +4032,37 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Sep 24, 2026</t>
+          <t>Sep 23, 2026</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
+          <t>Sep 25, 2026</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
           <t>Sep 28, 2026</t>
         </is>
       </c>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>Sep 29, 2026</t>
-        </is>
-      </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Oct 01, 2026</t>
+          <t>Sep 30, 2026</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>111</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>385-405</t>
+          <t>126-134</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>14985</t>
+          <t>14874</t>
         </is>
       </c>
       <c r="L47" t="inlineStr"/>
@@ -4072,19 +4072,19 @@
       <c r="P47" t="inlineStr"/>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/a-onesteelsindialtd/ASIL</t>
+          <t>https://www.moneycontrol.com/ipo/adroitindustriesindialtd/AIIL01</t>
         </is>
       </c>
       <c r="R47" t="inlineStr">
         <is>
-          <t>2026-09-18 23:59:33</t>
+          <t>2026-09-19 13:33:35</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>ArMee Infotech Ltd</t>
+          <t>Elevate Campuses Ltd</t>
         </is>
       </c>
       <c r="B48" t="inlineStr"/>
@@ -4109,14 +4109,26 @@
           <t>Sep 28, 2026</t>
         </is>
       </c>
-      <c r="H48" t="inlineStr"/>
-      <c r="I48" t="inlineStr"/>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Sep 30, 2026</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>350-375</t>
-        </is>
-      </c>
-      <c r="K48" t="inlineStr"/>
+          <t>343-362</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>14842</t>
+        </is>
+      </c>
       <c r="L48" t="inlineStr"/>
       <c r="M48" t="inlineStr"/>
       <c r="N48" t="inlineStr"/>
@@ -4124,19 +4136,19 @@
       <c r="P48" t="inlineStr"/>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/armeeinfotechltd/AIL12</t>
+          <t>https://www.moneycontrol.com/ipo/elevatecampusesltd/ECL04</t>
         </is>
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>2026-09-18 23:59:33</t>
+          <t>2026-09-19 13:33:35</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Complete Sports and Management India Ltd</t>
+          <t>Swastika Infra Ltd</t>
         </is>
       </c>
       <c r="B49" t="inlineStr"/>
@@ -4148,33 +4160,37 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Aug 28, 2026</t>
+          <t>Sep 23, 2026</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Sep 01, 2026</t>
+          <t>Sep 25, 2026</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Sep 02, 2026</t>
-        </is>
-      </c>
-      <c r="H49" t="inlineStr"/>
+          <t>Sep 28, 2026</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Sep 30, 2026</t>
+        </is>
+      </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>81</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>128-135</t>
+          <t>175-185</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>135000</t>
+          <t>14985</t>
         </is>
       </c>
       <c r="L49" t="inlineStr"/>
@@ -4184,19 +4200,19 @@
       <c r="P49" t="inlineStr"/>
       <c r="Q49" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/completesportsmanagementindialtd/CSMIL</t>
+          <t>https://www.moneycontrol.com/ipo/swastikainfraltd/SIL37</t>
         </is>
       </c>
       <c r="R49" t="inlineStr">
         <is>
-          <t>2026-08-25 09:29:52</t>
+          <t>2026-09-19 13:33:35</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Credent Connect N Care Ltd</t>
+          <t>A-One Steels India Ltd</t>
         </is>
       </c>
       <c r="B50" t="inlineStr"/>
@@ -4208,33 +4224,37 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Aug 13, 2026</t>
+          <t>Sep 24, 2026</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Aug 17, 2026</t>
+          <t>Sep 28, 2026</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Aug 18, 2026</t>
-        </is>
-      </c>
-      <c r="H50" t="inlineStr"/>
+          <t>Sep 29, 2026</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Oct 01, 2026</t>
+        </is>
+      </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>600</t>
+          <t>37</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>179-189</t>
+          <t>385-405</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>113400</t>
+          <t>14985</t>
         </is>
       </c>
       <c r="L50" t="inlineStr"/>
@@ -4244,19 +4264,19 @@
       <c r="P50" t="inlineStr"/>
       <c r="Q50" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/credentconnectncareltd/CCC04</t>
+          <t>https://www.moneycontrol.com/ipo/a-onesteelsindialtd/ASIL</t>
         </is>
       </c>
       <c r="R50" t="inlineStr">
         <is>
-          <t>2026-08-10 22:43:12</t>
+          <t>2026-09-19 13:33:35</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Elevate Campuses Ltd</t>
+          <t>ArMee Infotech Ltd</t>
         </is>
       </c>
       <c r="B51" t="inlineStr"/>
@@ -4285,7 +4305,7 @@
       <c r="I51" t="inlineStr"/>
       <c r="J51" t="inlineStr">
         <is>
-          <t>343-362</t>
+          <t>350-375</t>
         </is>
       </c>
       <c r="K51" t="inlineStr"/>
@@ -4296,19 +4316,19 @@
       <c r="P51" t="inlineStr"/>
       <c r="Q51" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/elevatecampusesltd/ECL04</t>
+          <t>https://www.moneycontrol.com/ipo/armeeinfotechltd/AIL12</t>
         </is>
       </c>
       <c r="R51" t="inlineStr">
         <is>
-          <t>2026-09-18 23:59:33</t>
+          <t>2026-09-19 13:33:35</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Farm Peace Ltd</t>
+          <t>Complete Sports and Management India Ltd</t>
         </is>
       </c>
       <c r="B52" t="inlineStr"/>
@@ -4320,33 +4340,33 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
+          <t>Aug 28, 2026</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
           <t>Sep 01, 2026</t>
         </is>
       </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>Sep 03, 2026</t>
-        </is>
-      </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Sep 04, 2026</t>
+          <t>Sep 02, 2026</t>
         </is>
       </c>
       <c r="H52" t="inlineStr"/>
       <c r="I52" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>128-135</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>118000</t>
+          <t>135000</t>
         </is>
       </c>
       <c r="L52" t="inlineStr"/>
@@ -4356,19 +4376,19 @@
       <c r="P52" t="inlineStr"/>
       <c r="Q52" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/farmpeaceltd/FPL02</t>
+          <t>https://www.moneycontrol.com/ipo/completesportsmanagementindialtd/CSMIL</t>
         </is>
       </c>
       <c r="R52" t="inlineStr">
         <is>
-          <t>2026-08-27 19:43:03</t>
+          <t>2026-08-25 09:29:52</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Kheria Autocomp Ltd</t>
+          <t>Credent Connect N Care Ltd</t>
         </is>
       </c>
       <c r="B53" t="inlineStr"/>
@@ -4380,33 +4400,33 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Sep 17, 2026</t>
+          <t>Aug 13, 2026</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Sep 21, 2026</t>
+          <t>Aug 17, 2026</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Sep 22, 2026</t>
+          <t>Aug 18, 2026</t>
         </is>
       </c>
       <c r="H53" t="inlineStr"/>
       <c r="I53" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>600</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>96-101</t>
+          <t>179-189</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>121200</t>
+          <t>113400</t>
         </is>
       </c>
       <c r="L53" t="inlineStr"/>
@@ -4416,19 +4436,19 @@
       <c r="P53" t="inlineStr"/>
       <c r="Q53" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/kheriaautocompltd/KAL05</t>
+          <t>https://www.moneycontrol.com/ipo/credentconnectncareltd/CCC04</t>
         </is>
       </c>
       <c r="R53" t="inlineStr">
         <is>
-          <t>2026-09-11 13:34:16</t>
+          <t>2026-08-10 22:43:12</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Mopshop Distribution Ltd</t>
+          <t>Farm Peace Ltd</t>
         </is>
       </c>
       <c r="B54" t="inlineStr"/>
@@ -4440,33 +4460,33 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Aug 19, 2026</t>
+          <t>Sep 01, 2026</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Aug 21, 2026</t>
+          <t>Sep 03, 2026</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Aug 24, 2026</t>
+          <t>Sep 04, 2026</t>
         </is>
       </c>
       <c r="H54" t="inlineStr"/>
       <c r="I54" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>138</t>
+          <t>59</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>138000</t>
+          <t>118000</t>
         </is>
       </c>
       <c r="L54" t="inlineStr"/>
@@ -4476,19 +4496,19 @@
       <c r="P54" t="inlineStr"/>
       <c r="Q54" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/mopshopdistributionltd/MDL03</t>
+          <t>https://www.moneycontrol.com/ipo/farmpeaceltd/FPL02</t>
         </is>
       </c>
       <c r="R54" t="inlineStr">
         <is>
-          <t>2026-08-14 21:36:23</t>
+          <t>2026-08-27 19:43:03</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Paluck Technologies Ltd</t>
+          <t>Kheria Autocomp Ltd</t>
         </is>
       </c>
       <c r="B55" t="inlineStr"/>
@@ -4500,33 +4520,33 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Aug 28, 2026</t>
+          <t>Sep 17, 2026</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Sep 01, 2026</t>
+          <t>Sep 21, 2026</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Sep 02, 2026</t>
+          <t>Sep 22, 2026</t>
         </is>
       </c>
       <c r="H55" t="inlineStr"/>
       <c r="I55" t="inlineStr">
         <is>
-          <t>3000</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>46-48</t>
+          <t>96-101</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>144000</t>
+          <t>121200</t>
         </is>
       </c>
       <c r="L55" t="inlineStr"/>
@@ -4536,75 +4556,79 @@
       <c r="P55" t="inlineStr"/>
       <c r="Q55" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/palucktechnologiesltd/PTL08</t>
+          <t>https://www.moneycontrol.com/ipo/kheriaautocompltd/KAL05</t>
         </is>
       </c>
       <c r="R55" t="inlineStr">
         <is>
-          <t>2026-08-25 09:29:52</t>
+          <t>2026-09-11 13:34:16</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Purple Style Labs Ltd</t>
+          <t>Mopshop Distribution Ltd</t>
         </is>
       </c>
       <c r="B56" t="inlineStr"/>
       <c r="C56" t="inlineStr"/>
-      <c r="D56" s="4" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="D56" s="5" t="inlineStr">
+        <is>
+          <t>Upcoming</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Aug 31, 2026</t>
+          <t>Aug 19, 2026</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Sep 02, 2026</t>
+          <t>Aug 21, 2026</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Sep 03, 2026</t>
+          <t>Aug 24, 2026</t>
         </is>
       </c>
       <c r="H56" t="inlineStr"/>
-      <c r="I56" t="inlineStr"/>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>575</t>
-        </is>
-      </c>
-      <c r="K56" t="inlineStr"/>
+          <t>138</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>138000</t>
+        </is>
+      </c>
       <c r="L56" t="inlineStr"/>
       <c r="M56" t="inlineStr"/>
-      <c r="N56" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="N56" t="inlineStr"/>
       <c r="O56" t="inlineStr"/>
       <c r="P56" t="inlineStr"/>
       <c r="Q56" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/purplestylelabsltd/PSL05</t>
+          <t>https://www.moneycontrol.com/ipo/mopshopdistributionltd/MDL03</t>
         </is>
       </c>
       <c r="R56" t="inlineStr">
         <is>
-          <t>2026-09-02 13:25:30</t>
+          <t>2026-08-14 21:36:23</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Q&amp;T Foods Ltd</t>
+          <t>Paluck Technologies Ltd</t>
         </is>
       </c>
       <c r="B57" t="inlineStr"/>
@@ -4616,33 +4640,33 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Aug 12, 2026</t>
+          <t>Aug 28, 2026</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Aug 14, 2026</t>
+          <t>Sep 01, 2026</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Aug 17, 2026</t>
+          <t>Sep 02, 2026</t>
         </is>
       </c>
       <c r="H57" t="inlineStr"/>
       <c r="I57" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>3000</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>115</t>
+          <t>46-48</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>138000</t>
+          <t>144000</t>
         </is>
       </c>
       <c r="L57" t="inlineStr"/>
@@ -4652,26 +4676,26 @@
       <c r="P57" t="inlineStr"/>
       <c r="Q57" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/qtfoodsltd/QFL</t>
+          <t>https://www.moneycontrol.com/ipo/palucktechnologiesltd/PTL08</t>
         </is>
       </c>
       <c r="R57" t="inlineStr">
         <is>
-          <t>2026-08-10 10:24:29</t>
+          <t>2026-08-25 09:29:52</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Shanti Inorganics Ltd</t>
+          <t>Purple Style Labs Ltd</t>
         </is>
       </c>
       <c r="B58" t="inlineStr"/>
       <c r="C58" t="inlineStr"/>
-      <c r="D58" s="5" t="inlineStr">
-        <is>
-          <t>Upcoming</t>
+      <c r="D58" s="4" t="inlineStr">
+        <is>
+          <t>Open</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -4690,41 +4714,37 @@
         </is>
       </c>
       <c r="H58" t="inlineStr"/>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>1600</t>
-        </is>
-      </c>
+      <c r="I58" t="inlineStr"/>
       <c r="J58" t="inlineStr">
         <is>
-          <t>79-83</t>
-        </is>
-      </c>
-      <c r="K58" t="inlineStr">
-        <is>
-          <t>132800</t>
-        </is>
-      </c>
+          <t>575</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr"/>
       <c r="L58" t="inlineStr"/>
       <c r="M58" t="inlineStr"/>
-      <c r="N58" t="inlineStr"/>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="O58" t="inlineStr"/>
       <c r="P58" t="inlineStr"/>
       <c r="Q58" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/shantiinorganicsltd/SIL34</t>
+          <t>https://www.moneycontrol.com/ipo/purplestylelabsltd/PSL05</t>
         </is>
       </c>
       <c r="R58" t="inlineStr">
         <is>
-          <t>2026-08-25 09:29:52</t>
+          <t>2026-09-02 13:25:30</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Swastika Infra Ltd</t>
+          <t>Q&amp;T Foods Ltd</t>
         </is>
       </c>
       <c r="B59" t="inlineStr"/>
@@ -4736,27 +4756,35 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Sep 23, 2026</t>
+          <t>Aug 12, 2026</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Sep 25, 2026</t>
+          <t>Aug 14, 2026</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Sep 28, 2026</t>
+          <t>Aug 17, 2026</t>
         </is>
       </c>
       <c r="H59" t="inlineStr"/>
-      <c r="I59" t="inlineStr"/>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>1200</t>
+        </is>
+      </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>175-185</t>
-        </is>
-      </c>
-      <c r="K59" t="inlineStr"/>
+          <t>115</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>138000</t>
+        </is>
+      </c>
       <c r="L59" t="inlineStr"/>
       <c r="M59" t="inlineStr"/>
       <c r="N59" t="inlineStr"/>
@@ -4764,19 +4792,19 @@
       <c r="P59" t="inlineStr"/>
       <c r="Q59" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/swastikainfraltd/SIL37</t>
+          <t>https://www.moneycontrol.com/ipo/qtfoodsltd/QFL</t>
         </is>
       </c>
       <c r="R59" t="inlineStr">
         <is>
-          <t>2026-09-18 23:59:33</t>
+          <t>2026-08-10 10:24:29</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Technocrats Plasma Systems Ltd</t>
+          <t>Shanti Inorganics Ltd</t>
         </is>
       </c>
       <c r="B60" t="inlineStr"/>
@@ -4788,33 +4816,33 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Aug 14, 2026</t>
+          <t>Aug 31, 2026</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Aug 18, 2026</t>
+          <t>Sep 02, 2026</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Aug 19, 2026</t>
+          <t>Sep 03, 2026</t>
         </is>
       </c>
       <c r="H60" t="inlineStr"/>
       <c r="I60" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>1600</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>125-132</t>
+          <t>79-83</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>132000</t>
+          <t>132800</t>
         </is>
       </c>
       <c r="L60" t="inlineStr"/>
@@ -4824,19 +4852,19 @@
       <c r="P60" t="inlineStr"/>
       <c r="Q60" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/technocratsplasmasystemsltd/TPSL</t>
+          <t>https://www.moneycontrol.com/ipo/shantiinorganicsltd/SIL34</t>
         </is>
       </c>
       <c r="R60" t="inlineStr">
         <is>
-          <t>2026-08-11 21:41:02</t>
+          <t>2026-08-25 09:29:52</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Unitec Fibres Ltd</t>
+          <t>Technocrats Plasma Systems Ltd</t>
         </is>
       </c>
       <c r="B61" t="inlineStr"/>
@@ -4848,27 +4876,35 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Sep 23, 2026</t>
+          <t>Aug 14, 2026</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Sep 25, 2026</t>
+          <t>Aug 18, 2026</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Sep 28, 2026</t>
+          <t>Aug 19, 2026</t>
         </is>
       </c>
       <c r="H61" t="inlineStr"/>
-      <c r="I61" t="inlineStr"/>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>83-88</t>
-        </is>
-      </c>
-      <c r="K61" t="inlineStr"/>
+          <t>125-132</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>132000</t>
+        </is>
+      </c>
       <c r="L61" t="inlineStr"/>
       <c r="M61" t="inlineStr"/>
       <c r="N61" t="inlineStr"/>
@@ -4876,19 +4912,19 @@
       <c r="P61" t="inlineStr"/>
       <c r="Q61" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/unitecfibresltd/UFL03</t>
+          <t>https://www.moneycontrol.com/ipo/technocratsplasmasystemsltd/TPSL</t>
         </is>
       </c>
       <c r="R61" t="inlineStr">
         <is>
-          <t>2026-09-18 23:59:33</t>
+          <t>2026-08-11 21:41:02</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Vama Wovenfab Ltd</t>
+          <t>Unitec Fibres Ltd</t>
         </is>
       </c>
       <c r="B62" t="inlineStr"/>
@@ -4900,33 +4936,33 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Sep 15, 2026</t>
+          <t>Sep 23, 2026</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Sep 17, 2026</t>
+          <t>Sep 25, 2026</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Sep 18, 2026</t>
+          <t>Sep 28, 2026</t>
         </is>
       </c>
       <c r="H62" t="inlineStr"/>
       <c r="I62" t="inlineStr">
         <is>
-          <t>400</t>
+          <t>1600</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>324-341</t>
+          <t>83-88</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>136400</t>
+          <t>140800</t>
         </is>
       </c>
       <c r="L62" t="inlineStr"/>
@@ -4936,17 +4972,77 @@
       <c r="P62" t="inlineStr"/>
       <c r="Q62" t="inlineStr">
         <is>
+          <t>https://www.moneycontrol.com/ipo/unitecfibresltd/UFL03</t>
+        </is>
+      </c>
+      <c r="R62" t="inlineStr">
+        <is>
+          <t>2026-09-18 23:59:33</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Vama Wovenfab Ltd</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr"/>
+      <c r="C63" t="inlineStr"/>
+      <c r="D63" s="5" t="inlineStr">
+        <is>
+          <t>Upcoming</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>Sep 15, 2026</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Sep 17, 2026</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Sep 18, 2026</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr"/>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>400</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>324-341</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>136400</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr"/>
+      <c r="M63" t="inlineStr"/>
+      <c r="N63" t="inlineStr"/>
+      <c r="O63" t="inlineStr"/>
+      <c r="P63" t="inlineStr"/>
+      <c r="Q63" t="inlineStr">
+        <is>
           <t>https://www.moneycontrol.com/ipo/vamawovenfabltd/VWL01</t>
         </is>
       </c>
-      <c r="R62" t="inlineStr">
+      <c r="R63" t="inlineStr">
         <is>
           <t>2026-09-11 13:34:16</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:R62"/>
+  <autoFilter ref="A1:R63"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/mainboard_ipos.xlsx
+++ b/data/mainboard_ipos.xlsx
@@ -3541,7 +3541,7 @@
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>2026-09-19 13:33:35</t>
+          <t>2026-09-19 23:31:50</t>
         </is>
       </c>
     </row>
@@ -3609,7 +3609,7 @@
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>2026-09-19 13:33:35</t>
+          <t>2026-09-19 23:31:50</t>
         </is>
       </c>
     </row>
@@ -3677,7 +3677,7 @@
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>2026-09-19 13:33:35</t>
+          <t>2026-09-19 23:31:50</t>
         </is>
       </c>
     </row>
@@ -3745,7 +3745,7 @@
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>2026-09-19 13:33:35</t>
+          <t>2026-09-19 23:31:50</t>
         </is>
       </c>
     </row>
@@ -3881,7 +3881,7 @@
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>2026-09-19 13:33:35</t>
+          <t>2026-09-19 23:31:50</t>
         </is>
       </c>
     </row>
@@ -3949,7 +3949,7 @@
       </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t>2026-09-19 13:33:35</t>
+          <t>2026-09-19 23:31:50</t>
         </is>
       </c>
     </row>
@@ -4013,7 +4013,7 @@
       </c>
       <c r="R46" t="inlineStr">
         <is>
-          <t>2026-09-19 13:33:35</t>
+          <t>2026-09-19 23:31:50</t>
         </is>
       </c>
     </row>
@@ -4077,7 +4077,7 @@
       </c>
       <c r="R47" t="inlineStr">
         <is>
-          <t>2026-09-19 13:33:35</t>
+          <t>2026-09-19 23:31:50</t>
         </is>
       </c>
     </row>
@@ -4141,7 +4141,7 @@
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>2026-09-19 13:33:35</t>
+          <t>2026-09-19 23:31:50</t>
         </is>
       </c>
     </row>
@@ -4205,7 +4205,7 @@
       </c>
       <c r="R49" t="inlineStr">
         <is>
-          <t>2026-09-19 13:33:35</t>
+          <t>2026-09-19 23:31:50</t>
         </is>
       </c>
     </row>
@@ -4269,7 +4269,7 @@
       </c>
       <c r="R50" t="inlineStr">
         <is>
-          <t>2026-09-19 13:33:35</t>
+          <t>2026-09-19 23:31:50</t>
         </is>
       </c>
     </row>
@@ -4321,7 +4321,7 @@
       </c>
       <c r="R51" t="inlineStr">
         <is>
-          <t>2026-09-19 13:33:35</t>
+          <t>2026-09-19 23:31:50</t>
         </is>
       </c>
     </row>

--- a/data/mainboard_ipos.xlsx
+++ b/data/mainboard_ipos.xlsx
@@ -3541,7 +3541,7 @@
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>2026-09-19 23:31:50</t>
+          <t>2026-09-20 14:06:06</t>
         </is>
       </c>
     </row>
@@ -3609,7 +3609,7 @@
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>2026-09-19 23:31:50</t>
+          <t>2026-09-20 14:06:06</t>
         </is>
       </c>
     </row>
@@ -3677,7 +3677,7 @@
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>2026-09-19 23:31:50</t>
+          <t>2026-09-20 14:06:06</t>
         </is>
       </c>
     </row>
@@ -3745,7 +3745,7 @@
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>2026-09-19 23:31:50</t>
+          <t>2026-09-20 14:06:06</t>
         </is>
       </c>
     </row>
@@ -3881,7 +3881,7 @@
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>2026-09-19 23:31:50</t>
+          <t>2026-09-20 14:06:06</t>
         </is>
       </c>
     </row>
@@ -3949,7 +3949,7 @@
       </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t>2026-09-19 23:31:50</t>
+          <t>2026-09-20 14:06:06</t>
         </is>
       </c>
     </row>
@@ -4013,7 +4013,7 @@
       </c>
       <c r="R46" t="inlineStr">
         <is>
-          <t>2026-09-19 23:31:50</t>
+          <t>2026-09-20 14:06:06</t>
         </is>
       </c>
     </row>
@@ -4077,14 +4077,14 @@
       </c>
       <c r="R47" t="inlineStr">
         <is>
-          <t>2026-09-19 23:31:50</t>
+          <t>2026-09-20 14:06:06</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Elevate Campuses Ltd</t>
+          <t>ArMee Infotech Ltd</t>
         </is>
       </c>
       <c r="B48" t="inlineStr"/>
@@ -4116,17 +4116,17 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>343-362</t>
+          <t>350-375</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>14842</t>
+          <t>15000</t>
         </is>
       </c>
       <c r="L48" t="inlineStr"/>
@@ -4136,19 +4136,19 @@
       <c r="P48" t="inlineStr"/>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/elevatecampusesltd/ECL04</t>
+          <t>https://www.moneycontrol.com/ipo/armeeinfotechltd/AIL12</t>
         </is>
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>2026-09-19 23:31:50</t>
+          <t>2026-09-20 14:06:06</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Swastika Infra Ltd</t>
+          <t>Elevate Campuses Ltd</t>
         </is>
       </c>
       <c r="B49" t="inlineStr"/>
@@ -4180,17 +4180,17 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>41</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>175-185</t>
+          <t>343-362</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>14985</t>
+          <t>14842</t>
         </is>
       </c>
       <c r="L49" t="inlineStr"/>
@@ -4200,19 +4200,19 @@
       <c r="P49" t="inlineStr"/>
       <c r="Q49" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/swastikainfraltd/SIL37</t>
+          <t>https://www.moneycontrol.com/ipo/elevatecampusesltd/ECL04</t>
         </is>
       </c>
       <c r="R49" t="inlineStr">
         <is>
-          <t>2026-09-19 23:31:50</t>
+          <t>2026-09-20 14:06:06</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A-One Steels India Ltd</t>
+          <t>Swastika Infra Ltd</t>
         </is>
       </c>
       <c r="B50" t="inlineStr"/>
@@ -4224,32 +4224,32 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Sep 24, 2026</t>
+          <t>Sep 23, 2026</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
+          <t>Sep 25, 2026</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
           <t>Sep 28, 2026</t>
         </is>
       </c>
-      <c r="G50" t="inlineStr">
-        <is>
-          <t>Sep 29, 2026</t>
-        </is>
-      </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Oct 01, 2026</t>
+          <t>Sep 30, 2026</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>81</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>385-405</t>
+          <t>175-185</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
@@ -4264,19 +4264,19 @@
       <c r="P50" t="inlineStr"/>
       <c r="Q50" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/a-onesteelsindialtd/ASIL</t>
+          <t>https://www.moneycontrol.com/ipo/swastikainfraltd/SIL37</t>
         </is>
       </c>
       <c r="R50" t="inlineStr">
         <is>
-          <t>2026-09-19 23:31:50</t>
+          <t>2026-09-20 14:06:06</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>ArMee Infotech Ltd</t>
+          <t>A-One Steels India Ltd</t>
         </is>
       </c>
       <c r="B51" t="inlineStr"/>
@@ -4288,27 +4288,39 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Sep 23, 2026</t>
+          <t>Sep 24, 2026</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Sep 25, 2026</t>
+          <t>Sep 28, 2026</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Sep 28, 2026</t>
-        </is>
-      </c>
-      <c r="H51" t="inlineStr"/>
-      <c r="I51" t="inlineStr"/>
+          <t>Sep 29, 2026</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>Oct 01, 2026</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>350-375</t>
-        </is>
-      </c>
-      <c r="K51" t="inlineStr"/>
+          <t>385-405</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>14985</t>
+        </is>
+      </c>
       <c r="L51" t="inlineStr"/>
       <c r="M51" t="inlineStr"/>
       <c r="N51" t="inlineStr"/>
@@ -4316,12 +4328,12 @@
       <c r="P51" t="inlineStr"/>
       <c r="Q51" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/armeeinfotechltd/AIL12</t>
+          <t>https://www.moneycontrol.com/ipo/a-onesteelsindialtd/ASIL</t>
         </is>
       </c>
       <c r="R51" t="inlineStr">
         <is>
-          <t>2026-09-19 23:31:50</t>
+          <t>2026-09-20 14:06:06</t>
         </is>
       </c>
     </row>

--- a/data/mainboard_ipos.xlsx
+++ b/data/mainboard_ipos.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Mainboard IPOs" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Mainboard IPOs'!$A$1:$R$63</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Mainboard IPOs'!$A$1:$R$67</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -449,7 +449,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R63"/>
+  <dimension ref="A1:R67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -3553,9 +3553,9 @@
       </c>
       <c r="B40" t="inlineStr"/>
       <c r="C40" t="inlineStr"/>
-      <c r="D40" s="3" t="inlineStr">
-        <is>
-          <t>Closed</t>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>Listed</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -3593,23 +3593,39 @@
           <t>14964</t>
         </is>
       </c>
-      <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr"/>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>14964</t>
+        </is>
+      </c>
       <c r="N40" t="inlineStr">
         <is>
           <t>28</t>
         </is>
       </c>
-      <c r="O40" t="inlineStr"/>
-      <c r="P40" t="inlineStr"/>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/manikaplastech/MPL06</t>
+          <t>https://www.moneycontrol.com/ipo/plastic-products/manikaplastech/MPL06</t>
         </is>
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>2026-09-20 14:06:06</t>
+          <t>2026-09-22 14:03:25</t>
         </is>
       </c>
     </row>
@@ -3677,7 +3693,7 @@
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>2026-09-20 14:06:06</t>
+          <t>2026-09-22 14:03:25</t>
         </is>
       </c>
     </row>
@@ -3745,7 +3761,7 @@
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>2026-09-20 14:06:06</t>
+          <t>2026-09-22 14:03:25</t>
         </is>
       </c>
     </row>
@@ -3757,9 +3773,9 @@
       </c>
       <c r="B43" t="inlineStr"/>
       <c r="C43" t="inlineStr"/>
-      <c r="D43" s="4" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="D43" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -3801,7 +3817,7 @@
       <c r="M43" t="inlineStr"/>
       <c r="N43" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>103</t>
         </is>
       </c>
       <c r="O43" t="inlineStr"/>
@@ -3813,7 +3829,7 @@
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>2026-09-18 23:59:33</t>
+          <t>2026-09-22 14:03:25</t>
         </is>
       </c>
     </row>
@@ -3825,9 +3841,9 @@
       </c>
       <c r="B44" t="inlineStr"/>
       <c r="C44" t="inlineStr"/>
-      <c r="D44" s="4" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="D44" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -3869,7 +3885,7 @@
       <c r="M44" t="inlineStr"/>
       <c r="N44" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="O44" t="inlineStr"/>
@@ -3881,7 +3897,7 @@
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>2026-09-20 14:06:06</t>
+          <t>2026-09-22 14:03:25</t>
         </is>
       </c>
     </row>
@@ -3893,9 +3909,9 @@
       </c>
       <c r="B45" t="inlineStr"/>
       <c r="C45" t="inlineStr"/>
-      <c r="D45" s="4" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="D45" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -3949,7 +3965,7 @@
       </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t>2026-09-20 14:06:06</t>
+          <t>2026-09-22 14:03:25</t>
         </is>
       </c>
     </row>
@@ -3961,9 +3977,9 @@
       </c>
       <c r="B46" t="inlineStr"/>
       <c r="C46" t="inlineStr"/>
-      <c r="D46" s="5" t="inlineStr">
-        <is>
-          <t>Upcoming</t>
+      <c r="D46" s="4" t="inlineStr">
+        <is>
+          <t>Open</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -3993,7 +4009,7 @@
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>140-148</t>
+          <t>148</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
@@ -4008,12 +4024,12 @@
       <c r="P46" t="inlineStr"/>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/varmoragranitoltd/VGL</t>
+          <t>https://www.moneycontrol.com/ipo/varmoragranito/VGL</t>
         </is>
       </c>
       <c r="R46" t="inlineStr">
         <is>
-          <t>2026-09-20 14:06:06</t>
+          <t>2026-09-22 14:03:25</t>
         </is>
       </c>
     </row>
@@ -4072,12 +4088,12 @@
       <c r="P47" t="inlineStr"/>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/adroitindustriesindialtd/AIIL01</t>
+          <t>https://www.moneycontrol.com/ipo/adroitindustriesindia/AIIL01</t>
         </is>
       </c>
       <c r="R47" t="inlineStr">
         <is>
-          <t>2026-09-20 14:06:06</t>
+          <t>2026-09-22 14:03:25</t>
         </is>
       </c>
     </row>
@@ -4136,12 +4152,12 @@
       <c r="P48" t="inlineStr"/>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/armeeinfotechltd/AIL12</t>
+          <t>https://www.moneycontrol.com/ipo/armeeinfotech/AIL12</t>
         </is>
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>2026-09-20 14:06:06</t>
+          <t>2026-09-22 14:03:25</t>
         </is>
       </c>
     </row>
@@ -4200,12 +4216,12 @@
       <c r="P49" t="inlineStr"/>
       <c r="Q49" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/elevatecampusesltd/ECL04</t>
+          <t>https://www.moneycontrol.com/ipo/elevatecampuses/ECL04</t>
         </is>
       </c>
       <c r="R49" t="inlineStr">
         <is>
-          <t>2026-09-20 14:06:06</t>
+          <t>2026-09-22 14:03:25</t>
         </is>
       </c>
     </row>
@@ -4264,12 +4280,12 @@
       <c r="P50" t="inlineStr"/>
       <c r="Q50" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/swastikainfraltd/SIL37</t>
+          <t>https://www.moneycontrol.com/ipo/swastikainfra/SIL37</t>
         </is>
       </c>
       <c r="R50" t="inlineStr">
         <is>
-          <t>2026-09-20 14:06:06</t>
+          <t>2026-09-22 14:03:25</t>
         </is>
       </c>
     </row>
@@ -4328,19 +4344,19 @@
       <c r="P51" t="inlineStr"/>
       <c r="Q51" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/a-onesteelsindialtd/ASIL</t>
+          <t>https://www.moneycontrol.com/ipo/a-onesteelsindia/ASIL</t>
         </is>
       </c>
       <c r="R51" t="inlineStr">
         <is>
-          <t>2026-09-20 14:06:06</t>
+          <t>2026-09-22 14:03:25</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Complete Sports and Management India Ltd</t>
+          <t>Moneyview Ltd</t>
         </is>
       </c>
       <c r="B52" t="inlineStr"/>
@@ -4352,33 +4368,37 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Aug 28, 2026</t>
+          <t>Sep 24, 2026</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Sep 01, 2026</t>
+          <t>Sep 28, 2026</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Sep 02, 2026</t>
-        </is>
-      </c>
-      <c r="H52" t="inlineStr"/>
+          <t>Sep 29, 2026</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Oct 01, 2026</t>
+        </is>
+      </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>441</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>128-135</t>
+          <t>32-34</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>135000</t>
+          <t>14994</t>
         </is>
       </c>
       <c r="L52" t="inlineStr"/>
@@ -4388,19 +4408,19 @@
       <c r="P52" t="inlineStr"/>
       <c r="Q52" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/completesportsmanagementindialtd/CSMIL</t>
+          <t>https://www.moneycontrol.com/ipo/moneyviewltd/ML15</t>
         </is>
       </c>
       <c r="R52" t="inlineStr">
         <is>
-          <t>2026-08-25 09:29:52</t>
+          <t>2026-09-22 14:03:25</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Credent Connect N Care Ltd</t>
+          <t>Complete Sports and Management India Ltd</t>
         </is>
       </c>
       <c r="B53" t="inlineStr"/>
@@ -4412,33 +4432,33 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Aug 13, 2026</t>
+          <t>Aug 28, 2026</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Aug 17, 2026</t>
+          <t>Sep 01, 2026</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Aug 18, 2026</t>
+          <t>Sep 02, 2026</t>
         </is>
       </c>
       <c r="H53" t="inlineStr"/>
       <c r="I53" t="inlineStr">
         <is>
-          <t>600</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>179-189</t>
+          <t>128-135</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>113400</t>
+          <t>135000</t>
         </is>
       </c>
       <c r="L53" t="inlineStr"/>
@@ -4448,19 +4468,19 @@
       <c r="P53" t="inlineStr"/>
       <c r="Q53" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/credentconnectncareltd/CCC04</t>
+          <t>https://www.moneycontrol.com/ipo/completesportsmanagementindialtd/CSMIL</t>
         </is>
       </c>
       <c r="R53" t="inlineStr">
         <is>
-          <t>2026-08-10 22:43:12</t>
+          <t>2026-08-25 09:29:52</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Farm Peace Ltd</t>
+          <t>Coreintegra Consulting Services</t>
         </is>
       </c>
       <c r="B54" t="inlineStr"/>
@@ -4472,35 +4492,27 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Sep 01, 2026</t>
+          <t>Sep 23, 2026</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Sep 03, 2026</t>
+          <t>Sep 25, 2026</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Sep 04, 2026</t>
+          <t>Sep 28, 2026</t>
         </is>
       </c>
       <c r="H54" t="inlineStr"/>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>2000</t>
-        </is>
-      </c>
+      <c r="I54" t="inlineStr"/>
       <c r="J54" t="inlineStr">
         <is>
-          <t>59</t>
-        </is>
-      </c>
-      <c r="K54" t="inlineStr">
-        <is>
-          <t>118000</t>
-        </is>
-      </c>
+          <t>74-78</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr"/>
       <c r="L54" t="inlineStr"/>
       <c r="M54" t="inlineStr"/>
       <c r="N54" t="inlineStr"/>
@@ -4508,19 +4520,19 @@
       <c r="P54" t="inlineStr"/>
       <c r="Q54" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/farmpeaceltd/FPL02</t>
+          <t>https://www.moneycontrol.com/ipo/coreintegraconsultingservices/CCSL</t>
         </is>
       </c>
       <c r="R54" t="inlineStr">
         <is>
-          <t>2026-08-27 19:43:03</t>
+          <t>2026-09-22 14:03:25</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Kheria Autocomp Ltd</t>
+          <t>Credent Connect N Care Ltd</t>
         </is>
       </c>
       <c r="B55" t="inlineStr"/>
@@ -4532,33 +4544,33 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Sep 17, 2026</t>
+          <t>Aug 13, 2026</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Sep 21, 2026</t>
+          <t>Aug 17, 2026</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Sep 22, 2026</t>
+          <t>Aug 18, 2026</t>
         </is>
       </c>
       <c r="H55" t="inlineStr"/>
       <c r="I55" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>600</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>96-101</t>
+          <t>179-189</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>121200</t>
+          <t>113400</t>
         </is>
       </c>
       <c r="L55" t="inlineStr"/>
@@ -4568,19 +4580,19 @@
       <c r="P55" t="inlineStr"/>
       <c r="Q55" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/kheriaautocompltd/KAL05</t>
+          <t>https://www.moneycontrol.com/ipo/credentconnectncareltd/CCC04</t>
         </is>
       </c>
       <c r="R55" t="inlineStr">
         <is>
-          <t>2026-09-11 13:34:16</t>
+          <t>2026-08-10 22:43:12</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Mopshop Distribution Ltd</t>
+          <t>Farm Peace Ltd</t>
         </is>
       </c>
       <c r="B56" t="inlineStr"/>
@@ -4592,33 +4604,33 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Aug 19, 2026</t>
+          <t>Sep 01, 2026</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Aug 21, 2026</t>
+          <t>Sep 03, 2026</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Aug 24, 2026</t>
+          <t>Sep 04, 2026</t>
         </is>
       </c>
       <c r="H56" t="inlineStr"/>
       <c r="I56" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>138</t>
+          <t>59</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>138000</t>
+          <t>118000</t>
         </is>
       </c>
       <c r="L56" t="inlineStr"/>
@@ -4628,19 +4640,19 @@
       <c r="P56" t="inlineStr"/>
       <c r="Q56" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/mopshopdistributionltd/MDL03</t>
+          <t>https://www.moneycontrol.com/ipo/farmpeaceltd/FPL02</t>
         </is>
       </c>
       <c r="R56" t="inlineStr">
         <is>
-          <t>2026-08-14 21:36:23</t>
+          <t>2026-08-27 19:43:03</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Paluck Technologies Ltd</t>
+          <t>Green Asia Impex Ltd</t>
         </is>
       </c>
       <c r="B57" t="inlineStr"/>
@@ -4652,35 +4664,27 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Aug 28, 2026</t>
+          <t>Sep 24, 2026</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Sep 01, 2026</t>
+          <t>Sep 28, 2026</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Sep 02, 2026</t>
+          <t>Sep 29, 2026</t>
         </is>
       </c>
       <c r="H57" t="inlineStr"/>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
+      <c r="I57" t="inlineStr"/>
       <c r="J57" t="inlineStr">
         <is>
-          <t>46-48</t>
-        </is>
-      </c>
-      <c r="K57" t="inlineStr">
-        <is>
-          <t>144000</t>
-        </is>
-      </c>
+          <t>85-90</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr"/>
       <c r="L57" t="inlineStr"/>
       <c r="M57" t="inlineStr"/>
       <c r="N57" t="inlineStr"/>
@@ -4688,75 +4692,79 @@
       <c r="P57" t="inlineStr"/>
       <c r="Q57" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/palucktechnologiesltd/PTL08</t>
+          <t>https://www.moneycontrol.com/ipo/greenasiaimpexltd/GAIL01</t>
         </is>
       </c>
       <c r="R57" t="inlineStr">
         <is>
-          <t>2026-08-25 09:29:52</t>
+          <t>2026-09-22 14:03:25</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Purple Style Labs Ltd</t>
+          <t>Kheria Autocomp Ltd</t>
         </is>
       </c>
       <c r="B58" t="inlineStr"/>
       <c r="C58" t="inlineStr"/>
-      <c r="D58" s="4" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="D58" s="5" t="inlineStr">
+        <is>
+          <t>Upcoming</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Aug 31, 2026</t>
+          <t>Sep 17, 2026</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Sep 02, 2026</t>
+          <t>Sep 21, 2026</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Sep 03, 2026</t>
+          <t>Sep 22, 2026</t>
         </is>
       </c>
       <c r="H58" t="inlineStr"/>
-      <c r="I58" t="inlineStr"/>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>1200</t>
+        </is>
+      </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>575</t>
-        </is>
-      </c>
-      <c r="K58" t="inlineStr"/>
+          <t>96-101</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>121200</t>
+        </is>
+      </c>
       <c r="L58" t="inlineStr"/>
       <c r="M58" t="inlineStr"/>
-      <c r="N58" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="N58" t="inlineStr"/>
       <c r="O58" t="inlineStr"/>
       <c r="P58" t="inlineStr"/>
       <c r="Q58" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/purplestylelabsltd/PSL05</t>
+          <t>https://www.moneycontrol.com/ipo/kheriaautocompltd/KAL05</t>
         </is>
       </c>
       <c r="R58" t="inlineStr">
         <is>
-          <t>2026-09-02 13:25:30</t>
+          <t>2026-09-11 13:34:16</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Q&amp;T Foods Ltd</t>
+          <t>Mopshop Distribution Ltd</t>
         </is>
       </c>
       <c r="B59" t="inlineStr"/>
@@ -4768,28 +4776,28 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Aug 12, 2026</t>
+          <t>Aug 19, 2026</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Aug 14, 2026</t>
+          <t>Aug 21, 2026</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Aug 17, 2026</t>
+          <t>Aug 24, 2026</t>
         </is>
       </c>
       <c r="H59" t="inlineStr"/>
       <c r="I59" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>115</t>
+          <t>138</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
@@ -4804,19 +4812,19 @@
       <c r="P59" t="inlineStr"/>
       <c r="Q59" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/qtfoodsltd/QFL</t>
+          <t>https://www.moneycontrol.com/ipo/mopshopdistributionltd/MDL03</t>
         </is>
       </c>
       <c r="R59" t="inlineStr">
         <is>
-          <t>2026-08-10 10:24:29</t>
+          <t>2026-08-14 21:36:23</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Shanti Inorganics Ltd</t>
+          <t>Paluck Technologies Ltd</t>
         </is>
       </c>
       <c r="B60" t="inlineStr"/>
@@ -4828,33 +4836,33 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Aug 31, 2026</t>
+          <t>Aug 28, 2026</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
+          <t>Sep 01, 2026</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
           <t>Sep 02, 2026</t>
-        </is>
-      </c>
-      <c r="G60" t="inlineStr">
-        <is>
-          <t>Sep 03, 2026</t>
         </is>
       </c>
       <c r="H60" t="inlineStr"/>
       <c r="I60" t="inlineStr">
         <is>
-          <t>1600</t>
+          <t>3000</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>79-83</t>
+          <t>46-48</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>132800</t>
+          <t>144000</t>
         </is>
       </c>
       <c r="L60" t="inlineStr"/>
@@ -4864,7 +4872,7 @@
       <c r="P60" t="inlineStr"/>
       <c r="Q60" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/shantiinorganicsltd/SIL34</t>
+          <t>https://www.moneycontrol.com/ipo/palucktechnologiesltd/PTL08</t>
         </is>
       </c>
       <c r="R60" t="inlineStr">
@@ -4876,7 +4884,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Technocrats Plasma Systems Ltd</t>
+          <t>Peshwa Wheat</t>
         </is>
       </c>
       <c r="B61" t="inlineStr"/>
@@ -4888,35 +4896,27 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Aug 14, 2026</t>
+          <t>Sep 24, 2026</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Aug 18, 2026</t>
+          <t>Sep 28, 2026</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Aug 19, 2026</t>
+          <t>Sep 29, 2026</t>
         </is>
       </c>
       <c r="H61" t="inlineStr"/>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>1000</t>
-        </is>
-      </c>
+      <c r="I61" t="inlineStr"/>
       <c r="J61" t="inlineStr">
         <is>
-          <t>125-132</t>
-        </is>
-      </c>
-      <c r="K61" t="inlineStr">
-        <is>
-          <t>132000</t>
-        </is>
-      </c>
+          <t>95-101</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr"/>
       <c r="L61" t="inlineStr"/>
       <c r="M61" t="inlineStr"/>
       <c r="N61" t="inlineStr"/>
@@ -4924,79 +4924,75 @@
       <c r="P61" t="inlineStr"/>
       <c r="Q61" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/technocratsplasmasystemsltd/TPSL</t>
+          <t>https://www.moneycontrol.com/ipo/peshwawheat/PWL01</t>
         </is>
       </c>
       <c r="R61" t="inlineStr">
         <is>
-          <t>2026-08-11 21:41:02</t>
+          <t>2026-09-22 14:03:25</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Unitec Fibres Ltd</t>
+          <t>Purple Style Labs Ltd</t>
         </is>
       </c>
       <c r="B62" t="inlineStr"/>
       <c r="C62" t="inlineStr"/>
-      <c r="D62" s="5" t="inlineStr">
-        <is>
-          <t>Upcoming</t>
+      <c r="D62" s="4" t="inlineStr">
+        <is>
+          <t>Open</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Sep 23, 2026</t>
+          <t>Aug 31, 2026</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Sep 25, 2026</t>
+          <t>Sep 02, 2026</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Sep 28, 2026</t>
+          <t>Sep 03, 2026</t>
         </is>
       </c>
       <c r="H62" t="inlineStr"/>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>1600</t>
-        </is>
-      </c>
+      <c r="I62" t="inlineStr"/>
       <c r="J62" t="inlineStr">
         <is>
-          <t>83-88</t>
-        </is>
-      </c>
-      <c r="K62" t="inlineStr">
-        <is>
-          <t>140800</t>
-        </is>
-      </c>
+          <t>575</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr"/>
       <c r="L62" t="inlineStr"/>
       <c r="M62" t="inlineStr"/>
-      <c r="N62" t="inlineStr"/>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="O62" t="inlineStr"/>
       <c r="P62" t="inlineStr"/>
       <c r="Q62" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/unitecfibresltd/UFL03</t>
+          <t>https://www.moneycontrol.com/ipo/purplestylelabsltd/PSL05</t>
         </is>
       </c>
       <c r="R62" t="inlineStr">
         <is>
-          <t>2026-09-18 23:59:33</t>
+          <t>2026-09-02 13:25:30</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Vama Wovenfab Ltd</t>
+          <t>Q&amp;T Foods Ltd</t>
         </is>
       </c>
       <c r="B63" t="inlineStr"/>
@@ -5008,33 +5004,33 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Sep 15, 2026</t>
+          <t>Aug 12, 2026</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Sep 17, 2026</t>
+          <t>Aug 14, 2026</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Sep 18, 2026</t>
+          <t>Aug 17, 2026</t>
         </is>
       </c>
       <c r="H63" t="inlineStr"/>
       <c r="I63" t="inlineStr">
         <is>
-          <t>400</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>324-341</t>
+          <t>115</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>136400</t>
+          <t>138000</t>
         </is>
       </c>
       <c r="L63" t="inlineStr"/>
@@ -5044,17 +5040,257 @@
       <c r="P63" t="inlineStr"/>
       <c r="Q63" t="inlineStr">
         <is>
+          <t>https://www.moneycontrol.com/ipo/qtfoodsltd/QFL</t>
+        </is>
+      </c>
+      <c r="R63" t="inlineStr">
+        <is>
+          <t>2026-08-10 10:24:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Shanti Inorganics Ltd</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr"/>
+      <c r="C64" t="inlineStr"/>
+      <c r="D64" s="5" t="inlineStr">
+        <is>
+          <t>Upcoming</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>Aug 31, 2026</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Sep 02, 2026</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Sep 03, 2026</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr"/>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>1600</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>79-83</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>132800</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr"/>
+      <c r="M64" t="inlineStr"/>
+      <c r="N64" t="inlineStr"/>
+      <c r="O64" t="inlineStr"/>
+      <c r="P64" t="inlineStr"/>
+      <c r="Q64" t="inlineStr">
+        <is>
+          <t>https://www.moneycontrol.com/ipo/shantiinorganicsltd/SIL34</t>
+        </is>
+      </c>
+      <c r="R64" t="inlineStr">
+        <is>
+          <t>2026-08-25 09:29:52</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Technocrats Plasma Systems Ltd</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr"/>
+      <c r="C65" t="inlineStr"/>
+      <c r="D65" s="5" t="inlineStr">
+        <is>
+          <t>Upcoming</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>Aug 14, 2026</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Aug 18, 2026</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Aug 19, 2026</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr"/>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>125-132</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>132000</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr"/>
+      <c r="M65" t="inlineStr"/>
+      <c r="N65" t="inlineStr"/>
+      <c r="O65" t="inlineStr"/>
+      <c r="P65" t="inlineStr"/>
+      <c r="Q65" t="inlineStr">
+        <is>
+          <t>https://www.moneycontrol.com/ipo/technocratsplasmasystemsltd/TPSL</t>
+        </is>
+      </c>
+      <c r="R65" t="inlineStr">
+        <is>
+          <t>2026-08-11 21:41:02</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Unitec Fibres Ltd</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr"/>
+      <c r="C66" t="inlineStr"/>
+      <c r="D66" s="5" t="inlineStr">
+        <is>
+          <t>Upcoming</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>Sep 23, 2026</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Sep 25, 2026</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Sep 28, 2026</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr"/>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>1600</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>83-88</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>140800</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr"/>
+      <c r="M66" t="inlineStr"/>
+      <c r="N66" t="inlineStr"/>
+      <c r="O66" t="inlineStr"/>
+      <c r="P66" t="inlineStr"/>
+      <c r="Q66" t="inlineStr">
+        <is>
+          <t>https://www.moneycontrol.com/ipo/unitecfibresltd/UFL03</t>
+        </is>
+      </c>
+      <c r="R66" t="inlineStr">
+        <is>
+          <t>2026-09-18 23:59:33</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Vama Wovenfab Ltd</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr"/>
+      <c r="C67" t="inlineStr"/>
+      <c r="D67" s="5" t="inlineStr">
+        <is>
+          <t>Upcoming</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>Sep 15, 2026</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Sep 17, 2026</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Sep 18, 2026</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr"/>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>400</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>324-341</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>136400</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr"/>
+      <c r="M67" t="inlineStr"/>
+      <c r="N67" t="inlineStr"/>
+      <c r="O67" t="inlineStr"/>
+      <c r="P67" t="inlineStr"/>
+      <c r="Q67" t="inlineStr">
+        <is>
           <t>https://www.moneycontrol.com/ipo/vamawovenfabltd/VWL01</t>
         </is>
       </c>
-      <c r="R63" t="inlineStr">
+      <c r="R67" t="inlineStr">
         <is>
           <t>2026-09-11 13:34:16</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:R63"/>
+  <autoFilter ref="A1:R67"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/mainboard_ipos.xlsx
+++ b/data/mainboard_ipos.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Mainboard IPOs" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Mainboard IPOs'!$A$1:$R$67</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Mainboard IPOs'!$A$1:$R$77</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -449,7 +449,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R67"/>
+  <dimension ref="A1:R77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -3705,9 +3705,9 @@
       </c>
       <c r="B42" t="inlineStr"/>
       <c r="C42" t="inlineStr"/>
-      <c r="D42" s="3" t="inlineStr">
-        <is>
-          <t>Closed</t>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>Listed</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -3745,23 +3745,39 @@
           <t>14973</t>
         </is>
       </c>
-      <c r="L42" t="inlineStr"/>
-      <c r="M42" t="inlineStr"/>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>19320</t>
+        </is>
+      </c>
       <c r="N42" t="inlineStr">
         <is>
           <t>181</t>
         </is>
       </c>
-      <c r="O42" t="inlineStr"/>
-      <c r="P42" t="inlineStr"/>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>4347</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/jindalsupremeindia/JSI01</t>
+          <t>https://www.moneycontrol.com/ipo/ironsteel/jindalsupremeindia/JSI01</t>
         </is>
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>2026-09-22 14:03:25</t>
+          <t>2026-09-25 14:20:09</t>
         </is>
       </c>
     </row>
@@ -3841,9 +3857,9 @@
       </c>
       <c r="B44" t="inlineStr"/>
       <c r="C44" t="inlineStr"/>
-      <c r="D44" s="3" t="inlineStr">
-        <is>
-          <t>Closed</t>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>Listed</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -3885,19 +3901,19 @@
       <c r="M44" t="inlineStr"/>
       <c r="N44" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="O44" t="inlineStr"/>
       <c r="P44" t="inlineStr"/>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/nationalstockexchangeindia/NSEoIL</t>
+          <t>https://www.moneycontrol.com/ipo/finance-stock-broking/nationalstockexchangeindia/NSEoIL</t>
         </is>
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>2026-09-22 14:03:25</t>
+          <t>2026-09-25 14:20:09</t>
         </is>
       </c>
     </row>
@@ -3909,9 +3925,9 @@
       </c>
       <c r="B45" t="inlineStr"/>
       <c r="C45" t="inlineStr"/>
-      <c r="D45" s="3" t="inlineStr">
-        <is>
-          <t>Closed</t>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>Listed</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -3949,23 +3965,39 @@
           <t>14850</t>
         </is>
       </c>
-      <c r="L45" t="inlineStr"/>
-      <c r="M45" t="inlineStr"/>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>102</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>15300</t>
+        </is>
+      </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="O45" t="inlineStr"/>
-      <c r="P45" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>450</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/sonaselectionindia/SIL36</t>
+          <t>https://www.moneycontrol.com/ipo/textilesapparel/sonaselectionindia/SIL36</t>
         </is>
       </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t>2026-09-22 14:03:25</t>
+          <t>2026-09-25 14:20:09</t>
         </is>
       </c>
     </row>
@@ -3977,9 +4009,9 @@
       </c>
       <c r="B46" t="inlineStr"/>
       <c r="C46" t="inlineStr"/>
-      <c r="D46" s="4" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="D46" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -4019,7 +4051,11 @@
       </c>
       <c r="L46" t="inlineStr"/>
       <c r="M46" t="inlineStr"/>
-      <c r="N46" t="inlineStr"/>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="O46" t="inlineStr"/>
       <c r="P46" t="inlineStr"/>
       <c r="Q46" t="inlineStr">
@@ -4029,7 +4065,7 @@
       </c>
       <c r="R46" t="inlineStr">
         <is>
-          <t>2026-09-22 14:03:25</t>
+          <t>2026-09-25 14:20:09</t>
         </is>
       </c>
     </row>
@@ -4041,9 +4077,9 @@
       </c>
       <c r="B47" t="inlineStr"/>
       <c r="C47" t="inlineStr"/>
-      <c r="D47" s="5" t="inlineStr">
-        <is>
-          <t>Upcoming</t>
+      <c r="D47" s="4" t="inlineStr">
+        <is>
+          <t>Open</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -4073,7 +4109,7 @@
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>126-134</t>
+          <t>134</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
@@ -4083,7 +4119,11 @@
       </c>
       <c r="L47" t="inlineStr"/>
       <c r="M47" t="inlineStr"/>
-      <c r="N47" t="inlineStr"/>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
       <c r="O47" t="inlineStr"/>
       <c r="P47" t="inlineStr"/>
       <c r="Q47" t="inlineStr">
@@ -4093,7 +4133,7 @@
       </c>
       <c r="R47" t="inlineStr">
         <is>
-          <t>2026-09-22 14:03:25</t>
+          <t>2026-09-25 14:20:09</t>
         </is>
       </c>
     </row>
@@ -4105,9 +4145,9 @@
       </c>
       <c r="B48" t="inlineStr"/>
       <c r="C48" t="inlineStr"/>
-      <c r="D48" s="5" t="inlineStr">
-        <is>
-          <t>Upcoming</t>
+      <c r="D48" s="4" t="inlineStr">
+        <is>
+          <t>Open</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -4137,7 +4177,7 @@
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>350-375</t>
+          <t>375</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
@@ -4147,7 +4187,11 @@
       </c>
       <c r="L48" t="inlineStr"/>
       <c r="M48" t="inlineStr"/>
-      <c r="N48" t="inlineStr"/>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="O48" t="inlineStr"/>
       <c r="P48" t="inlineStr"/>
       <c r="Q48" t="inlineStr">
@@ -4157,7 +4201,7 @@
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>2026-09-22 14:03:25</t>
+          <t>2026-09-25 14:20:09</t>
         </is>
       </c>
     </row>
@@ -4169,9 +4213,9 @@
       </c>
       <c r="B49" t="inlineStr"/>
       <c r="C49" t="inlineStr"/>
-      <c r="D49" s="5" t="inlineStr">
-        <is>
-          <t>Upcoming</t>
+      <c r="D49" s="4" t="inlineStr">
+        <is>
+          <t>Open</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -4201,7 +4245,7 @@
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>343-362</t>
+          <t>362</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
@@ -4211,7 +4255,11 @@
       </c>
       <c r="L49" t="inlineStr"/>
       <c r="M49" t="inlineStr"/>
-      <c r="N49" t="inlineStr"/>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="O49" t="inlineStr"/>
       <c r="P49" t="inlineStr"/>
       <c r="Q49" t="inlineStr">
@@ -4221,7 +4269,7 @@
       </c>
       <c r="R49" t="inlineStr">
         <is>
-          <t>2026-09-22 14:03:25</t>
+          <t>2026-09-25 14:20:09</t>
         </is>
       </c>
     </row>
@@ -4233,9 +4281,9 @@
       </c>
       <c r="B50" t="inlineStr"/>
       <c r="C50" t="inlineStr"/>
-      <c r="D50" s="5" t="inlineStr">
-        <is>
-          <t>Upcoming</t>
+      <c r="D50" s="4" t="inlineStr">
+        <is>
+          <t>Open</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -4265,7 +4313,7 @@
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>175-185</t>
+          <t>185</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
@@ -4275,7 +4323,11 @@
       </c>
       <c r="L50" t="inlineStr"/>
       <c r="M50" t="inlineStr"/>
-      <c r="N50" t="inlineStr"/>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="O50" t="inlineStr"/>
       <c r="P50" t="inlineStr"/>
       <c r="Q50" t="inlineStr">
@@ -4285,7 +4337,7 @@
       </c>
       <c r="R50" t="inlineStr">
         <is>
-          <t>2026-09-22 14:03:25</t>
+          <t>2026-09-25 14:20:09</t>
         </is>
       </c>
     </row>
@@ -4297,9 +4349,9 @@
       </c>
       <c r="B51" t="inlineStr"/>
       <c r="C51" t="inlineStr"/>
-      <c r="D51" s="5" t="inlineStr">
-        <is>
-          <t>Upcoming</t>
+      <c r="D51" s="4" t="inlineStr">
+        <is>
+          <t>Open</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -4329,7 +4381,7 @@
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>385-405</t>
+          <t>405</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
@@ -4339,7 +4391,11 @@
       </c>
       <c r="L51" t="inlineStr"/>
       <c r="M51" t="inlineStr"/>
-      <c r="N51" t="inlineStr"/>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="O51" t="inlineStr"/>
       <c r="P51" t="inlineStr"/>
       <c r="Q51" t="inlineStr">
@@ -4349,7 +4405,7 @@
       </c>
       <c r="R51" t="inlineStr">
         <is>
-          <t>2026-09-22 14:03:25</t>
+          <t>2026-09-25 14:20:09</t>
         </is>
       </c>
     </row>
@@ -4361,9 +4417,9 @@
       </c>
       <c r="B52" t="inlineStr"/>
       <c r="C52" t="inlineStr"/>
-      <c r="D52" s="5" t="inlineStr">
-        <is>
-          <t>Upcoming</t>
+      <c r="D52" s="4" t="inlineStr">
+        <is>
+          <t>Open</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -4393,7 +4449,7 @@
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>32-34</t>
+          <t>34</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
@@ -4403,7 +4459,11 @@
       </c>
       <c r="L52" t="inlineStr"/>
       <c r="M52" t="inlineStr"/>
-      <c r="N52" t="inlineStr"/>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="O52" t="inlineStr"/>
       <c r="P52" t="inlineStr"/>
       <c r="Q52" t="inlineStr">
@@ -4413,52 +4473,56 @@
       </c>
       <c r="R52" t="inlineStr">
         <is>
-          <t>2026-09-22 14:03:25</t>
+          <t>2026-09-25 14:20:09</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Complete Sports and Management India Ltd</t>
+          <t>AceVector Ltd</t>
         </is>
       </c>
       <c r="B53" t="inlineStr"/>
       <c r="C53" t="inlineStr"/>
-      <c r="D53" s="5" t="inlineStr">
-        <is>
-          <t>Upcoming</t>
+      <c r="D53" s="4" t="inlineStr">
+        <is>
+          <t>Open</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Aug 28, 2026</t>
+          <t>Sep 25, 2026</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Sep 01, 2026</t>
+          <t>Sep 29, 2026</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Sep 02, 2026</t>
-        </is>
-      </c>
-      <c r="H53" t="inlineStr"/>
+          <t>Sep 30, 2026</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Oct 05, 2026</t>
+        </is>
+      </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>468</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>128-135</t>
+          <t>32</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>135000</t>
+          <t>14976</t>
         </is>
       </c>
       <c r="L53" t="inlineStr"/>
@@ -4468,51 +4532,63 @@
       <c r="P53" t="inlineStr"/>
       <c r="Q53" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/completesportsmanagementindialtd/CSMIL</t>
+          <t>https://www.moneycontrol.com/ipo/acevectorltd/AL19</t>
         </is>
       </c>
       <c r="R53" t="inlineStr">
         <is>
-          <t>2026-08-25 09:29:52</t>
+          <t>2026-09-25 14:20:09</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Coreintegra Consulting Services</t>
+          <t>German Green Steel &amp; Power Ltd</t>
         </is>
       </c>
       <c r="B54" t="inlineStr"/>
       <c r="C54" t="inlineStr"/>
-      <c r="D54" s="5" t="inlineStr">
-        <is>
-          <t>Upcoming</t>
+      <c r="D54" s="4" t="inlineStr">
+        <is>
+          <t>Open</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Sep 23, 2026</t>
+          <t>Sep 25, 2026</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Sep 25, 2026</t>
+          <t>Sep 29, 2026</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Sep 28, 2026</t>
-        </is>
-      </c>
-      <c r="H54" t="inlineStr"/>
-      <c r="I54" t="inlineStr"/>
+          <t>Sep 30, 2026</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Oct 05, 2026</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>107</t>
+        </is>
+      </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>74-78</t>
-        </is>
-      </c>
-      <c r="K54" t="inlineStr"/>
+          <t>139</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>14873</t>
+        </is>
+      </c>
       <c r="L54" t="inlineStr"/>
       <c r="M54" t="inlineStr"/>
       <c r="N54" t="inlineStr"/>
@@ -4520,57 +4596,61 @@
       <c r="P54" t="inlineStr"/>
       <c r="Q54" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/coreintegraconsultingservices/CCSL</t>
+          <t>https://www.moneycontrol.com/ipo/germangreensteelpowerltd/GGSPL</t>
         </is>
       </c>
       <c r="R54" t="inlineStr">
         <is>
-          <t>2026-09-22 14:03:25</t>
+          <t>2026-09-25 14:20:09</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Credent Connect N Care Ltd</t>
+          <t>Orient Cables India Ltd</t>
         </is>
       </c>
       <c r="B55" t="inlineStr"/>
       <c r="C55" t="inlineStr"/>
-      <c r="D55" s="5" t="inlineStr">
-        <is>
-          <t>Upcoming</t>
+      <c r="D55" s="4" t="inlineStr">
+        <is>
+          <t>Open</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Aug 13, 2026</t>
+          <t>Sep 25, 2026</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Aug 17, 2026</t>
+          <t>Sep 29, 2026</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Aug 18, 2026</t>
-        </is>
-      </c>
-      <c r="H55" t="inlineStr"/>
+          <t>Sep 30, 2026</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>Oct 05, 2026</t>
+        </is>
+      </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>600</t>
+          <t>55</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>179-189</t>
+          <t>272</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>113400</t>
+          <t>14960</t>
         </is>
       </c>
       <c r="L55" t="inlineStr"/>
@@ -4580,57 +4660,61 @@
       <c r="P55" t="inlineStr"/>
       <c r="Q55" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/credentconnectncareltd/CCC04</t>
+          <t>https://www.moneycontrol.com/ipo/orientcablesindialtd/OCIL</t>
         </is>
       </c>
       <c r="R55" t="inlineStr">
         <is>
-          <t>2026-08-10 22:43:12</t>
+          <t>2026-09-25 14:20:09</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Farm Peace Ltd</t>
+          <t>Runwal Enterprises Ltd</t>
         </is>
       </c>
       <c r="B56" t="inlineStr"/>
       <c r="C56" t="inlineStr"/>
-      <c r="D56" s="5" t="inlineStr">
-        <is>
-          <t>Upcoming</t>
+      <c r="D56" s="4" t="inlineStr">
+        <is>
+          <t>Open</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Sep 01, 2026</t>
+          <t>Sep 25, 2026</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Sep 03, 2026</t>
+          <t>Sep 29, 2026</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Sep 04, 2026</t>
-        </is>
-      </c>
-      <c r="H56" t="inlineStr"/>
+          <t>Sep 30, 2026</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Oct 05, 2026</t>
+        </is>
+      </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>49</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>305</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>118000</t>
+          <t>14945</t>
         </is>
       </c>
       <c r="L56" t="inlineStr"/>
@@ -4640,19 +4724,19 @@
       <c r="P56" t="inlineStr"/>
       <c r="Q56" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/farmpeaceltd/FPL02</t>
+          <t>https://www.moneycontrol.com/ipo/runwalenterprisesltd/REL04</t>
         </is>
       </c>
       <c r="R56" t="inlineStr">
         <is>
-          <t>2026-08-27 19:43:03</t>
+          <t>2026-09-25 14:20:09</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Green Asia Impex Ltd</t>
+          <t>SRIT India Ltd</t>
         </is>
       </c>
       <c r="B57" t="inlineStr"/>
@@ -4664,27 +4748,39 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Sep 24, 2026</t>
+          <t>Sep 28, 2026</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Sep 28, 2026</t>
+          <t>Sep 30, 2026</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Sep 29, 2026</t>
-        </is>
-      </c>
-      <c r="H57" t="inlineStr"/>
-      <c r="I57" t="inlineStr"/>
+          <t>Oct 01, 2026</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>Oct 06, 2026</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>115</t>
+        </is>
+      </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>85-90</t>
-        </is>
-      </c>
-      <c r="K57" t="inlineStr"/>
+          <t>123-130</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>14950</t>
+        </is>
+      </c>
       <c r="L57" t="inlineStr"/>
       <c r="M57" t="inlineStr"/>
       <c r="N57" t="inlineStr"/>
@@ -4692,19 +4788,19 @@
       <c r="P57" t="inlineStr"/>
       <c r="Q57" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/greenasiaimpexltd/GAIL01</t>
+          <t>https://www.moneycontrol.com/ipo/sritindialtd/SIL38</t>
         </is>
       </c>
       <c r="R57" t="inlineStr">
         <is>
-          <t>2026-09-22 14:03:25</t>
+          <t>2026-09-25 14:20:09</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Kheria Autocomp Ltd</t>
+          <t>Shah Investors Home Ltd</t>
         </is>
       </c>
       <c r="B58" t="inlineStr"/>
@@ -4716,33 +4812,37 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Sep 17, 2026</t>
+          <t>Sep 28, 2026</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Sep 21, 2026</t>
+          <t>Sep 30, 2026</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Sep 22, 2026</t>
-        </is>
-      </c>
-      <c r="H58" t="inlineStr"/>
+          <t>Oct 01, 2026</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>Oct 06, 2026</t>
+        </is>
+      </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>85</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>96-101</t>
+          <t>159-167</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>121200</t>
+          <t>14195</t>
         </is>
       </c>
       <c r="L58" t="inlineStr"/>
@@ -4752,19 +4852,19 @@
       <c r="P58" t="inlineStr"/>
       <c r="Q58" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/kheriaautocompltd/KAL05</t>
+          <t>https://www.moneycontrol.com/ipo/shahinvestorshomeltd/SIHL</t>
         </is>
       </c>
       <c r="R58" t="inlineStr">
         <is>
-          <t>2026-09-11 13:34:16</t>
+          <t>2026-09-25 14:20:09</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Mopshop Distribution Ltd</t>
+          <t>Complete Sports and Management India Ltd</t>
         </is>
       </c>
       <c r="B59" t="inlineStr"/>
@@ -4776,17 +4876,17 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Aug 19, 2026</t>
+          <t>Aug 28, 2026</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Aug 21, 2026</t>
+          <t>Sep 01, 2026</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Aug 24, 2026</t>
+          <t>Sep 02, 2026</t>
         </is>
       </c>
       <c r="H59" t="inlineStr"/>
@@ -4797,12 +4897,12 @@
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>138</t>
+          <t>128-135</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>138000</t>
+          <t>135000</t>
         </is>
       </c>
       <c r="L59" t="inlineStr"/>
@@ -4812,19 +4912,19 @@
       <c r="P59" t="inlineStr"/>
       <c r="Q59" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/mopshopdistributionltd/MDL03</t>
+          <t>https://www.moneycontrol.com/ipo/completesportsmanagementindialtd/CSMIL</t>
         </is>
       </c>
       <c r="R59" t="inlineStr">
         <is>
-          <t>2026-08-14 21:36:23</t>
+          <t>2026-08-25 09:29:52</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Paluck Technologies Ltd</t>
+          <t>Coreintegra Consulting Services</t>
         </is>
       </c>
       <c r="B60" t="inlineStr"/>
@@ -4836,33 +4936,33 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Aug 28, 2026</t>
+          <t>Sep 23, 2026</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Sep 01, 2026</t>
+          <t>Sep 25, 2026</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Sep 02, 2026</t>
+          <t>Sep 28, 2026</t>
         </is>
       </c>
       <c r="H60" t="inlineStr"/>
       <c r="I60" t="inlineStr">
         <is>
-          <t>3000</t>
+          <t>1600</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>46-48</t>
+          <t>74-78</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>144000</t>
+          <t>124800</t>
         </is>
       </c>
       <c r="L60" t="inlineStr"/>
@@ -4872,19 +4972,19 @@
       <c r="P60" t="inlineStr"/>
       <c r="Q60" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/palucktechnologiesltd/PTL08</t>
+          <t>https://www.moneycontrol.com/ipo/coreintegraconsultingservices/CCSL</t>
         </is>
       </c>
       <c r="R60" t="inlineStr">
         <is>
-          <t>2026-08-25 09:29:52</t>
+          <t>2026-09-22 14:03:25</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Peshwa Wheat</t>
+          <t>Credent Connect N Care Ltd</t>
         </is>
       </c>
       <c r="B61" t="inlineStr"/>
@@ -4896,27 +4996,35 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Sep 24, 2026</t>
+          <t>Aug 13, 2026</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Sep 28, 2026</t>
+          <t>Aug 17, 2026</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Sep 29, 2026</t>
+          <t>Aug 18, 2026</t>
         </is>
       </c>
       <c r="H61" t="inlineStr"/>
-      <c r="I61" t="inlineStr"/>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>600</t>
+        </is>
+      </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>95-101</t>
-        </is>
-      </c>
-      <c r="K61" t="inlineStr"/>
+          <t>179-189</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>113400</t>
+        </is>
+      </c>
       <c r="L61" t="inlineStr"/>
       <c r="M61" t="inlineStr"/>
       <c r="N61" t="inlineStr"/>
@@ -4924,75 +5032,71 @@
       <c r="P61" t="inlineStr"/>
       <c r="Q61" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/peshwawheat/PWL01</t>
+          <t>https://www.moneycontrol.com/ipo/credentconnectncareltd/CCC04</t>
         </is>
       </c>
       <c r="R61" t="inlineStr">
         <is>
-          <t>2026-09-22 14:03:25</t>
+          <t>2026-08-10 22:43:12</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Purple Style Labs Ltd</t>
+          <t>Dove Soft Ltd</t>
         </is>
       </c>
       <c r="B62" t="inlineStr"/>
       <c r="C62" t="inlineStr"/>
-      <c r="D62" s="4" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="D62" s="5" t="inlineStr">
+        <is>
+          <t>Upcoming</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Aug 31, 2026</t>
+          <t>Sep 30, 2026</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Sep 02, 2026</t>
+          <t>Oct 05, 2026</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Sep 03, 2026</t>
+          <t>Oct 06, 2026</t>
         </is>
       </c>
       <c r="H62" t="inlineStr"/>
       <c r="I62" t="inlineStr"/>
       <c r="J62" t="inlineStr">
         <is>
-          <t>575</t>
+          <t>104-111</t>
         </is>
       </c>
       <c r="K62" t="inlineStr"/>
       <c r="L62" t="inlineStr"/>
       <c r="M62" t="inlineStr"/>
-      <c r="N62" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="N62" t="inlineStr"/>
       <c r="O62" t="inlineStr"/>
       <c r="P62" t="inlineStr"/>
       <c r="Q62" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/purplestylelabsltd/PSL05</t>
+          <t>https://www.moneycontrol.com/ipo/dovesoftltd/DSL04</t>
         </is>
       </c>
       <c r="R62" t="inlineStr">
         <is>
-          <t>2026-09-02 13:25:30</t>
+          <t>2026-09-25 14:20:09</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Q&amp;T Foods Ltd</t>
+          <t>Farm Peace Ltd</t>
         </is>
       </c>
       <c r="B63" t="inlineStr"/>
@@ -5004,33 +5108,33 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Aug 12, 2026</t>
+          <t>Sep 01, 2026</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Aug 14, 2026</t>
+          <t>Sep 03, 2026</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Aug 17, 2026</t>
+          <t>Sep 04, 2026</t>
         </is>
       </c>
       <c r="H63" t="inlineStr"/>
       <c r="I63" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>115</t>
+          <t>59</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>138000</t>
+          <t>118000</t>
         </is>
       </c>
       <c r="L63" t="inlineStr"/>
@@ -5040,19 +5144,19 @@
       <c r="P63" t="inlineStr"/>
       <c r="Q63" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/qtfoodsltd/QFL</t>
+          <t>https://www.moneycontrol.com/ipo/farmpeaceltd/FPL02</t>
         </is>
       </c>
       <c r="R63" t="inlineStr">
         <is>
-          <t>2026-08-10 10:24:29</t>
+          <t>2026-08-27 19:43:03</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Shanti Inorganics Ltd</t>
+          <t>Green Asia Impex Ltd</t>
         </is>
       </c>
       <c r="B64" t="inlineStr"/>
@@ -5064,17 +5168,17 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Aug 31, 2026</t>
+          <t>Sep 24, 2026</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Sep 02, 2026</t>
+          <t>Sep 28, 2026</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Sep 03, 2026</t>
+          <t>Sep 29, 2026</t>
         </is>
       </c>
       <c r="H64" t="inlineStr"/>
@@ -5085,12 +5189,12 @@
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>79-83</t>
+          <t>85-90</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>132800</t>
+          <t>144000</t>
         </is>
       </c>
       <c r="L64" t="inlineStr"/>
@@ -5100,19 +5204,19 @@
       <c r="P64" t="inlineStr"/>
       <c r="Q64" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/shantiinorganicsltd/SIL34</t>
+          <t>https://www.moneycontrol.com/ipo/greenasiaimpexltd/GAIL01</t>
         </is>
       </c>
       <c r="R64" t="inlineStr">
         <is>
-          <t>2026-08-25 09:29:52</t>
+          <t>2026-09-22 14:03:25</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Technocrats Plasma Systems Ltd</t>
+          <t>Kheria Autocomp Ltd</t>
         </is>
       </c>
       <c r="B65" t="inlineStr"/>
@@ -5124,33 +5228,33 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Aug 14, 2026</t>
+          <t>Sep 17, 2026</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Aug 18, 2026</t>
+          <t>Sep 21, 2026</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Aug 19, 2026</t>
+          <t>Sep 22, 2026</t>
         </is>
       </c>
       <c r="H65" t="inlineStr"/>
       <c r="I65" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>125-132</t>
+          <t>96-101</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>132000</t>
+          <t>121200</t>
         </is>
       </c>
       <c r="L65" t="inlineStr"/>
@@ -5160,19 +5264,19 @@
       <c r="P65" t="inlineStr"/>
       <c r="Q65" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/technocratsplasmasystemsltd/TPSL</t>
+          <t>https://www.moneycontrol.com/ipo/kheriaautocompltd/KAL05</t>
         </is>
       </c>
       <c r="R65" t="inlineStr">
         <is>
-          <t>2026-08-11 21:41:02</t>
+          <t>2026-09-11 13:34:16</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Unitec Fibres Ltd</t>
+          <t>Mopshop Distribution Ltd</t>
         </is>
       </c>
       <c r="B66" t="inlineStr"/>
@@ -5184,33 +5288,33 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Sep 23, 2026</t>
+          <t>Aug 19, 2026</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Sep 25, 2026</t>
+          <t>Aug 21, 2026</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Sep 28, 2026</t>
+          <t>Aug 24, 2026</t>
         </is>
       </c>
       <c r="H66" t="inlineStr"/>
       <c r="I66" t="inlineStr">
         <is>
-          <t>1600</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>83-88</t>
+          <t>138</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>140800</t>
+          <t>138000</t>
         </is>
       </c>
       <c r="L66" t="inlineStr"/>
@@ -5220,19 +5324,19 @@
       <c r="P66" t="inlineStr"/>
       <c r="Q66" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/unitecfibresltd/UFL03</t>
+          <t>https://www.moneycontrol.com/ipo/mopshopdistributionltd/MDL03</t>
         </is>
       </c>
       <c r="R66" t="inlineStr">
         <is>
-          <t>2026-09-18 23:59:33</t>
+          <t>2026-08-14 21:36:23</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Vama Wovenfab Ltd</t>
+          <t>Paluck Technologies Ltd</t>
         </is>
       </c>
       <c r="B67" t="inlineStr"/>
@@ -5244,33 +5348,33 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Sep 15, 2026</t>
+          <t>Aug 28, 2026</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Sep 17, 2026</t>
+          <t>Sep 01, 2026</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Sep 18, 2026</t>
+          <t>Sep 02, 2026</t>
         </is>
       </c>
       <c r="H67" t="inlineStr"/>
       <c r="I67" t="inlineStr">
         <is>
-          <t>400</t>
+          <t>3000</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>324-341</t>
+          <t>46-48</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>136400</t>
+          <t>144000</t>
         </is>
       </c>
       <c r="L67" t="inlineStr"/>
@@ -5280,17 +5384,589 @@
       <c r="P67" t="inlineStr"/>
       <c r="Q67" t="inlineStr">
         <is>
+          <t>https://www.moneycontrol.com/ipo/palucktechnologiesltd/PTL08</t>
+        </is>
+      </c>
+      <c r="R67" t="inlineStr">
+        <is>
+          <t>2026-08-25 09:29:52</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Papadmalji Agro Foods Ltd</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr"/>
+      <c r="C68" t="inlineStr"/>
+      <c r="D68" s="5" t="inlineStr">
+        <is>
+          <t>Upcoming</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>Sep 29, 2026</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Oct 01, 2026</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Oct 05, 2026</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr"/>
+      <c r="I68" t="inlineStr"/>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>69-72</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr"/>
+      <c r="L68" t="inlineStr"/>
+      <c r="M68" t="inlineStr"/>
+      <c r="N68" t="inlineStr"/>
+      <c r="O68" t="inlineStr"/>
+      <c r="P68" t="inlineStr"/>
+      <c r="Q68" t="inlineStr">
+        <is>
+          <t>https://www.moneycontrol.com/ipo/papadmaljiagrofoodsltd/PAF</t>
+        </is>
+      </c>
+      <c r="R68" t="inlineStr">
+        <is>
+          <t>2026-09-25 14:20:09</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Paramount Syntex Ltd</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr"/>
+      <c r="C69" t="inlineStr"/>
+      <c r="D69" s="5" t="inlineStr">
+        <is>
+          <t>Upcoming</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>Sep 30, 2026</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Oct 06, 2026</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Oct 07, 2026</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr"/>
+      <c r="I69" t="inlineStr"/>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>119-127</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr"/>
+      <c r="L69" t="inlineStr"/>
+      <c r="M69" t="inlineStr"/>
+      <c r="N69" t="inlineStr"/>
+      <c r="O69" t="inlineStr"/>
+      <c r="P69" t="inlineStr"/>
+      <c r="Q69" t="inlineStr">
+        <is>
+          <t>https://www.moneycontrol.com/ipo/paramountsyntexltd/PSL06</t>
+        </is>
+      </c>
+      <c r="R69" t="inlineStr">
+        <is>
+          <t>2026-09-25 14:20:09</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Peshwa Wheat</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr"/>
+      <c r="C70" t="inlineStr"/>
+      <c r="D70" s="5" t="inlineStr">
+        <is>
+          <t>Upcoming</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>Sep 24, 2026</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Sep 28, 2026</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Sep 29, 2026</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr"/>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>1200</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>95-101</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>121200</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr"/>
+      <c r="M70" t="inlineStr"/>
+      <c r="N70" t="inlineStr"/>
+      <c r="O70" t="inlineStr"/>
+      <c r="P70" t="inlineStr"/>
+      <c r="Q70" t="inlineStr">
+        <is>
+          <t>https://www.moneycontrol.com/ipo/peshwawheat/PWL01</t>
+        </is>
+      </c>
+      <c r="R70" t="inlineStr">
+        <is>
+          <t>2026-09-22 14:03:25</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Purple Style Labs Ltd</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr"/>
+      <c r="C71" t="inlineStr"/>
+      <c r="D71" s="4" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>Aug 31, 2026</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Sep 02, 2026</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Sep 03, 2026</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr"/>
+      <c r="I71" t="inlineStr"/>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>575</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr"/>
+      <c r="L71" t="inlineStr"/>
+      <c r="M71" t="inlineStr"/>
+      <c r="N71" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O71" t="inlineStr"/>
+      <c r="P71" t="inlineStr"/>
+      <c r="Q71" t="inlineStr">
+        <is>
+          <t>https://www.moneycontrol.com/ipo/purplestylelabsltd/PSL05</t>
+        </is>
+      </c>
+      <c r="R71" t="inlineStr">
+        <is>
+          <t>2026-09-02 13:25:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Q&amp;T Foods Ltd</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr"/>
+      <c r="C72" t="inlineStr"/>
+      <c r="D72" s="5" t="inlineStr">
+        <is>
+          <t>Upcoming</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>Aug 12, 2026</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Aug 14, 2026</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Aug 17, 2026</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr"/>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>1200</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>115</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>138000</t>
+        </is>
+      </c>
+      <c r="L72" t="inlineStr"/>
+      <c r="M72" t="inlineStr"/>
+      <c r="N72" t="inlineStr"/>
+      <c r="O72" t="inlineStr"/>
+      <c r="P72" t="inlineStr"/>
+      <c r="Q72" t="inlineStr">
+        <is>
+          <t>https://www.moneycontrol.com/ipo/qtfoodsltd/QFL</t>
+        </is>
+      </c>
+      <c r="R72" t="inlineStr">
+        <is>
+          <t>2026-08-10 10:24:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Shanti Inorganics Ltd</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr"/>
+      <c r="C73" t="inlineStr"/>
+      <c r="D73" s="5" t="inlineStr">
+        <is>
+          <t>Upcoming</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>Aug 31, 2026</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Sep 02, 2026</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Sep 03, 2026</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr"/>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>1600</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>79-83</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>132800</t>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr"/>
+      <c r="M73" t="inlineStr"/>
+      <c r="N73" t="inlineStr"/>
+      <c r="O73" t="inlineStr"/>
+      <c r="P73" t="inlineStr"/>
+      <c r="Q73" t="inlineStr">
+        <is>
+          <t>https://www.moneycontrol.com/ipo/shantiinorganicsltd/SIL34</t>
+        </is>
+      </c>
+      <c r="R73" t="inlineStr">
+        <is>
+          <t>2026-08-25 09:29:52</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Technocrats Plasma Systems Ltd</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr"/>
+      <c r="C74" t="inlineStr"/>
+      <c r="D74" s="5" t="inlineStr">
+        <is>
+          <t>Upcoming</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>Aug 14, 2026</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Aug 18, 2026</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Aug 19, 2026</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr"/>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>125-132</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>132000</t>
+        </is>
+      </c>
+      <c r="L74" t="inlineStr"/>
+      <c r="M74" t="inlineStr"/>
+      <c r="N74" t="inlineStr"/>
+      <c r="O74" t="inlineStr"/>
+      <c r="P74" t="inlineStr"/>
+      <c r="Q74" t="inlineStr">
+        <is>
+          <t>https://www.moneycontrol.com/ipo/technocratsplasmasystemsltd/TPSL</t>
+        </is>
+      </c>
+      <c r="R74" t="inlineStr">
+        <is>
+          <t>2026-08-11 21:41:02</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Unitec Fibres Ltd</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr"/>
+      <c r="C75" t="inlineStr"/>
+      <c r="D75" s="5" t="inlineStr">
+        <is>
+          <t>Upcoming</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>Sep 23, 2026</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Sep 25, 2026</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Sep 28, 2026</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr"/>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>1600</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>83-88</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>140800</t>
+        </is>
+      </c>
+      <c r="L75" t="inlineStr"/>
+      <c r="M75" t="inlineStr"/>
+      <c r="N75" t="inlineStr"/>
+      <c r="O75" t="inlineStr"/>
+      <c r="P75" t="inlineStr"/>
+      <c r="Q75" t="inlineStr">
+        <is>
+          <t>https://www.moneycontrol.com/ipo/unitecfibresltd/UFL03</t>
+        </is>
+      </c>
+      <c r="R75" t="inlineStr">
+        <is>
+          <t>2026-09-18 23:59:33</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>VANS Electroengineerings Ltd</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr"/>
+      <c r="C76" t="inlineStr"/>
+      <c r="D76" s="5" t="inlineStr">
+        <is>
+          <t>Upcoming</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>Sep 29, 2026</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Oct 01, 2026</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Oct 05, 2026</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr"/>
+      <c r="I76" t="inlineStr"/>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>112-118</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr"/>
+      <c r="L76" t="inlineStr"/>
+      <c r="M76" t="inlineStr"/>
+      <c r="N76" t="inlineStr"/>
+      <c r="O76" t="inlineStr"/>
+      <c r="P76" t="inlineStr"/>
+      <c r="Q76" t="inlineStr">
+        <is>
+          <t>https://www.moneycontrol.com/ipo/vanselectroengineeringsltd/VEL03</t>
+        </is>
+      </c>
+      <c r="R76" t="inlineStr">
+        <is>
+          <t>2026-09-25 14:20:09</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Vama Wovenfab Ltd</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr"/>
+      <c r="C77" t="inlineStr"/>
+      <c r="D77" s="5" t="inlineStr">
+        <is>
+          <t>Upcoming</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>Sep 15, 2026</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Sep 17, 2026</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Sep 18, 2026</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr"/>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>400</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>324-341</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>136400</t>
+        </is>
+      </c>
+      <c r="L77" t="inlineStr"/>
+      <c r="M77" t="inlineStr"/>
+      <c r="N77" t="inlineStr"/>
+      <c r="O77" t="inlineStr"/>
+      <c r="P77" t="inlineStr"/>
+      <c r="Q77" t="inlineStr">
+        <is>
           <t>https://www.moneycontrol.com/ipo/vamawovenfabltd/VWL01</t>
         </is>
       </c>
-      <c r="R67" t="inlineStr">
+      <c r="R77" t="inlineStr">
         <is>
           <t>2026-09-11 13:34:16</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:R67"/>
+  <autoFilter ref="A1:R77"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/mainboard_ipos.xlsx
+++ b/data/mainboard_ipos.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Mainboard IPOs" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Mainboard IPOs'!$A$1:$R$77</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Mainboard IPOs'!$A$1:$R$78</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -449,7 +449,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R77"/>
+  <dimension ref="A1:R78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -3777,7 +3777,7 @@
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>2026-09-25 14:20:09</t>
+          <t>2026-09-27 14:46:28</t>
         </is>
       </c>
     </row>
@@ -3913,7 +3913,7 @@
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>2026-09-25 14:20:09</t>
+          <t>2026-09-27 14:46:28</t>
         </is>
       </c>
     </row>
@@ -3997,7 +3997,7 @@
       </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t>2026-09-25 14:20:09</t>
+          <t>2026-09-27 14:46:28</t>
         </is>
       </c>
     </row>
@@ -4077,9 +4077,9 @@
       </c>
       <c r="B47" t="inlineStr"/>
       <c r="C47" t="inlineStr"/>
-      <c r="D47" s="4" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="D47" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -4121,7 +4121,7 @@
       <c r="M47" t="inlineStr"/>
       <c r="N47" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>177</t>
         </is>
       </c>
       <c r="O47" t="inlineStr"/>
@@ -4133,7 +4133,7 @@
       </c>
       <c r="R47" t="inlineStr">
         <is>
-          <t>2026-09-25 14:20:09</t>
+          <t>2026-09-27 14:46:28</t>
         </is>
       </c>
     </row>
@@ -4145,9 +4145,9 @@
       </c>
       <c r="B48" t="inlineStr"/>
       <c r="C48" t="inlineStr"/>
-      <c r="D48" s="4" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="D48" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -4189,7 +4189,7 @@
       <c r="M48" t="inlineStr"/>
       <c r="N48" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O48" t="inlineStr"/>
@@ -4201,7 +4201,7 @@
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>2026-09-25 14:20:09</t>
+          <t>2026-09-27 14:46:28</t>
         </is>
       </c>
     </row>
@@ -4213,9 +4213,9 @@
       </c>
       <c r="B49" t="inlineStr"/>
       <c r="C49" t="inlineStr"/>
-      <c r="D49" s="4" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="D49" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -4257,7 +4257,7 @@
       <c r="M49" t="inlineStr"/>
       <c r="N49" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O49" t="inlineStr"/>
@@ -4269,7 +4269,7 @@
       </c>
       <c r="R49" t="inlineStr">
         <is>
-          <t>2026-09-25 14:20:09</t>
+          <t>2026-09-27 14:46:28</t>
         </is>
       </c>
     </row>
@@ -4405,7 +4405,7 @@
       </c>
       <c r="R51" t="inlineStr">
         <is>
-          <t>2026-09-25 14:20:09</t>
+          <t>2026-09-27 14:46:28</t>
         </is>
       </c>
     </row>
@@ -4461,7 +4461,7 @@
       <c r="M52" t="inlineStr"/>
       <c r="N52" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="O52" t="inlineStr"/>
@@ -4473,7 +4473,7 @@
       </c>
       <c r="R52" t="inlineStr">
         <is>
-          <t>2026-09-25 14:20:09</t>
+          <t>2026-09-27 14:46:28</t>
         </is>
       </c>
     </row>
@@ -4527,7 +4527,11 @@
       </c>
       <c r="L53" t="inlineStr"/>
       <c r="M53" t="inlineStr"/>
-      <c r="N53" t="inlineStr"/>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="O53" t="inlineStr"/>
       <c r="P53" t="inlineStr"/>
       <c r="Q53" t="inlineStr">
@@ -4537,7 +4541,7 @@
       </c>
       <c r="R53" t="inlineStr">
         <is>
-          <t>2026-09-25 14:20:09</t>
+          <t>2026-09-27 14:46:28</t>
         </is>
       </c>
     </row>
@@ -4591,7 +4595,11 @@
       </c>
       <c r="L54" t="inlineStr"/>
       <c r="M54" t="inlineStr"/>
-      <c r="N54" t="inlineStr"/>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="O54" t="inlineStr"/>
       <c r="P54" t="inlineStr"/>
       <c r="Q54" t="inlineStr">
@@ -4601,7 +4609,7 @@
       </c>
       <c r="R54" t="inlineStr">
         <is>
-          <t>2026-09-25 14:20:09</t>
+          <t>2026-09-27 14:46:28</t>
         </is>
       </c>
     </row>
@@ -4655,7 +4663,11 @@
       </c>
       <c r="L55" t="inlineStr"/>
       <c r="M55" t="inlineStr"/>
-      <c r="N55" t="inlineStr"/>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="O55" t="inlineStr"/>
       <c r="P55" t="inlineStr"/>
       <c r="Q55" t="inlineStr">
@@ -4665,7 +4677,7 @@
       </c>
       <c r="R55" t="inlineStr">
         <is>
-          <t>2026-09-25 14:20:09</t>
+          <t>2026-09-27 14:46:28</t>
         </is>
       </c>
     </row>
@@ -4719,7 +4731,11 @@
       </c>
       <c r="L56" t="inlineStr"/>
       <c r="M56" t="inlineStr"/>
-      <c r="N56" t="inlineStr"/>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="O56" t="inlineStr"/>
       <c r="P56" t="inlineStr"/>
       <c r="Q56" t="inlineStr">
@@ -4729,7 +4745,7 @@
       </c>
       <c r="R56" t="inlineStr">
         <is>
-          <t>2026-09-25 14:20:09</t>
+          <t>2026-09-27 14:46:28</t>
         </is>
       </c>
     </row>
@@ -4793,7 +4809,7 @@
       </c>
       <c r="R57" t="inlineStr">
         <is>
-          <t>2026-09-25 14:20:09</t>
+          <t>2026-09-27 14:46:28</t>
         </is>
       </c>
     </row>
@@ -4857,14 +4873,14 @@
       </c>
       <c r="R58" t="inlineStr">
         <is>
-          <t>2026-09-25 14:20:09</t>
+          <t>2026-09-27 14:46:28</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Complete Sports and Management India Ltd</t>
+          <t>Nityas Gems and Jewellery Ltd</t>
         </is>
       </c>
       <c r="B59" t="inlineStr"/>
@@ -4876,33 +4892,37 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Aug 28, 2026</t>
+          <t>Sep 30, 2026</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Sep 01, 2026</t>
+          <t>Oct 05, 2026</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Sep 02, 2026</t>
-        </is>
-      </c>
-      <c r="H59" t="inlineStr"/>
+          <t>Oct 06, 2026</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>Oct 08, 2026</t>
+        </is>
+      </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>200</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>128-135</t>
+          <t>70-75</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>135000</t>
+          <t>15000</t>
         </is>
       </c>
       <c r="L59" t="inlineStr"/>
@@ -4912,19 +4932,19 @@
       <c r="P59" t="inlineStr"/>
       <c r="Q59" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/completesportsmanagementindialtd/CSMIL</t>
+          <t>https://www.moneycontrol.com/ipo/nityasgemsjewelleryltd/NGJL</t>
         </is>
       </c>
       <c r="R59" t="inlineStr">
         <is>
-          <t>2026-08-25 09:29:52</t>
+          <t>2026-09-27 14:46:28</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Coreintegra Consulting Services</t>
+          <t>Complete Sports and Management India Ltd</t>
         </is>
       </c>
       <c r="B60" t="inlineStr"/>
@@ -4936,33 +4956,33 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Sep 23, 2026</t>
+          <t>Aug 28, 2026</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Sep 25, 2026</t>
+          <t>Sep 01, 2026</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Sep 28, 2026</t>
+          <t>Sep 02, 2026</t>
         </is>
       </c>
       <c r="H60" t="inlineStr"/>
       <c r="I60" t="inlineStr">
         <is>
-          <t>1600</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>74-78</t>
+          <t>128-135</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>124800</t>
+          <t>135000</t>
         </is>
       </c>
       <c r="L60" t="inlineStr"/>
@@ -4972,19 +4992,19 @@
       <c r="P60" t="inlineStr"/>
       <c r="Q60" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/coreintegraconsultingservices/CCSL</t>
+          <t>https://www.moneycontrol.com/ipo/completesportsmanagementindialtd/CSMIL</t>
         </is>
       </c>
       <c r="R60" t="inlineStr">
         <is>
-          <t>2026-09-22 14:03:25</t>
+          <t>2026-08-25 09:29:52</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Credent Connect N Care Ltd</t>
+          <t>Coreintegra Consulting Services</t>
         </is>
       </c>
       <c r="B61" t="inlineStr"/>
@@ -4996,33 +5016,33 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Aug 13, 2026</t>
+          <t>Sep 23, 2026</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Aug 17, 2026</t>
+          <t>Sep 25, 2026</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Aug 18, 2026</t>
+          <t>Sep 28, 2026</t>
         </is>
       </c>
       <c r="H61" t="inlineStr"/>
       <c r="I61" t="inlineStr">
         <is>
-          <t>600</t>
+          <t>1600</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>179-189</t>
+          <t>74-78</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>113400</t>
+          <t>124800</t>
         </is>
       </c>
       <c r="L61" t="inlineStr"/>
@@ -5032,19 +5052,19 @@
       <c r="P61" t="inlineStr"/>
       <c r="Q61" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/credentconnectncareltd/CCC04</t>
+          <t>https://www.moneycontrol.com/ipo/coreintegraconsultingservices/CCSL</t>
         </is>
       </c>
       <c r="R61" t="inlineStr">
         <is>
-          <t>2026-08-10 22:43:12</t>
+          <t>2026-09-22 14:03:25</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Dove Soft Ltd</t>
+          <t>Credent Connect N Care Ltd</t>
         </is>
       </c>
       <c r="B62" t="inlineStr"/>
@@ -5056,27 +5076,35 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Sep 30, 2026</t>
+          <t>Aug 13, 2026</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Oct 05, 2026</t>
+          <t>Aug 17, 2026</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Oct 06, 2026</t>
+          <t>Aug 18, 2026</t>
         </is>
       </c>
       <c r="H62" t="inlineStr"/>
-      <c r="I62" t="inlineStr"/>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>600</t>
+        </is>
+      </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>104-111</t>
-        </is>
-      </c>
-      <c r="K62" t="inlineStr"/>
+          <t>179-189</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>113400</t>
+        </is>
+      </c>
       <c r="L62" t="inlineStr"/>
       <c r="M62" t="inlineStr"/>
       <c r="N62" t="inlineStr"/>
@@ -5084,19 +5112,19 @@
       <c r="P62" t="inlineStr"/>
       <c r="Q62" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/dovesoftltd/DSL04</t>
+          <t>https://www.moneycontrol.com/ipo/credentconnectncareltd/CCC04</t>
         </is>
       </c>
       <c r="R62" t="inlineStr">
         <is>
-          <t>2026-09-25 14:20:09</t>
+          <t>2026-08-10 22:43:12</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Farm Peace Ltd</t>
+          <t>Dove Soft Ltd</t>
         </is>
       </c>
       <c r="B63" t="inlineStr"/>
@@ -5108,33 +5136,33 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Sep 01, 2026</t>
+          <t>Sep 30, 2026</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Sep 03, 2026</t>
+          <t>Oct 05, 2026</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Sep 04, 2026</t>
+          <t>Oct 06, 2026</t>
         </is>
       </c>
       <c r="H63" t="inlineStr"/>
       <c r="I63" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>104-111</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>118000</t>
+          <t>133200</t>
         </is>
       </c>
       <c r="L63" t="inlineStr"/>
@@ -5144,19 +5172,19 @@
       <c r="P63" t="inlineStr"/>
       <c r="Q63" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/farmpeaceltd/FPL02</t>
+          <t>https://www.moneycontrol.com/ipo/dovesoftltd/DSL04</t>
         </is>
       </c>
       <c r="R63" t="inlineStr">
         <is>
-          <t>2026-08-27 19:43:03</t>
+          <t>2026-09-25 14:20:09</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Green Asia Impex Ltd</t>
+          <t>Farm Peace Ltd</t>
         </is>
       </c>
       <c r="B64" t="inlineStr"/>
@@ -5168,33 +5196,33 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Sep 24, 2026</t>
+          <t>Sep 01, 2026</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Sep 28, 2026</t>
+          <t>Sep 03, 2026</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Sep 29, 2026</t>
+          <t>Sep 04, 2026</t>
         </is>
       </c>
       <c r="H64" t="inlineStr"/>
       <c r="I64" t="inlineStr">
         <is>
-          <t>1600</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>85-90</t>
+          <t>59</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>144000</t>
+          <t>118000</t>
         </is>
       </c>
       <c r="L64" t="inlineStr"/>
@@ -5204,19 +5232,19 @@
       <c r="P64" t="inlineStr"/>
       <c r="Q64" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/greenasiaimpexltd/GAIL01</t>
+          <t>https://www.moneycontrol.com/ipo/farmpeaceltd/FPL02</t>
         </is>
       </c>
       <c r="R64" t="inlineStr">
         <is>
-          <t>2026-09-22 14:03:25</t>
+          <t>2026-08-27 19:43:03</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Kheria Autocomp Ltd</t>
+          <t>Green Asia Impex Ltd</t>
         </is>
       </c>
       <c r="B65" t="inlineStr"/>
@@ -5228,33 +5256,33 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Sep 17, 2026</t>
+          <t>Sep 24, 2026</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Sep 21, 2026</t>
+          <t>Sep 28, 2026</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Sep 22, 2026</t>
+          <t>Sep 29, 2026</t>
         </is>
       </c>
       <c r="H65" t="inlineStr"/>
       <c r="I65" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>1600</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>96-101</t>
+          <t>85-90</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>121200</t>
+          <t>144000</t>
         </is>
       </c>
       <c r="L65" t="inlineStr"/>
@@ -5264,19 +5292,19 @@
       <c r="P65" t="inlineStr"/>
       <c r="Q65" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/kheriaautocompltd/KAL05</t>
+          <t>https://www.moneycontrol.com/ipo/greenasiaimpexltd/GAIL01</t>
         </is>
       </c>
       <c r="R65" t="inlineStr">
         <is>
-          <t>2026-09-11 13:34:16</t>
+          <t>2026-09-22 14:03:25</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Mopshop Distribution Ltd</t>
+          <t>Kheria Autocomp Ltd</t>
         </is>
       </c>
       <c r="B66" t="inlineStr"/>
@@ -5288,33 +5316,33 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Aug 19, 2026</t>
+          <t>Sep 17, 2026</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Aug 21, 2026</t>
+          <t>Sep 21, 2026</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Aug 24, 2026</t>
+          <t>Sep 22, 2026</t>
         </is>
       </c>
       <c r="H66" t="inlineStr"/>
       <c r="I66" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>138</t>
+          <t>96-101</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>138000</t>
+          <t>121200</t>
         </is>
       </c>
       <c r="L66" t="inlineStr"/>
@@ -5324,19 +5352,19 @@
       <c r="P66" t="inlineStr"/>
       <c r="Q66" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/mopshopdistributionltd/MDL03</t>
+          <t>https://www.moneycontrol.com/ipo/kheriaautocompltd/KAL05</t>
         </is>
       </c>
       <c r="R66" t="inlineStr">
         <is>
-          <t>2026-08-14 21:36:23</t>
+          <t>2026-09-11 13:34:16</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Paluck Technologies Ltd</t>
+          <t>Mopshop Distribution Ltd</t>
         </is>
       </c>
       <c r="B67" t="inlineStr"/>
@@ -5348,33 +5376,33 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Aug 28, 2026</t>
+          <t>Aug 19, 2026</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Sep 01, 2026</t>
+          <t>Aug 21, 2026</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Sep 02, 2026</t>
+          <t>Aug 24, 2026</t>
         </is>
       </c>
       <c r="H67" t="inlineStr"/>
       <c r="I67" t="inlineStr">
         <is>
-          <t>3000</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>46-48</t>
+          <t>138</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>144000</t>
+          <t>138000</t>
         </is>
       </c>
       <c r="L67" t="inlineStr"/>
@@ -5384,19 +5412,19 @@
       <c r="P67" t="inlineStr"/>
       <c r="Q67" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/palucktechnologiesltd/PTL08</t>
+          <t>https://www.moneycontrol.com/ipo/mopshopdistributionltd/MDL03</t>
         </is>
       </c>
       <c r="R67" t="inlineStr">
         <is>
-          <t>2026-08-25 09:29:52</t>
+          <t>2026-08-14 21:36:23</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Papadmalji Agro Foods Ltd</t>
+          <t>Paluck Technologies Ltd</t>
         </is>
       </c>
       <c r="B68" t="inlineStr"/>
@@ -5408,27 +5436,35 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Sep 29, 2026</t>
+          <t>Aug 28, 2026</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Oct 01, 2026</t>
+          <t>Sep 01, 2026</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Oct 05, 2026</t>
+          <t>Sep 02, 2026</t>
         </is>
       </c>
       <c r="H68" t="inlineStr"/>
-      <c r="I68" t="inlineStr"/>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>69-72</t>
-        </is>
-      </c>
-      <c r="K68" t="inlineStr"/>
+          <t>46-48</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>144000</t>
+        </is>
+      </c>
       <c r="L68" t="inlineStr"/>
       <c r="M68" t="inlineStr"/>
       <c r="N68" t="inlineStr"/>
@@ -5436,19 +5472,19 @@
       <c r="P68" t="inlineStr"/>
       <c r="Q68" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/papadmaljiagrofoodsltd/PAF</t>
+          <t>https://www.moneycontrol.com/ipo/palucktechnologiesltd/PTL08</t>
         </is>
       </c>
       <c r="R68" t="inlineStr">
         <is>
-          <t>2026-09-25 14:20:09</t>
+          <t>2026-08-25 09:29:52</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Paramount Syntex Ltd</t>
+          <t>Papadmalji Agro Foods Ltd</t>
         </is>
       </c>
       <c r="B69" t="inlineStr"/>
@@ -5460,27 +5496,35 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Sep 30, 2026</t>
+          <t>Sep 29, 2026</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Oct 06, 2026</t>
+          <t>Oct 01, 2026</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Oct 07, 2026</t>
+          <t>Oct 05, 2026</t>
         </is>
       </c>
       <c r="H69" t="inlineStr"/>
-      <c r="I69" t="inlineStr"/>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>1600</t>
+        </is>
+      </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>119-127</t>
-        </is>
-      </c>
-      <c r="K69" t="inlineStr"/>
+          <t>69-72</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>115200</t>
+        </is>
+      </c>
       <c r="L69" t="inlineStr"/>
       <c r="M69" t="inlineStr"/>
       <c r="N69" t="inlineStr"/>
@@ -5488,7 +5532,7 @@
       <c r="P69" t="inlineStr"/>
       <c r="Q69" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/paramountsyntexltd/PSL06</t>
+          <t>https://www.moneycontrol.com/ipo/papadmaljiagrofoodsltd/PAF</t>
         </is>
       </c>
       <c r="R69" t="inlineStr">
@@ -5500,7 +5544,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Peshwa Wheat</t>
+          <t>Paramount Syntex Ltd</t>
         </is>
       </c>
       <c r="B70" t="inlineStr"/>
@@ -5512,33 +5556,33 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Sep 24, 2026</t>
+          <t>Sep 30, 2026</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Sep 28, 2026</t>
+          <t>Oct 06, 2026</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Sep 29, 2026</t>
+          <t>Oct 07, 2026</t>
         </is>
       </c>
       <c r="H70" t="inlineStr"/>
       <c r="I70" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>95-101</t>
+          <t>119-127</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>121200</t>
+          <t>127000</t>
         </is>
       </c>
       <c r="L70" t="inlineStr"/>
@@ -5548,135 +5592,135 @@
       <c r="P70" t="inlineStr"/>
       <c r="Q70" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/peshwawheat/PWL01</t>
+          <t>https://www.moneycontrol.com/ipo/paramountsyntexltd/PSL06</t>
         </is>
       </c>
       <c r="R70" t="inlineStr">
         <is>
-          <t>2026-09-22 14:03:25</t>
+          <t>2026-09-25 14:20:09</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Purple Style Labs Ltd</t>
+          <t>Peshwa Wheat</t>
         </is>
       </c>
       <c r="B71" t="inlineStr"/>
       <c r="C71" t="inlineStr"/>
-      <c r="D71" s="4" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="D71" s="5" t="inlineStr">
+        <is>
+          <t>Upcoming</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Aug 31, 2026</t>
+          <t>Sep 24, 2026</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Sep 02, 2026</t>
+          <t>Sep 28, 2026</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Sep 03, 2026</t>
+          <t>Sep 29, 2026</t>
         </is>
       </c>
       <c r="H71" t="inlineStr"/>
-      <c r="I71" t="inlineStr"/>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>1200</t>
+        </is>
+      </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>575</t>
-        </is>
-      </c>
-      <c r="K71" t="inlineStr"/>
+          <t>95-101</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>121200</t>
+        </is>
+      </c>
       <c r="L71" t="inlineStr"/>
       <c r="M71" t="inlineStr"/>
-      <c r="N71" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="N71" t="inlineStr"/>
       <c r="O71" t="inlineStr"/>
       <c r="P71" t="inlineStr"/>
       <c r="Q71" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/purplestylelabsltd/PSL05</t>
+          <t>https://www.moneycontrol.com/ipo/peshwawheat/PWL01</t>
         </is>
       </c>
       <c r="R71" t="inlineStr">
         <is>
-          <t>2026-09-02 13:25:30</t>
+          <t>2026-09-22 14:03:25</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Q&amp;T Foods Ltd</t>
+          <t>Purple Style Labs Ltd</t>
         </is>
       </c>
       <c r="B72" t="inlineStr"/>
       <c r="C72" t="inlineStr"/>
-      <c r="D72" s="5" t="inlineStr">
-        <is>
-          <t>Upcoming</t>
+      <c r="D72" s="4" t="inlineStr">
+        <is>
+          <t>Open</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Aug 12, 2026</t>
+          <t>Aug 31, 2026</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Aug 14, 2026</t>
+          <t>Sep 02, 2026</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Aug 17, 2026</t>
+          <t>Sep 03, 2026</t>
         </is>
       </c>
       <c r="H72" t="inlineStr"/>
-      <c r="I72" t="inlineStr">
-        <is>
-          <t>1200</t>
-        </is>
-      </c>
+      <c r="I72" t="inlineStr"/>
       <c r="J72" t="inlineStr">
         <is>
-          <t>115</t>
-        </is>
-      </c>
-      <c r="K72" t="inlineStr">
-        <is>
-          <t>138000</t>
-        </is>
-      </c>
+          <t>575</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr"/>
       <c r="L72" t="inlineStr"/>
       <c r="M72" t="inlineStr"/>
-      <c r="N72" t="inlineStr"/>
+      <c r="N72" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="O72" t="inlineStr"/>
       <c r="P72" t="inlineStr"/>
       <c r="Q72" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/qtfoodsltd/QFL</t>
+          <t>https://www.moneycontrol.com/ipo/purplestylelabsltd/PSL05</t>
         </is>
       </c>
       <c r="R72" t="inlineStr">
         <is>
-          <t>2026-08-10 10:24:29</t>
+          <t>2026-09-02 13:25:30</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Shanti Inorganics Ltd</t>
+          <t>Q&amp;T Foods Ltd</t>
         </is>
       </c>
       <c r="B73" t="inlineStr"/>
@@ -5688,33 +5732,33 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Aug 31, 2026</t>
+          <t>Aug 12, 2026</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Sep 02, 2026</t>
+          <t>Aug 14, 2026</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Sep 03, 2026</t>
+          <t>Aug 17, 2026</t>
         </is>
       </c>
       <c r="H73" t="inlineStr"/>
       <c r="I73" t="inlineStr">
         <is>
-          <t>1600</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>79-83</t>
+          <t>115</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>132800</t>
+          <t>138000</t>
         </is>
       </c>
       <c r="L73" t="inlineStr"/>
@@ -5724,19 +5768,19 @@
       <c r="P73" t="inlineStr"/>
       <c r="Q73" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/shantiinorganicsltd/SIL34</t>
+          <t>https://www.moneycontrol.com/ipo/qtfoodsltd/QFL</t>
         </is>
       </c>
       <c r="R73" t="inlineStr">
         <is>
-          <t>2026-08-25 09:29:52</t>
+          <t>2026-08-10 10:24:29</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Technocrats Plasma Systems Ltd</t>
+          <t>Shanti Inorganics Ltd</t>
         </is>
       </c>
       <c r="B74" t="inlineStr"/>
@@ -5748,33 +5792,33 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Aug 14, 2026</t>
+          <t>Aug 31, 2026</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Aug 18, 2026</t>
+          <t>Sep 02, 2026</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Aug 19, 2026</t>
+          <t>Sep 03, 2026</t>
         </is>
       </c>
       <c r="H74" t="inlineStr"/>
       <c r="I74" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>1600</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>125-132</t>
+          <t>79-83</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>132000</t>
+          <t>132800</t>
         </is>
       </c>
       <c r="L74" t="inlineStr"/>
@@ -5784,19 +5828,19 @@
       <c r="P74" t="inlineStr"/>
       <c r="Q74" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/technocratsplasmasystemsltd/TPSL</t>
+          <t>https://www.moneycontrol.com/ipo/shantiinorganicsltd/SIL34</t>
         </is>
       </c>
       <c r="R74" t="inlineStr">
         <is>
-          <t>2026-08-11 21:41:02</t>
+          <t>2026-08-25 09:29:52</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Unitec Fibres Ltd</t>
+          <t>Technocrats Plasma Systems Ltd</t>
         </is>
       </c>
       <c r="B75" t="inlineStr"/>
@@ -5808,33 +5852,33 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Sep 23, 2026</t>
+          <t>Aug 14, 2026</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Sep 25, 2026</t>
+          <t>Aug 18, 2026</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Sep 28, 2026</t>
+          <t>Aug 19, 2026</t>
         </is>
       </c>
       <c r="H75" t="inlineStr"/>
       <c r="I75" t="inlineStr">
         <is>
-          <t>1600</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>83-88</t>
+          <t>125-132</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>140800</t>
+          <t>132000</t>
         </is>
       </c>
       <c r="L75" t="inlineStr"/>
@@ -5844,19 +5888,19 @@
       <c r="P75" t="inlineStr"/>
       <c r="Q75" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/unitecfibresltd/UFL03</t>
+          <t>https://www.moneycontrol.com/ipo/technocratsplasmasystemsltd/TPSL</t>
         </is>
       </c>
       <c r="R75" t="inlineStr">
         <is>
-          <t>2026-09-18 23:59:33</t>
+          <t>2026-08-11 21:41:02</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>VANS Electroengineerings Ltd</t>
+          <t>Unitec Fibres Ltd</t>
         </is>
       </c>
       <c r="B76" t="inlineStr"/>
@@ -5868,27 +5912,35 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Sep 29, 2026</t>
+          <t>Sep 23, 2026</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Oct 01, 2026</t>
+          <t>Sep 25, 2026</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Oct 05, 2026</t>
+          <t>Sep 28, 2026</t>
         </is>
       </c>
       <c r="H76" t="inlineStr"/>
-      <c r="I76" t="inlineStr"/>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>1600</t>
+        </is>
+      </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>112-118</t>
-        </is>
-      </c>
-      <c r="K76" t="inlineStr"/>
+          <t>83-88</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>140800</t>
+        </is>
+      </c>
       <c r="L76" t="inlineStr"/>
       <c r="M76" t="inlineStr"/>
       <c r="N76" t="inlineStr"/>
@@ -5896,19 +5948,19 @@
       <c r="P76" t="inlineStr"/>
       <c r="Q76" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/vanselectroengineeringsltd/VEL03</t>
+          <t>https://www.moneycontrol.com/ipo/unitecfibresltd/UFL03</t>
         </is>
       </c>
       <c r="R76" t="inlineStr">
         <is>
-          <t>2026-09-25 14:20:09</t>
+          <t>2026-09-18 23:59:33</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Vama Wovenfab Ltd</t>
+          <t>VANS Electroengineerings Ltd</t>
         </is>
       </c>
       <c r="B77" t="inlineStr"/>
@@ -5920,33 +5972,33 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Sep 15, 2026</t>
+          <t>Sep 29, 2026</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Sep 17, 2026</t>
+          <t>Oct 01, 2026</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Sep 18, 2026</t>
+          <t>Oct 05, 2026</t>
         </is>
       </c>
       <c r="H77" t="inlineStr"/>
       <c r="I77" t="inlineStr">
         <is>
-          <t>400</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>324-341</t>
+          <t>112-118</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>136400</t>
+          <t>141600</t>
         </is>
       </c>
       <c r="L77" t="inlineStr"/>
@@ -5956,17 +6008,77 @@
       <c r="P77" t="inlineStr"/>
       <c r="Q77" t="inlineStr">
         <is>
+          <t>https://www.moneycontrol.com/ipo/vanselectroengineeringsltd/VEL03</t>
+        </is>
+      </c>
+      <c r="R77" t="inlineStr">
+        <is>
+          <t>2026-09-25 14:20:09</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Vama Wovenfab Ltd</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr"/>
+      <c r="C78" t="inlineStr"/>
+      <c r="D78" s="5" t="inlineStr">
+        <is>
+          <t>Upcoming</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>Sep 15, 2026</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Sep 17, 2026</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Sep 18, 2026</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr"/>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>400</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>324-341</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>136400</t>
+        </is>
+      </c>
+      <c r="L78" t="inlineStr"/>
+      <c r="M78" t="inlineStr"/>
+      <c r="N78" t="inlineStr"/>
+      <c r="O78" t="inlineStr"/>
+      <c r="P78" t="inlineStr"/>
+      <c r="Q78" t="inlineStr">
+        <is>
           <t>https://www.moneycontrol.com/ipo/vamawovenfabltd/VWL01</t>
         </is>
       </c>
-      <c r="R77" t="inlineStr">
+      <c r="R78" t="inlineStr">
         <is>
           <t>2026-09-11 13:34:16</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:R77"/>
+  <autoFilter ref="A1:R78"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/mainboard_ipos.xlsx
+++ b/data/mainboard_ipos.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Mainboard IPOs" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Mainboard IPOs'!$A$1:$R$78</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Mainboard IPOs'!$A$1:$R$79</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -449,7 +449,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R78"/>
+  <dimension ref="A1:R79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -3913,7 +3913,7 @@
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>2026-09-27 14:46:28</t>
+          <t>2026-09-28 15:18:07</t>
         </is>
       </c>
     </row>
@@ -4133,7 +4133,7 @@
       </c>
       <c r="R47" t="inlineStr">
         <is>
-          <t>2026-09-27 14:46:28</t>
+          <t>2026-09-28 15:18:07</t>
         </is>
       </c>
     </row>
@@ -4201,7 +4201,7 @@
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>2026-09-27 14:46:28</t>
+          <t>2026-09-28 15:18:07</t>
         </is>
       </c>
     </row>
@@ -4269,7 +4269,7 @@
       </c>
       <c r="R49" t="inlineStr">
         <is>
-          <t>2026-09-27 14:46:28</t>
+          <t>2026-09-28 15:18:07</t>
         </is>
       </c>
     </row>
@@ -4393,7 +4393,7 @@
       <c r="M51" t="inlineStr"/>
       <c r="N51" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="O51" t="inlineStr"/>
@@ -4405,7 +4405,7 @@
       </c>
       <c r="R51" t="inlineStr">
         <is>
-          <t>2026-09-27 14:46:28</t>
+          <t>2026-09-28 15:18:07</t>
         </is>
       </c>
     </row>
@@ -4461,7 +4461,7 @@
       <c r="M52" t="inlineStr"/>
       <c r="N52" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>30</t>
         </is>
       </c>
       <c r="O52" t="inlineStr"/>
@@ -4473,7 +4473,7 @@
       </c>
       <c r="R52" t="inlineStr">
         <is>
-          <t>2026-09-27 14:46:28</t>
+          <t>2026-09-28 15:18:07</t>
         </is>
       </c>
     </row>
@@ -4529,7 +4529,7 @@
       <c r="M53" t="inlineStr"/>
       <c r="N53" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="O53" t="inlineStr"/>
@@ -4541,7 +4541,7 @@
       </c>
       <c r="R53" t="inlineStr">
         <is>
-          <t>2026-09-27 14:46:28</t>
+          <t>2026-09-28 15:18:07</t>
         </is>
       </c>
     </row>
@@ -4597,7 +4597,7 @@
       <c r="M54" t="inlineStr"/>
       <c r="N54" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="O54" t="inlineStr"/>
@@ -4609,7 +4609,7 @@
       </c>
       <c r="R54" t="inlineStr">
         <is>
-          <t>2026-09-27 14:46:28</t>
+          <t>2026-09-28 15:18:07</t>
         </is>
       </c>
     </row>
@@ -4665,7 +4665,7 @@
       <c r="M55" t="inlineStr"/>
       <c r="N55" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="O55" t="inlineStr"/>
@@ -4677,7 +4677,7 @@
       </c>
       <c r="R55" t="inlineStr">
         <is>
-          <t>2026-09-27 14:46:28</t>
+          <t>2026-09-28 15:18:07</t>
         </is>
       </c>
     </row>
@@ -4733,7 +4733,7 @@
       <c r="M56" t="inlineStr"/>
       <c r="N56" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="O56" t="inlineStr"/>
@@ -4745,7 +4745,7 @@
       </c>
       <c r="R56" t="inlineStr">
         <is>
-          <t>2026-09-27 14:46:28</t>
+          <t>2026-09-28 15:18:07</t>
         </is>
       </c>
     </row>
@@ -4757,9 +4757,9 @@
       </c>
       <c r="B57" t="inlineStr"/>
       <c r="C57" t="inlineStr"/>
-      <c r="D57" s="5" t="inlineStr">
-        <is>
-          <t>Upcoming</t>
+      <c r="D57" s="4" t="inlineStr">
+        <is>
+          <t>Open</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -4789,7 +4789,7 @@
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>123-130</t>
+          <t>130</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
@@ -4799,7 +4799,11 @@
       </c>
       <c r="L57" t="inlineStr"/>
       <c r="M57" t="inlineStr"/>
-      <c r="N57" t="inlineStr"/>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="O57" t="inlineStr"/>
       <c r="P57" t="inlineStr"/>
       <c r="Q57" t="inlineStr">
@@ -4809,7 +4813,7 @@
       </c>
       <c r="R57" t="inlineStr">
         <is>
-          <t>2026-09-27 14:46:28</t>
+          <t>2026-09-28 15:18:07</t>
         </is>
       </c>
     </row>
@@ -4821,9 +4825,9 @@
       </c>
       <c r="B58" t="inlineStr"/>
       <c r="C58" t="inlineStr"/>
-      <c r="D58" s="5" t="inlineStr">
-        <is>
-          <t>Upcoming</t>
+      <c r="D58" s="4" t="inlineStr">
+        <is>
+          <t>Open</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -4853,7 +4857,7 @@
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>159-167</t>
+          <t>167</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
@@ -4863,7 +4867,11 @@
       </c>
       <c r="L58" t="inlineStr"/>
       <c r="M58" t="inlineStr"/>
-      <c r="N58" t="inlineStr"/>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="O58" t="inlineStr"/>
       <c r="P58" t="inlineStr"/>
       <c r="Q58" t="inlineStr">
@@ -4873,16 +4881,12 @@
       </c>
       <c r="R58" t="inlineStr">
         <is>
-          <t>2026-09-27 14:46:28</t>
+          <t>2026-09-28 15:18:07</t>
         </is>
       </c>
     </row>
     <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>Nityas Gems and Jewellery Ltd</t>
-        </is>
-      </c>
+      <c r="A59" t="inlineStr"/>
       <c r="B59" t="inlineStr"/>
       <c r="C59" t="inlineStr"/>
       <c r="D59" s="5" t="inlineStr">
@@ -4912,17 +4916,17 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>68</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>70-75</t>
+          <t>208-220</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>15000</t>
+          <t>14960</t>
         </is>
       </c>
       <c r="L59" t="inlineStr"/>
@@ -4932,19 +4936,19 @@
       <c r="P59" t="inlineStr"/>
       <c r="Q59" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/nityasgemsjewelleryltd/NGJL</t>
+          <t>https://www.moneycontrol.com/ipo/</t>
         </is>
       </c>
       <c r="R59" t="inlineStr">
         <is>
-          <t>2026-09-27 14:46:28</t>
+          <t>2026-09-28 15:18:07</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Complete Sports and Management India Ltd</t>
+          <t>Nityas Gems and Jewellery Ltd</t>
         </is>
       </c>
       <c r="B60" t="inlineStr"/>
@@ -4956,33 +4960,37 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Aug 28, 2026</t>
+          <t>Sep 30, 2026</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Sep 01, 2026</t>
+          <t>Oct 05, 2026</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Sep 02, 2026</t>
-        </is>
-      </c>
-      <c r="H60" t="inlineStr"/>
+          <t>Oct 06, 2026</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>Oct 08, 2026</t>
+        </is>
+      </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>200</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>128-135</t>
+          <t>70-75</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>135000</t>
+          <t>15000</t>
         </is>
       </c>
       <c r="L60" t="inlineStr"/>
@@ -4992,19 +5000,19 @@
       <c r="P60" t="inlineStr"/>
       <c r="Q60" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/completesportsmanagementindialtd/CSMIL</t>
+          <t>https://www.moneycontrol.com/ipo/nityasgemsjewelleryltd/NGJL</t>
         </is>
       </c>
       <c r="R60" t="inlineStr">
         <is>
-          <t>2026-08-25 09:29:52</t>
+          <t>2026-09-28 15:18:07</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Coreintegra Consulting Services</t>
+          <t>Complete Sports and Management India Ltd</t>
         </is>
       </c>
       <c r="B61" t="inlineStr"/>
@@ -5016,33 +5024,33 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Sep 23, 2026</t>
+          <t>Aug 28, 2026</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Sep 25, 2026</t>
+          <t>Sep 01, 2026</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Sep 28, 2026</t>
+          <t>Sep 02, 2026</t>
         </is>
       </c>
       <c r="H61" t="inlineStr"/>
       <c r="I61" t="inlineStr">
         <is>
-          <t>1600</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>74-78</t>
+          <t>128-135</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>124800</t>
+          <t>135000</t>
         </is>
       </c>
       <c r="L61" t="inlineStr"/>
@@ -5052,19 +5060,19 @@
       <c r="P61" t="inlineStr"/>
       <c r="Q61" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/coreintegraconsultingservices/CCSL</t>
+          <t>https://www.moneycontrol.com/ipo/completesportsmanagementindialtd/CSMIL</t>
         </is>
       </c>
       <c r="R61" t="inlineStr">
         <is>
-          <t>2026-09-22 14:03:25</t>
+          <t>2026-08-25 09:29:52</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Credent Connect N Care Ltd</t>
+          <t>Coreintegra Consulting Services</t>
         </is>
       </c>
       <c r="B62" t="inlineStr"/>
@@ -5076,33 +5084,33 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Aug 13, 2026</t>
+          <t>Sep 23, 2026</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Aug 17, 2026</t>
+          <t>Sep 25, 2026</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Aug 18, 2026</t>
+          <t>Sep 28, 2026</t>
         </is>
       </c>
       <c r="H62" t="inlineStr"/>
       <c r="I62" t="inlineStr">
         <is>
-          <t>600</t>
+          <t>1600</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>179-189</t>
+          <t>74-78</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>113400</t>
+          <t>124800</t>
         </is>
       </c>
       <c r="L62" t="inlineStr"/>
@@ -5112,19 +5120,19 @@
       <c r="P62" t="inlineStr"/>
       <c r="Q62" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/credentconnectncareltd/CCC04</t>
+          <t>https://www.moneycontrol.com/ipo/coreintegraconsultingservices/CCSL</t>
         </is>
       </c>
       <c r="R62" t="inlineStr">
         <is>
-          <t>2026-08-10 22:43:12</t>
+          <t>2026-09-22 14:03:25</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Dove Soft Ltd</t>
+          <t>Credent Connect N Care Ltd</t>
         </is>
       </c>
       <c r="B63" t="inlineStr"/>
@@ -5136,33 +5144,33 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Sep 30, 2026</t>
+          <t>Aug 13, 2026</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Oct 05, 2026</t>
+          <t>Aug 17, 2026</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Oct 06, 2026</t>
+          <t>Aug 18, 2026</t>
         </is>
       </c>
       <c r="H63" t="inlineStr"/>
       <c r="I63" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>600</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>104-111</t>
+          <t>179-189</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>133200</t>
+          <t>113400</t>
         </is>
       </c>
       <c r="L63" t="inlineStr"/>
@@ -5172,19 +5180,19 @@
       <c r="P63" t="inlineStr"/>
       <c r="Q63" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/dovesoftltd/DSL04</t>
+          <t>https://www.moneycontrol.com/ipo/credentconnectncareltd/CCC04</t>
         </is>
       </c>
       <c r="R63" t="inlineStr">
         <is>
-          <t>2026-09-25 14:20:09</t>
+          <t>2026-08-10 22:43:12</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Farm Peace Ltd</t>
+          <t>Dove Soft Ltd</t>
         </is>
       </c>
       <c r="B64" t="inlineStr"/>
@@ -5196,33 +5204,33 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Sep 01, 2026</t>
+          <t>Sep 30, 2026</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Sep 03, 2026</t>
+          <t>Oct 05, 2026</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Sep 04, 2026</t>
+          <t>Oct 06, 2026</t>
         </is>
       </c>
       <c r="H64" t="inlineStr"/>
       <c r="I64" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>104-111</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>118000</t>
+          <t>133200</t>
         </is>
       </c>
       <c r="L64" t="inlineStr"/>
@@ -5232,19 +5240,19 @@
       <c r="P64" t="inlineStr"/>
       <c r="Q64" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/farmpeaceltd/FPL02</t>
+          <t>https://www.moneycontrol.com/ipo/dovesoftltd/DSL04</t>
         </is>
       </c>
       <c r="R64" t="inlineStr">
         <is>
-          <t>2026-08-27 19:43:03</t>
+          <t>2026-09-25 14:20:09</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Green Asia Impex Ltd</t>
+          <t>Farm Peace Ltd</t>
         </is>
       </c>
       <c r="B65" t="inlineStr"/>
@@ -5256,33 +5264,33 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Sep 24, 2026</t>
+          <t>Sep 01, 2026</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Sep 28, 2026</t>
+          <t>Sep 03, 2026</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Sep 29, 2026</t>
+          <t>Sep 04, 2026</t>
         </is>
       </c>
       <c r="H65" t="inlineStr"/>
       <c r="I65" t="inlineStr">
         <is>
-          <t>1600</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>85-90</t>
+          <t>59</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>144000</t>
+          <t>118000</t>
         </is>
       </c>
       <c r="L65" t="inlineStr"/>
@@ -5292,19 +5300,19 @@
       <c r="P65" t="inlineStr"/>
       <c r="Q65" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/greenasiaimpexltd/GAIL01</t>
+          <t>https://www.moneycontrol.com/ipo/farmpeaceltd/FPL02</t>
         </is>
       </c>
       <c r="R65" t="inlineStr">
         <is>
-          <t>2026-09-22 14:03:25</t>
+          <t>2026-08-27 19:43:03</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Kheria Autocomp Ltd</t>
+          <t>Green Asia Impex Ltd</t>
         </is>
       </c>
       <c r="B66" t="inlineStr"/>
@@ -5316,33 +5324,33 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Sep 17, 2026</t>
+          <t>Sep 24, 2026</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Sep 21, 2026</t>
+          <t>Sep 28, 2026</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Sep 22, 2026</t>
+          <t>Sep 29, 2026</t>
         </is>
       </c>
       <c r="H66" t="inlineStr"/>
       <c r="I66" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>1600</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>96-101</t>
+          <t>85-90</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>121200</t>
+          <t>144000</t>
         </is>
       </c>
       <c r="L66" t="inlineStr"/>
@@ -5352,19 +5360,19 @@
       <c r="P66" t="inlineStr"/>
       <c r="Q66" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/kheriaautocompltd/KAL05</t>
+          <t>https://www.moneycontrol.com/ipo/greenasiaimpexltd/GAIL01</t>
         </is>
       </c>
       <c r="R66" t="inlineStr">
         <is>
-          <t>2026-09-11 13:34:16</t>
+          <t>2026-09-22 14:03:25</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Mopshop Distribution Ltd</t>
+          <t>Kheria Autocomp Ltd</t>
         </is>
       </c>
       <c r="B67" t="inlineStr"/>
@@ -5376,33 +5384,33 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Aug 19, 2026</t>
+          <t>Sep 17, 2026</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Aug 21, 2026</t>
+          <t>Sep 21, 2026</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Aug 24, 2026</t>
+          <t>Sep 22, 2026</t>
         </is>
       </c>
       <c r="H67" t="inlineStr"/>
       <c r="I67" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>138</t>
+          <t>96-101</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>138000</t>
+          <t>121200</t>
         </is>
       </c>
       <c r="L67" t="inlineStr"/>
@@ -5412,19 +5420,19 @@
       <c r="P67" t="inlineStr"/>
       <c r="Q67" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/mopshopdistributionltd/MDL03</t>
+          <t>https://www.moneycontrol.com/ipo/kheriaautocompltd/KAL05</t>
         </is>
       </c>
       <c r="R67" t="inlineStr">
         <is>
-          <t>2026-08-14 21:36:23</t>
+          <t>2026-09-11 13:34:16</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Paluck Technologies Ltd</t>
+          <t>Mopshop Distribution Ltd</t>
         </is>
       </c>
       <c r="B68" t="inlineStr"/>
@@ -5436,33 +5444,33 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Aug 28, 2026</t>
+          <t>Aug 19, 2026</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Sep 01, 2026</t>
+          <t>Aug 21, 2026</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Sep 02, 2026</t>
+          <t>Aug 24, 2026</t>
         </is>
       </c>
       <c r="H68" t="inlineStr"/>
       <c r="I68" t="inlineStr">
         <is>
-          <t>3000</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>46-48</t>
+          <t>138</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>144000</t>
+          <t>138000</t>
         </is>
       </c>
       <c r="L68" t="inlineStr"/>
@@ -5472,19 +5480,19 @@
       <c r="P68" t="inlineStr"/>
       <c r="Q68" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/palucktechnologiesltd/PTL08</t>
+          <t>https://www.moneycontrol.com/ipo/mopshopdistributionltd/MDL03</t>
         </is>
       </c>
       <c r="R68" t="inlineStr">
         <is>
-          <t>2026-08-25 09:29:52</t>
+          <t>2026-08-14 21:36:23</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Papadmalji Agro Foods Ltd</t>
+          <t>Paluck Technologies Ltd</t>
         </is>
       </c>
       <c r="B69" t="inlineStr"/>
@@ -5496,33 +5504,33 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Sep 29, 2026</t>
+          <t>Aug 28, 2026</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Oct 01, 2026</t>
+          <t>Sep 01, 2026</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Oct 05, 2026</t>
+          <t>Sep 02, 2026</t>
         </is>
       </c>
       <c r="H69" t="inlineStr"/>
       <c r="I69" t="inlineStr">
         <is>
-          <t>1600</t>
+          <t>3000</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>69-72</t>
+          <t>46-48</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>115200</t>
+          <t>144000</t>
         </is>
       </c>
       <c r="L69" t="inlineStr"/>
@@ -5532,19 +5540,19 @@
       <c r="P69" t="inlineStr"/>
       <c r="Q69" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/papadmaljiagrofoodsltd/PAF</t>
+          <t>https://www.moneycontrol.com/ipo/palucktechnologiesltd/PTL08</t>
         </is>
       </c>
       <c r="R69" t="inlineStr">
         <is>
-          <t>2026-09-25 14:20:09</t>
+          <t>2026-08-25 09:29:52</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Paramount Syntex Ltd</t>
+          <t>Papadmalji Agro Foods Ltd</t>
         </is>
       </c>
       <c r="B70" t="inlineStr"/>
@@ -5556,33 +5564,33 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Sep 30, 2026</t>
+          <t>Sep 29, 2026</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Oct 06, 2026</t>
+          <t>Oct 01, 2026</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Oct 07, 2026</t>
+          <t>Oct 05, 2026</t>
         </is>
       </c>
       <c r="H70" t="inlineStr"/>
       <c r="I70" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>1600</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>119-127</t>
+          <t>69-72</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>127000</t>
+          <t>115200</t>
         </is>
       </c>
       <c r="L70" t="inlineStr"/>
@@ -5592,7 +5600,7 @@
       <c r="P70" t="inlineStr"/>
       <c r="Q70" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/paramountsyntexltd/PSL06</t>
+          <t>https://www.moneycontrol.com/ipo/papadmaljiagrofoodsltd/PAF</t>
         </is>
       </c>
       <c r="R70" t="inlineStr">
@@ -5604,7 +5612,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Peshwa Wheat</t>
+          <t>Paramount Syntex Ltd</t>
         </is>
       </c>
       <c r="B71" t="inlineStr"/>
@@ -5616,33 +5624,33 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Sep 24, 2026</t>
+          <t>Sep 30, 2026</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Sep 28, 2026</t>
+          <t>Oct 06, 2026</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Sep 29, 2026</t>
+          <t>Oct 07, 2026</t>
         </is>
       </c>
       <c r="H71" t="inlineStr"/>
       <c r="I71" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>95-101</t>
+          <t>119-127</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>121200</t>
+          <t>127000</t>
         </is>
       </c>
       <c r="L71" t="inlineStr"/>
@@ -5652,135 +5660,135 @@
       <c r="P71" t="inlineStr"/>
       <c r="Q71" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/peshwawheat/PWL01</t>
+          <t>https://www.moneycontrol.com/ipo/paramountsyntexltd/PSL06</t>
         </is>
       </c>
       <c r="R71" t="inlineStr">
         <is>
-          <t>2026-09-22 14:03:25</t>
+          <t>2026-09-25 14:20:09</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Purple Style Labs Ltd</t>
+          <t>Peshwa Wheat</t>
         </is>
       </c>
       <c r="B72" t="inlineStr"/>
       <c r="C72" t="inlineStr"/>
-      <c r="D72" s="4" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="D72" s="5" t="inlineStr">
+        <is>
+          <t>Upcoming</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Aug 31, 2026</t>
+          <t>Sep 24, 2026</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Sep 02, 2026</t>
+          <t>Sep 28, 2026</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Sep 03, 2026</t>
+          <t>Sep 29, 2026</t>
         </is>
       </c>
       <c r="H72" t="inlineStr"/>
-      <c r="I72" t="inlineStr"/>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>1200</t>
+        </is>
+      </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>575</t>
-        </is>
-      </c>
-      <c r="K72" t="inlineStr"/>
+          <t>95-101</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>121200</t>
+        </is>
+      </c>
       <c r="L72" t="inlineStr"/>
       <c r="M72" t="inlineStr"/>
-      <c r="N72" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="N72" t="inlineStr"/>
       <c r="O72" t="inlineStr"/>
       <c r="P72" t="inlineStr"/>
       <c r="Q72" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/purplestylelabsltd/PSL05</t>
+          <t>https://www.moneycontrol.com/ipo/peshwawheat/PWL01</t>
         </is>
       </c>
       <c r="R72" t="inlineStr">
         <is>
-          <t>2026-09-02 13:25:30</t>
+          <t>2026-09-22 14:03:25</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Q&amp;T Foods Ltd</t>
+          <t>Purple Style Labs Ltd</t>
         </is>
       </c>
       <c r="B73" t="inlineStr"/>
       <c r="C73" t="inlineStr"/>
-      <c r="D73" s="5" t="inlineStr">
-        <is>
-          <t>Upcoming</t>
+      <c r="D73" s="4" t="inlineStr">
+        <is>
+          <t>Open</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Aug 12, 2026</t>
+          <t>Aug 31, 2026</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Aug 14, 2026</t>
+          <t>Sep 02, 2026</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Aug 17, 2026</t>
+          <t>Sep 03, 2026</t>
         </is>
       </c>
       <c r="H73" t="inlineStr"/>
-      <c r="I73" t="inlineStr">
-        <is>
-          <t>1200</t>
-        </is>
-      </c>
+      <c r="I73" t="inlineStr"/>
       <c r="J73" t="inlineStr">
         <is>
-          <t>115</t>
-        </is>
-      </c>
-      <c r="K73" t="inlineStr">
-        <is>
-          <t>138000</t>
-        </is>
-      </c>
+          <t>575</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr"/>
       <c r="L73" t="inlineStr"/>
       <c r="M73" t="inlineStr"/>
-      <c r="N73" t="inlineStr"/>
+      <c r="N73" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="O73" t="inlineStr"/>
       <c r="P73" t="inlineStr"/>
       <c r="Q73" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/qtfoodsltd/QFL</t>
+          <t>https://www.moneycontrol.com/ipo/purplestylelabsltd/PSL05</t>
         </is>
       </c>
       <c r="R73" t="inlineStr">
         <is>
-          <t>2026-08-10 10:24:29</t>
+          <t>2026-09-02 13:25:30</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Shanti Inorganics Ltd</t>
+          <t>Q&amp;T Foods Ltd</t>
         </is>
       </c>
       <c r="B74" t="inlineStr"/>
@@ -5792,33 +5800,33 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Aug 31, 2026</t>
+          <t>Aug 12, 2026</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Sep 02, 2026</t>
+          <t>Aug 14, 2026</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Sep 03, 2026</t>
+          <t>Aug 17, 2026</t>
         </is>
       </c>
       <c r="H74" t="inlineStr"/>
       <c r="I74" t="inlineStr">
         <is>
-          <t>1600</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>79-83</t>
+          <t>115</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>132800</t>
+          <t>138000</t>
         </is>
       </c>
       <c r="L74" t="inlineStr"/>
@@ -5828,19 +5836,19 @@
       <c r="P74" t="inlineStr"/>
       <c r="Q74" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/shantiinorganicsltd/SIL34</t>
+          <t>https://www.moneycontrol.com/ipo/qtfoodsltd/QFL</t>
         </is>
       </c>
       <c r="R74" t="inlineStr">
         <is>
-          <t>2026-08-25 09:29:52</t>
+          <t>2026-08-10 10:24:29</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Technocrats Plasma Systems Ltd</t>
+          <t>Shanti Inorganics Ltd</t>
         </is>
       </c>
       <c r="B75" t="inlineStr"/>
@@ -5852,33 +5860,33 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Aug 14, 2026</t>
+          <t>Aug 31, 2026</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Aug 18, 2026</t>
+          <t>Sep 02, 2026</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Aug 19, 2026</t>
+          <t>Sep 03, 2026</t>
         </is>
       </c>
       <c r="H75" t="inlineStr"/>
       <c r="I75" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>1600</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>125-132</t>
+          <t>79-83</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>132000</t>
+          <t>132800</t>
         </is>
       </c>
       <c r="L75" t="inlineStr"/>
@@ -5888,19 +5896,19 @@
       <c r="P75" t="inlineStr"/>
       <c r="Q75" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/technocratsplasmasystemsltd/TPSL</t>
+          <t>https://www.moneycontrol.com/ipo/shantiinorganicsltd/SIL34</t>
         </is>
       </c>
       <c r="R75" t="inlineStr">
         <is>
-          <t>2026-08-11 21:41:02</t>
+          <t>2026-08-25 09:29:52</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Unitec Fibres Ltd</t>
+          <t>Technocrats Plasma Systems Ltd</t>
         </is>
       </c>
       <c r="B76" t="inlineStr"/>
@@ -5912,33 +5920,33 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Sep 23, 2026</t>
+          <t>Aug 14, 2026</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Sep 25, 2026</t>
+          <t>Aug 18, 2026</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Sep 28, 2026</t>
+          <t>Aug 19, 2026</t>
         </is>
       </c>
       <c r="H76" t="inlineStr"/>
       <c r="I76" t="inlineStr">
         <is>
-          <t>1600</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>83-88</t>
+          <t>125-132</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>140800</t>
+          <t>132000</t>
         </is>
       </c>
       <c r="L76" t="inlineStr"/>
@@ -5948,19 +5956,19 @@
       <c r="P76" t="inlineStr"/>
       <c r="Q76" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/unitecfibresltd/UFL03</t>
+          <t>https://www.moneycontrol.com/ipo/technocratsplasmasystemsltd/TPSL</t>
         </is>
       </c>
       <c r="R76" t="inlineStr">
         <is>
-          <t>2026-09-18 23:59:33</t>
+          <t>2026-08-11 21:41:02</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>VANS Electroengineerings Ltd</t>
+          <t>Unitec Fibres Ltd</t>
         </is>
       </c>
       <c r="B77" t="inlineStr"/>
@@ -5972,33 +5980,33 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Sep 29, 2026</t>
+          <t>Sep 23, 2026</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Oct 01, 2026</t>
+          <t>Sep 25, 2026</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Oct 05, 2026</t>
+          <t>Sep 28, 2026</t>
         </is>
       </c>
       <c r="H77" t="inlineStr"/>
       <c r="I77" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>1600</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>112-118</t>
+          <t>83-88</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>141600</t>
+          <t>140800</t>
         </is>
       </c>
       <c r="L77" t="inlineStr"/>
@@ -6008,19 +6016,19 @@
       <c r="P77" t="inlineStr"/>
       <c r="Q77" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/vanselectroengineeringsltd/VEL03</t>
+          <t>https://www.moneycontrol.com/ipo/unitecfibresltd/UFL03</t>
         </is>
       </c>
       <c r="R77" t="inlineStr">
         <is>
-          <t>2026-09-25 14:20:09</t>
+          <t>2026-09-18 23:59:33</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Vama Wovenfab Ltd</t>
+          <t>VANS Electroengineerings Ltd</t>
         </is>
       </c>
       <c r="B78" t="inlineStr"/>
@@ -6032,33 +6040,33 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Sep 15, 2026</t>
+          <t>Sep 29, 2026</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Sep 17, 2026</t>
+          <t>Oct 01, 2026</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Sep 18, 2026</t>
+          <t>Oct 05, 2026</t>
         </is>
       </c>
       <c r="H78" t="inlineStr"/>
       <c r="I78" t="inlineStr">
         <is>
-          <t>400</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>324-341</t>
+          <t>112-118</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>136400</t>
+          <t>141600</t>
         </is>
       </c>
       <c r="L78" t="inlineStr"/>
@@ -6068,17 +6076,77 @@
       <c r="P78" t="inlineStr"/>
       <c r="Q78" t="inlineStr">
         <is>
+          <t>https://www.moneycontrol.com/ipo/vanselectroengineeringsltd/VEL03</t>
+        </is>
+      </c>
+      <c r="R78" t="inlineStr">
+        <is>
+          <t>2026-09-25 14:20:09</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Vama Wovenfab Ltd</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr"/>
+      <c r="C79" t="inlineStr"/>
+      <c r="D79" s="5" t="inlineStr">
+        <is>
+          <t>Upcoming</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>Sep 15, 2026</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Sep 17, 2026</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Sep 18, 2026</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr"/>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>400</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>324-341</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>136400</t>
+        </is>
+      </c>
+      <c r="L79" t="inlineStr"/>
+      <c r="M79" t="inlineStr"/>
+      <c r="N79" t="inlineStr"/>
+      <c r="O79" t="inlineStr"/>
+      <c r="P79" t="inlineStr"/>
+      <c r="Q79" t="inlineStr">
+        <is>
           <t>https://www.moneycontrol.com/ipo/vamawovenfabltd/VWL01</t>
         </is>
       </c>
-      <c r="R78" t="inlineStr">
+      <c r="R79" t="inlineStr">
         <is>
           <t>2026-09-11 13:34:16</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:R78"/>
+  <autoFilter ref="A1:R79"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/mainboard_ipos.xlsx
+++ b/data/mainboard_ipos.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Mainboard IPOs" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Mainboard IPOs'!$A$1:$R$79</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Mainboard IPOs'!$A$1:$R$80</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -449,7 +449,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R79"/>
+  <dimension ref="A1:R80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -4009,9 +4009,9 @@
       </c>
       <c r="B46" t="inlineStr"/>
       <c r="C46" t="inlineStr"/>
-      <c r="D46" s="3" t="inlineStr">
-        <is>
-          <t>Closed</t>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>Listed</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -4060,12 +4060,12 @@
       <c r="P46" t="inlineStr"/>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/varmoragranito/VGL</t>
+          <t>https://www.moneycontrol.com/ipo/ceramicsmarblegranitesanitaryware/varmoragranito/VGL</t>
         </is>
       </c>
       <c r="R46" t="inlineStr">
         <is>
-          <t>2026-09-25 14:20:09</t>
+          <t>2026-09-29 15:20:41</t>
         </is>
       </c>
     </row>
@@ -4133,7 +4133,7 @@
       </c>
       <c r="R47" t="inlineStr">
         <is>
-          <t>2026-09-28 15:18:07</t>
+          <t>2026-09-29 15:20:41</t>
         </is>
       </c>
     </row>
@@ -4201,7 +4201,7 @@
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>2026-09-28 15:18:07</t>
+          <t>2026-09-29 15:20:41</t>
         </is>
       </c>
     </row>
@@ -4269,7 +4269,7 @@
       </c>
       <c r="R49" t="inlineStr">
         <is>
-          <t>2026-09-28 15:18:07</t>
+          <t>2026-09-29 15:20:41</t>
         </is>
       </c>
     </row>
@@ -4349,9 +4349,9 @@
       </c>
       <c r="B51" t="inlineStr"/>
       <c r="C51" t="inlineStr"/>
-      <c r="D51" s="4" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="D51" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -4393,7 +4393,7 @@
       <c r="M51" t="inlineStr"/>
       <c r="N51" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>12</t>
         </is>
       </c>
       <c r="O51" t="inlineStr"/>
@@ -4405,7 +4405,7 @@
       </c>
       <c r="R51" t="inlineStr">
         <is>
-          <t>2026-09-28 15:18:07</t>
+          <t>2026-09-29 15:20:41</t>
         </is>
       </c>
     </row>
@@ -4541,7 +4541,7 @@
       </c>
       <c r="R53" t="inlineStr">
         <is>
-          <t>2026-09-28 15:18:07</t>
+          <t>2026-09-29 15:20:41</t>
         </is>
       </c>
     </row>
@@ -4597,7 +4597,7 @@
       <c r="M54" t="inlineStr"/>
       <c r="N54" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="O54" t="inlineStr"/>
@@ -4609,7 +4609,7 @@
       </c>
       <c r="R54" t="inlineStr">
         <is>
-          <t>2026-09-28 15:18:07</t>
+          <t>2026-09-29 15:20:41</t>
         </is>
       </c>
     </row>
@@ -4665,7 +4665,7 @@
       <c r="M55" t="inlineStr"/>
       <c r="N55" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8</t>
         </is>
       </c>
       <c r="O55" t="inlineStr"/>
@@ -4677,7 +4677,7 @@
       </c>
       <c r="R55" t="inlineStr">
         <is>
-          <t>2026-09-28 15:18:07</t>
+          <t>2026-09-29 15:20:41</t>
         </is>
       </c>
     </row>
@@ -4745,7 +4745,7 @@
       </c>
       <c r="R56" t="inlineStr">
         <is>
-          <t>2026-09-28 15:18:07</t>
+          <t>2026-09-29 15:20:41</t>
         </is>
       </c>
     </row>
@@ -4813,7 +4813,7 @@
       </c>
       <c r="R57" t="inlineStr">
         <is>
-          <t>2026-09-28 15:18:07</t>
+          <t>2026-09-29 15:20:41</t>
         </is>
       </c>
     </row>
@@ -4881,7 +4881,7 @@
       </c>
       <c r="R58" t="inlineStr">
         <is>
-          <t>2026-09-28 15:18:07</t>
+          <t>2026-09-29 15:20:41</t>
         </is>
       </c>
     </row>
@@ -5005,14 +5005,14 @@
       </c>
       <c r="R60" t="inlineStr">
         <is>
-          <t>2026-09-28 15:18:07</t>
+          <t>2026-09-29 15:20:41</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Complete Sports and Management India Ltd</t>
+          <t>Vishal Nirmiti Ltd</t>
         </is>
       </c>
       <c r="B61" t="inlineStr"/>
@@ -5024,33 +5024,37 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Aug 28, 2026</t>
+          <t>Sep 30, 2026</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Sep 01, 2026</t>
+          <t>Oct 05, 2026</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Sep 02, 2026</t>
-        </is>
-      </c>
-      <c r="H61" t="inlineStr"/>
+          <t>Oct 06, 2026</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>Oct 08, 2026</t>
+        </is>
+      </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>68</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>128-135</t>
+          <t>208-220</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>135000</t>
+          <t>14960</t>
         </is>
       </c>
       <c r="L61" t="inlineStr"/>
@@ -5060,19 +5064,19 @@
       <c r="P61" t="inlineStr"/>
       <c r="Q61" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/completesportsmanagementindialtd/CSMIL</t>
+          <t>https://www.moneycontrol.com/ipo/vishalnirmitiltd/VNL01</t>
         </is>
       </c>
       <c r="R61" t="inlineStr">
         <is>
-          <t>2026-08-25 09:29:52</t>
+          <t>2026-09-29 15:20:41</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Coreintegra Consulting Services</t>
+          <t>Complete Sports and Management India Ltd</t>
         </is>
       </c>
       <c r="B62" t="inlineStr"/>
@@ -5084,33 +5088,33 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Sep 23, 2026</t>
+          <t>Aug 28, 2026</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Sep 25, 2026</t>
+          <t>Sep 01, 2026</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Sep 28, 2026</t>
+          <t>Sep 02, 2026</t>
         </is>
       </c>
       <c r="H62" t="inlineStr"/>
       <c r="I62" t="inlineStr">
         <is>
-          <t>1600</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>74-78</t>
+          <t>128-135</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>124800</t>
+          <t>135000</t>
         </is>
       </c>
       <c r="L62" t="inlineStr"/>
@@ -5120,19 +5124,19 @@
       <c r="P62" t="inlineStr"/>
       <c r="Q62" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/coreintegraconsultingservices/CCSL</t>
+          <t>https://www.moneycontrol.com/ipo/completesportsmanagementindialtd/CSMIL</t>
         </is>
       </c>
       <c r="R62" t="inlineStr">
         <is>
-          <t>2026-09-22 14:03:25</t>
+          <t>2026-08-25 09:29:52</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Credent Connect N Care Ltd</t>
+          <t>Coreintegra Consulting Services</t>
         </is>
       </c>
       <c r="B63" t="inlineStr"/>
@@ -5144,33 +5148,33 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Aug 13, 2026</t>
+          <t>Sep 23, 2026</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Aug 17, 2026</t>
+          <t>Sep 25, 2026</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Aug 18, 2026</t>
+          <t>Sep 28, 2026</t>
         </is>
       </c>
       <c r="H63" t="inlineStr"/>
       <c r="I63" t="inlineStr">
         <is>
-          <t>600</t>
+          <t>1600</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>179-189</t>
+          <t>74-78</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>113400</t>
+          <t>124800</t>
         </is>
       </c>
       <c r="L63" t="inlineStr"/>
@@ -5180,19 +5184,19 @@
       <c r="P63" t="inlineStr"/>
       <c r="Q63" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/credentconnectncareltd/CCC04</t>
+          <t>https://www.moneycontrol.com/ipo/coreintegraconsultingservices/CCSL</t>
         </is>
       </c>
       <c r="R63" t="inlineStr">
         <is>
-          <t>2026-08-10 22:43:12</t>
+          <t>2026-09-22 14:03:25</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Dove Soft Ltd</t>
+          <t>Credent Connect N Care Ltd</t>
         </is>
       </c>
       <c r="B64" t="inlineStr"/>
@@ -5204,33 +5208,33 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Sep 30, 2026</t>
+          <t>Aug 13, 2026</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Oct 05, 2026</t>
+          <t>Aug 17, 2026</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Oct 06, 2026</t>
+          <t>Aug 18, 2026</t>
         </is>
       </c>
       <c r="H64" t="inlineStr"/>
       <c r="I64" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>600</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>104-111</t>
+          <t>179-189</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>133200</t>
+          <t>113400</t>
         </is>
       </c>
       <c r="L64" t="inlineStr"/>
@@ -5240,19 +5244,19 @@
       <c r="P64" t="inlineStr"/>
       <c r="Q64" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/dovesoftltd/DSL04</t>
+          <t>https://www.moneycontrol.com/ipo/credentconnectncareltd/CCC04</t>
         </is>
       </c>
       <c r="R64" t="inlineStr">
         <is>
-          <t>2026-09-25 14:20:09</t>
+          <t>2026-08-10 22:43:12</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Farm Peace Ltd</t>
+          <t>Dove Soft Ltd</t>
         </is>
       </c>
       <c r="B65" t="inlineStr"/>
@@ -5264,33 +5268,33 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Sep 01, 2026</t>
+          <t>Sep 30, 2026</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Sep 03, 2026</t>
+          <t>Oct 05, 2026</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Sep 04, 2026</t>
+          <t>Oct 06, 2026</t>
         </is>
       </c>
       <c r="H65" t="inlineStr"/>
       <c r="I65" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>104-111</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>118000</t>
+          <t>133200</t>
         </is>
       </c>
       <c r="L65" t="inlineStr"/>
@@ -5300,19 +5304,19 @@
       <c r="P65" t="inlineStr"/>
       <c r="Q65" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/farmpeaceltd/FPL02</t>
+          <t>https://www.moneycontrol.com/ipo/dovesoftltd/DSL04</t>
         </is>
       </c>
       <c r="R65" t="inlineStr">
         <is>
-          <t>2026-08-27 19:43:03</t>
+          <t>2026-09-25 14:20:09</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Green Asia Impex Ltd</t>
+          <t>Farm Peace Ltd</t>
         </is>
       </c>
       <c r="B66" t="inlineStr"/>
@@ -5324,33 +5328,33 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Sep 24, 2026</t>
+          <t>Sep 01, 2026</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Sep 28, 2026</t>
+          <t>Sep 03, 2026</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Sep 29, 2026</t>
+          <t>Sep 04, 2026</t>
         </is>
       </c>
       <c r="H66" t="inlineStr"/>
       <c r="I66" t="inlineStr">
         <is>
-          <t>1600</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>85-90</t>
+          <t>59</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>144000</t>
+          <t>118000</t>
         </is>
       </c>
       <c r="L66" t="inlineStr"/>
@@ -5360,19 +5364,19 @@
       <c r="P66" t="inlineStr"/>
       <c r="Q66" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/greenasiaimpexltd/GAIL01</t>
+          <t>https://www.moneycontrol.com/ipo/farmpeaceltd/FPL02</t>
         </is>
       </c>
       <c r="R66" t="inlineStr">
         <is>
-          <t>2026-09-22 14:03:25</t>
+          <t>2026-08-27 19:43:03</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Kheria Autocomp Ltd</t>
+          <t>Green Asia Impex Ltd</t>
         </is>
       </c>
       <c r="B67" t="inlineStr"/>
@@ -5384,33 +5388,33 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Sep 17, 2026</t>
+          <t>Sep 24, 2026</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Sep 21, 2026</t>
+          <t>Sep 28, 2026</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Sep 22, 2026</t>
+          <t>Sep 29, 2026</t>
         </is>
       </c>
       <c r="H67" t="inlineStr"/>
       <c r="I67" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>1600</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>96-101</t>
+          <t>85-90</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>121200</t>
+          <t>144000</t>
         </is>
       </c>
       <c r="L67" t="inlineStr"/>
@@ -5420,19 +5424,19 @@
       <c r="P67" t="inlineStr"/>
       <c r="Q67" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/kheriaautocompltd/KAL05</t>
+          <t>https://www.moneycontrol.com/ipo/greenasiaimpexltd/GAIL01</t>
         </is>
       </c>
       <c r="R67" t="inlineStr">
         <is>
-          <t>2026-09-11 13:34:16</t>
+          <t>2026-09-22 14:03:25</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Mopshop Distribution Ltd</t>
+          <t>Kheria Autocomp Ltd</t>
         </is>
       </c>
       <c r="B68" t="inlineStr"/>
@@ -5444,33 +5448,33 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Aug 19, 2026</t>
+          <t>Sep 17, 2026</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Aug 21, 2026</t>
+          <t>Sep 21, 2026</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Aug 24, 2026</t>
+          <t>Sep 22, 2026</t>
         </is>
       </c>
       <c r="H68" t="inlineStr"/>
       <c r="I68" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>138</t>
+          <t>96-101</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>138000</t>
+          <t>121200</t>
         </is>
       </c>
       <c r="L68" t="inlineStr"/>
@@ -5480,19 +5484,19 @@
       <c r="P68" t="inlineStr"/>
       <c r="Q68" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/mopshopdistributionltd/MDL03</t>
+          <t>https://www.moneycontrol.com/ipo/kheriaautocompltd/KAL05</t>
         </is>
       </c>
       <c r="R68" t="inlineStr">
         <is>
-          <t>2026-08-14 21:36:23</t>
+          <t>2026-09-11 13:34:16</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Paluck Technologies Ltd</t>
+          <t>Mopshop Distribution Ltd</t>
         </is>
       </c>
       <c r="B69" t="inlineStr"/>
@@ -5504,33 +5508,33 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Aug 28, 2026</t>
+          <t>Aug 19, 2026</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Sep 01, 2026</t>
+          <t>Aug 21, 2026</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Sep 02, 2026</t>
+          <t>Aug 24, 2026</t>
         </is>
       </c>
       <c r="H69" t="inlineStr"/>
       <c r="I69" t="inlineStr">
         <is>
-          <t>3000</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>46-48</t>
+          <t>138</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>144000</t>
+          <t>138000</t>
         </is>
       </c>
       <c r="L69" t="inlineStr"/>
@@ -5540,19 +5544,19 @@
       <c r="P69" t="inlineStr"/>
       <c r="Q69" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/palucktechnologiesltd/PTL08</t>
+          <t>https://www.moneycontrol.com/ipo/mopshopdistributionltd/MDL03</t>
         </is>
       </c>
       <c r="R69" t="inlineStr">
         <is>
-          <t>2026-08-25 09:29:52</t>
+          <t>2026-08-14 21:36:23</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Papadmalji Agro Foods Ltd</t>
+          <t>Paluck Technologies Ltd</t>
         </is>
       </c>
       <c r="B70" t="inlineStr"/>
@@ -5564,33 +5568,33 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Sep 29, 2026</t>
+          <t>Aug 28, 2026</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Oct 01, 2026</t>
+          <t>Sep 01, 2026</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Oct 05, 2026</t>
+          <t>Sep 02, 2026</t>
         </is>
       </c>
       <c r="H70" t="inlineStr"/>
       <c r="I70" t="inlineStr">
         <is>
-          <t>1600</t>
+          <t>3000</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>69-72</t>
+          <t>46-48</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>115200</t>
+          <t>144000</t>
         </is>
       </c>
       <c r="L70" t="inlineStr"/>
@@ -5600,19 +5604,19 @@
       <c r="P70" t="inlineStr"/>
       <c r="Q70" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/papadmaljiagrofoodsltd/PAF</t>
+          <t>https://www.moneycontrol.com/ipo/palucktechnologiesltd/PTL08</t>
         </is>
       </c>
       <c r="R70" t="inlineStr">
         <is>
-          <t>2026-09-25 14:20:09</t>
+          <t>2026-08-25 09:29:52</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Paramount Syntex Ltd</t>
+          <t>Papadmalji Agro Foods Ltd</t>
         </is>
       </c>
       <c r="B71" t="inlineStr"/>
@@ -5624,33 +5628,33 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Sep 30, 2026</t>
+          <t>Sep 29, 2026</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Oct 06, 2026</t>
+          <t>Oct 01, 2026</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Oct 07, 2026</t>
+          <t>Oct 05, 2026</t>
         </is>
       </c>
       <c r="H71" t="inlineStr"/>
       <c r="I71" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>1600</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>119-127</t>
+          <t>69-72</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>127000</t>
+          <t>115200</t>
         </is>
       </c>
       <c r="L71" t="inlineStr"/>
@@ -5660,7 +5664,7 @@
       <c r="P71" t="inlineStr"/>
       <c r="Q71" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/paramountsyntexltd/PSL06</t>
+          <t>https://www.moneycontrol.com/ipo/papadmaljiagrofoodsltd/PAF</t>
         </is>
       </c>
       <c r="R71" t="inlineStr">
@@ -5672,7 +5676,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Peshwa Wheat</t>
+          <t>Paramount Syntex Ltd</t>
         </is>
       </c>
       <c r="B72" t="inlineStr"/>
@@ -5684,33 +5688,33 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Sep 24, 2026</t>
+          <t>Sep 30, 2026</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Sep 28, 2026</t>
+          <t>Oct 06, 2026</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Sep 29, 2026</t>
+          <t>Oct 07, 2026</t>
         </is>
       </c>
       <c r="H72" t="inlineStr"/>
       <c r="I72" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>95-101</t>
+          <t>119-127</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>121200</t>
+          <t>127000</t>
         </is>
       </c>
       <c r="L72" t="inlineStr"/>
@@ -5720,135 +5724,135 @@
       <c r="P72" t="inlineStr"/>
       <c r="Q72" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/peshwawheat/PWL01</t>
+          <t>https://www.moneycontrol.com/ipo/paramountsyntexltd/PSL06</t>
         </is>
       </c>
       <c r="R72" t="inlineStr">
         <is>
-          <t>2026-09-22 14:03:25</t>
+          <t>2026-09-25 14:20:09</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Purple Style Labs Ltd</t>
+          <t>Peshwa Wheat</t>
         </is>
       </c>
       <c r="B73" t="inlineStr"/>
       <c r="C73" t="inlineStr"/>
-      <c r="D73" s="4" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="D73" s="5" t="inlineStr">
+        <is>
+          <t>Upcoming</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Aug 31, 2026</t>
+          <t>Sep 24, 2026</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Sep 02, 2026</t>
+          <t>Sep 28, 2026</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Sep 03, 2026</t>
+          <t>Sep 29, 2026</t>
         </is>
       </c>
       <c r="H73" t="inlineStr"/>
-      <c r="I73" t="inlineStr"/>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>1200</t>
+        </is>
+      </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>575</t>
-        </is>
-      </c>
-      <c r="K73" t="inlineStr"/>
+          <t>95-101</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>121200</t>
+        </is>
+      </c>
       <c r="L73" t="inlineStr"/>
       <c r="M73" t="inlineStr"/>
-      <c r="N73" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="N73" t="inlineStr"/>
       <c r="O73" t="inlineStr"/>
       <c r="P73" t="inlineStr"/>
       <c r="Q73" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/purplestylelabsltd/PSL05</t>
+          <t>https://www.moneycontrol.com/ipo/peshwawheat/PWL01</t>
         </is>
       </c>
       <c r="R73" t="inlineStr">
         <is>
-          <t>2026-09-02 13:25:30</t>
+          <t>2026-09-22 14:03:25</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Q&amp;T Foods Ltd</t>
+          <t>Purple Style Labs Ltd</t>
         </is>
       </c>
       <c r="B74" t="inlineStr"/>
       <c r="C74" t="inlineStr"/>
-      <c r="D74" s="5" t="inlineStr">
-        <is>
-          <t>Upcoming</t>
+      <c r="D74" s="4" t="inlineStr">
+        <is>
+          <t>Open</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Aug 12, 2026</t>
+          <t>Aug 31, 2026</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Aug 14, 2026</t>
+          <t>Sep 02, 2026</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Aug 17, 2026</t>
+          <t>Sep 03, 2026</t>
         </is>
       </c>
       <c r="H74" t="inlineStr"/>
-      <c r="I74" t="inlineStr">
-        <is>
-          <t>1200</t>
-        </is>
-      </c>
+      <c r="I74" t="inlineStr"/>
       <c r="J74" t="inlineStr">
         <is>
-          <t>115</t>
-        </is>
-      </c>
-      <c r="K74" t="inlineStr">
-        <is>
-          <t>138000</t>
-        </is>
-      </c>
+          <t>575</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr"/>
       <c r="L74" t="inlineStr"/>
       <c r="M74" t="inlineStr"/>
-      <c r="N74" t="inlineStr"/>
+      <c r="N74" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="O74" t="inlineStr"/>
       <c r="P74" t="inlineStr"/>
       <c r="Q74" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/qtfoodsltd/QFL</t>
+          <t>https://www.moneycontrol.com/ipo/purplestylelabsltd/PSL05</t>
         </is>
       </c>
       <c r="R74" t="inlineStr">
         <is>
-          <t>2026-08-10 10:24:29</t>
+          <t>2026-09-02 13:25:30</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Shanti Inorganics Ltd</t>
+          <t>Q&amp;T Foods Ltd</t>
         </is>
       </c>
       <c r="B75" t="inlineStr"/>
@@ -5860,33 +5864,33 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Aug 31, 2026</t>
+          <t>Aug 12, 2026</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Sep 02, 2026</t>
+          <t>Aug 14, 2026</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Sep 03, 2026</t>
+          <t>Aug 17, 2026</t>
         </is>
       </c>
       <c r="H75" t="inlineStr"/>
       <c r="I75" t="inlineStr">
         <is>
-          <t>1600</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>79-83</t>
+          <t>115</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>132800</t>
+          <t>138000</t>
         </is>
       </c>
       <c r="L75" t="inlineStr"/>
@@ -5896,19 +5900,19 @@
       <c r="P75" t="inlineStr"/>
       <c r="Q75" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/shantiinorganicsltd/SIL34</t>
+          <t>https://www.moneycontrol.com/ipo/qtfoodsltd/QFL</t>
         </is>
       </c>
       <c r="R75" t="inlineStr">
         <is>
-          <t>2026-08-25 09:29:52</t>
+          <t>2026-08-10 10:24:29</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Technocrats Plasma Systems Ltd</t>
+          <t>Shanti Inorganics Ltd</t>
         </is>
       </c>
       <c r="B76" t="inlineStr"/>
@@ -5920,33 +5924,33 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Aug 14, 2026</t>
+          <t>Aug 31, 2026</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Aug 18, 2026</t>
+          <t>Sep 02, 2026</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Aug 19, 2026</t>
+          <t>Sep 03, 2026</t>
         </is>
       </c>
       <c r="H76" t="inlineStr"/>
       <c r="I76" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>1600</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>125-132</t>
+          <t>79-83</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>132000</t>
+          <t>132800</t>
         </is>
       </c>
       <c r="L76" t="inlineStr"/>
@@ -5956,19 +5960,19 @@
       <c r="P76" t="inlineStr"/>
       <c r="Q76" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/technocratsplasmasystemsltd/TPSL</t>
+          <t>https://www.moneycontrol.com/ipo/shantiinorganicsltd/SIL34</t>
         </is>
       </c>
       <c r="R76" t="inlineStr">
         <is>
-          <t>2026-08-11 21:41:02</t>
+          <t>2026-08-25 09:29:52</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Unitec Fibres Ltd</t>
+          <t>Technocrats Plasma Systems Ltd</t>
         </is>
       </c>
       <c r="B77" t="inlineStr"/>
@@ -5980,33 +5984,33 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Sep 23, 2026</t>
+          <t>Aug 14, 2026</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Sep 25, 2026</t>
+          <t>Aug 18, 2026</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Sep 28, 2026</t>
+          <t>Aug 19, 2026</t>
         </is>
       </c>
       <c r="H77" t="inlineStr"/>
       <c r="I77" t="inlineStr">
         <is>
-          <t>1600</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>83-88</t>
+          <t>125-132</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>140800</t>
+          <t>132000</t>
         </is>
       </c>
       <c r="L77" t="inlineStr"/>
@@ -6016,19 +6020,19 @@
       <c r="P77" t="inlineStr"/>
       <c r="Q77" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/unitecfibresltd/UFL03</t>
+          <t>https://www.moneycontrol.com/ipo/technocratsplasmasystemsltd/TPSL</t>
         </is>
       </c>
       <c r="R77" t="inlineStr">
         <is>
-          <t>2026-09-18 23:59:33</t>
+          <t>2026-08-11 21:41:02</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>VANS Electroengineerings Ltd</t>
+          <t>Unitec Fibres Ltd</t>
         </is>
       </c>
       <c r="B78" t="inlineStr"/>
@@ -6040,33 +6044,33 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Sep 29, 2026</t>
+          <t>Sep 23, 2026</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Oct 01, 2026</t>
+          <t>Sep 25, 2026</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Oct 05, 2026</t>
+          <t>Sep 28, 2026</t>
         </is>
       </c>
       <c r="H78" t="inlineStr"/>
       <c r="I78" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>1600</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>112-118</t>
+          <t>83-88</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>141600</t>
+          <t>140800</t>
         </is>
       </c>
       <c r="L78" t="inlineStr"/>
@@ -6076,19 +6080,19 @@
       <c r="P78" t="inlineStr"/>
       <c r="Q78" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/vanselectroengineeringsltd/VEL03</t>
+          <t>https://www.moneycontrol.com/ipo/unitecfibresltd/UFL03</t>
         </is>
       </c>
       <c r="R78" t="inlineStr">
         <is>
-          <t>2026-09-25 14:20:09</t>
+          <t>2026-09-18 23:59:33</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Vama Wovenfab Ltd</t>
+          <t>VANS Electroengineerings Ltd</t>
         </is>
       </c>
       <c r="B79" t="inlineStr"/>
@@ -6100,33 +6104,33 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Sep 15, 2026</t>
+          <t>Sep 29, 2026</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Sep 17, 2026</t>
+          <t>Oct 01, 2026</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Sep 18, 2026</t>
+          <t>Oct 05, 2026</t>
         </is>
       </c>
       <c r="H79" t="inlineStr"/>
       <c r="I79" t="inlineStr">
         <is>
-          <t>400</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>324-341</t>
+          <t>112-118</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>136400</t>
+          <t>141600</t>
         </is>
       </c>
       <c r="L79" t="inlineStr"/>
@@ -6136,17 +6140,77 @@
       <c r="P79" t="inlineStr"/>
       <c r="Q79" t="inlineStr">
         <is>
+          <t>https://www.moneycontrol.com/ipo/vanselectroengineeringsltd/VEL03</t>
+        </is>
+      </c>
+      <c r="R79" t="inlineStr">
+        <is>
+          <t>2026-09-25 14:20:09</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Vama Wovenfab Ltd</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr"/>
+      <c r="C80" t="inlineStr"/>
+      <c r="D80" s="5" t="inlineStr">
+        <is>
+          <t>Upcoming</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>Sep 15, 2026</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Sep 17, 2026</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>Sep 18, 2026</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr"/>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>400</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>324-341</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>136400</t>
+        </is>
+      </c>
+      <c r="L80" t="inlineStr"/>
+      <c r="M80" t="inlineStr"/>
+      <c r="N80" t="inlineStr"/>
+      <c r="O80" t="inlineStr"/>
+      <c r="P80" t="inlineStr"/>
+      <c r="Q80" t="inlineStr">
+        <is>
           <t>https://www.moneycontrol.com/ipo/vamawovenfabltd/VWL01</t>
         </is>
       </c>
-      <c r="R79" t="inlineStr">
+      <c r="R80" t="inlineStr">
         <is>
           <t>2026-09-11 13:34:16</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:R79"/>
+  <autoFilter ref="A1:R80"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/mainboard_ipos.xlsx
+++ b/data/mainboard_ipos.xlsx
@@ -4077,9 +4077,9 @@
       </c>
       <c r="B47" t="inlineStr"/>
       <c r="C47" t="inlineStr"/>
-      <c r="D47" s="3" t="inlineStr">
-        <is>
-          <t>Closed</t>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>Listed</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -4128,12 +4128,12 @@
       <c r="P47" t="inlineStr"/>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/adroitindustriesindia/AIIL01</t>
+          <t>https://www.moneycontrol.com/ipo/auto-ancillaries/adroitindustriesindia/AIIL01</t>
         </is>
       </c>
       <c r="R47" t="inlineStr">
         <is>
-          <t>2026-09-29 15:20:41</t>
+          <t>2026-09-30 15:13:12</t>
         </is>
       </c>
     </row>
@@ -4145,9 +4145,9 @@
       </c>
       <c r="B48" t="inlineStr"/>
       <c r="C48" t="inlineStr"/>
-      <c r="D48" s="3" t="inlineStr">
-        <is>
-          <t>Closed</t>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>Listed</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -4196,12 +4196,12 @@
       <c r="P48" t="inlineStr"/>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/armeeinfotech/AIL12</t>
+          <t>https://www.moneycontrol.com/ipo/computer-peripherals/armeeinfotech/AIL12</t>
         </is>
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>2026-09-29 15:20:41</t>
+          <t>2026-09-30 15:13:12</t>
         </is>
       </c>
     </row>
@@ -4281,9 +4281,9 @@
       </c>
       <c r="B50" t="inlineStr"/>
       <c r="C50" t="inlineStr"/>
-      <c r="D50" s="4" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>Listed</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -4325,19 +4325,19 @@
       <c r="M50" t="inlineStr"/>
       <c r="N50" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>8</t>
         </is>
       </c>
       <c r="O50" t="inlineStr"/>
       <c r="P50" t="inlineStr"/>
       <c r="Q50" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/swastikainfra/SIL37</t>
+          <t>https://www.moneycontrol.com/ipo/construction-infrastructure/swastikainfra/SIL37</t>
         </is>
       </c>
       <c r="R50" t="inlineStr">
         <is>
-          <t>2026-09-25 14:20:09</t>
+          <t>2026-09-30 15:13:12</t>
         </is>
       </c>
     </row>
@@ -4405,7 +4405,7 @@
       </c>
       <c r="R51" t="inlineStr">
         <is>
-          <t>2026-09-29 15:20:41</t>
+          <t>2026-09-30 15:13:12</t>
         </is>
       </c>
     </row>
@@ -4485,9 +4485,9 @@
       </c>
       <c r="B53" t="inlineStr"/>
       <c r="C53" t="inlineStr"/>
-      <c r="D53" s="4" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="D53" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -4529,7 +4529,7 @@
       <c r="M53" t="inlineStr"/>
       <c r="N53" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="O53" t="inlineStr"/>
@@ -4541,7 +4541,7 @@
       </c>
       <c r="R53" t="inlineStr">
         <is>
-          <t>2026-09-29 15:20:41</t>
+          <t>2026-09-30 15:13:12</t>
         </is>
       </c>
     </row>
@@ -4553,9 +4553,9 @@
       </c>
       <c r="B54" t="inlineStr"/>
       <c r="C54" t="inlineStr"/>
-      <c r="D54" s="4" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="D54" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -4597,7 +4597,7 @@
       <c r="M54" t="inlineStr"/>
       <c r="N54" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>29</t>
         </is>
       </c>
       <c r="O54" t="inlineStr"/>
@@ -4609,7 +4609,7 @@
       </c>
       <c r="R54" t="inlineStr">
         <is>
-          <t>2026-09-29 15:20:41</t>
+          <t>2026-09-30 15:13:12</t>
         </is>
       </c>
     </row>
@@ -4801,7 +4801,7 @@
       <c r="M57" t="inlineStr"/>
       <c r="N57" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>41</t>
         </is>
       </c>
       <c r="O57" t="inlineStr"/>
@@ -4813,7 +4813,7 @@
       </c>
       <c r="R57" t="inlineStr">
         <is>
-          <t>2026-09-29 15:20:41</t>
+          <t>2026-09-30 15:13:12</t>
         </is>
       </c>
     </row>
@@ -4869,7 +4869,7 @@
       <c r="M58" t="inlineStr"/>
       <c r="N58" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>10</t>
         </is>
       </c>
       <c r="O58" t="inlineStr"/>
@@ -4881,7 +4881,7 @@
       </c>
       <c r="R58" t="inlineStr">
         <is>
-          <t>2026-09-29 15:20:41</t>
+          <t>2026-09-30 15:13:12</t>
         </is>
       </c>
     </row>
@@ -4953,9 +4953,9 @@
       </c>
       <c r="B60" t="inlineStr"/>
       <c r="C60" t="inlineStr"/>
-      <c r="D60" s="5" t="inlineStr">
-        <is>
-          <t>Upcoming</t>
+      <c r="D60" s="4" t="inlineStr">
+        <is>
+          <t>Open</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -4985,7 +4985,7 @@
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>70-75</t>
+          <t>75</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
@@ -4995,7 +4995,11 @@
       </c>
       <c r="L60" t="inlineStr"/>
       <c r="M60" t="inlineStr"/>
-      <c r="N60" t="inlineStr"/>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="O60" t="inlineStr"/>
       <c r="P60" t="inlineStr"/>
       <c r="Q60" t="inlineStr">
@@ -5005,7 +5009,7 @@
       </c>
       <c r="R60" t="inlineStr">
         <is>
-          <t>2026-09-29 15:20:41</t>
+          <t>2026-09-30 15:13:12</t>
         </is>
       </c>
     </row>
@@ -5017,9 +5021,9 @@
       </c>
       <c r="B61" t="inlineStr"/>
       <c r="C61" t="inlineStr"/>
-      <c r="D61" s="5" t="inlineStr">
-        <is>
-          <t>Upcoming</t>
+      <c r="D61" s="4" t="inlineStr">
+        <is>
+          <t>Open</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -5049,7 +5053,7 @@
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>208-220</t>
+          <t>220</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
@@ -5059,7 +5063,11 @@
       </c>
       <c r="L61" t="inlineStr"/>
       <c r="M61" t="inlineStr"/>
-      <c r="N61" t="inlineStr"/>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="O61" t="inlineStr"/>
       <c r="P61" t="inlineStr"/>
       <c r="Q61" t="inlineStr">
@@ -5069,7 +5077,7 @@
       </c>
       <c r="R61" t="inlineStr">
         <is>
-          <t>2026-09-29 15:20:41</t>
+          <t>2026-09-30 15:13:12</t>
         </is>
       </c>
     </row>

--- a/data/mainboard_ipos.xlsx
+++ b/data/mainboard_ipos.xlsx
@@ -4349,9 +4349,9 @@
       </c>
       <c r="B51" t="inlineStr"/>
       <c r="C51" t="inlineStr"/>
-      <c r="D51" s="3" t="inlineStr">
-        <is>
-          <t>Closed</t>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>Listed</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -4389,23 +4389,39 @@
           <t>14985</t>
         </is>
       </c>
-      <c r="L51" t="inlineStr"/>
-      <c r="M51" t="inlineStr"/>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>455</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>16835</t>
+        </is>
+      </c>
       <c r="N51" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="O51" t="inlineStr"/>
-      <c r="P51" t="inlineStr"/>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>1850</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
       <c r="Q51" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/a-onesteelsindia/ASIL</t>
+          <t>https://www.moneycontrol.com/ipo/ironsteel/a-onesteelsindia/ASIL</t>
         </is>
       </c>
       <c r="R51" t="inlineStr">
         <is>
-          <t>2026-09-30 15:13:12</t>
+          <t>2026-10-02 15:17:02</t>
         </is>
       </c>
     </row>
@@ -4417,9 +4433,9 @@
       </c>
       <c r="B52" t="inlineStr"/>
       <c r="C52" t="inlineStr"/>
-      <c r="D52" s="4" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>Listed</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -4457,23 +4473,39 @@
           <t>14994</t>
         </is>
       </c>
-      <c r="L52" t="inlineStr"/>
-      <c r="M52" t="inlineStr"/>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>24255</t>
+        </is>
+      </c>
       <c r="N52" t="inlineStr">
         <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="O52" t="inlineStr"/>
-      <c r="P52" t="inlineStr"/>
+          <t>98</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>9261</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
       <c r="Q52" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/moneyviewltd/ML15</t>
+          <t>https://www.moneycontrol.com/ipo/finance-nbfc/moneyview/ML15</t>
         </is>
       </c>
       <c r="R52" t="inlineStr">
         <is>
-          <t>2026-09-28 15:18:07</t>
+          <t>2026-10-02 15:17:02</t>
         </is>
       </c>
     </row>
@@ -4541,7 +4573,7 @@
       </c>
       <c r="R53" t="inlineStr">
         <is>
-          <t>2026-09-30 15:13:12</t>
+          <t>2026-10-02 15:17:02</t>
         </is>
       </c>
     </row>
@@ -4997,7 +5029,7 @@
       <c r="M60" t="inlineStr"/>
       <c r="N60" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="O60" t="inlineStr"/>
@@ -5009,7 +5041,7 @@
       </c>
       <c r="R60" t="inlineStr">
         <is>
-          <t>2026-09-30 15:13:12</t>
+          <t>2026-10-02 15:17:02</t>
         </is>
       </c>
     </row>
@@ -5065,7 +5097,7 @@
       <c r="M61" t="inlineStr"/>
       <c r="N61" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="O61" t="inlineStr"/>
@@ -5077,7 +5109,7 @@
       </c>
       <c r="R61" t="inlineStr">
         <is>
-          <t>2026-09-30 15:13:12</t>
+          <t>2026-10-02 15:17:02</t>
         </is>
       </c>
     </row>

--- a/data/mainboard_ipos.xlsx
+++ b/data/mainboard_ipos.xlsx
@@ -4421,7 +4421,7 @@
       </c>
       <c r="R51" t="inlineStr">
         <is>
-          <t>2026-10-02 15:17:02</t>
+          <t>2026-10-03 14:40:11</t>
         </is>
       </c>
     </row>
@@ -4505,7 +4505,7 @@
       </c>
       <c r="R52" t="inlineStr">
         <is>
-          <t>2026-10-02 15:17:02</t>
+          <t>2026-10-03 14:40:11</t>
         </is>
       </c>
     </row>
@@ -4573,7 +4573,7 @@
       </c>
       <c r="R53" t="inlineStr">
         <is>
-          <t>2026-10-02 15:17:02</t>
+          <t>2026-10-03 14:40:11</t>
         </is>
       </c>
     </row>
@@ -5041,7 +5041,7 @@
       </c>
       <c r="R60" t="inlineStr">
         <is>
-          <t>2026-10-02 15:17:02</t>
+          <t>2026-10-03 14:40:11</t>
         </is>
       </c>
     </row>
@@ -5109,7 +5109,7 @@
       </c>
       <c r="R61" t="inlineStr">
         <is>
-          <t>2026-10-02 15:17:02</t>
+          <t>2026-10-03 14:40:11</t>
         </is>
       </c>
     </row>

--- a/data/mainboard_ipos.xlsx
+++ b/data/mainboard_ipos.xlsx
@@ -4421,7 +4421,7 @@
       </c>
       <c r="R51" t="inlineStr">
         <is>
-          <t>2026-10-03 14:40:11</t>
+          <t>2026-10-04 15:19:21</t>
         </is>
       </c>
     </row>
@@ -4505,7 +4505,7 @@
       </c>
       <c r="R52" t="inlineStr">
         <is>
-          <t>2026-10-03 14:40:11</t>
+          <t>2026-10-04 15:19:21</t>
         </is>
       </c>
     </row>
@@ -4568,12 +4568,12 @@
       <c r="P53" t="inlineStr"/>
       <c r="Q53" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/acevectorltd/AL19</t>
+          <t>https://www.moneycontrol.com/ipo/acevector/AL19</t>
         </is>
       </c>
       <c r="R53" t="inlineStr">
         <is>
-          <t>2026-10-03 14:40:11</t>
+          <t>2026-10-04 15:19:21</t>
         </is>
       </c>
     </row>
@@ -5041,7 +5041,7 @@
       </c>
       <c r="R60" t="inlineStr">
         <is>
-          <t>2026-10-03 14:40:11</t>
+          <t>2026-10-04 15:19:21</t>
         </is>
       </c>
     </row>
@@ -5109,7 +5109,7 @@
       </c>
       <c r="R61" t="inlineStr">
         <is>
-          <t>2026-10-03 14:40:11</t>
+          <t>2026-10-04 15:19:21</t>
         </is>
       </c>
     </row>

--- a/data/mainboard_ipos.xlsx
+++ b/data/mainboard_ipos.xlsx
@@ -4517,9 +4517,9 @@
       </c>
       <c r="B53" t="inlineStr"/>
       <c r="C53" t="inlineStr"/>
-      <c r="D53" s="3" t="inlineStr">
-        <is>
-          <t>Closed</t>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>Listed</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -4568,12 +4568,12 @@
       <c r="P53" t="inlineStr"/>
       <c r="Q53" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/acevector/AL19</t>
+          <t>https://www.moneycontrol.com/ipo/online-services/acevector/AL19</t>
         </is>
       </c>
       <c r="R53" t="inlineStr">
         <is>
-          <t>2026-10-04 15:19:21</t>
+          <t>2026-10-05 15:57:40</t>
         </is>
       </c>
     </row>
@@ -4653,9 +4653,9 @@
       </c>
       <c r="B55" t="inlineStr"/>
       <c r="C55" t="inlineStr"/>
-      <c r="D55" s="4" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>Listed</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -4697,19 +4697,19 @@
       <c r="M55" t="inlineStr"/>
       <c r="N55" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>92</t>
         </is>
       </c>
       <c r="O55" t="inlineStr"/>
       <c r="P55" t="inlineStr"/>
       <c r="Q55" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/orientcablesindialtd/OCIL</t>
+          <t>https://www.moneycontrol.com/ipo/cables/orientcablesindia/OCIL</t>
         </is>
       </c>
       <c r="R55" t="inlineStr">
         <is>
-          <t>2026-09-29 15:20:41</t>
+          <t>2026-10-05 15:57:40</t>
         </is>
       </c>
     </row>
@@ -5041,7 +5041,7 @@
       </c>
       <c r="R60" t="inlineStr">
         <is>
-          <t>2026-10-04 15:19:21</t>
+          <t>2026-10-05 15:57:40</t>
         </is>
       </c>
     </row>
@@ -5109,7 +5109,7 @@
       </c>
       <c r="R61" t="inlineStr">
         <is>
-          <t>2026-10-04 15:19:21</t>
+          <t>2026-10-05 15:57:40</t>
         </is>
       </c>
     </row>

--- a/data/mainboard_ipos.xlsx
+++ b/data/mainboard_ipos.xlsx
@@ -4789,9 +4789,9 @@
       </c>
       <c r="B57" t="inlineStr"/>
       <c r="C57" t="inlineStr"/>
-      <c r="D57" s="4" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>Listed</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -4833,19 +4833,19 @@
       <c r="M57" t="inlineStr"/>
       <c r="N57" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>125</t>
         </is>
       </c>
       <c r="O57" t="inlineStr"/>
       <c r="P57" t="inlineStr"/>
       <c r="Q57" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/sritindialtd/SIL38</t>
+          <t>https://www.moneycontrol.com/ipo/it-servicesconsulting/sritindia/SIL38</t>
         </is>
       </c>
       <c r="R57" t="inlineStr">
         <is>
-          <t>2026-09-30 15:13:12</t>
+          <t>2026-10-06 15:49:03</t>
         </is>
       </c>
     </row>
@@ -4857,9 +4857,9 @@
       </c>
       <c r="B58" t="inlineStr"/>
       <c r="C58" t="inlineStr"/>
-      <c r="D58" s="4" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>Listed</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -4901,19 +4901,19 @@
       <c r="M58" t="inlineStr"/>
       <c r="N58" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>38</t>
         </is>
       </c>
       <c r="O58" t="inlineStr"/>
       <c r="P58" t="inlineStr"/>
       <c r="Q58" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/shahinvestorshomeltd/SIHL</t>
+          <t>https://www.moneycontrol.com/ipo/finance-stock-broking/shahinvestorshome/SIHL</t>
         </is>
       </c>
       <c r="R58" t="inlineStr">
         <is>
-          <t>2026-09-30 15:13:12</t>
+          <t>2026-10-06 15:49:03</t>
         </is>
       </c>
     </row>

--- a/data/mainboard_ipos.xlsx
+++ b/data/mainboard_ipos.xlsx
@@ -4985,9 +4985,9 @@
       </c>
       <c r="B60" t="inlineStr"/>
       <c r="C60" t="inlineStr"/>
-      <c r="D60" s="4" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="D60" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -5029,19 +5029,19 @@
       <c r="M60" t="inlineStr"/>
       <c r="N60" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O60" t="inlineStr"/>
       <c r="P60" t="inlineStr"/>
       <c r="Q60" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/nityasgemsjewelleryltd/NGJL</t>
+          <t>https://www.moneycontrol.com/ipo/nityasgemsjewellery/NGJL</t>
         </is>
       </c>
       <c r="R60" t="inlineStr">
         <is>
-          <t>2026-10-05 15:57:40</t>
+          <t>2026-10-07 15:46:42</t>
         </is>
       </c>
     </row>

--- a/data/mainboard_ipos.xlsx
+++ b/data/mainboard_ipos.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Mainboard IPOs" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Mainboard IPOs'!$A$1:$R$80</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Mainboard IPOs'!$A$1:$R$83</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -449,7 +449,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R80"/>
+  <dimension ref="A1:R83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -4985,9 +4985,9 @@
       </c>
       <c r="B60" t="inlineStr"/>
       <c r="C60" t="inlineStr"/>
-      <c r="D60" s="3" t="inlineStr">
-        <is>
-          <t>Closed</t>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>Listed</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -5036,12 +5036,12 @@
       <c r="P60" t="inlineStr"/>
       <c r="Q60" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/nityasgemsjewellery/NGJL</t>
+          <t>https://www.moneycontrol.com/ipo/diamondjewellery/nityasgemsjewellery/NGJL</t>
         </is>
       </c>
       <c r="R60" t="inlineStr">
         <is>
-          <t>2026-10-07 15:46:42</t>
+          <t>2026-10-08 16:06:11</t>
         </is>
       </c>
     </row>
@@ -5053,9 +5053,9 @@
       </c>
       <c r="B61" t="inlineStr"/>
       <c r="C61" t="inlineStr"/>
-      <c r="D61" s="4" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="D61" s="2" t="inlineStr">
+        <is>
+          <t>Listed</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -5097,26 +5097,26 @@
       <c r="M61" t="inlineStr"/>
       <c r="N61" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O61" t="inlineStr"/>
       <c r="P61" t="inlineStr"/>
       <c r="Q61" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/vishalnirmitiltd/VNL01</t>
+          <t>https://www.moneycontrol.com/ipo/other-construction-materials/vishalnirmiti/VNL01</t>
         </is>
       </c>
       <c r="R61" t="inlineStr">
         <is>
-          <t>2026-10-05 15:57:40</t>
+          <t>2026-10-08 16:06:11</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Complete Sports and Management India Ltd</t>
+          <t>HD Fire Protect Ltd</t>
         </is>
       </c>
       <c r="B62" t="inlineStr"/>
@@ -5128,33 +5128,37 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Aug 28, 2026</t>
+          <t>Oct 13, 2026</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Sep 01, 2026</t>
+          <t>Oct 15, 2026</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Sep 02, 2026</t>
-        </is>
-      </c>
-      <c r="H62" t="inlineStr"/>
+          <t>Oct 16, 2026</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>Oct 21, 2026</t>
+        </is>
+      </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>55</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>128-135</t>
+          <t>258-271</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>135000</t>
+          <t>14905</t>
         </is>
       </c>
       <c r="L62" t="inlineStr"/>
@@ -5164,19 +5168,19 @@
       <c r="P62" t="inlineStr"/>
       <c r="Q62" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/completesportsmanagementindialtd/CSMIL</t>
+          <t>https://www.moneycontrol.com/ipo/hdfireprotectltd/HFP</t>
         </is>
       </c>
       <c r="R62" t="inlineStr">
         <is>
-          <t>2026-08-25 09:29:52</t>
+          <t>2026-10-08 16:06:11</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Coreintegra Consulting Services</t>
+          <t>Complete Sports and Management India Ltd</t>
         </is>
       </c>
       <c r="B63" t="inlineStr"/>
@@ -5188,33 +5192,33 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Sep 23, 2026</t>
+          <t>Aug 28, 2026</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Sep 25, 2026</t>
+          <t>Sep 01, 2026</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Sep 28, 2026</t>
+          <t>Sep 02, 2026</t>
         </is>
       </c>
       <c r="H63" t="inlineStr"/>
       <c r="I63" t="inlineStr">
         <is>
-          <t>1600</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>74-78</t>
+          <t>128-135</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>124800</t>
+          <t>135000</t>
         </is>
       </c>
       <c r="L63" t="inlineStr"/>
@@ -5224,19 +5228,19 @@
       <c r="P63" t="inlineStr"/>
       <c r="Q63" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/coreintegraconsultingservices/CCSL</t>
+          <t>https://www.moneycontrol.com/ipo/completesportsmanagementindialtd/CSMIL</t>
         </is>
       </c>
       <c r="R63" t="inlineStr">
         <is>
-          <t>2026-09-22 14:03:25</t>
+          <t>2026-08-25 09:29:52</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Credent Connect N Care Ltd</t>
+          <t>Coreintegra Consulting Services</t>
         </is>
       </c>
       <c r="B64" t="inlineStr"/>
@@ -5248,33 +5252,33 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Aug 13, 2026</t>
+          <t>Sep 23, 2026</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Aug 17, 2026</t>
+          <t>Sep 25, 2026</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Aug 18, 2026</t>
+          <t>Sep 28, 2026</t>
         </is>
       </c>
       <c r="H64" t="inlineStr"/>
       <c r="I64" t="inlineStr">
         <is>
-          <t>600</t>
+          <t>1600</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>179-189</t>
+          <t>74-78</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>113400</t>
+          <t>124800</t>
         </is>
       </c>
       <c r="L64" t="inlineStr"/>
@@ -5284,19 +5288,19 @@
       <c r="P64" t="inlineStr"/>
       <c r="Q64" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/credentconnectncareltd/CCC04</t>
+          <t>https://www.moneycontrol.com/ipo/coreintegraconsultingservices/CCSL</t>
         </is>
       </c>
       <c r="R64" t="inlineStr">
         <is>
-          <t>2026-08-10 22:43:12</t>
+          <t>2026-09-22 14:03:25</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Dove Soft Ltd</t>
+          <t>Credent Connect N Care Ltd</t>
         </is>
       </c>
       <c r="B65" t="inlineStr"/>
@@ -5308,33 +5312,33 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Sep 30, 2026</t>
+          <t>Aug 13, 2026</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Oct 05, 2026</t>
+          <t>Aug 17, 2026</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Oct 06, 2026</t>
+          <t>Aug 18, 2026</t>
         </is>
       </c>
       <c r="H65" t="inlineStr"/>
       <c r="I65" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>600</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>104-111</t>
+          <t>179-189</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>133200</t>
+          <t>113400</t>
         </is>
       </c>
       <c r="L65" t="inlineStr"/>
@@ -5344,19 +5348,19 @@
       <c r="P65" t="inlineStr"/>
       <c r="Q65" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/dovesoftltd/DSL04</t>
+          <t>https://www.moneycontrol.com/ipo/credentconnectncareltd/CCC04</t>
         </is>
       </c>
       <c r="R65" t="inlineStr">
         <is>
-          <t>2026-09-25 14:20:09</t>
+          <t>2026-08-10 22:43:12</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Farm Peace Ltd</t>
+          <t>Dove Soft Ltd</t>
         </is>
       </c>
       <c r="B66" t="inlineStr"/>
@@ -5368,33 +5372,33 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Sep 01, 2026</t>
+          <t>Sep 30, 2026</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Sep 03, 2026</t>
+          <t>Oct 05, 2026</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Sep 04, 2026</t>
+          <t>Oct 06, 2026</t>
         </is>
       </c>
       <c r="H66" t="inlineStr"/>
       <c r="I66" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>104-111</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>118000</t>
+          <t>133200</t>
         </is>
       </c>
       <c r="L66" t="inlineStr"/>
@@ -5404,19 +5408,19 @@
       <c r="P66" t="inlineStr"/>
       <c r="Q66" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/farmpeaceltd/FPL02</t>
+          <t>https://www.moneycontrol.com/ipo/dovesoftltd/DSL04</t>
         </is>
       </c>
       <c r="R66" t="inlineStr">
         <is>
-          <t>2026-08-27 19:43:03</t>
+          <t>2026-09-25 14:20:09</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Green Asia Impex Ltd</t>
+          <t>Farm Peace Ltd</t>
         </is>
       </c>
       <c r="B67" t="inlineStr"/>
@@ -5428,33 +5432,33 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Sep 24, 2026</t>
+          <t>Sep 01, 2026</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Sep 28, 2026</t>
+          <t>Sep 03, 2026</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Sep 29, 2026</t>
+          <t>Sep 04, 2026</t>
         </is>
       </c>
       <c r="H67" t="inlineStr"/>
       <c r="I67" t="inlineStr">
         <is>
-          <t>1600</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>85-90</t>
+          <t>59</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>144000</t>
+          <t>118000</t>
         </is>
       </c>
       <c r="L67" t="inlineStr"/>
@@ -5464,19 +5468,19 @@
       <c r="P67" t="inlineStr"/>
       <c r="Q67" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/greenasiaimpexltd/GAIL01</t>
+          <t>https://www.moneycontrol.com/ipo/farmpeaceltd/FPL02</t>
         </is>
       </c>
       <c r="R67" t="inlineStr">
         <is>
-          <t>2026-09-22 14:03:25</t>
+          <t>2026-08-27 19:43:03</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Kheria Autocomp Ltd</t>
+          <t>Green Asia Impex Ltd</t>
         </is>
       </c>
       <c r="B68" t="inlineStr"/>
@@ -5488,33 +5492,33 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Sep 17, 2026</t>
+          <t>Sep 24, 2026</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Sep 21, 2026</t>
+          <t>Sep 28, 2026</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Sep 22, 2026</t>
+          <t>Sep 29, 2026</t>
         </is>
       </c>
       <c r="H68" t="inlineStr"/>
       <c r="I68" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>1600</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>96-101</t>
+          <t>85-90</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>121200</t>
+          <t>144000</t>
         </is>
       </c>
       <c r="L68" t="inlineStr"/>
@@ -5524,19 +5528,19 @@
       <c r="P68" t="inlineStr"/>
       <c r="Q68" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/kheriaautocompltd/KAL05</t>
+          <t>https://www.moneycontrol.com/ipo/greenasiaimpexltd/GAIL01</t>
         </is>
       </c>
       <c r="R68" t="inlineStr">
         <is>
-          <t>2026-09-11 13:34:16</t>
+          <t>2026-09-22 14:03:25</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Mopshop Distribution Ltd</t>
+          <t>Kheria Autocomp Ltd</t>
         </is>
       </c>
       <c r="B69" t="inlineStr"/>
@@ -5548,33 +5552,33 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Aug 19, 2026</t>
+          <t>Sep 17, 2026</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Aug 21, 2026</t>
+          <t>Sep 21, 2026</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Aug 24, 2026</t>
+          <t>Sep 22, 2026</t>
         </is>
       </c>
       <c r="H69" t="inlineStr"/>
       <c r="I69" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>138</t>
+          <t>96-101</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>138000</t>
+          <t>121200</t>
         </is>
       </c>
       <c r="L69" t="inlineStr"/>
@@ -5584,19 +5588,19 @@
       <c r="P69" t="inlineStr"/>
       <c r="Q69" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/mopshopdistributionltd/MDL03</t>
+          <t>https://www.moneycontrol.com/ipo/kheriaautocompltd/KAL05</t>
         </is>
       </c>
       <c r="R69" t="inlineStr">
         <is>
-          <t>2026-08-14 21:36:23</t>
+          <t>2026-09-11 13:34:16</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Paluck Technologies Ltd</t>
+          <t>Mopshop Distribution Ltd</t>
         </is>
       </c>
       <c r="B70" t="inlineStr"/>
@@ -5608,33 +5612,33 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Aug 28, 2026</t>
+          <t>Aug 19, 2026</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Sep 01, 2026</t>
+          <t>Aug 21, 2026</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Sep 02, 2026</t>
+          <t>Aug 24, 2026</t>
         </is>
       </c>
       <c r="H70" t="inlineStr"/>
       <c r="I70" t="inlineStr">
         <is>
-          <t>3000</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>46-48</t>
+          <t>138</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>144000</t>
+          <t>138000</t>
         </is>
       </c>
       <c r="L70" t="inlineStr"/>
@@ -5644,19 +5648,19 @@
       <c r="P70" t="inlineStr"/>
       <c r="Q70" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/palucktechnologiesltd/PTL08</t>
+          <t>https://www.moneycontrol.com/ipo/mopshopdistributionltd/MDL03</t>
         </is>
       </c>
       <c r="R70" t="inlineStr">
         <is>
-          <t>2026-08-25 09:29:52</t>
+          <t>2026-08-14 21:36:23</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Papadmalji Agro Foods Ltd</t>
+          <t>Paluck Technologies Ltd</t>
         </is>
       </c>
       <c r="B71" t="inlineStr"/>
@@ -5668,33 +5672,33 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Sep 29, 2026</t>
+          <t>Aug 28, 2026</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Oct 01, 2026</t>
+          <t>Sep 01, 2026</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Oct 05, 2026</t>
+          <t>Sep 02, 2026</t>
         </is>
       </c>
       <c r="H71" t="inlineStr"/>
       <c r="I71" t="inlineStr">
         <is>
-          <t>1600</t>
+          <t>3000</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>69-72</t>
+          <t>46-48</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>115200</t>
+          <t>144000</t>
         </is>
       </c>
       <c r="L71" t="inlineStr"/>
@@ -5704,19 +5708,19 @@
       <c r="P71" t="inlineStr"/>
       <c r="Q71" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/papadmaljiagrofoodsltd/PAF</t>
+          <t>https://www.moneycontrol.com/ipo/palucktechnologiesltd/PTL08</t>
         </is>
       </c>
       <c r="R71" t="inlineStr">
         <is>
-          <t>2026-09-25 14:20:09</t>
+          <t>2026-08-25 09:29:52</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Paramount Syntex Ltd</t>
+          <t>Papadmalji Agro Foods Ltd</t>
         </is>
       </c>
       <c r="B72" t="inlineStr"/>
@@ -5728,33 +5732,33 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Sep 30, 2026</t>
+          <t>Sep 29, 2026</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Oct 06, 2026</t>
+          <t>Oct 01, 2026</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Oct 07, 2026</t>
+          <t>Oct 05, 2026</t>
         </is>
       </c>
       <c r="H72" t="inlineStr"/>
       <c r="I72" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>1600</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>119-127</t>
+          <t>69-72</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>127000</t>
+          <t>115200</t>
         </is>
       </c>
       <c r="L72" t="inlineStr"/>
@@ -5764,7 +5768,7 @@
       <c r="P72" t="inlineStr"/>
       <c r="Q72" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/paramountsyntexltd/PSL06</t>
+          <t>https://www.moneycontrol.com/ipo/papadmaljiagrofoodsltd/PAF</t>
         </is>
       </c>
       <c r="R72" t="inlineStr">
@@ -5776,7 +5780,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Peshwa Wheat</t>
+          <t>Paramount Syntex Ltd</t>
         </is>
       </c>
       <c r="B73" t="inlineStr"/>
@@ -5788,33 +5792,33 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Sep 24, 2026</t>
+          <t>Sep 30, 2026</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Sep 28, 2026</t>
+          <t>Oct 06, 2026</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Sep 29, 2026</t>
+          <t>Oct 07, 2026</t>
         </is>
       </c>
       <c r="H73" t="inlineStr"/>
       <c r="I73" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>95-101</t>
+          <t>119-127</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>121200</t>
+          <t>127000</t>
         </is>
       </c>
       <c r="L73" t="inlineStr"/>
@@ -5824,135 +5828,135 @@
       <c r="P73" t="inlineStr"/>
       <c r="Q73" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/peshwawheat/PWL01</t>
+          <t>https://www.moneycontrol.com/ipo/paramountsyntexltd/PSL06</t>
         </is>
       </c>
       <c r="R73" t="inlineStr">
         <is>
-          <t>2026-09-22 14:03:25</t>
+          <t>2026-09-25 14:20:09</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Purple Style Labs Ltd</t>
+          <t>Peshwa Wheat</t>
         </is>
       </c>
       <c r="B74" t="inlineStr"/>
       <c r="C74" t="inlineStr"/>
-      <c r="D74" s="4" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="D74" s="5" t="inlineStr">
+        <is>
+          <t>Upcoming</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Aug 31, 2026</t>
+          <t>Sep 24, 2026</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Sep 02, 2026</t>
+          <t>Sep 28, 2026</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Sep 03, 2026</t>
+          <t>Sep 29, 2026</t>
         </is>
       </c>
       <c r="H74" t="inlineStr"/>
-      <c r="I74" t="inlineStr"/>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>1200</t>
+        </is>
+      </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>575</t>
-        </is>
-      </c>
-      <c r="K74" t="inlineStr"/>
+          <t>95-101</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>121200</t>
+        </is>
+      </c>
       <c r="L74" t="inlineStr"/>
       <c r="M74" t="inlineStr"/>
-      <c r="N74" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="N74" t="inlineStr"/>
       <c r="O74" t="inlineStr"/>
       <c r="P74" t="inlineStr"/>
       <c r="Q74" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/purplestylelabsltd/PSL05</t>
+          <t>https://www.moneycontrol.com/ipo/peshwawheat/PWL01</t>
         </is>
       </c>
       <c r="R74" t="inlineStr">
         <is>
-          <t>2026-09-02 13:25:30</t>
+          <t>2026-09-22 14:03:25</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Q&amp;T Foods Ltd</t>
+          <t>Purple Style Labs Ltd</t>
         </is>
       </c>
       <c r="B75" t="inlineStr"/>
       <c r="C75" t="inlineStr"/>
-      <c r="D75" s="5" t="inlineStr">
-        <is>
-          <t>Upcoming</t>
+      <c r="D75" s="4" t="inlineStr">
+        <is>
+          <t>Open</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Aug 12, 2026</t>
+          <t>Aug 31, 2026</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Aug 14, 2026</t>
+          <t>Sep 02, 2026</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Aug 17, 2026</t>
+          <t>Sep 03, 2026</t>
         </is>
       </c>
       <c r="H75" t="inlineStr"/>
-      <c r="I75" t="inlineStr">
-        <is>
-          <t>1200</t>
-        </is>
-      </c>
+      <c r="I75" t="inlineStr"/>
       <c r="J75" t="inlineStr">
         <is>
-          <t>115</t>
-        </is>
-      </c>
-      <c r="K75" t="inlineStr">
-        <is>
-          <t>138000</t>
-        </is>
-      </c>
+          <t>575</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr"/>
       <c r="L75" t="inlineStr"/>
       <c r="M75" t="inlineStr"/>
-      <c r="N75" t="inlineStr"/>
+      <c r="N75" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="O75" t="inlineStr"/>
       <c r="P75" t="inlineStr"/>
       <c r="Q75" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/qtfoodsltd/QFL</t>
+          <t>https://www.moneycontrol.com/ipo/purplestylelabsltd/PSL05</t>
         </is>
       </c>
       <c r="R75" t="inlineStr">
         <is>
-          <t>2026-08-10 10:24:29</t>
+          <t>2026-09-02 13:25:30</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Shanti Inorganics Ltd</t>
+          <t>Q&amp;T Foods Ltd</t>
         </is>
       </c>
       <c r="B76" t="inlineStr"/>
@@ -5964,33 +5968,33 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Aug 31, 2026</t>
+          <t>Aug 12, 2026</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Sep 02, 2026</t>
+          <t>Aug 14, 2026</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Sep 03, 2026</t>
+          <t>Aug 17, 2026</t>
         </is>
       </c>
       <c r="H76" t="inlineStr"/>
       <c r="I76" t="inlineStr">
         <is>
-          <t>1600</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>79-83</t>
+          <t>115</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>132800</t>
+          <t>138000</t>
         </is>
       </c>
       <c r="L76" t="inlineStr"/>
@@ -6000,19 +6004,19 @@
       <c r="P76" t="inlineStr"/>
       <c r="Q76" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/shantiinorganicsltd/SIL34</t>
+          <t>https://www.moneycontrol.com/ipo/qtfoodsltd/QFL</t>
         </is>
       </c>
       <c r="R76" t="inlineStr">
         <is>
-          <t>2026-08-25 09:29:52</t>
+          <t>2026-08-10 10:24:29</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Technocrats Plasma Systems Ltd</t>
+          <t>Ravita Engineering Services Ltd</t>
         </is>
       </c>
       <c r="B77" t="inlineStr"/>
@@ -6024,35 +6028,27 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Aug 14, 2026</t>
+          <t>Oct 13, 2026</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Aug 18, 2026</t>
+          <t>Oct 15, 2026</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Aug 19, 2026</t>
+          <t>Oct 16, 2026</t>
         </is>
       </c>
       <c r="H77" t="inlineStr"/>
-      <c r="I77" t="inlineStr">
-        <is>
-          <t>1000</t>
-        </is>
-      </c>
+      <c r="I77" t="inlineStr"/>
       <c r="J77" t="inlineStr">
         <is>
-          <t>125-132</t>
-        </is>
-      </c>
-      <c r="K77" t="inlineStr">
-        <is>
-          <t>132000</t>
-        </is>
-      </c>
+          <t>105-112</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr"/>
       <c r="L77" t="inlineStr"/>
       <c r="M77" t="inlineStr"/>
       <c r="N77" t="inlineStr"/>
@@ -6060,19 +6056,19 @@
       <c r="P77" t="inlineStr"/>
       <c r="Q77" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/technocratsplasmasystemsltd/TPSL</t>
+          <t>https://www.moneycontrol.com/ipo/ravitaengineeringservicesltd/RESL</t>
         </is>
       </c>
       <c r="R77" t="inlineStr">
         <is>
-          <t>2026-08-11 21:41:02</t>
+          <t>2026-10-08 16:06:11</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Unitec Fibres Ltd</t>
+          <t>Shanti Inorganics Ltd</t>
         </is>
       </c>
       <c r="B78" t="inlineStr"/>
@@ -6084,17 +6080,17 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Sep 23, 2026</t>
+          <t>Aug 31, 2026</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Sep 25, 2026</t>
+          <t>Sep 02, 2026</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Sep 28, 2026</t>
+          <t>Sep 03, 2026</t>
         </is>
       </c>
       <c r="H78" t="inlineStr"/>
@@ -6105,12 +6101,12 @@
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>83-88</t>
+          <t>79-83</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>140800</t>
+          <t>132800</t>
         </is>
       </c>
       <c r="L78" t="inlineStr"/>
@@ -6120,19 +6116,19 @@
       <c r="P78" t="inlineStr"/>
       <c r="Q78" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/unitecfibresltd/UFL03</t>
+          <t>https://www.moneycontrol.com/ipo/shantiinorganicsltd/SIL34</t>
         </is>
       </c>
       <c r="R78" t="inlineStr">
         <is>
-          <t>2026-09-18 23:59:33</t>
+          <t>2026-08-25 09:29:52</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>VANS Electroengineerings Ltd</t>
+          <t>Technocrats Plasma Systems Ltd</t>
         </is>
       </c>
       <c r="B79" t="inlineStr"/>
@@ -6144,33 +6140,33 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Sep 29, 2026</t>
+          <t>Aug 14, 2026</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Oct 01, 2026</t>
+          <t>Aug 18, 2026</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Oct 05, 2026</t>
+          <t>Aug 19, 2026</t>
         </is>
       </c>
       <c r="H79" t="inlineStr"/>
       <c r="I79" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>112-118</t>
+          <t>125-132</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>141600</t>
+          <t>132000</t>
         </is>
       </c>
       <c r="L79" t="inlineStr"/>
@@ -6180,19 +6176,19 @@
       <c r="P79" t="inlineStr"/>
       <c r="Q79" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/vanselectroengineeringsltd/VEL03</t>
+          <t>https://www.moneycontrol.com/ipo/technocratsplasmasystemsltd/TPSL</t>
         </is>
       </c>
       <c r="R79" t="inlineStr">
         <is>
-          <t>2026-09-25 14:20:09</t>
+          <t>2026-08-11 21:41:02</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Vama Wovenfab Ltd</t>
+          <t>Unitec Fibres Ltd</t>
         </is>
       </c>
       <c r="B80" t="inlineStr"/>
@@ -6204,33 +6200,33 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Sep 15, 2026</t>
+          <t>Sep 23, 2026</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Sep 17, 2026</t>
+          <t>Sep 25, 2026</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Sep 18, 2026</t>
+          <t>Sep 28, 2026</t>
         </is>
       </c>
       <c r="H80" t="inlineStr"/>
       <c r="I80" t="inlineStr">
         <is>
-          <t>400</t>
+          <t>1600</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>324-341</t>
+          <t>83-88</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>136400</t>
+          <t>140800</t>
         </is>
       </c>
       <c r="L80" t="inlineStr"/>
@@ -6240,17 +6236,189 @@
       <c r="P80" t="inlineStr"/>
       <c r="Q80" t="inlineStr">
         <is>
+          <t>https://www.moneycontrol.com/ipo/unitecfibresltd/UFL03</t>
+        </is>
+      </c>
+      <c r="R80" t="inlineStr">
+        <is>
+          <t>2026-09-18 23:59:33</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>VANS Electroengineerings Ltd</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr"/>
+      <c r="C81" t="inlineStr"/>
+      <c r="D81" s="5" t="inlineStr">
+        <is>
+          <t>Upcoming</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>Sep 29, 2026</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Oct 01, 2026</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>Oct 05, 2026</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr"/>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>1200</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>112-118</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>141600</t>
+        </is>
+      </c>
+      <c r="L81" t="inlineStr"/>
+      <c r="M81" t="inlineStr"/>
+      <c r="N81" t="inlineStr"/>
+      <c r="O81" t="inlineStr"/>
+      <c r="P81" t="inlineStr"/>
+      <c r="Q81" t="inlineStr">
+        <is>
+          <t>https://www.moneycontrol.com/ipo/vanselectroengineeringsltd/VEL03</t>
+        </is>
+      </c>
+      <c r="R81" t="inlineStr">
+        <is>
+          <t>2026-09-25 14:20:09</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Vaibhav Vyapaar Ltd</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr"/>
+      <c r="C82" t="inlineStr"/>
+      <c r="D82" s="5" t="inlineStr">
+        <is>
+          <t>Upcoming</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>Oct 13, 2026</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Oct 15, 2026</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>Oct 16, 2026</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr"/>
+      <c r="I82" t="inlineStr"/>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>50-52</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr"/>
+      <c r="L82" t="inlineStr"/>
+      <c r="M82" t="inlineStr"/>
+      <c r="N82" t="inlineStr"/>
+      <c r="O82" t="inlineStr"/>
+      <c r="P82" t="inlineStr"/>
+      <c r="Q82" t="inlineStr">
+        <is>
+          <t>https://www.moneycontrol.com/ipo/vaibhavvyapaarltd/VVL01</t>
+        </is>
+      </c>
+      <c r="R82" t="inlineStr">
+        <is>
+          <t>2026-10-08 16:06:11</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Vama Wovenfab Ltd</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr"/>
+      <c r="C83" t="inlineStr"/>
+      <c r="D83" s="5" t="inlineStr">
+        <is>
+          <t>Upcoming</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>Sep 15, 2026</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Sep 17, 2026</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>Sep 18, 2026</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr"/>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>400</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>324-341</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>136400</t>
+        </is>
+      </c>
+      <c r="L83" t="inlineStr"/>
+      <c r="M83" t="inlineStr"/>
+      <c r="N83" t="inlineStr"/>
+      <c r="O83" t="inlineStr"/>
+      <c r="P83" t="inlineStr"/>
+      <c r="Q83" t="inlineStr">
+        <is>
           <t>https://www.moneycontrol.com/ipo/vamawovenfabltd/VWL01</t>
         </is>
       </c>
-      <c r="R80" t="inlineStr">
+      <c r="R83" t="inlineStr">
         <is>
           <t>2026-09-11 13:34:16</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:R80"/>
+  <autoFilter ref="A1:R83"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/mainboard_ipos.xlsx
+++ b/data/mainboard_ipos.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Mainboard IPOs" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Mainboard IPOs'!$A$1:$R$83</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Mainboard IPOs'!$A$1:$R$84</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -449,7 +449,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R83"/>
+  <dimension ref="A1:R84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -5093,15 +5093,31 @@
           <t>14960</t>
         </is>
       </c>
-      <c r="L61" t="inlineStr"/>
-      <c r="M61" t="inlineStr"/>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>215</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>14620</t>
+        </is>
+      </c>
       <c r="N61" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="O61" t="inlineStr"/>
-      <c r="P61" t="inlineStr"/>
+      <c r="O61" t="inlineStr">
+        <is>
+          <t>-340</t>
+        </is>
+      </c>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>-2</t>
+        </is>
+      </c>
       <c r="Q61" t="inlineStr">
         <is>
           <t>https://www.moneycontrol.com/ipo/other-construction-materials/vishalnirmiti/VNL01</t>
@@ -5109,7 +5125,7 @@
       </c>
       <c r="R61" t="inlineStr">
         <is>
-          <t>2026-10-08 16:06:11</t>
+          <t>2026-10-09 16:04:28</t>
         </is>
       </c>
     </row>
@@ -5173,14 +5189,14 @@
       </c>
       <c r="R62" t="inlineStr">
         <is>
-          <t>2026-10-08 16:06:11</t>
+          <t>2026-10-09 16:04:28</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Complete Sports and Management India Ltd</t>
+          <t>Fusion CX Ltd</t>
         </is>
       </c>
       <c r="B63" t="inlineStr"/>
@@ -5192,33 +5208,37 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Aug 28, 2026</t>
+          <t>Oct 14, 2026</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Sep 01, 2026</t>
+          <t>Oct 16, 2026</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Sep 02, 2026</t>
-        </is>
-      </c>
-      <c r="H63" t="inlineStr"/>
+          <t>Oct 19, 2026</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>Oct 22, 2026</t>
+        </is>
+      </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>51</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>128-135</t>
+          <t>275-289</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>135000</t>
+          <t>14739</t>
         </is>
       </c>
       <c r="L63" t="inlineStr"/>
@@ -5228,19 +5248,19 @@
       <c r="P63" t="inlineStr"/>
       <c r="Q63" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/completesportsmanagementindialtd/CSMIL</t>
+          <t>https://www.moneycontrol.com/ipo/</t>
         </is>
       </c>
       <c r="R63" t="inlineStr">
         <is>
-          <t>2026-08-25 09:29:52</t>
+          <t>2026-10-09 16:04:28</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Coreintegra Consulting Services</t>
+          <t>Complete Sports and Management India Ltd</t>
         </is>
       </c>
       <c r="B64" t="inlineStr"/>
@@ -5252,33 +5272,33 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Sep 23, 2026</t>
+          <t>Aug 28, 2026</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Sep 25, 2026</t>
+          <t>Sep 01, 2026</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Sep 28, 2026</t>
+          <t>Sep 02, 2026</t>
         </is>
       </c>
       <c r="H64" t="inlineStr"/>
       <c r="I64" t="inlineStr">
         <is>
-          <t>1600</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>74-78</t>
+          <t>128-135</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>124800</t>
+          <t>135000</t>
         </is>
       </c>
       <c r="L64" t="inlineStr"/>
@@ -5288,19 +5308,19 @@
       <c r="P64" t="inlineStr"/>
       <c r="Q64" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/coreintegraconsultingservices/CCSL</t>
+          <t>https://www.moneycontrol.com/ipo/completesportsmanagementindialtd/CSMIL</t>
         </is>
       </c>
       <c r="R64" t="inlineStr">
         <is>
-          <t>2026-09-22 14:03:25</t>
+          <t>2026-08-25 09:29:52</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Credent Connect N Care Ltd</t>
+          <t>Coreintegra Consulting Services</t>
         </is>
       </c>
       <c r="B65" t="inlineStr"/>
@@ -5312,33 +5332,33 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Aug 13, 2026</t>
+          <t>Sep 23, 2026</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Aug 17, 2026</t>
+          <t>Sep 25, 2026</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Aug 18, 2026</t>
+          <t>Sep 28, 2026</t>
         </is>
       </c>
       <c r="H65" t="inlineStr"/>
       <c r="I65" t="inlineStr">
         <is>
-          <t>600</t>
+          <t>1600</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>179-189</t>
+          <t>74-78</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>113400</t>
+          <t>124800</t>
         </is>
       </c>
       <c r="L65" t="inlineStr"/>
@@ -5348,19 +5368,19 @@
       <c r="P65" t="inlineStr"/>
       <c r="Q65" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/credentconnectncareltd/CCC04</t>
+          <t>https://www.moneycontrol.com/ipo/coreintegraconsultingservices/CCSL</t>
         </is>
       </c>
       <c r="R65" t="inlineStr">
         <is>
-          <t>2026-08-10 22:43:12</t>
+          <t>2026-09-22 14:03:25</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Dove Soft Ltd</t>
+          <t>Credent Connect N Care Ltd</t>
         </is>
       </c>
       <c r="B66" t="inlineStr"/>
@@ -5372,33 +5392,33 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Sep 30, 2026</t>
+          <t>Aug 13, 2026</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Oct 05, 2026</t>
+          <t>Aug 17, 2026</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Oct 06, 2026</t>
+          <t>Aug 18, 2026</t>
         </is>
       </c>
       <c r="H66" t="inlineStr"/>
       <c r="I66" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>600</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>104-111</t>
+          <t>179-189</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>133200</t>
+          <t>113400</t>
         </is>
       </c>
       <c r="L66" t="inlineStr"/>
@@ -5408,19 +5428,19 @@
       <c r="P66" t="inlineStr"/>
       <c r="Q66" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/dovesoftltd/DSL04</t>
+          <t>https://www.moneycontrol.com/ipo/credentconnectncareltd/CCC04</t>
         </is>
       </c>
       <c r="R66" t="inlineStr">
         <is>
-          <t>2026-09-25 14:20:09</t>
+          <t>2026-08-10 22:43:12</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Farm Peace Ltd</t>
+          <t>Dove Soft Ltd</t>
         </is>
       </c>
       <c r="B67" t="inlineStr"/>
@@ -5432,33 +5452,33 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Sep 01, 2026</t>
+          <t>Sep 30, 2026</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Sep 03, 2026</t>
+          <t>Oct 05, 2026</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Sep 04, 2026</t>
+          <t>Oct 06, 2026</t>
         </is>
       </c>
       <c r="H67" t="inlineStr"/>
       <c r="I67" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>104-111</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>118000</t>
+          <t>133200</t>
         </is>
       </c>
       <c r="L67" t="inlineStr"/>
@@ -5468,19 +5488,19 @@
       <c r="P67" t="inlineStr"/>
       <c r="Q67" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/farmpeaceltd/FPL02</t>
+          <t>https://www.moneycontrol.com/ipo/dovesoftltd/DSL04</t>
         </is>
       </c>
       <c r="R67" t="inlineStr">
         <is>
-          <t>2026-08-27 19:43:03</t>
+          <t>2026-09-25 14:20:09</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Green Asia Impex Ltd</t>
+          <t>Farm Peace Ltd</t>
         </is>
       </c>
       <c r="B68" t="inlineStr"/>
@@ -5492,33 +5512,33 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Sep 24, 2026</t>
+          <t>Sep 01, 2026</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Sep 28, 2026</t>
+          <t>Sep 03, 2026</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Sep 29, 2026</t>
+          <t>Sep 04, 2026</t>
         </is>
       </c>
       <c r="H68" t="inlineStr"/>
       <c r="I68" t="inlineStr">
         <is>
-          <t>1600</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>85-90</t>
+          <t>59</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>144000</t>
+          <t>118000</t>
         </is>
       </c>
       <c r="L68" t="inlineStr"/>
@@ -5528,19 +5548,19 @@
       <c r="P68" t="inlineStr"/>
       <c r="Q68" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/greenasiaimpexltd/GAIL01</t>
+          <t>https://www.moneycontrol.com/ipo/farmpeaceltd/FPL02</t>
         </is>
       </c>
       <c r="R68" t="inlineStr">
         <is>
-          <t>2026-09-22 14:03:25</t>
+          <t>2026-08-27 19:43:03</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Kheria Autocomp Ltd</t>
+          <t>Green Asia Impex Ltd</t>
         </is>
       </c>
       <c r="B69" t="inlineStr"/>
@@ -5552,33 +5572,33 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Sep 17, 2026</t>
+          <t>Sep 24, 2026</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Sep 21, 2026</t>
+          <t>Sep 28, 2026</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Sep 22, 2026</t>
+          <t>Sep 29, 2026</t>
         </is>
       </c>
       <c r="H69" t="inlineStr"/>
       <c r="I69" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>1600</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>96-101</t>
+          <t>85-90</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>121200</t>
+          <t>144000</t>
         </is>
       </c>
       <c r="L69" t="inlineStr"/>
@@ -5588,19 +5608,19 @@
       <c r="P69" t="inlineStr"/>
       <c r="Q69" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/kheriaautocompltd/KAL05</t>
+          <t>https://www.moneycontrol.com/ipo/greenasiaimpexltd/GAIL01</t>
         </is>
       </c>
       <c r="R69" t="inlineStr">
         <is>
-          <t>2026-09-11 13:34:16</t>
+          <t>2026-09-22 14:03:25</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Mopshop Distribution Ltd</t>
+          <t>Kheria Autocomp Ltd</t>
         </is>
       </c>
       <c r="B70" t="inlineStr"/>
@@ -5612,33 +5632,33 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Aug 19, 2026</t>
+          <t>Sep 17, 2026</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Aug 21, 2026</t>
+          <t>Sep 21, 2026</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Aug 24, 2026</t>
+          <t>Sep 22, 2026</t>
         </is>
       </c>
       <c r="H70" t="inlineStr"/>
       <c r="I70" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>138</t>
+          <t>96-101</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>138000</t>
+          <t>121200</t>
         </is>
       </c>
       <c r="L70" t="inlineStr"/>
@@ -5648,19 +5668,19 @@
       <c r="P70" t="inlineStr"/>
       <c r="Q70" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/mopshopdistributionltd/MDL03</t>
+          <t>https://www.moneycontrol.com/ipo/kheriaautocompltd/KAL05</t>
         </is>
       </c>
       <c r="R70" t="inlineStr">
         <is>
-          <t>2026-08-14 21:36:23</t>
+          <t>2026-09-11 13:34:16</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Paluck Technologies Ltd</t>
+          <t>Mopshop Distribution Ltd</t>
         </is>
       </c>
       <c r="B71" t="inlineStr"/>
@@ -5672,33 +5692,33 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Aug 28, 2026</t>
+          <t>Aug 19, 2026</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Sep 01, 2026</t>
+          <t>Aug 21, 2026</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Sep 02, 2026</t>
+          <t>Aug 24, 2026</t>
         </is>
       </c>
       <c r="H71" t="inlineStr"/>
       <c r="I71" t="inlineStr">
         <is>
-          <t>3000</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>46-48</t>
+          <t>138</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>144000</t>
+          <t>138000</t>
         </is>
       </c>
       <c r="L71" t="inlineStr"/>
@@ -5708,19 +5728,19 @@
       <c r="P71" t="inlineStr"/>
       <c r="Q71" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/palucktechnologiesltd/PTL08</t>
+          <t>https://www.moneycontrol.com/ipo/mopshopdistributionltd/MDL03</t>
         </is>
       </c>
       <c r="R71" t="inlineStr">
         <is>
-          <t>2026-08-25 09:29:52</t>
+          <t>2026-08-14 21:36:23</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Papadmalji Agro Foods Ltd</t>
+          <t>Paluck Technologies Ltd</t>
         </is>
       </c>
       <c r="B72" t="inlineStr"/>
@@ -5732,33 +5752,33 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Sep 29, 2026</t>
+          <t>Aug 28, 2026</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Oct 01, 2026</t>
+          <t>Sep 01, 2026</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Oct 05, 2026</t>
+          <t>Sep 02, 2026</t>
         </is>
       </c>
       <c r="H72" t="inlineStr"/>
       <c r="I72" t="inlineStr">
         <is>
-          <t>1600</t>
+          <t>3000</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>69-72</t>
+          <t>46-48</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>115200</t>
+          <t>144000</t>
         </is>
       </c>
       <c r="L72" t="inlineStr"/>
@@ -5768,19 +5788,19 @@
       <c r="P72" t="inlineStr"/>
       <c r="Q72" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/papadmaljiagrofoodsltd/PAF</t>
+          <t>https://www.moneycontrol.com/ipo/palucktechnologiesltd/PTL08</t>
         </is>
       </c>
       <c r="R72" t="inlineStr">
         <is>
-          <t>2026-09-25 14:20:09</t>
+          <t>2026-08-25 09:29:52</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Paramount Syntex Ltd</t>
+          <t>Papadmalji Agro Foods Ltd</t>
         </is>
       </c>
       <c r="B73" t="inlineStr"/>
@@ -5792,33 +5812,33 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Sep 30, 2026</t>
+          <t>Sep 29, 2026</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Oct 06, 2026</t>
+          <t>Oct 01, 2026</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Oct 07, 2026</t>
+          <t>Oct 05, 2026</t>
         </is>
       </c>
       <c r="H73" t="inlineStr"/>
       <c r="I73" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>1600</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>119-127</t>
+          <t>69-72</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>127000</t>
+          <t>115200</t>
         </is>
       </c>
       <c r="L73" t="inlineStr"/>
@@ -5828,7 +5848,7 @@
       <c r="P73" t="inlineStr"/>
       <c r="Q73" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/paramountsyntexltd/PSL06</t>
+          <t>https://www.moneycontrol.com/ipo/papadmaljiagrofoodsltd/PAF</t>
         </is>
       </c>
       <c r="R73" t="inlineStr">
@@ -5840,7 +5860,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Peshwa Wheat</t>
+          <t>Paramount Syntex Ltd</t>
         </is>
       </c>
       <c r="B74" t="inlineStr"/>
@@ -5852,33 +5872,33 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Sep 24, 2026</t>
+          <t>Sep 30, 2026</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Sep 28, 2026</t>
+          <t>Oct 06, 2026</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Sep 29, 2026</t>
+          <t>Oct 07, 2026</t>
         </is>
       </c>
       <c r="H74" t="inlineStr"/>
       <c r="I74" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>95-101</t>
+          <t>119-127</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>121200</t>
+          <t>127000</t>
         </is>
       </c>
       <c r="L74" t="inlineStr"/>
@@ -5888,135 +5908,135 @@
       <c r="P74" t="inlineStr"/>
       <c r="Q74" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/peshwawheat/PWL01</t>
+          <t>https://www.moneycontrol.com/ipo/paramountsyntexltd/PSL06</t>
         </is>
       </c>
       <c r="R74" t="inlineStr">
         <is>
-          <t>2026-09-22 14:03:25</t>
+          <t>2026-09-25 14:20:09</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Purple Style Labs Ltd</t>
+          <t>Peshwa Wheat</t>
         </is>
       </c>
       <c r="B75" t="inlineStr"/>
       <c r="C75" t="inlineStr"/>
-      <c r="D75" s="4" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="D75" s="5" t="inlineStr">
+        <is>
+          <t>Upcoming</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Aug 31, 2026</t>
+          <t>Sep 24, 2026</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Sep 02, 2026</t>
+          <t>Sep 28, 2026</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Sep 03, 2026</t>
+          <t>Sep 29, 2026</t>
         </is>
       </c>
       <c r="H75" t="inlineStr"/>
-      <c r="I75" t="inlineStr"/>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>1200</t>
+        </is>
+      </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>575</t>
-        </is>
-      </c>
-      <c r="K75" t="inlineStr"/>
+          <t>95-101</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>121200</t>
+        </is>
+      </c>
       <c r="L75" t="inlineStr"/>
       <c r="M75" t="inlineStr"/>
-      <c r="N75" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="N75" t="inlineStr"/>
       <c r="O75" t="inlineStr"/>
       <c r="P75" t="inlineStr"/>
       <c r="Q75" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/purplestylelabsltd/PSL05</t>
+          <t>https://www.moneycontrol.com/ipo/peshwawheat/PWL01</t>
         </is>
       </c>
       <c r="R75" t="inlineStr">
         <is>
-          <t>2026-09-02 13:25:30</t>
+          <t>2026-09-22 14:03:25</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Q&amp;T Foods Ltd</t>
+          <t>Purple Style Labs Ltd</t>
         </is>
       </c>
       <c r="B76" t="inlineStr"/>
       <c r="C76" t="inlineStr"/>
-      <c r="D76" s="5" t="inlineStr">
-        <is>
-          <t>Upcoming</t>
+      <c r="D76" s="4" t="inlineStr">
+        <is>
+          <t>Open</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Aug 12, 2026</t>
+          <t>Aug 31, 2026</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Aug 14, 2026</t>
+          <t>Sep 02, 2026</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Aug 17, 2026</t>
+          <t>Sep 03, 2026</t>
         </is>
       </c>
       <c r="H76" t="inlineStr"/>
-      <c r="I76" t="inlineStr">
-        <is>
-          <t>1200</t>
-        </is>
-      </c>
+      <c r="I76" t="inlineStr"/>
       <c r="J76" t="inlineStr">
         <is>
-          <t>115</t>
-        </is>
-      </c>
-      <c r="K76" t="inlineStr">
-        <is>
-          <t>138000</t>
-        </is>
-      </c>
+          <t>575</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr"/>
       <c r="L76" t="inlineStr"/>
       <c r="M76" t="inlineStr"/>
-      <c r="N76" t="inlineStr"/>
+      <c r="N76" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="O76" t="inlineStr"/>
       <c r="P76" t="inlineStr"/>
       <c r="Q76" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/qtfoodsltd/QFL</t>
+          <t>https://www.moneycontrol.com/ipo/purplestylelabsltd/PSL05</t>
         </is>
       </c>
       <c r="R76" t="inlineStr">
         <is>
-          <t>2026-08-10 10:24:29</t>
+          <t>2026-09-02 13:25:30</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Ravita Engineering Services Ltd</t>
+          <t>Q&amp;T Foods Ltd</t>
         </is>
       </c>
       <c r="B77" t="inlineStr"/>
@@ -6028,27 +6048,35 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Oct 13, 2026</t>
+          <t>Aug 12, 2026</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Oct 15, 2026</t>
+          <t>Aug 14, 2026</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Oct 16, 2026</t>
+          <t>Aug 17, 2026</t>
         </is>
       </c>
       <c r="H77" t="inlineStr"/>
-      <c r="I77" t="inlineStr"/>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>1200</t>
+        </is>
+      </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>105-112</t>
-        </is>
-      </c>
-      <c r="K77" t="inlineStr"/>
+          <t>115</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>138000</t>
+        </is>
+      </c>
       <c r="L77" t="inlineStr"/>
       <c r="M77" t="inlineStr"/>
       <c r="N77" t="inlineStr"/>
@@ -6056,19 +6084,19 @@
       <c r="P77" t="inlineStr"/>
       <c r="Q77" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/ravitaengineeringservicesltd/RESL</t>
+          <t>https://www.moneycontrol.com/ipo/qtfoodsltd/QFL</t>
         </is>
       </c>
       <c r="R77" t="inlineStr">
         <is>
-          <t>2026-10-08 16:06:11</t>
+          <t>2026-08-10 10:24:29</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Shanti Inorganics Ltd</t>
+          <t>Ravita Engineering Services Ltd</t>
         </is>
       </c>
       <c r="B78" t="inlineStr"/>
@@ -6080,33 +6108,33 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Aug 31, 2026</t>
+          <t>Oct 13, 2026</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Sep 02, 2026</t>
+          <t>Oct 15, 2026</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Sep 03, 2026</t>
+          <t>Oct 16, 2026</t>
         </is>
       </c>
       <c r="H78" t="inlineStr"/>
       <c r="I78" t="inlineStr">
         <is>
-          <t>1600</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>79-83</t>
+          <t>105-112</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>132800</t>
+          <t>134400</t>
         </is>
       </c>
       <c r="L78" t="inlineStr"/>
@@ -6116,19 +6144,19 @@
       <c r="P78" t="inlineStr"/>
       <c r="Q78" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/shantiinorganicsltd/SIL34</t>
+          <t>https://www.moneycontrol.com/ipo/ravitaengineeringservicesltd/RESL</t>
         </is>
       </c>
       <c r="R78" t="inlineStr">
         <is>
-          <t>2026-08-25 09:29:52</t>
+          <t>2026-10-08 16:06:11</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Technocrats Plasma Systems Ltd</t>
+          <t>Shanti Inorganics Ltd</t>
         </is>
       </c>
       <c r="B79" t="inlineStr"/>
@@ -6140,33 +6168,33 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Aug 14, 2026</t>
+          <t>Aug 31, 2026</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Aug 18, 2026</t>
+          <t>Sep 02, 2026</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Aug 19, 2026</t>
+          <t>Sep 03, 2026</t>
         </is>
       </c>
       <c r="H79" t="inlineStr"/>
       <c r="I79" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>1600</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>125-132</t>
+          <t>79-83</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>132000</t>
+          <t>132800</t>
         </is>
       </c>
       <c r="L79" t="inlineStr"/>
@@ -6176,19 +6204,19 @@
       <c r="P79" t="inlineStr"/>
       <c r="Q79" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/technocratsplasmasystemsltd/TPSL</t>
+          <t>https://www.moneycontrol.com/ipo/shantiinorganicsltd/SIL34</t>
         </is>
       </c>
       <c r="R79" t="inlineStr">
         <is>
-          <t>2026-08-11 21:41:02</t>
+          <t>2026-08-25 09:29:52</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Unitec Fibres Ltd</t>
+          <t>Technocrats Plasma Systems Ltd</t>
         </is>
       </c>
       <c r="B80" t="inlineStr"/>
@@ -6200,33 +6228,33 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Sep 23, 2026</t>
+          <t>Aug 14, 2026</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Sep 25, 2026</t>
+          <t>Aug 18, 2026</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Sep 28, 2026</t>
+          <t>Aug 19, 2026</t>
         </is>
       </c>
       <c r="H80" t="inlineStr"/>
       <c r="I80" t="inlineStr">
         <is>
-          <t>1600</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>83-88</t>
+          <t>125-132</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>140800</t>
+          <t>132000</t>
         </is>
       </c>
       <c r="L80" t="inlineStr"/>
@@ -6236,19 +6264,19 @@
       <c r="P80" t="inlineStr"/>
       <c r="Q80" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/unitecfibresltd/UFL03</t>
+          <t>https://www.moneycontrol.com/ipo/technocratsplasmasystemsltd/TPSL</t>
         </is>
       </c>
       <c r="R80" t="inlineStr">
         <is>
-          <t>2026-09-18 23:59:33</t>
+          <t>2026-08-11 21:41:02</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>VANS Electroengineerings Ltd</t>
+          <t>Unitec Fibres Ltd</t>
         </is>
       </c>
       <c r="B81" t="inlineStr"/>
@@ -6260,33 +6288,33 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Sep 29, 2026</t>
+          <t>Sep 23, 2026</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Oct 01, 2026</t>
+          <t>Sep 25, 2026</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Oct 05, 2026</t>
+          <t>Sep 28, 2026</t>
         </is>
       </c>
       <c r="H81" t="inlineStr"/>
       <c r="I81" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>1600</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>112-118</t>
+          <t>83-88</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>141600</t>
+          <t>140800</t>
         </is>
       </c>
       <c r="L81" t="inlineStr"/>
@@ -6296,19 +6324,19 @@
       <c r="P81" t="inlineStr"/>
       <c r="Q81" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/vanselectroengineeringsltd/VEL03</t>
+          <t>https://www.moneycontrol.com/ipo/unitecfibresltd/UFL03</t>
         </is>
       </c>
       <c r="R81" t="inlineStr">
         <is>
-          <t>2026-09-25 14:20:09</t>
+          <t>2026-09-18 23:59:33</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Vaibhav Vyapaar Ltd</t>
+          <t>VANS Electroengineerings Ltd</t>
         </is>
       </c>
       <c r="B82" t="inlineStr"/>
@@ -6320,27 +6348,35 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Oct 13, 2026</t>
+          <t>Sep 29, 2026</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Oct 15, 2026</t>
+          <t>Oct 01, 2026</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Oct 16, 2026</t>
+          <t>Oct 05, 2026</t>
         </is>
       </c>
       <c r="H82" t="inlineStr"/>
-      <c r="I82" t="inlineStr"/>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>1200</t>
+        </is>
+      </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>50-52</t>
-        </is>
-      </c>
-      <c r="K82" t="inlineStr"/>
+          <t>112-118</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>141600</t>
+        </is>
+      </c>
       <c r="L82" t="inlineStr"/>
       <c r="M82" t="inlineStr"/>
       <c r="N82" t="inlineStr"/>
@@ -6348,19 +6384,19 @@
       <c r="P82" t="inlineStr"/>
       <c r="Q82" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/vaibhavvyapaarltd/VVL01</t>
+          <t>https://www.moneycontrol.com/ipo/vanselectroengineeringsltd/VEL03</t>
         </is>
       </c>
       <c r="R82" t="inlineStr">
         <is>
-          <t>2026-10-08 16:06:11</t>
+          <t>2026-09-25 14:20:09</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Vama Wovenfab Ltd</t>
+          <t>Vaibhav Vyapaar Ltd</t>
         </is>
       </c>
       <c r="B83" t="inlineStr"/>
@@ -6372,33 +6408,33 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Sep 15, 2026</t>
+          <t>Oct 13, 2026</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Sep 17, 2026</t>
+          <t>Oct 15, 2026</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Sep 18, 2026</t>
+          <t>Oct 16, 2026</t>
         </is>
       </c>
       <c r="H83" t="inlineStr"/>
       <c r="I83" t="inlineStr">
         <is>
-          <t>400</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>324-341</t>
+          <t>50-52</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>136400</t>
+          <t>104000</t>
         </is>
       </c>
       <c r="L83" t="inlineStr"/>
@@ -6408,17 +6444,77 @@
       <c r="P83" t="inlineStr"/>
       <c r="Q83" t="inlineStr">
         <is>
+          <t>https://www.moneycontrol.com/ipo/vaibhavvyapaarltd/VVL01</t>
+        </is>
+      </c>
+      <c r="R83" t="inlineStr">
+        <is>
+          <t>2026-10-08 16:06:11</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Vama Wovenfab Ltd</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr"/>
+      <c r="C84" t="inlineStr"/>
+      <c r="D84" s="5" t="inlineStr">
+        <is>
+          <t>Upcoming</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>Sep 15, 2026</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>Sep 17, 2026</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>Sep 18, 2026</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr"/>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>400</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>324-341</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>136400</t>
+        </is>
+      </c>
+      <c r="L84" t="inlineStr"/>
+      <c r="M84" t="inlineStr"/>
+      <c r="N84" t="inlineStr"/>
+      <c r="O84" t="inlineStr"/>
+      <c r="P84" t="inlineStr"/>
+      <c r="Q84" t="inlineStr">
+        <is>
           <t>https://www.moneycontrol.com/ipo/vamawovenfabltd/VWL01</t>
         </is>
       </c>
-      <c r="R83" t="inlineStr">
+      <c r="R84" t="inlineStr">
         <is>
           <t>2026-09-11 13:34:16</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:R83"/>
+  <autoFilter ref="A1:R84"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/mainboard_ipos.xlsx
+++ b/data/mainboard_ipos.xlsx
@@ -5125,7 +5125,7 @@
       </c>
       <c r="R61" t="inlineStr">
         <is>
-          <t>2026-10-09 16:04:28</t>
+          <t>2026-10-10 15:21:23</t>
         </is>
       </c>
     </row>
@@ -5189,7 +5189,7 @@
       </c>
       <c r="R62" t="inlineStr">
         <is>
-          <t>2026-10-09 16:04:28</t>
+          <t>2026-10-10 15:21:23</t>
         </is>
       </c>
     </row>
@@ -5248,12 +5248,12 @@
       <c r="P63" t="inlineStr"/>
       <c r="Q63" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/</t>
+          <t>https://www.moneycontrol.com/ipo/fusioncxltd/FCL02</t>
         </is>
       </c>
       <c r="R63" t="inlineStr">
         <is>
-          <t>2026-10-09 16:04:28</t>
+          <t>2026-10-10 15:21:23</t>
         </is>
       </c>
     </row>

--- a/data/mainboard_ipos.xlsx
+++ b/data/mainboard_ipos.xlsx
@@ -5125,7 +5125,7 @@
       </c>
       <c r="R61" t="inlineStr">
         <is>
-          <t>2026-10-10 15:21:23</t>
+          <t>2026-10-11 15:31:12</t>
         </is>
       </c>
     </row>
@@ -5189,7 +5189,7 @@
       </c>
       <c r="R62" t="inlineStr">
         <is>
-          <t>2026-10-10 15:21:23</t>
+          <t>2026-10-11 15:31:12</t>
         </is>
       </c>
     </row>
@@ -5253,7 +5253,7 @@
       </c>
       <c r="R63" t="inlineStr">
         <is>
-          <t>2026-10-10 15:21:23</t>
+          <t>2026-10-11 15:31:12</t>
         </is>
       </c>
     </row>

--- a/data/mainboard_ipos.xlsx
+++ b/data/mainboard_ipos.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Mainboard IPOs" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Mainboard IPOs'!$A$1:$R$84</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Mainboard IPOs'!$A$1:$R$87</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -449,7 +449,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R84"/>
+  <dimension ref="A1:R87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -5189,7 +5189,7 @@
       </c>
       <c r="R62" t="inlineStr">
         <is>
-          <t>2026-10-11 15:31:12</t>
+          <t>2026-10-12 16:21:01</t>
         </is>
       </c>
     </row>
@@ -5253,14 +5253,14 @@
       </c>
       <c r="R63" t="inlineStr">
         <is>
-          <t>2026-10-11 15:31:12</t>
+          <t>2026-10-12 16:21:01</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Complete Sports and Management India Ltd</t>
+          <t>Bonfiglioli Transmissions Ltd</t>
         </is>
       </c>
       <c r="B64" t="inlineStr"/>
@@ -5272,33 +5272,37 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Aug 28, 2026</t>
+          <t>Oct 15, 2026</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Sep 01, 2026</t>
+          <t>Oct 19, 2026</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Sep 02, 2026</t>
-        </is>
-      </c>
-      <c r="H64" t="inlineStr"/>
+          <t>Oct 21, 2026</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>Oct 23, 2026</t>
+        </is>
+      </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>128-135</t>
+          <t>558-586</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>135000</t>
+          <t>14650</t>
         </is>
       </c>
       <c r="L64" t="inlineStr"/>
@@ -5308,19 +5312,19 @@
       <c r="P64" t="inlineStr"/>
       <c r="Q64" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/completesportsmanagementindialtd/CSMIL</t>
+          <t>https://www.moneycontrol.com/ipo/bonfigliolitransmissionsltd/BTL04</t>
         </is>
       </c>
       <c r="R64" t="inlineStr">
         <is>
-          <t>2026-08-25 09:29:52</t>
+          <t>2026-10-12 16:21:01</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Coreintegra Consulting Services</t>
+          <t>Tonbo Imaging India Ltd</t>
         </is>
       </c>
       <c r="B65" t="inlineStr"/>
@@ -5332,33 +5336,37 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Sep 23, 2026</t>
+          <t>Oct 15, 2026</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Sep 25, 2026</t>
+          <t>Oct 19, 2026</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Sep 28, 2026</t>
-        </is>
-      </c>
-      <c r="H65" t="inlineStr"/>
+          <t>Oct 21, 2026</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>Oct 23, 2026</t>
+        </is>
+      </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>1600</t>
+          <t>21</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>74-78</t>
+          <t>665-700</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>124800</t>
+          <t>14700</t>
         </is>
       </c>
       <c r="L65" t="inlineStr"/>
@@ -5368,19 +5376,19 @@
       <c r="P65" t="inlineStr"/>
       <c r="Q65" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/coreintegraconsultingservices/CCSL</t>
+          <t>https://www.moneycontrol.com/ipo/tonboimagingindialtd/TIIL</t>
         </is>
       </c>
       <c r="R65" t="inlineStr">
         <is>
-          <t>2026-09-22 14:03:25</t>
+          <t>2026-10-12 16:21:01</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Credent Connect N Care Ltd</t>
+          <t>Zetwerk Manufacturing Businesses Ltd</t>
         </is>
       </c>
       <c r="B66" t="inlineStr"/>
@@ -5392,33 +5400,37 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Aug 13, 2026</t>
+          <t>Oct 15, 2026</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Aug 17, 2026</t>
+          <t>Oct 19, 2026</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Aug 18, 2026</t>
-        </is>
-      </c>
-      <c r="H66" t="inlineStr"/>
+          <t>Oct 21, 2026</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>Oct 23, 2026</t>
+        </is>
+      </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>600</t>
+          <t>99</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>179-189</t>
+          <t>143-151</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>113400</t>
+          <t>14949</t>
         </is>
       </c>
       <c r="L66" t="inlineStr"/>
@@ -5428,19 +5440,19 @@
       <c r="P66" t="inlineStr"/>
       <c r="Q66" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/credentconnectncareltd/CCC04</t>
+          <t>https://www.moneycontrol.com/ipo/zetwerkmanufacturingbusinessesltd/ZMBL</t>
         </is>
       </c>
       <c r="R66" t="inlineStr">
         <is>
-          <t>2026-08-10 22:43:12</t>
+          <t>2026-10-12 16:21:01</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Dove Soft Ltd</t>
+          <t>Complete Sports and Management India Ltd</t>
         </is>
       </c>
       <c r="B67" t="inlineStr"/>
@@ -5452,33 +5464,33 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Sep 30, 2026</t>
+          <t>Aug 28, 2026</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Oct 05, 2026</t>
+          <t>Sep 01, 2026</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Oct 06, 2026</t>
+          <t>Sep 02, 2026</t>
         </is>
       </c>
       <c r="H67" t="inlineStr"/>
       <c r="I67" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>104-111</t>
+          <t>128-135</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>133200</t>
+          <t>135000</t>
         </is>
       </c>
       <c r="L67" t="inlineStr"/>
@@ -5488,19 +5500,19 @@
       <c r="P67" t="inlineStr"/>
       <c r="Q67" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/dovesoftltd/DSL04</t>
+          <t>https://www.moneycontrol.com/ipo/completesportsmanagementindialtd/CSMIL</t>
         </is>
       </c>
       <c r="R67" t="inlineStr">
         <is>
-          <t>2026-09-25 14:20:09</t>
+          <t>2026-08-25 09:29:52</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Farm Peace Ltd</t>
+          <t>Coreintegra Consulting Services</t>
         </is>
       </c>
       <c r="B68" t="inlineStr"/>
@@ -5512,33 +5524,33 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Sep 01, 2026</t>
+          <t>Sep 23, 2026</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Sep 03, 2026</t>
+          <t>Sep 25, 2026</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Sep 04, 2026</t>
+          <t>Sep 28, 2026</t>
         </is>
       </c>
       <c r="H68" t="inlineStr"/>
       <c r="I68" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>1600</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>74-78</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>118000</t>
+          <t>124800</t>
         </is>
       </c>
       <c r="L68" t="inlineStr"/>
@@ -5548,19 +5560,19 @@
       <c r="P68" t="inlineStr"/>
       <c r="Q68" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/farmpeaceltd/FPL02</t>
+          <t>https://www.moneycontrol.com/ipo/coreintegraconsultingservices/CCSL</t>
         </is>
       </c>
       <c r="R68" t="inlineStr">
         <is>
-          <t>2026-08-27 19:43:03</t>
+          <t>2026-09-22 14:03:25</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Green Asia Impex Ltd</t>
+          <t>Credent Connect N Care Ltd</t>
         </is>
       </c>
       <c r="B69" t="inlineStr"/>
@@ -5572,33 +5584,33 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Sep 24, 2026</t>
+          <t>Aug 13, 2026</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Sep 28, 2026</t>
+          <t>Aug 17, 2026</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Sep 29, 2026</t>
+          <t>Aug 18, 2026</t>
         </is>
       </c>
       <c r="H69" t="inlineStr"/>
       <c r="I69" t="inlineStr">
         <is>
-          <t>1600</t>
+          <t>600</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>85-90</t>
+          <t>179-189</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>144000</t>
+          <t>113400</t>
         </is>
       </c>
       <c r="L69" t="inlineStr"/>
@@ -5608,19 +5620,19 @@
       <c r="P69" t="inlineStr"/>
       <c r="Q69" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/greenasiaimpexltd/GAIL01</t>
+          <t>https://www.moneycontrol.com/ipo/credentconnectncareltd/CCC04</t>
         </is>
       </c>
       <c r="R69" t="inlineStr">
         <is>
-          <t>2026-09-22 14:03:25</t>
+          <t>2026-08-10 22:43:12</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Kheria Autocomp Ltd</t>
+          <t>Dove Soft Ltd</t>
         </is>
       </c>
       <c r="B70" t="inlineStr"/>
@@ -5632,17 +5644,17 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Sep 17, 2026</t>
+          <t>Sep 30, 2026</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Sep 21, 2026</t>
+          <t>Oct 05, 2026</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Sep 22, 2026</t>
+          <t>Oct 06, 2026</t>
         </is>
       </c>
       <c r="H70" t="inlineStr"/>
@@ -5653,12 +5665,12 @@
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>96-101</t>
+          <t>104-111</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>121200</t>
+          <t>133200</t>
         </is>
       </c>
       <c r="L70" t="inlineStr"/>
@@ -5668,19 +5680,19 @@
       <c r="P70" t="inlineStr"/>
       <c r="Q70" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/kheriaautocompltd/KAL05</t>
+          <t>https://www.moneycontrol.com/ipo/dovesoftltd/DSL04</t>
         </is>
       </c>
       <c r="R70" t="inlineStr">
         <is>
-          <t>2026-09-11 13:34:16</t>
+          <t>2026-09-25 14:20:09</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Mopshop Distribution Ltd</t>
+          <t>Farm Peace Ltd</t>
         </is>
       </c>
       <c r="B71" t="inlineStr"/>
@@ -5692,33 +5704,33 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Aug 19, 2026</t>
+          <t>Sep 01, 2026</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Aug 21, 2026</t>
+          <t>Sep 03, 2026</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Aug 24, 2026</t>
+          <t>Sep 04, 2026</t>
         </is>
       </c>
       <c r="H71" t="inlineStr"/>
       <c r="I71" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>138</t>
+          <t>59</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>138000</t>
+          <t>118000</t>
         </is>
       </c>
       <c r="L71" t="inlineStr"/>
@@ -5728,19 +5740,19 @@
       <c r="P71" t="inlineStr"/>
       <c r="Q71" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/mopshopdistributionltd/MDL03</t>
+          <t>https://www.moneycontrol.com/ipo/farmpeaceltd/FPL02</t>
         </is>
       </c>
       <c r="R71" t="inlineStr">
         <is>
-          <t>2026-08-14 21:36:23</t>
+          <t>2026-08-27 19:43:03</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Paluck Technologies Ltd</t>
+          <t>Green Asia Impex Ltd</t>
         </is>
       </c>
       <c r="B72" t="inlineStr"/>
@@ -5752,28 +5764,28 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Aug 28, 2026</t>
+          <t>Sep 24, 2026</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Sep 01, 2026</t>
+          <t>Sep 28, 2026</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Sep 02, 2026</t>
+          <t>Sep 29, 2026</t>
         </is>
       </c>
       <c r="H72" t="inlineStr"/>
       <c r="I72" t="inlineStr">
         <is>
-          <t>3000</t>
+          <t>1600</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>46-48</t>
+          <t>85-90</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
@@ -5788,19 +5800,19 @@
       <c r="P72" t="inlineStr"/>
       <c r="Q72" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/palucktechnologiesltd/PTL08</t>
+          <t>https://www.moneycontrol.com/ipo/greenasiaimpexltd/GAIL01</t>
         </is>
       </c>
       <c r="R72" t="inlineStr">
         <is>
-          <t>2026-08-25 09:29:52</t>
+          <t>2026-09-22 14:03:25</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Papadmalji Agro Foods Ltd</t>
+          <t>Kheria Autocomp Ltd</t>
         </is>
       </c>
       <c r="B73" t="inlineStr"/>
@@ -5812,33 +5824,33 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Sep 29, 2026</t>
+          <t>Sep 17, 2026</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Oct 01, 2026</t>
+          <t>Sep 21, 2026</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Oct 05, 2026</t>
+          <t>Sep 22, 2026</t>
         </is>
       </c>
       <c r="H73" t="inlineStr"/>
       <c r="I73" t="inlineStr">
         <is>
-          <t>1600</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>69-72</t>
+          <t>96-101</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>115200</t>
+          <t>121200</t>
         </is>
       </c>
       <c r="L73" t="inlineStr"/>
@@ -5848,19 +5860,19 @@
       <c r="P73" t="inlineStr"/>
       <c r="Q73" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/papadmaljiagrofoodsltd/PAF</t>
+          <t>https://www.moneycontrol.com/ipo/kheriaautocompltd/KAL05</t>
         </is>
       </c>
       <c r="R73" t="inlineStr">
         <is>
-          <t>2026-09-25 14:20:09</t>
+          <t>2026-09-11 13:34:16</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Paramount Syntex Ltd</t>
+          <t>Mopshop Distribution Ltd</t>
         </is>
       </c>
       <c r="B74" t="inlineStr"/>
@@ -5872,17 +5884,17 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Sep 30, 2026</t>
+          <t>Aug 19, 2026</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Oct 06, 2026</t>
+          <t>Aug 21, 2026</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Oct 07, 2026</t>
+          <t>Aug 24, 2026</t>
         </is>
       </c>
       <c r="H74" t="inlineStr"/>
@@ -5893,12 +5905,12 @@
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>119-127</t>
+          <t>138</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>127000</t>
+          <t>138000</t>
         </is>
       </c>
       <c r="L74" t="inlineStr"/>
@@ -5908,19 +5920,19 @@
       <c r="P74" t="inlineStr"/>
       <c r="Q74" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/paramountsyntexltd/PSL06</t>
+          <t>https://www.moneycontrol.com/ipo/mopshopdistributionltd/MDL03</t>
         </is>
       </c>
       <c r="R74" t="inlineStr">
         <is>
-          <t>2026-09-25 14:20:09</t>
+          <t>2026-08-14 21:36:23</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Peshwa Wheat</t>
+          <t>Paluck Technologies Ltd</t>
         </is>
       </c>
       <c r="B75" t="inlineStr"/>
@@ -5932,33 +5944,33 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Sep 24, 2026</t>
+          <t>Aug 28, 2026</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Sep 28, 2026</t>
+          <t>Sep 01, 2026</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Sep 29, 2026</t>
+          <t>Sep 02, 2026</t>
         </is>
       </c>
       <c r="H75" t="inlineStr"/>
       <c r="I75" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>3000</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>95-101</t>
+          <t>46-48</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>121200</t>
+          <t>144000</t>
         </is>
       </c>
       <c r="L75" t="inlineStr"/>
@@ -5968,75 +5980,79 @@
       <c r="P75" t="inlineStr"/>
       <c r="Q75" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/peshwawheat/PWL01</t>
+          <t>https://www.moneycontrol.com/ipo/palucktechnologiesltd/PTL08</t>
         </is>
       </c>
       <c r="R75" t="inlineStr">
         <is>
-          <t>2026-09-22 14:03:25</t>
+          <t>2026-08-25 09:29:52</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Purple Style Labs Ltd</t>
+          <t>Papadmalji Agro Foods Ltd</t>
         </is>
       </c>
       <c r="B76" t="inlineStr"/>
       <c r="C76" t="inlineStr"/>
-      <c r="D76" s="4" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="D76" s="5" t="inlineStr">
+        <is>
+          <t>Upcoming</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Aug 31, 2026</t>
+          <t>Sep 29, 2026</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Sep 02, 2026</t>
+          <t>Oct 01, 2026</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Sep 03, 2026</t>
+          <t>Oct 05, 2026</t>
         </is>
       </c>
       <c r="H76" t="inlineStr"/>
-      <c r="I76" t="inlineStr"/>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>1600</t>
+        </is>
+      </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>575</t>
-        </is>
-      </c>
-      <c r="K76" t="inlineStr"/>
+          <t>69-72</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>115200</t>
+        </is>
+      </c>
       <c r="L76" t="inlineStr"/>
       <c r="M76" t="inlineStr"/>
-      <c r="N76" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="N76" t="inlineStr"/>
       <c r="O76" t="inlineStr"/>
       <c r="P76" t="inlineStr"/>
       <c r="Q76" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/purplestylelabsltd/PSL05</t>
+          <t>https://www.moneycontrol.com/ipo/papadmaljiagrofoodsltd/PAF</t>
         </is>
       </c>
       <c r="R76" t="inlineStr">
         <is>
-          <t>2026-09-02 13:25:30</t>
+          <t>2026-09-25 14:20:09</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Q&amp;T Foods Ltd</t>
+          <t>Paramount Syntex Ltd</t>
         </is>
       </c>
       <c r="B77" t="inlineStr"/>
@@ -6048,33 +6064,33 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Aug 12, 2026</t>
+          <t>Sep 30, 2026</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Aug 14, 2026</t>
+          <t>Oct 06, 2026</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Aug 17, 2026</t>
+          <t>Oct 07, 2026</t>
         </is>
       </c>
       <c r="H77" t="inlineStr"/>
       <c r="I77" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>115</t>
+          <t>119-127</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>138000</t>
+          <t>127000</t>
         </is>
       </c>
       <c r="L77" t="inlineStr"/>
@@ -6084,19 +6100,19 @@
       <c r="P77" t="inlineStr"/>
       <c r="Q77" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/qtfoodsltd/QFL</t>
+          <t>https://www.moneycontrol.com/ipo/paramountsyntexltd/PSL06</t>
         </is>
       </c>
       <c r="R77" t="inlineStr">
         <is>
-          <t>2026-08-10 10:24:29</t>
+          <t>2026-09-25 14:20:09</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Ravita Engineering Services Ltd</t>
+          <t>Peshwa Wheat</t>
         </is>
       </c>
       <c r="B78" t="inlineStr"/>
@@ -6108,17 +6124,17 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Oct 13, 2026</t>
+          <t>Sep 24, 2026</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Oct 15, 2026</t>
+          <t>Sep 28, 2026</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Oct 16, 2026</t>
+          <t>Sep 29, 2026</t>
         </is>
       </c>
       <c r="H78" t="inlineStr"/>
@@ -6129,12 +6145,12 @@
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>105-112</t>
+          <t>95-101</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>134400</t>
+          <t>121200</t>
         </is>
       </c>
       <c r="L78" t="inlineStr"/>
@@ -6144,26 +6160,26 @@
       <c r="P78" t="inlineStr"/>
       <c r="Q78" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/ravitaengineeringservicesltd/RESL</t>
+          <t>https://www.moneycontrol.com/ipo/peshwawheat/PWL01</t>
         </is>
       </c>
       <c r="R78" t="inlineStr">
         <is>
-          <t>2026-10-08 16:06:11</t>
+          <t>2026-09-22 14:03:25</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Shanti Inorganics Ltd</t>
+          <t>Purple Style Labs Ltd</t>
         </is>
       </c>
       <c r="B79" t="inlineStr"/>
       <c r="C79" t="inlineStr"/>
-      <c r="D79" s="5" t="inlineStr">
-        <is>
-          <t>Upcoming</t>
+      <c r="D79" s="4" t="inlineStr">
+        <is>
+          <t>Open</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -6182,41 +6198,37 @@
         </is>
       </c>
       <c r="H79" t="inlineStr"/>
-      <c r="I79" t="inlineStr">
-        <is>
-          <t>1600</t>
-        </is>
-      </c>
+      <c r="I79" t="inlineStr"/>
       <c r="J79" t="inlineStr">
         <is>
-          <t>79-83</t>
-        </is>
-      </c>
-      <c r="K79" t="inlineStr">
-        <is>
-          <t>132800</t>
-        </is>
-      </c>
+          <t>575</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr"/>
       <c r="L79" t="inlineStr"/>
       <c r="M79" t="inlineStr"/>
-      <c r="N79" t="inlineStr"/>
+      <c r="N79" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="O79" t="inlineStr"/>
       <c r="P79" t="inlineStr"/>
       <c r="Q79" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/shantiinorganicsltd/SIL34</t>
+          <t>https://www.moneycontrol.com/ipo/purplestylelabsltd/PSL05</t>
         </is>
       </c>
       <c r="R79" t="inlineStr">
         <is>
-          <t>2026-08-25 09:29:52</t>
+          <t>2026-09-02 13:25:30</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Technocrats Plasma Systems Ltd</t>
+          <t>Q&amp;T Foods Ltd</t>
         </is>
       </c>
       <c r="B80" t="inlineStr"/>
@@ -6228,33 +6240,33 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
+          <t>Aug 12, 2026</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
           <t>Aug 14, 2026</t>
         </is>
       </c>
-      <c r="F80" t="inlineStr">
-        <is>
-          <t>Aug 18, 2026</t>
-        </is>
-      </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Aug 19, 2026</t>
+          <t>Aug 17, 2026</t>
         </is>
       </c>
       <c r="H80" t="inlineStr"/>
       <c r="I80" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>125-132</t>
+          <t>115</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>132000</t>
+          <t>138000</t>
         </is>
       </c>
       <c r="L80" t="inlineStr"/>
@@ -6264,19 +6276,19 @@
       <c r="P80" t="inlineStr"/>
       <c r="Q80" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/technocratsplasmasystemsltd/TPSL</t>
+          <t>https://www.moneycontrol.com/ipo/qtfoodsltd/QFL</t>
         </is>
       </c>
       <c r="R80" t="inlineStr">
         <is>
-          <t>2026-08-11 21:41:02</t>
+          <t>2026-08-10 10:24:29</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Unitec Fibres Ltd</t>
+          <t>Ravita Engineering Services Ltd</t>
         </is>
       </c>
       <c r="B81" t="inlineStr"/>
@@ -6288,33 +6300,33 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Sep 23, 2026</t>
+          <t>Oct 13, 2026</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Sep 25, 2026</t>
+          <t>Oct 15, 2026</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Sep 28, 2026</t>
+          <t>Oct 16, 2026</t>
         </is>
       </c>
       <c r="H81" t="inlineStr"/>
       <c r="I81" t="inlineStr">
         <is>
-          <t>1600</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>83-88</t>
+          <t>105-112</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>140800</t>
+          <t>134400</t>
         </is>
       </c>
       <c r="L81" t="inlineStr"/>
@@ -6324,19 +6336,19 @@
       <c r="P81" t="inlineStr"/>
       <c r="Q81" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/unitecfibresltd/UFL03</t>
+          <t>https://www.moneycontrol.com/ipo/ravitaengineeringservicesltd/RESL</t>
         </is>
       </c>
       <c r="R81" t="inlineStr">
         <is>
-          <t>2026-09-18 23:59:33</t>
+          <t>2026-10-08 16:06:11</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>VANS Electroengineerings Ltd</t>
+          <t>Shanti Inorganics Ltd</t>
         </is>
       </c>
       <c r="B82" t="inlineStr"/>
@@ -6348,33 +6360,33 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Sep 29, 2026</t>
+          <t>Aug 31, 2026</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Oct 01, 2026</t>
+          <t>Sep 02, 2026</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Oct 05, 2026</t>
+          <t>Sep 03, 2026</t>
         </is>
       </c>
       <c r="H82" t="inlineStr"/>
       <c r="I82" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>1600</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>112-118</t>
+          <t>79-83</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>141600</t>
+          <t>132800</t>
         </is>
       </c>
       <c r="L82" t="inlineStr"/>
@@ -6384,19 +6396,19 @@
       <c r="P82" t="inlineStr"/>
       <c r="Q82" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/vanselectroengineeringsltd/VEL03</t>
+          <t>https://www.moneycontrol.com/ipo/shantiinorganicsltd/SIL34</t>
         </is>
       </c>
       <c r="R82" t="inlineStr">
         <is>
-          <t>2026-09-25 14:20:09</t>
+          <t>2026-08-25 09:29:52</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Vaibhav Vyapaar Ltd</t>
+          <t>Technocrats Plasma Systems Ltd</t>
         </is>
       </c>
       <c r="B83" t="inlineStr"/>
@@ -6408,33 +6420,33 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Oct 13, 2026</t>
+          <t>Aug 14, 2026</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Oct 15, 2026</t>
+          <t>Aug 18, 2026</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Oct 16, 2026</t>
+          <t>Aug 19, 2026</t>
         </is>
       </c>
       <c r="H83" t="inlineStr"/>
       <c r="I83" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>50-52</t>
+          <t>125-132</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>104000</t>
+          <t>132000</t>
         </is>
       </c>
       <c r="L83" t="inlineStr"/>
@@ -6444,19 +6456,19 @@
       <c r="P83" t="inlineStr"/>
       <c r="Q83" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/vaibhavvyapaarltd/VVL01</t>
+          <t>https://www.moneycontrol.com/ipo/technocratsplasmasystemsltd/TPSL</t>
         </is>
       </c>
       <c r="R83" t="inlineStr">
         <is>
-          <t>2026-10-08 16:06:11</t>
+          <t>2026-08-11 21:41:02</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Vama Wovenfab Ltd</t>
+          <t>Unitec Fibres Ltd</t>
         </is>
       </c>
       <c r="B84" t="inlineStr"/>
@@ -6468,33 +6480,33 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Sep 15, 2026</t>
+          <t>Sep 23, 2026</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Sep 17, 2026</t>
+          <t>Sep 25, 2026</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Sep 18, 2026</t>
+          <t>Sep 28, 2026</t>
         </is>
       </c>
       <c r="H84" t="inlineStr"/>
       <c r="I84" t="inlineStr">
         <is>
-          <t>400</t>
+          <t>1600</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>324-341</t>
+          <t>83-88</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>136400</t>
+          <t>140800</t>
         </is>
       </c>
       <c r="L84" t="inlineStr"/>
@@ -6504,17 +6516,197 @@
       <c r="P84" t="inlineStr"/>
       <c r="Q84" t="inlineStr">
         <is>
+          <t>https://www.moneycontrol.com/ipo/unitecfibresltd/UFL03</t>
+        </is>
+      </c>
+      <c r="R84" t="inlineStr">
+        <is>
+          <t>2026-09-18 23:59:33</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>VANS Electroengineerings Ltd</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr"/>
+      <c r="C85" t="inlineStr"/>
+      <c r="D85" s="5" t="inlineStr">
+        <is>
+          <t>Upcoming</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>Sep 29, 2026</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>Oct 01, 2026</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>Oct 05, 2026</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr"/>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>1200</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>112-118</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>141600</t>
+        </is>
+      </c>
+      <c r="L85" t="inlineStr"/>
+      <c r="M85" t="inlineStr"/>
+      <c r="N85" t="inlineStr"/>
+      <c r="O85" t="inlineStr"/>
+      <c r="P85" t="inlineStr"/>
+      <c r="Q85" t="inlineStr">
+        <is>
+          <t>https://www.moneycontrol.com/ipo/vanselectroengineeringsltd/VEL03</t>
+        </is>
+      </c>
+      <c r="R85" t="inlineStr">
+        <is>
+          <t>2026-09-25 14:20:09</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Vaibhav Vyapaar Ltd</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr"/>
+      <c r="C86" t="inlineStr"/>
+      <c r="D86" s="5" t="inlineStr">
+        <is>
+          <t>Upcoming</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>Oct 13, 2026</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>Oct 15, 2026</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>Oct 16, 2026</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr"/>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>50-52</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>104000</t>
+        </is>
+      </c>
+      <c r="L86" t="inlineStr"/>
+      <c r="M86" t="inlineStr"/>
+      <c r="N86" t="inlineStr"/>
+      <c r="O86" t="inlineStr"/>
+      <c r="P86" t="inlineStr"/>
+      <c r="Q86" t="inlineStr">
+        <is>
+          <t>https://www.moneycontrol.com/ipo/vaibhavvyapaarltd/VVL01</t>
+        </is>
+      </c>
+      <c r="R86" t="inlineStr">
+        <is>
+          <t>2026-10-08 16:06:11</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Vama Wovenfab Ltd</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr"/>
+      <c r="C87" t="inlineStr"/>
+      <c r="D87" s="5" t="inlineStr">
+        <is>
+          <t>Upcoming</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>Sep 15, 2026</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>Sep 17, 2026</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>Sep 18, 2026</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr"/>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>400</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>324-341</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>136400</t>
+        </is>
+      </c>
+      <c r="L87" t="inlineStr"/>
+      <c r="M87" t="inlineStr"/>
+      <c r="N87" t="inlineStr"/>
+      <c r="O87" t="inlineStr"/>
+      <c r="P87" t="inlineStr"/>
+      <c r="Q87" t="inlineStr">
+        <is>
           <t>https://www.moneycontrol.com/ipo/vamawovenfabltd/VWL01</t>
         </is>
       </c>
-      <c r="R84" t="inlineStr">
+      <c r="R87" t="inlineStr">
         <is>
           <t>2026-09-11 13:34:16</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:R84"/>
+  <autoFilter ref="A1:R87"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/mainboard_ipos.xlsx
+++ b/data/mainboard_ipos.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Mainboard IPOs" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Mainboard IPOs'!$A$1:$R$87</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Mainboard IPOs'!$A$1:$R$88</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -449,7 +449,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R87"/>
+  <dimension ref="A1:R88"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -5137,9 +5137,9 @@
       </c>
       <c r="B62" t="inlineStr"/>
       <c r="C62" t="inlineStr"/>
-      <c r="D62" s="5" t="inlineStr">
-        <is>
-          <t>Upcoming</t>
+      <c r="D62" s="4" t="inlineStr">
+        <is>
+          <t>Open</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -5169,7 +5169,7 @@
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>258-271</t>
+          <t>271</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
@@ -5179,7 +5179,11 @@
       </c>
       <c r="L62" t="inlineStr"/>
       <c r="M62" t="inlineStr"/>
-      <c r="N62" t="inlineStr"/>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="O62" t="inlineStr"/>
       <c r="P62" t="inlineStr"/>
       <c r="Q62" t="inlineStr">
@@ -5189,7 +5193,7 @@
       </c>
       <c r="R62" t="inlineStr">
         <is>
-          <t>2026-10-12 16:21:01</t>
+          <t>2026-10-13 16:07:06</t>
         </is>
       </c>
     </row>
@@ -5253,7 +5257,7 @@
       </c>
       <c r="R63" t="inlineStr">
         <is>
-          <t>2026-10-12 16:21:01</t>
+          <t>2026-10-13 16:07:06</t>
         </is>
       </c>
     </row>
@@ -5317,14 +5321,14 @@
       </c>
       <c r="R64" t="inlineStr">
         <is>
-          <t>2026-10-12 16:21:01</t>
+          <t>2026-10-13 16:07:06</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Tonbo Imaging India Ltd</t>
+          <t>Sahajanand Medical Technologies Ltd</t>
         </is>
       </c>
       <c r="B65" t="inlineStr"/>
@@ -5356,17 +5360,17 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>43</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>665-700</t>
+          <t>327-344</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>14700</t>
+          <t>14792</t>
         </is>
       </c>
       <c r="L65" t="inlineStr"/>
@@ -5376,19 +5380,19 @@
       <c r="P65" t="inlineStr"/>
       <c r="Q65" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/tonboimagingindialtd/TIIL</t>
+          <t>https://www.moneycontrol.com/ipo/sahajanandmedicaltechnologiesltd/SMTL</t>
         </is>
       </c>
       <c r="R65" t="inlineStr">
         <is>
-          <t>2026-10-12 16:21:01</t>
+          <t>2026-10-13 16:07:06</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Zetwerk Manufacturing Businesses Ltd</t>
+          <t>Tonbo Imaging India Ltd</t>
         </is>
       </c>
       <c r="B66" t="inlineStr"/>
@@ -5420,17 +5424,17 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>21</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>143-151</t>
+          <t>665-700</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>14949</t>
+          <t>14700</t>
         </is>
       </c>
       <c r="L66" t="inlineStr"/>
@@ -5440,19 +5444,19 @@
       <c r="P66" t="inlineStr"/>
       <c r="Q66" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/zetwerkmanufacturingbusinessesltd/ZMBL</t>
+          <t>https://www.moneycontrol.com/ipo/tonboimagingindialtd/TIIL</t>
         </is>
       </c>
       <c r="R66" t="inlineStr">
         <is>
-          <t>2026-10-12 16:21:01</t>
+          <t>2026-10-13 16:07:06</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Complete Sports and Management India Ltd</t>
+          <t>Zetwerk Manufacturing Businesses Ltd</t>
         </is>
       </c>
       <c r="B67" t="inlineStr"/>
@@ -5464,33 +5468,37 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Aug 28, 2026</t>
+          <t>Oct 15, 2026</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Sep 01, 2026</t>
+          <t>Oct 19, 2026</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Sep 02, 2026</t>
-        </is>
-      </c>
-      <c r="H67" t="inlineStr"/>
+          <t>Oct 21, 2026</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>Oct 23, 2026</t>
+        </is>
+      </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>99</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>128-135</t>
+          <t>143-151</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>135000</t>
+          <t>14949</t>
         </is>
       </c>
       <c r="L67" t="inlineStr"/>
@@ -5500,19 +5508,19 @@
       <c r="P67" t="inlineStr"/>
       <c r="Q67" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/completesportsmanagementindialtd/CSMIL</t>
+          <t>https://www.moneycontrol.com/ipo/zetwerkmanufacturingbusinessesltd/ZMBL</t>
         </is>
       </c>
       <c r="R67" t="inlineStr">
         <is>
-          <t>2026-08-25 09:29:52</t>
+          <t>2026-10-13 16:07:06</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Coreintegra Consulting Services</t>
+          <t>Complete Sports and Management India Ltd</t>
         </is>
       </c>
       <c r="B68" t="inlineStr"/>
@@ -5524,33 +5532,33 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Sep 23, 2026</t>
+          <t>Aug 28, 2026</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Sep 25, 2026</t>
+          <t>Sep 01, 2026</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Sep 28, 2026</t>
+          <t>Sep 02, 2026</t>
         </is>
       </c>
       <c r="H68" t="inlineStr"/>
       <c r="I68" t="inlineStr">
         <is>
-          <t>1600</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>74-78</t>
+          <t>128-135</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>124800</t>
+          <t>135000</t>
         </is>
       </c>
       <c r="L68" t="inlineStr"/>
@@ -5560,19 +5568,19 @@
       <c r="P68" t="inlineStr"/>
       <c r="Q68" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/coreintegraconsultingservices/CCSL</t>
+          <t>https://www.moneycontrol.com/ipo/completesportsmanagementindialtd/CSMIL</t>
         </is>
       </c>
       <c r="R68" t="inlineStr">
         <is>
-          <t>2026-09-22 14:03:25</t>
+          <t>2026-08-25 09:29:52</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Credent Connect N Care Ltd</t>
+          <t>Coreintegra Consulting Services</t>
         </is>
       </c>
       <c r="B69" t="inlineStr"/>
@@ -5584,33 +5592,33 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Aug 13, 2026</t>
+          <t>Sep 23, 2026</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Aug 17, 2026</t>
+          <t>Sep 25, 2026</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Aug 18, 2026</t>
+          <t>Sep 28, 2026</t>
         </is>
       </c>
       <c r="H69" t="inlineStr"/>
       <c r="I69" t="inlineStr">
         <is>
-          <t>600</t>
+          <t>1600</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>179-189</t>
+          <t>74-78</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>113400</t>
+          <t>124800</t>
         </is>
       </c>
       <c r="L69" t="inlineStr"/>
@@ -5620,19 +5628,19 @@
       <c r="P69" t="inlineStr"/>
       <c r="Q69" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/credentconnectncareltd/CCC04</t>
+          <t>https://www.moneycontrol.com/ipo/coreintegraconsultingservices/CCSL</t>
         </is>
       </c>
       <c r="R69" t="inlineStr">
         <is>
-          <t>2026-08-10 22:43:12</t>
+          <t>2026-09-22 14:03:25</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Dove Soft Ltd</t>
+          <t>Credent Connect N Care Ltd</t>
         </is>
       </c>
       <c r="B70" t="inlineStr"/>
@@ -5644,33 +5652,33 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Sep 30, 2026</t>
+          <t>Aug 13, 2026</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Oct 05, 2026</t>
+          <t>Aug 17, 2026</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Oct 06, 2026</t>
+          <t>Aug 18, 2026</t>
         </is>
       </c>
       <c r="H70" t="inlineStr"/>
       <c r="I70" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>600</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>104-111</t>
+          <t>179-189</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>133200</t>
+          <t>113400</t>
         </is>
       </c>
       <c r="L70" t="inlineStr"/>
@@ -5680,19 +5688,19 @@
       <c r="P70" t="inlineStr"/>
       <c r="Q70" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/dovesoftltd/DSL04</t>
+          <t>https://www.moneycontrol.com/ipo/credentconnectncareltd/CCC04</t>
         </is>
       </c>
       <c r="R70" t="inlineStr">
         <is>
-          <t>2026-09-25 14:20:09</t>
+          <t>2026-08-10 22:43:12</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Farm Peace Ltd</t>
+          <t>Dove Soft Ltd</t>
         </is>
       </c>
       <c r="B71" t="inlineStr"/>
@@ -5704,33 +5712,33 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Sep 01, 2026</t>
+          <t>Sep 30, 2026</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Sep 03, 2026</t>
+          <t>Oct 05, 2026</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Sep 04, 2026</t>
+          <t>Oct 06, 2026</t>
         </is>
       </c>
       <c r="H71" t="inlineStr"/>
       <c r="I71" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>104-111</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>118000</t>
+          <t>133200</t>
         </is>
       </c>
       <c r="L71" t="inlineStr"/>
@@ -5740,19 +5748,19 @@
       <c r="P71" t="inlineStr"/>
       <c r="Q71" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/farmpeaceltd/FPL02</t>
+          <t>https://www.moneycontrol.com/ipo/dovesoftltd/DSL04</t>
         </is>
       </c>
       <c r="R71" t="inlineStr">
         <is>
-          <t>2026-08-27 19:43:03</t>
+          <t>2026-09-25 14:20:09</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Green Asia Impex Ltd</t>
+          <t>Farm Peace Ltd</t>
         </is>
       </c>
       <c r="B72" t="inlineStr"/>
@@ -5764,33 +5772,33 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Sep 24, 2026</t>
+          <t>Sep 01, 2026</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Sep 28, 2026</t>
+          <t>Sep 03, 2026</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Sep 29, 2026</t>
+          <t>Sep 04, 2026</t>
         </is>
       </c>
       <c r="H72" t="inlineStr"/>
       <c r="I72" t="inlineStr">
         <is>
-          <t>1600</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>85-90</t>
+          <t>59</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>144000</t>
+          <t>118000</t>
         </is>
       </c>
       <c r="L72" t="inlineStr"/>
@@ -5800,19 +5808,19 @@
       <c r="P72" t="inlineStr"/>
       <c r="Q72" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/greenasiaimpexltd/GAIL01</t>
+          <t>https://www.moneycontrol.com/ipo/farmpeaceltd/FPL02</t>
         </is>
       </c>
       <c r="R72" t="inlineStr">
         <is>
-          <t>2026-09-22 14:03:25</t>
+          <t>2026-08-27 19:43:03</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Kheria Autocomp Ltd</t>
+          <t>Green Asia Impex Ltd</t>
         </is>
       </c>
       <c r="B73" t="inlineStr"/>
@@ -5824,33 +5832,33 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Sep 17, 2026</t>
+          <t>Sep 24, 2026</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Sep 21, 2026</t>
+          <t>Sep 28, 2026</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Sep 22, 2026</t>
+          <t>Sep 29, 2026</t>
         </is>
       </c>
       <c r="H73" t="inlineStr"/>
       <c r="I73" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>1600</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>96-101</t>
+          <t>85-90</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>121200</t>
+          <t>144000</t>
         </is>
       </c>
       <c r="L73" t="inlineStr"/>
@@ -5860,19 +5868,19 @@
       <c r="P73" t="inlineStr"/>
       <c r="Q73" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/kheriaautocompltd/KAL05</t>
+          <t>https://www.moneycontrol.com/ipo/greenasiaimpexltd/GAIL01</t>
         </is>
       </c>
       <c r="R73" t="inlineStr">
         <is>
-          <t>2026-09-11 13:34:16</t>
+          <t>2026-09-22 14:03:25</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Mopshop Distribution Ltd</t>
+          <t>Kheria Autocomp Ltd</t>
         </is>
       </c>
       <c r="B74" t="inlineStr"/>
@@ -5884,33 +5892,33 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Aug 19, 2026</t>
+          <t>Sep 17, 2026</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Aug 21, 2026</t>
+          <t>Sep 21, 2026</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Aug 24, 2026</t>
+          <t>Sep 22, 2026</t>
         </is>
       </c>
       <c r="H74" t="inlineStr"/>
       <c r="I74" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>138</t>
+          <t>96-101</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>138000</t>
+          <t>121200</t>
         </is>
       </c>
       <c r="L74" t="inlineStr"/>
@@ -5920,19 +5928,19 @@
       <c r="P74" t="inlineStr"/>
       <c r="Q74" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/mopshopdistributionltd/MDL03</t>
+          <t>https://www.moneycontrol.com/ipo/kheriaautocompltd/KAL05</t>
         </is>
       </c>
       <c r="R74" t="inlineStr">
         <is>
-          <t>2026-08-14 21:36:23</t>
+          <t>2026-09-11 13:34:16</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Paluck Technologies Ltd</t>
+          <t>Mopshop Distribution Ltd</t>
         </is>
       </c>
       <c r="B75" t="inlineStr"/>
@@ -5944,33 +5952,33 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Aug 28, 2026</t>
+          <t>Aug 19, 2026</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Sep 01, 2026</t>
+          <t>Aug 21, 2026</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Sep 02, 2026</t>
+          <t>Aug 24, 2026</t>
         </is>
       </c>
       <c r="H75" t="inlineStr"/>
       <c r="I75" t="inlineStr">
         <is>
-          <t>3000</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>46-48</t>
+          <t>138</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>144000</t>
+          <t>138000</t>
         </is>
       </c>
       <c r="L75" t="inlineStr"/>
@@ -5980,19 +5988,19 @@
       <c r="P75" t="inlineStr"/>
       <c r="Q75" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/palucktechnologiesltd/PTL08</t>
+          <t>https://www.moneycontrol.com/ipo/mopshopdistributionltd/MDL03</t>
         </is>
       </c>
       <c r="R75" t="inlineStr">
         <is>
-          <t>2026-08-25 09:29:52</t>
+          <t>2026-08-14 21:36:23</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Papadmalji Agro Foods Ltd</t>
+          <t>Paluck Technologies Ltd</t>
         </is>
       </c>
       <c r="B76" t="inlineStr"/>
@@ -6004,33 +6012,33 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Sep 29, 2026</t>
+          <t>Aug 28, 2026</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Oct 01, 2026</t>
+          <t>Sep 01, 2026</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Oct 05, 2026</t>
+          <t>Sep 02, 2026</t>
         </is>
       </c>
       <c r="H76" t="inlineStr"/>
       <c r="I76" t="inlineStr">
         <is>
-          <t>1600</t>
+          <t>3000</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>69-72</t>
+          <t>46-48</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>115200</t>
+          <t>144000</t>
         </is>
       </c>
       <c r="L76" t="inlineStr"/>
@@ -6040,19 +6048,19 @@
       <c r="P76" t="inlineStr"/>
       <c r="Q76" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/papadmaljiagrofoodsltd/PAF</t>
+          <t>https://www.moneycontrol.com/ipo/palucktechnologiesltd/PTL08</t>
         </is>
       </c>
       <c r="R76" t="inlineStr">
         <is>
-          <t>2026-09-25 14:20:09</t>
+          <t>2026-08-25 09:29:52</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Paramount Syntex Ltd</t>
+          <t>Papadmalji Agro Foods Ltd</t>
         </is>
       </c>
       <c r="B77" t="inlineStr"/>
@@ -6064,33 +6072,33 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Sep 30, 2026</t>
+          <t>Sep 29, 2026</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Oct 06, 2026</t>
+          <t>Oct 01, 2026</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Oct 07, 2026</t>
+          <t>Oct 05, 2026</t>
         </is>
       </c>
       <c r="H77" t="inlineStr"/>
       <c r="I77" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>1600</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>119-127</t>
+          <t>69-72</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>127000</t>
+          <t>115200</t>
         </is>
       </c>
       <c r="L77" t="inlineStr"/>
@@ -6100,7 +6108,7 @@
       <c r="P77" t="inlineStr"/>
       <c r="Q77" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/paramountsyntexltd/PSL06</t>
+          <t>https://www.moneycontrol.com/ipo/papadmaljiagrofoodsltd/PAF</t>
         </is>
       </c>
       <c r="R77" t="inlineStr">
@@ -6112,7 +6120,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Peshwa Wheat</t>
+          <t>Paramount Syntex Ltd</t>
         </is>
       </c>
       <c r="B78" t="inlineStr"/>
@@ -6124,33 +6132,33 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Sep 24, 2026</t>
+          <t>Sep 30, 2026</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Sep 28, 2026</t>
+          <t>Oct 06, 2026</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Sep 29, 2026</t>
+          <t>Oct 07, 2026</t>
         </is>
       </c>
       <c r="H78" t="inlineStr"/>
       <c r="I78" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>95-101</t>
+          <t>119-127</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>121200</t>
+          <t>127000</t>
         </is>
       </c>
       <c r="L78" t="inlineStr"/>
@@ -6160,135 +6168,135 @@
       <c r="P78" t="inlineStr"/>
       <c r="Q78" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/peshwawheat/PWL01</t>
+          <t>https://www.moneycontrol.com/ipo/paramountsyntexltd/PSL06</t>
         </is>
       </c>
       <c r="R78" t="inlineStr">
         <is>
-          <t>2026-09-22 14:03:25</t>
+          <t>2026-09-25 14:20:09</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Purple Style Labs Ltd</t>
+          <t>Peshwa Wheat</t>
         </is>
       </c>
       <c r="B79" t="inlineStr"/>
       <c r="C79" t="inlineStr"/>
-      <c r="D79" s="4" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="D79" s="5" t="inlineStr">
+        <is>
+          <t>Upcoming</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Aug 31, 2026</t>
+          <t>Sep 24, 2026</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Sep 02, 2026</t>
+          <t>Sep 28, 2026</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Sep 03, 2026</t>
+          <t>Sep 29, 2026</t>
         </is>
       </c>
       <c r="H79" t="inlineStr"/>
-      <c r="I79" t="inlineStr"/>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>1200</t>
+        </is>
+      </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>575</t>
-        </is>
-      </c>
-      <c r="K79" t="inlineStr"/>
+          <t>95-101</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>121200</t>
+        </is>
+      </c>
       <c r="L79" t="inlineStr"/>
       <c r="M79" t="inlineStr"/>
-      <c r="N79" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="N79" t="inlineStr"/>
       <c r="O79" t="inlineStr"/>
       <c r="P79" t="inlineStr"/>
       <c r="Q79" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/purplestylelabsltd/PSL05</t>
+          <t>https://www.moneycontrol.com/ipo/peshwawheat/PWL01</t>
         </is>
       </c>
       <c r="R79" t="inlineStr">
         <is>
-          <t>2026-09-02 13:25:30</t>
+          <t>2026-09-22 14:03:25</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Q&amp;T Foods Ltd</t>
+          <t>Purple Style Labs Ltd</t>
         </is>
       </c>
       <c r="B80" t="inlineStr"/>
       <c r="C80" t="inlineStr"/>
-      <c r="D80" s="5" t="inlineStr">
-        <is>
-          <t>Upcoming</t>
+      <c r="D80" s="4" t="inlineStr">
+        <is>
+          <t>Open</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Aug 12, 2026</t>
+          <t>Aug 31, 2026</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Aug 14, 2026</t>
+          <t>Sep 02, 2026</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Aug 17, 2026</t>
+          <t>Sep 03, 2026</t>
         </is>
       </c>
       <c r="H80" t="inlineStr"/>
-      <c r="I80" t="inlineStr">
-        <is>
-          <t>1200</t>
-        </is>
-      </c>
+      <c r="I80" t="inlineStr"/>
       <c r="J80" t="inlineStr">
         <is>
-          <t>115</t>
-        </is>
-      </c>
-      <c r="K80" t="inlineStr">
-        <is>
-          <t>138000</t>
-        </is>
-      </c>
+          <t>575</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr"/>
       <c r="L80" t="inlineStr"/>
       <c r="M80" t="inlineStr"/>
-      <c r="N80" t="inlineStr"/>
+      <c r="N80" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="O80" t="inlineStr"/>
       <c r="P80" t="inlineStr"/>
       <c r="Q80" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/qtfoodsltd/QFL</t>
+          <t>https://www.moneycontrol.com/ipo/purplestylelabsltd/PSL05</t>
         </is>
       </c>
       <c r="R80" t="inlineStr">
         <is>
-          <t>2026-08-10 10:24:29</t>
+          <t>2026-09-02 13:25:30</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Ravita Engineering Services Ltd</t>
+          <t>Q&amp;T Foods Ltd</t>
         </is>
       </c>
       <c r="B81" t="inlineStr"/>
@@ -6300,17 +6308,17 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Oct 13, 2026</t>
+          <t>Aug 12, 2026</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Oct 15, 2026</t>
+          <t>Aug 14, 2026</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Oct 16, 2026</t>
+          <t>Aug 17, 2026</t>
         </is>
       </c>
       <c r="H81" t="inlineStr"/>
@@ -6321,12 +6329,12 @@
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>105-112</t>
+          <t>115</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>134400</t>
+          <t>138000</t>
         </is>
       </c>
       <c r="L81" t="inlineStr"/>
@@ -6336,19 +6344,19 @@
       <c r="P81" t="inlineStr"/>
       <c r="Q81" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/ravitaengineeringservicesltd/RESL</t>
+          <t>https://www.moneycontrol.com/ipo/qtfoodsltd/QFL</t>
         </is>
       </c>
       <c r="R81" t="inlineStr">
         <is>
-          <t>2026-10-08 16:06:11</t>
+          <t>2026-08-10 10:24:29</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Shanti Inorganics Ltd</t>
+          <t>Ravita Engineering Services Ltd</t>
         </is>
       </c>
       <c r="B82" t="inlineStr"/>
@@ -6360,33 +6368,33 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Aug 31, 2026</t>
+          <t>Oct 13, 2026</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Sep 02, 2026</t>
+          <t>Oct 15, 2026</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Sep 03, 2026</t>
+          <t>Oct 16, 2026</t>
         </is>
       </c>
       <c r="H82" t="inlineStr"/>
       <c r="I82" t="inlineStr">
         <is>
-          <t>1600</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>79-83</t>
+          <t>105-112</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>132800</t>
+          <t>134400</t>
         </is>
       </c>
       <c r="L82" t="inlineStr"/>
@@ -6396,19 +6404,19 @@
       <c r="P82" t="inlineStr"/>
       <c r="Q82" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/shantiinorganicsltd/SIL34</t>
+          <t>https://www.moneycontrol.com/ipo/ravitaengineeringservicesltd/RESL</t>
         </is>
       </c>
       <c r="R82" t="inlineStr">
         <is>
-          <t>2026-08-25 09:29:52</t>
+          <t>2026-10-08 16:06:11</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Technocrats Plasma Systems Ltd</t>
+          <t>Shanti Inorganics Ltd</t>
         </is>
       </c>
       <c r="B83" t="inlineStr"/>
@@ -6420,33 +6428,33 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Aug 14, 2026</t>
+          <t>Aug 31, 2026</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Aug 18, 2026</t>
+          <t>Sep 02, 2026</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Aug 19, 2026</t>
+          <t>Sep 03, 2026</t>
         </is>
       </c>
       <c r="H83" t="inlineStr"/>
       <c r="I83" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>1600</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>125-132</t>
+          <t>79-83</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>132000</t>
+          <t>132800</t>
         </is>
       </c>
       <c r="L83" t="inlineStr"/>
@@ -6456,19 +6464,19 @@
       <c r="P83" t="inlineStr"/>
       <c r="Q83" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/technocratsplasmasystemsltd/TPSL</t>
+          <t>https://www.moneycontrol.com/ipo/shantiinorganicsltd/SIL34</t>
         </is>
       </c>
       <c r="R83" t="inlineStr">
         <is>
-          <t>2026-08-11 21:41:02</t>
+          <t>2026-08-25 09:29:52</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Unitec Fibres Ltd</t>
+          <t>Technocrats Plasma Systems Ltd</t>
         </is>
       </c>
       <c r="B84" t="inlineStr"/>
@@ -6480,33 +6488,33 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Sep 23, 2026</t>
+          <t>Aug 14, 2026</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Sep 25, 2026</t>
+          <t>Aug 18, 2026</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Sep 28, 2026</t>
+          <t>Aug 19, 2026</t>
         </is>
       </c>
       <c r="H84" t="inlineStr"/>
       <c r="I84" t="inlineStr">
         <is>
-          <t>1600</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>83-88</t>
+          <t>125-132</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>140800</t>
+          <t>132000</t>
         </is>
       </c>
       <c r="L84" t="inlineStr"/>
@@ -6516,19 +6524,19 @@
       <c r="P84" t="inlineStr"/>
       <c r="Q84" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/unitecfibresltd/UFL03</t>
+          <t>https://www.moneycontrol.com/ipo/technocratsplasmasystemsltd/TPSL</t>
         </is>
       </c>
       <c r="R84" t="inlineStr">
         <is>
-          <t>2026-09-18 23:59:33</t>
+          <t>2026-08-11 21:41:02</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>VANS Electroengineerings Ltd</t>
+          <t>Unitec Fibres Ltd</t>
         </is>
       </c>
       <c r="B85" t="inlineStr"/>
@@ -6540,33 +6548,33 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Sep 29, 2026</t>
+          <t>Sep 23, 2026</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Oct 01, 2026</t>
+          <t>Sep 25, 2026</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Oct 05, 2026</t>
+          <t>Sep 28, 2026</t>
         </is>
       </c>
       <c r="H85" t="inlineStr"/>
       <c r="I85" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>1600</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>112-118</t>
+          <t>83-88</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>141600</t>
+          <t>140800</t>
         </is>
       </c>
       <c r="L85" t="inlineStr"/>
@@ -6576,19 +6584,19 @@
       <c r="P85" t="inlineStr"/>
       <c r="Q85" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/vanselectroengineeringsltd/VEL03</t>
+          <t>https://www.moneycontrol.com/ipo/unitecfibresltd/UFL03</t>
         </is>
       </c>
       <c r="R85" t="inlineStr">
         <is>
-          <t>2026-09-25 14:20:09</t>
+          <t>2026-09-18 23:59:33</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Vaibhav Vyapaar Ltd</t>
+          <t>VANS Electroengineerings Ltd</t>
         </is>
       </c>
       <c r="B86" t="inlineStr"/>
@@ -6600,33 +6608,33 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Oct 13, 2026</t>
+          <t>Sep 29, 2026</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Oct 15, 2026</t>
+          <t>Oct 01, 2026</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Oct 16, 2026</t>
+          <t>Oct 05, 2026</t>
         </is>
       </c>
       <c r="H86" t="inlineStr"/>
       <c r="I86" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>50-52</t>
+          <t>112-118</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>104000</t>
+          <t>141600</t>
         </is>
       </c>
       <c r="L86" t="inlineStr"/>
@@ -6636,19 +6644,19 @@
       <c r="P86" t="inlineStr"/>
       <c r="Q86" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/vaibhavvyapaarltd/VVL01</t>
+          <t>https://www.moneycontrol.com/ipo/vanselectroengineeringsltd/VEL03</t>
         </is>
       </c>
       <c r="R86" t="inlineStr">
         <is>
-          <t>2026-10-08 16:06:11</t>
+          <t>2026-09-25 14:20:09</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Vama Wovenfab Ltd</t>
+          <t>Vaibhav Vyapaar Ltd</t>
         </is>
       </c>
       <c r="B87" t="inlineStr"/>
@@ -6660,33 +6668,33 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Sep 15, 2026</t>
+          <t>Oct 13, 2026</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Sep 17, 2026</t>
+          <t>Oct 15, 2026</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Sep 18, 2026</t>
+          <t>Oct 16, 2026</t>
         </is>
       </c>
       <c r="H87" t="inlineStr"/>
       <c r="I87" t="inlineStr">
         <is>
-          <t>400</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>324-341</t>
+          <t>50-52</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>136400</t>
+          <t>104000</t>
         </is>
       </c>
       <c r="L87" t="inlineStr"/>
@@ -6696,17 +6704,77 @@
       <c r="P87" t="inlineStr"/>
       <c r="Q87" t="inlineStr">
         <is>
+          <t>https://www.moneycontrol.com/ipo/vaibhavvyapaarltd/VVL01</t>
+        </is>
+      </c>
+      <c r="R87" t="inlineStr">
+        <is>
+          <t>2026-10-08 16:06:11</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>Vama Wovenfab Ltd</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr"/>
+      <c r="C88" t="inlineStr"/>
+      <c r="D88" s="5" t="inlineStr">
+        <is>
+          <t>Upcoming</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>Sep 15, 2026</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>Sep 17, 2026</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>Sep 18, 2026</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr"/>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>400</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>324-341</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>136400</t>
+        </is>
+      </c>
+      <c r="L88" t="inlineStr"/>
+      <c r="M88" t="inlineStr"/>
+      <c r="N88" t="inlineStr"/>
+      <c r="O88" t="inlineStr"/>
+      <c r="P88" t="inlineStr"/>
+      <c r="Q88" t="inlineStr">
+        <is>
           <t>https://www.moneycontrol.com/ipo/vamawovenfabltd/VWL01</t>
         </is>
       </c>
-      <c r="R87" t="inlineStr">
+      <c r="R88" t="inlineStr">
         <is>
           <t>2026-09-11 13:34:16</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:R87"/>
+  <autoFilter ref="A1:R88"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/mainboard_ipos.xlsx
+++ b/data/mainboard_ipos.xlsx
@@ -5181,7 +5181,7 @@
       <c r="M62" t="inlineStr"/>
       <c r="N62" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="O62" t="inlineStr"/>
@@ -5193,7 +5193,7 @@
       </c>
       <c r="R62" t="inlineStr">
         <is>
-          <t>2026-10-13 16:07:06</t>
+          <t>2026-10-14 14:13:53</t>
         </is>
       </c>
     </row>
@@ -5205,9 +5205,9 @@
       </c>
       <c r="B63" t="inlineStr"/>
       <c r="C63" t="inlineStr"/>
-      <c r="D63" s="5" t="inlineStr">
-        <is>
-          <t>Upcoming</t>
+      <c r="D63" s="4" t="inlineStr">
+        <is>
+          <t>Open</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -5237,7 +5237,7 @@
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>275-289</t>
+          <t>289</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
@@ -5257,7 +5257,7 @@
       </c>
       <c r="R63" t="inlineStr">
         <is>
-          <t>2026-10-13 16:07:06</t>
+          <t>2026-10-14 14:13:53</t>
         </is>
       </c>
     </row>
@@ -5321,7 +5321,7 @@
       </c>
       <c r="R64" t="inlineStr">
         <is>
-          <t>2026-10-13 16:07:06</t>
+          <t>2026-10-14 14:13:53</t>
         </is>
       </c>
     </row>
@@ -5385,7 +5385,7 @@
       </c>
       <c r="R65" t="inlineStr">
         <is>
-          <t>2026-10-13 16:07:06</t>
+          <t>2026-10-14 14:13:53</t>
         </is>
       </c>
     </row>
@@ -5449,7 +5449,7 @@
       </c>
       <c r="R66" t="inlineStr">
         <is>
-          <t>2026-10-13 16:07:06</t>
+          <t>2026-10-14 14:13:53</t>
         </is>
       </c>
     </row>
@@ -5513,7 +5513,7 @@
       </c>
       <c r="R67" t="inlineStr">
         <is>
-          <t>2026-10-13 16:07:06</t>
+          <t>2026-10-14 14:13:53</t>
         </is>
       </c>
     </row>

--- a/data/mainboard_ipos.xlsx
+++ b/data/mainboard_ipos.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Mainboard IPOs" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Mainboard IPOs'!$A$1:$R$88</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Mainboard IPOs'!$A$1:$R$90</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -449,7 +449,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R88"/>
+  <dimension ref="A1:R90"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -5137,9 +5137,9 @@
       </c>
       <c r="B62" t="inlineStr"/>
       <c r="C62" t="inlineStr"/>
-      <c r="D62" s="4" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="D62" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -5181,7 +5181,7 @@
       <c r="M62" t="inlineStr"/>
       <c r="N62" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>132</t>
         </is>
       </c>
       <c r="O62" t="inlineStr"/>
@@ -5193,7 +5193,7 @@
       </c>
       <c r="R62" t="inlineStr">
         <is>
-          <t>2026-10-14 14:13:53</t>
+          <t>2026-10-16 13:41:40</t>
         </is>
       </c>
     </row>
@@ -5247,7 +5247,11 @@
       </c>
       <c r="L63" t="inlineStr"/>
       <c r="M63" t="inlineStr"/>
-      <c r="N63" t="inlineStr"/>
+      <c r="N63" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="O63" t="inlineStr"/>
       <c r="P63" t="inlineStr"/>
       <c r="Q63" t="inlineStr">
@@ -5257,7 +5261,7 @@
       </c>
       <c r="R63" t="inlineStr">
         <is>
-          <t>2026-10-14 14:13:53</t>
+          <t>2026-10-16 13:41:40</t>
         </is>
       </c>
     </row>
@@ -5269,9 +5273,9 @@
       </c>
       <c r="B64" t="inlineStr"/>
       <c r="C64" t="inlineStr"/>
-      <c r="D64" s="5" t="inlineStr">
-        <is>
-          <t>Upcoming</t>
+      <c r="D64" s="4" t="inlineStr">
+        <is>
+          <t>Open</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -5301,7 +5305,7 @@
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>558-586</t>
+          <t>586</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
@@ -5311,7 +5315,11 @@
       </c>
       <c r="L64" t="inlineStr"/>
       <c r="M64" t="inlineStr"/>
-      <c r="N64" t="inlineStr"/>
+      <c r="N64" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="O64" t="inlineStr"/>
       <c r="P64" t="inlineStr"/>
       <c r="Q64" t="inlineStr">
@@ -5321,7 +5329,7 @@
       </c>
       <c r="R64" t="inlineStr">
         <is>
-          <t>2026-10-14 14:13:53</t>
+          <t>2026-10-16 13:41:40</t>
         </is>
       </c>
     </row>
@@ -5333,9 +5341,9 @@
       </c>
       <c r="B65" t="inlineStr"/>
       <c r="C65" t="inlineStr"/>
-      <c r="D65" s="5" t="inlineStr">
-        <is>
-          <t>Upcoming</t>
+      <c r="D65" s="4" t="inlineStr">
+        <is>
+          <t>Open</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -5365,7 +5373,7 @@
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>327-344</t>
+          <t>344</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
@@ -5375,7 +5383,11 @@
       </c>
       <c r="L65" t="inlineStr"/>
       <c r="M65" t="inlineStr"/>
-      <c r="N65" t="inlineStr"/>
+      <c r="N65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="O65" t="inlineStr"/>
       <c r="P65" t="inlineStr"/>
       <c r="Q65" t="inlineStr">
@@ -5385,7 +5397,7 @@
       </c>
       <c r="R65" t="inlineStr">
         <is>
-          <t>2026-10-14 14:13:53</t>
+          <t>2026-10-16 13:41:40</t>
         </is>
       </c>
     </row>
@@ -5397,9 +5409,9 @@
       </c>
       <c r="B66" t="inlineStr"/>
       <c r="C66" t="inlineStr"/>
-      <c r="D66" s="5" t="inlineStr">
-        <is>
-          <t>Upcoming</t>
+      <c r="D66" s="4" t="inlineStr">
+        <is>
+          <t>Open</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -5429,7 +5441,7 @@
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>665-700</t>
+          <t>700</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
@@ -5439,7 +5451,11 @@
       </c>
       <c r="L66" t="inlineStr"/>
       <c r="M66" t="inlineStr"/>
-      <c r="N66" t="inlineStr"/>
+      <c r="N66" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="O66" t="inlineStr"/>
       <c r="P66" t="inlineStr"/>
       <c r="Q66" t="inlineStr">
@@ -5449,7 +5465,7 @@
       </c>
       <c r="R66" t="inlineStr">
         <is>
-          <t>2026-10-14 14:13:53</t>
+          <t>2026-10-16 13:41:40</t>
         </is>
       </c>
     </row>
@@ -5461,9 +5477,9 @@
       </c>
       <c r="B67" t="inlineStr"/>
       <c r="C67" t="inlineStr"/>
-      <c r="D67" s="5" t="inlineStr">
-        <is>
-          <t>Upcoming</t>
+      <c r="D67" s="4" t="inlineStr">
+        <is>
+          <t>Open</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -5493,7 +5509,7 @@
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>143-151</t>
+          <t>151</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
@@ -5503,7 +5519,11 @@
       </c>
       <c r="L67" t="inlineStr"/>
       <c r="M67" t="inlineStr"/>
-      <c r="N67" t="inlineStr"/>
+      <c r="N67" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="O67" t="inlineStr"/>
       <c r="P67" t="inlineStr"/>
       <c r="Q67" t="inlineStr">
@@ -5513,14 +5533,14 @@
       </c>
       <c r="R67" t="inlineStr">
         <is>
-          <t>2026-10-14 14:13:53</t>
+          <t>2026-10-16 13:41:40</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Complete Sports and Management India Ltd</t>
+          <t>Jio Platforms Ltd</t>
         </is>
       </c>
       <c r="B68" t="inlineStr"/>
@@ -5532,33 +5552,37 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Aug 28, 2026</t>
+          <t>Oct 21, 2026</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Sep 01, 2026</t>
+          <t>Oct 23, 2026</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Sep 02, 2026</t>
-        </is>
-      </c>
-      <c r="H68" t="inlineStr"/>
+          <t>Oct 26, 2026</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>Oct 28, 2026</t>
+        </is>
+      </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>128-135</t>
+          <t>1065-1119</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>135000</t>
+          <t>13428</t>
         </is>
       </c>
       <c r="L68" t="inlineStr"/>
@@ -5568,19 +5592,19 @@
       <c r="P68" t="inlineStr"/>
       <c r="Q68" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/completesportsmanagementindialtd/CSMIL</t>
+          <t>https://www.moneycontrol.com/ipo/jioplatformsltd/JPL</t>
         </is>
       </c>
       <c r="R68" t="inlineStr">
         <is>
-          <t>2026-08-25 09:29:52</t>
+          <t>2026-10-16 13:41:40</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Coreintegra Consulting Services</t>
+          <t>Paras Healthcare Ltd</t>
         </is>
       </c>
       <c r="B69" t="inlineStr"/>
@@ -5592,33 +5616,37 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Sep 23, 2026</t>
+          <t>Oct 21, 2026</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Sep 25, 2026</t>
+          <t>Oct 23, 2026</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Sep 28, 2026</t>
-        </is>
-      </c>
-      <c r="H69" t="inlineStr"/>
+          <t>Oct 26, 2026</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>Oct 28, 2026</t>
+        </is>
+      </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>1600</t>
+          <t>21</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>74-78</t>
+          <t>660-693</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>124800</t>
+          <t>14553</t>
         </is>
       </c>
       <c r="L69" t="inlineStr"/>
@@ -5628,19 +5656,19 @@
       <c r="P69" t="inlineStr"/>
       <c r="Q69" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/coreintegraconsultingservices/CCSL</t>
+          <t>https://www.moneycontrol.com/ipo/parashealthcareltd/PHL01</t>
         </is>
       </c>
       <c r="R69" t="inlineStr">
         <is>
-          <t>2026-09-22 14:03:25</t>
+          <t>2026-10-16 13:41:40</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Credent Connect N Care Ltd</t>
+          <t>Complete Sports and Management India Ltd</t>
         </is>
       </c>
       <c r="B70" t="inlineStr"/>
@@ -5652,33 +5680,33 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Aug 13, 2026</t>
+          <t>Aug 28, 2026</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Aug 17, 2026</t>
+          <t>Sep 01, 2026</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Aug 18, 2026</t>
+          <t>Sep 02, 2026</t>
         </is>
       </c>
       <c r="H70" t="inlineStr"/>
       <c r="I70" t="inlineStr">
         <is>
-          <t>600</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>179-189</t>
+          <t>128-135</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>113400</t>
+          <t>135000</t>
         </is>
       </c>
       <c r="L70" t="inlineStr"/>
@@ -5688,19 +5716,19 @@
       <c r="P70" t="inlineStr"/>
       <c r="Q70" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/credentconnectncareltd/CCC04</t>
+          <t>https://www.moneycontrol.com/ipo/completesportsmanagementindialtd/CSMIL</t>
         </is>
       </c>
       <c r="R70" t="inlineStr">
         <is>
-          <t>2026-08-10 22:43:12</t>
+          <t>2026-08-25 09:29:52</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Dove Soft Ltd</t>
+          <t>Coreintegra Consulting Services</t>
         </is>
       </c>
       <c r="B71" t="inlineStr"/>
@@ -5712,33 +5740,33 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Sep 30, 2026</t>
+          <t>Sep 23, 2026</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Oct 05, 2026</t>
+          <t>Sep 25, 2026</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Oct 06, 2026</t>
+          <t>Sep 28, 2026</t>
         </is>
       </c>
       <c r="H71" t="inlineStr"/>
       <c r="I71" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>1600</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>104-111</t>
+          <t>74-78</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>133200</t>
+          <t>124800</t>
         </is>
       </c>
       <c r="L71" t="inlineStr"/>
@@ -5748,19 +5776,19 @@
       <c r="P71" t="inlineStr"/>
       <c r="Q71" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/dovesoftltd/DSL04</t>
+          <t>https://www.moneycontrol.com/ipo/coreintegraconsultingservices/CCSL</t>
         </is>
       </c>
       <c r="R71" t="inlineStr">
         <is>
-          <t>2026-09-25 14:20:09</t>
+          <t>2026-09-22 14:03:25</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Farm Peace Ltd</t>
+          <t>Credent Connect N Care Ltd</t>
         </is>
       </c>
       <c r="B72" t="inlineStr"/>
@@ -5772,33 +5800,33 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Sep 01, 2026</t>
+          <t>Aug 13, 2026</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Sep 03, 2026</t>
+          <t>Aug 17, 2026</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Sep 04, 2026</t>
+          <t>Aug 18, 2026</t>
         </is>
       </c>
       <c r="H72" t="inlineStr"/>
       <c r="I72" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>600</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>179-189</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>118000</t>
+          <t>113400</t>
         </is>
       </c>
       <c r="L72" t="inlineStr"/>
@@ -5808,19 +5836,19 @@
       <c r="P72" t="inlineStr"/>
       <c r="Q72" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/farmpeaceltd/FPL02</t>
+          <t>https://www.moneycontrol.com/ipo/credentconnectncareltd/CCC04</t>
         </is>
       </c>
       <c r="R72" t="inlineStr">
         <is>
-          <t>2026-08-27 19:43:03</t>
+          <t>2026-08-10 22:43:12</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Green Asia Impex Ltd</t>
+          <t>Dove Soft Ltd</t>
         </is>
       </c>
       <c r="B73" t="inlineStr"/>
@@ -5832,33 +5860,33 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Sep 24, 2026</t>
+          <t>Sep 30, 2026</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Sep 28, 2026</t>
+          <t>Oct 05, 2026</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Sep 29, 2026</t>
+          <t>Oct 06, 2026</t>
         </is>
       </c>
       <c r="H73" t="inlineStr"/>
       <c r="I73" t="inlineStr">
         <is>
-          <t>1600</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>85-90</t>
+          <t>104-111</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>144000</t>
+          <t>133200</t>
         </is>
       </c>
       <c r="L73" t="inlineStr"/>
@@ -5868,19 +5896,19 @@
       <c r="P73" t="inlineStr"/>
       <c r="Q73" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/greenasiaimpexltd/GAIL01</t>
+          <t>https://www.moneycontrol.com/ipo/dovesoftltd/DSL04</t>
         </is>
       </c>
       <c r="R73" t="inlineStr">
         <is>
-          <t>2026-09-22 14:03:25</t>
+          <t>2026-09-25 14:20:09</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Kheria Autocomp Ltd</t>
+          <t>Farm Peace Ltd</t>
         </is>
       </c>
       <c r="B74" t="inlineStr"/>
@@ -5892,33 +5920,33 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Sep 17, 2026</t>
+          <t>Sep 01, 2026</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Sep 21, 2026</t>
+          <t>Sep 03, 2026</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Sep 22, 2026</t>
+          <t>Sep 04, 2026</t>
         </is>
       </c>
       <c r="H74" t="inlineStr"/>
       <c r="I74" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>96-101</t>
+          <t>59</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>121200</t>
+          <t>118000</t>
         </is>
       </c>
       <c r="L74" t="inlineStr"/>
@@ -5928,19 +5956,19 @@
       <c r="P74" t="inlineStr"/>
       <c r="Q74" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/kheriaautocompltd/KAL05</t>
+          <t>https://www.moneycontrol.com/ipo/farmpeaceltd/FPL02</t>
         </is>
       </c>
       <c r="R74" t="inlineStr">
         <is>
-          <t>2026-09-11 13:34:16</t>
+          <t>2026-08-27 19:43:03</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Mopshop Distribution Ltd</t>
+          <t>Green Asia Impex Ltd</t>
         </is>
       </c>
       <c r="B75" t="inlineStr"/>
@@ -5952,33 +5980,33 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Aug 19, 2026</t>
+          <t>Sep 24, 2026</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Aug 21, 2026</t>
+          <t>Sep 28, 2026</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Aug 24, 2026</t>
+          <t>Sep 29, 2026</t>
         </is>
       </c>
       <c r="H75" t="inlineStr"/>
       <c r="I75" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>1600</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>138</t>
+          <t>85-90</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>138000</t>
+          <t>144000</t>
         </is>
       </c>
       <c r="L75" t="inlineStr"/>
@@ -5988,19 +6016,19 @@
       <c r="P75" t="inlineStr"/>
       <c r="Q75" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/mopshopdistributionltd/MDL03</t>
+          <t>https://www.moneycontrol.com/ipo/greenasiaimpexltd/GAIL01</t>
         </is>
       </c>
       <c r="R75" t="inlineStr">
         <is>
-          <t>2026-08-14 21:36:23</t>
+          <t>2026-09-22 14:03:25</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Paluck Technologies Ltd</t>
+          <t>Kheria Autocomp Ltd</t>
         </is>
       </c>
       <c r="B76" t="inlineStr"/>
@@ -6012,33 +6040,33 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Aug 28, 2026</t>
+          <t>Sep 17, 2026</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Sep 01, 2026</t>
+          <t>Sep 21, 2026</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Sep 02, 2026</t>
+          <t>Sep 22, 2026</t>
         </is>
       </c>
       <c r="H76" t="inlineStr"/>
       <c r="I76" t="inlineStr">
         <is>
-          <t>3000</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>46-48</t>
+          <t>96-101</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>144000</t>
+          <t>121200</t>
         </is>
       </c>
       <c r="L76" t="inlineStr"/>
@@ -6048,19 +6076,19 @@
       <c r="P76" t="inlineStr"/>
       <c r="Q76" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/palucktechnologiesltd/PTL08</t>
+          <t>https://www.moneycontrol.com/ipo/kheriaautocompltd/KAL05</t>
         </is>
       </c>
       <c r="R76" t="inlineStr">
         <is>
-          <t>2026-08-25 09:29:52</t>
+          <t>2026-09-11 13:34:16</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Papadmalji Agro Foods Ltd</t>
+          <t>Mopshop Distribution Ltd</t>
         </is>
       </c>
       <c r="B77" t="inlineStr"/>
@@ -6072,33 +6100,33 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Sep 29, 2026</t>
+          <t>Aug 19, 2026</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Oct 01, 2026</t>
+          <t>Aug 21, 2026</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Oct 05, 2026</t>
+          <t>Aug 24, 2026</t>
         </is>
       </c>
       <c r="H77" t="inlineStr"/>
       <c r="I77" t="inlineStr">
         <is>
-          <t>1600</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>69-72</t>
+          <t>138</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>115200</t>
+          <t>138000</t>
         </is>
       </c>
       <c r="L77" t="inlineStr"/>
@@ -6108,19 +6136,19 @@
       <c r="P77" t="inlineStr"/>
       <c r="Q77" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/papadmaljiagrofoodsltd/PAF</t>
+          <t>https://www.moneycontrol.com/ipo/mopshopdistributionltd/MDL03</t>
         </is>
       </c>
       <c r="R77" t="inlineStr">
         <is>
-          <t>2026-09-25 14:20:09</t>
+          <t>2026-08-14 21:36:23</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Paramount Syntex Ltd</t>
+          <t>Paluck Technologies Ltd</t>
         </is>
       </c>
       <c r="B78" t="inlineStr"/>
@@ -6132,33 +6160,33 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Sep 30, 2026</t>
+          <t>Aug 28, 2026</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Oct 06, 2026</t>
+          <t>Sep 01, 2026</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Oct 07, 2026</t>
+          <t>Sep 02, 2026</t>
         </is>
       </c>
       <c r="H78" t="inlineStr"/>
       <c r="I78" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>3000</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>119-127</t>
+          <t>46-48</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>127000</t>
+          <t>144000</t>
         </is>
       </c>
       <c r="L78" t="inlineStr"/>
@@ -6168,19 +6196,19 @@
       <c r="P78" t="inlineStr"/>
       <c r="Q78" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/paramountsyntexltd/PSL06</t>
+          <t>https://www.moneycontrol.com/ipo/palucktechnologiesltd/PTL08</t>
         </is>
       </c>
       <c r="R78" t="inlineStr">
         <is>
-          <t>2026-09-25 14:20:09</t>
+          <t>2026-08-25 09:29:52</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Peshwa Wheat</t>
+          <t>Papadmalji Agro Foods Ltd</t>
         </is>
       </c>
       <c r="B79" t="inlineStr"/>
@@ -6192,33 +6220,33 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Sep 24, 2026</t>
+          <t>Sep 29, 2026</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Sep 28, 2026</t>
+          <t>Oct 01, 2026</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Sep 29, 2026</t>
+          <t>Oct 05, 2026</t>
         </is>
       </c>
       <c r="H79" t="inlineStr"/>
       <c r="I79" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>1600</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>95-101</t>
+          <t>69-72</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>121200</t>
+          <t>115200</t>
         </is>
       </c>
       <c r="L79" t="inlineStr"/>
@@ -6228,75 +6256,79 @@
       <c r="P79" t="inlineStr"/>
       <c r="Q79" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/peshwawheat/PWL01</t>
+          <t>https://www.moneycontrol.com/ipo/papadmaljiagrofoodsltd/PAF</t>
         </is>
       </c>
       <c r="R79" t="inlineStr">
         <is>
-          <t>2026-09-22 14:03:25</t>
+          <t>2026-09-25 14:20:09</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Purple Style Labs Ltd</t>
+          <t>Paramount Syntex Ltd</t>
         </is>
       </c>
       <c r="B80" t="inlineStr"/>
       <c r="C80" t="inlineStr"/>
-      <c r="D80" s="4" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="D80" s="5" t="inlineStr">
+        <is>
+          <t>Upcoming</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Aug 31, 2026</t>
+          <t>Sep 30, 2026</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Sep 02, 2026</t>
+          <t>Oct 06, 2026</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Sep 03, 2026</t>
+          <t>Oct 07, 2026</t>
         </is>
       </c>
       <c r="H80" t="inlineStr"/>
-      <c r="I80" t="inlineStr"/>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>575</t>
-        </is>
-      </c>
-      <c r="K80" t="inlineStr"/>
+          <t>119-127</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>127000</t>
+        </is>
+      </c>
       <c r="L80" t="inlineStr"/>
       <c r="M80" t="inlineStr"/>
-      <c r="N80" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="N80" t="inlineStr"/>
       <c r="O80" t="inlineStr"/>
       <c r="P80" t="inlineStr"/>
       <c r="Q80" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/purplestylelabsltd/PSL05</t>
+          <t>https://www.moneycontrol.com/ipo/paramountsyntexltd/PSL06</t>
         </is>
       </c>
       <c r="R80" t="inlineStr">
         <is>
-          <t>2026-09-02 13:25:30</t>
+          <t>2026-09-25 14:20:09</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Q&amp;T Foods Ltd</t>
+          <t>Peshwa Wheat</t>
         </is>
       </c>
       <c r="B81" t="inlineStr"/>
@@ -6308,17 +6340,17 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Aug 12, 2026</t>
+          <t>Sep 24, 2026</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Aug 14, 2026</t>
+          <t>Sep 28, 2026</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Aug 17, 2026</t>
+          <t>Sep 29, 2026</t>
         </is>
       </c>
       <c r="H81" t="inlineStr"/>
@@ -6329,12 +6361,12 @@
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>115</t>
+          <t>95-101</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>138000</t>
+          <t>121200</t>
         </is>
       </c>
       <c r="L81" t="inlineStr"/>
@@ -6344,79 +6376,75 @@
       <c r="P81" t="inlineStr"/>
       <c r="Q81" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/qtfoodsltd/QFL</t>
+          <t>https://www.moneycontrol.com/ipo/peshwawheat/PWL01</t>
         </is>
       </c>
       <c r="R81" t="inlineStr">
         <is>
-          <t>2026-08-10 10:24:29</t>
+          <t>2026-09-22 14:03:25</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Ravita Engineering Services Ltd</t>
+          <t>Purple Style Labs Ltd</t>
         </is>
       </c>
       <c r="B82" t="inlineStr"/>
       <c r="C82" t="inlineStr"/>
-      <c r="D82" s="5" t="inlineStr">
-        <is>
-          <t>Upcoming</t>
+      <c r="D82" s="4" t="inlineStr">
+        <is>
+          <t>Open</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Oct 13, 2026</t>
+          <t>Aug 31, 2026</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Oct 15, 2026</t>
+          <t>Sep 02, 2026</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Oct 16, 2026</t>
+          <t>Sep 03, 2026</t>
         </is>
       </c>
       <c r="H82" t="inlineStr"/>
-      <c r="I82" t="inlineStr">
-        <is>
-          <t>1200</t>
-        </is>
-      </c>
+      <c r="I82" t="inlineStr"/>
       <c r="J82" t="inlineStr">
         <is>
-          <t>105-112</t>
-        </is>
-      </c>
-      <c r="K82" t="inlineStr">
-        <is>
-          <t>134400</t>
-        </is>
-      </c>
+          <t>575</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr"/>
       <c r="L82" t="inlineStr"/>
       <c r="M82" t="inlineStr"/>
-      <c r="N82" t="inlineStr"/>
+      <c r="N82" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="O82" t="inlineStr"/>
       <c r="P82" t="inlineStr"/>
       <c r="Q82" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/ravitaengineeringservicesltd/RESL</t>
+          <t>https://www.moneycontrol.com/ipo/purplestylelabsltd/PSL05</t>
         </is>
       </c>
       <c r="R82" t="inlineStr">
         <is>
-          <t>2026-10-08 16:06:11</t>
+          <t>2026-09-02 13:25:30</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Shanti Inorganics Ltd</t>
+          <t>Q&amp;T Foods Ltd</t>
         </is>
       </c>
       <c r="B83" t="inlineStr"/>
@@ -6428,33 +6456,33 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Aug 31, 2026</t>
+          <t>Aug 12, 2026</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Sep 02, 2026</t>
+          <t>Aug 14, 2026</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Sep 03, 2026</t>
+          <t>Aug 17, 2026</t>
         </is>
       </c>
       <c r="H83" t="inlineStr"/>
       <c r="I83" t="inlineStr">
         <is>
-          <t>1600</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>79-83</t>
+          <t>115</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>132800</t>
+          <t>138000</t>
         </is>
       </c>
       <c r="L83" t="inlineStr"/>
@@ -6464,19 +6492,19 @@
       <c r="P83" t="inlineStr"/>
       <c r="Q83" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/shantiinorganicsltd/SIL34</t>
+          <t>https://www.moneycontrol.com/ipo/qtfoodsltd/QFL</t>
         </is>
       </c>
       <c r="R83" t="inlineStr">
         <is>
-          <t>2026-08-25 09:29:52</t>
+          <t>2026-08-10 10:24:29</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Technocrats Plasma Systems Ltd</t>
+          <t>Ravita Engineering Services Ltd</t>
         </is>
       </c>
       <c r="B84" t="inlineStr"/>
@@ -6488,33 +6516,33 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Aug 14, 2026</t>
+          <t>Oct 13, 2026</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Aug 18, 2026</t>
+          <t>Oct 15, 2026</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Aug 19, 2026</t>
+          <t>Oct 16, 2026</t>
         </is>
       </c>
       <c r="H84" t="inlineStr"/>
       <c r="I84" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>125-132</t>
+          <t>105-112</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>132000</t>
+          <t>134400</t>
         </is>
       </c>
       <c r="L84" t="inlineStr"/>
@@ -6524,19 +6552,19 @@
       <c r="P84" t="inlineStr"/>
       <c r="Q84" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/technocratsplasmasystemsltd/TPSL</t>
+          <t>https://www.moneycontrol.com/ipo/ravitaengineeringservicesltd/RESL</t>
         </is>
       </c>
       <c r="R84" t="inlineStr">
         <is>
-          <t>2026-08-11 21:41:02</t>
+          <t>2026-10-08 16:06:11</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Unitec Fibres Ltd</t>
+          <t>Shanti Inorganics Ltd</t>
         </is>
       </c>
       <c r="B85" t="inlineStr"/>
@@ -6548,17 +6576,17 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Sep 23, 2026</t>
+          <t>Aug 31, 2026</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Sep 25, 2026</t>
+          <t>Sep 02, 2026</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Sep 28, 2026</t>
+          <t>Sep 03, 2026</t>
         </is>
       </c>
       <c r="H85" t="inlineStr"/>
@@ -6569,12 +6597,12 @@
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>83-88</t>
+          <t>79-83</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>140800</t>
+          <t>132800</t>
         </is>
       </c>
       <c r="L85" t="inlineStr"/>
@@ -6584,19 +6612,19 @@
       <c r="P85" t="inlineStr"/>
       <c r="Q85" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/unitecfibresltd/UFL03</t>
+          <t>https://www.moneycontrol.com/ipo/shantiinorganicsltd/SIL34</t>
         </is>
       </c>
       <c r="R85" t="inlineStr">
         <is>
-          <t>2026-09-18 23:59:33</t>
+          <t>2026-08-25 09:29:52</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>VANS Electroengineerings Ltd</t>
+          <t>Technocrats Plasma Systems Ltd</t>
         </is>
       </c>
       <c r="B86" t="inlineStr"/>
@@ -6608,33 +6636,33 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Sep 29, 2026</t>
+          <t>Aug 14, 2026</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Oct 01, 2026</t>
+          <t>Aug 18, 2026</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Oct 05, 2026</t>
+          <t>Aug 19, 2026</t>
         </is>
       </c>
       <c r="H86" t="inlineStr"/>
       <c r="I86" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>112-118</t>
+          <t>125-132</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>141600</t>
+          <t>132000</t>
         </is>
       </c>
       <c r="L86" t="inlineStr"/>
@@ -6644,19 +6672,19 @@
       <c r="P86" t="inlineStr"/>
       <c r="Q86" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/vanselectroengineeringsltd/VEL03</t>
+          <t>https://www.moneycontrol.com/ipo/technocratsplasmasystemsltd/TPSL</t>
         </is>
       </c>
       <c r="R86" t="inlineStr">
         <is>
-          <t>2026-09-25 14:20:09</t>
+          <t>2026-08-11 21:41:02</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Vaibhav Vyapaar Ltd</t>
+          <t>Unitec Fibres Ltd</t>
         </is>
       </c>
       <c r="B87" t="inlineStr"/>
@@ -6668,33 +6696,33 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Oct 13, 2026</t>
+          <t>Sep 23, 2026</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Oct 15, 2026</t>
+          <t>Sep 25, 2026</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Oct 16, 2026</t>
+          <t>Sep 28, 2026</t>
         </is>
       </c>
       <c r="H87" t="inlineStr"/>
       <c r="I87" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>1600</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>50-52</t>
+          <t>83-88</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>104000</t>
+          <t>140800</t>
         </is>
       </c>
       <c r="L87" t="inlineStr"/>
@@ -6704,19 +6732,19 @@
       <c r="P87" t="inlineStr"/>
       <c r="Q87" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/vaibhavvyapaarltd/VVL01</t>
+          <t>https://www.moneycontrol.com/ipo/unitecfibresltd/UFL03</t>
         </is>
       </c>
       <c r="R87" t="inlineStr">
         <is>
-          <t>2026-10-08 16:06:11</t>
+          <t>2026-09-18 23:59:33</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Vama Wovenfab Ltd</t>
+          <t>VANS Electroengineerings Ltd</t>
         </is>
       </c>
       <c r="B88" t="inlineStr"/>
@@ -6728,33 +6756,33 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Sep 15, 2026</t>
+          <t>Sep 29, 2026</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Sep 17, 2026</t>
+          <t>Oct 01, 2026</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Sep 18, 2026</t>
+          <t>Oct 05, 2026</t>
         </is>
       </c>
       <c r="H88" t="inlineStr"/>
       <c r="I88" t="inlineStr">
         <is>
-          <t>400</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>324-341</t>
+          <t>112-118</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>136400</t>
+          <t>141600</t>
         </is>
       </c>
       <c r="L88" t="inlineStr"/>
@@ -6764,17 +6792,137 @@
       <c r="P88" t="inlineStr"/>
       <c r="Q88" t="inlineStr">
         <is>
+          <t>https://www.moneycontrol.com/ipo/vanselectroengineeringsltd/VEL03</t>
+        </is>
+      </c>
+      <c r="R88" t="inlineStr">
+        <is>
+          <t>2026-09-25 14:20:09</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Vaibhav Vyapaar Ltd</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr"/>
+      <c r="C89" t="inlineStr"/>
+      <c r="D89" s="5" t="inlineStr">
+        <is>
+          <t>Upcoming</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>Oct 13, 2026</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>Oct 15, 2026</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>Oct 16, 2026</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr"/>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>50-52</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>104000</t>
+        </is>
+      </c>
+      <c r="L89" t="inlineStr"/>
+      <c r="M89" t="inlineStr"/>
+      <c r="N89" t="inlineStr"/>
+      <c r="O89" t="inlineStr"/>
+      <c r="P89" t="inlineStr"/>
+      <c r="Q89" t="inlineStr">
+        <is>
+          <t>https://www.moneycontrol.com/ipo/vaibhavvyapaarltd/VVL01</t>
+        </is>
+      </c>
+      <c r="R89" t="inlineStr">
+        <is>
+          <t>2026-10-08 16:06:11</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Vama Wovenfab Ltd</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr"/>
+      <c r="C90" t="inlineStr"/>
+      <c r="D90" s="5" t="inlineStr">
+        <is>
+          <t>Upcoming</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>Sep 15, 2026</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>Sep 17, 2026</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>Sep 18, 2026</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr"/>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>400</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>324-341</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>136400</t>
+        </is>
+      </c>
+      <c r="L90" t="inlineStr"/>
+      <c r="M90" t="inlineStr"/>
+      <c r="N90" t="inlineStr"/>
+      <c r="O90" t="inlineStr"/>
+      <c r="P90" t="inlineStr"/>
+      <c r="Q90" t="inlineStr">
+        <is>
           <t>https://www.moneycontrol.com/ipo/vamawovenfabltd/VWL01</t>
         </is>
       </c>
-      <c r="R88" t="inlineStr">
+      <c r="R90" t="inlineStr">
         <is>
           <t>2026-09-11 13:34:16</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:R88"/>
+  <autoFilter ref="A1:R90"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/mainboard_ipos.xlsx
+++ b/data/mainboard_ipos.xlsx
@@ -5188,12 +5188,12 @@
       <c r="P62" t="inlineStr"/>
       <c r="Q62" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/hdfireprotectltd/HFP</t>
+          <t>https://www.moneycontrol.com/ipo/hdfireprotect/HFP</t>
         </is>
       </c>
       <c r="R62" t="inlineStr">
         <is>
-          <t>2026-10-16 13:41:40</t>
+          <t>2026-10-17 13:18:36</t>
         </is>
       </c>
     </row>
@@ -5205,9 +5205,9 @@
       </c>
       <c r="B63" t="inlineStr"/>
       <c r="C63" t="inlineStr"/>
-      <c r="D63" s="4" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="D63" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -5249,19 +5249,19 @@
       <c r="M63" t="inlineStr"/>
       <c r="N63" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O63" t="inlineStr"/>
       <c r="P63" t="inlineStr"/>
       <c r="Q63" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/fusioncxltd/FCL02</t>
+          <t>https://www.moneycontrol.com/ipo/fusioncx/FCL02</t>
         </is>
       </c>
       <c r="R63" t="inlineStr">
         <is>
-          <t>2026-10-16 13:41:40</t>
+          <t>2026-10-17 13:18:36</t>
         </is>
       </c>
     </row>
@@ -5317,19 +5317,19 @@
       <c r="M64" t="inlineStr"/>
       <c r="N64" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="O64" t="inlineStr"/>
       <c r="P64" t="inlineStr"/>
       <c r="Q64" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/bonfigliolitransmissionsltd/BTL04</t>
+          <t>https://www.moneycontrol.com/ipo/bonfigliolitransmissions/BTL04</t>
         </is>
       </c>
       <c r="R64" t="inlineStr">
         <is>
-          <t>2026-10-16 13:41:40</t>
+          <t>2026-10-17 13:18:36</t>
         </is>
       </c>
     </row>
@@ -5392,12 +5392,12 @@
       <c r="P65" t="inlineStr"/>
       <c r="Q65" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/sahajanandmedicaltechnologiesltd/SMTL</t>
+          <t>https://www.moneycontrol.com/ipo/sahajanandmedicaltechnologies/SMTL</t>
         </is>
       </c>
       <c r="R65" t="inlineStr">
         <is>
-          <t>2026-10-16 13:41:40</t>
+          <t>2026-10-17 13:18:36</t>
         </is>
       </c>
     </row>
@@ -5453,19 +5453,19 @@
       <c r="M66" t="inlineStr"/>
       <c r="N66" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="O66" t="inlineStr"/>
       <c r="P66" t="inlineStr"/>
       <c r="Q66" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/tonboimagingindialtd/TIIL</t>
+          <t>https://www.moneycontrol.com/ipo/tonboimagingindia/TIIL</t>
         </is>
       </c>
       <c r="R66" t="inlineStr">
         <is>
-          <t>2026-10-16 13:41:40</t>
+          <t>2026-10-17 13:18:36</t>
         </is>
       </c>
     </row>
@@ -5528,12 +5528,12 @@
       <c r="P67" t="inlineStr"/>
       <c r="Q67" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/zetwerkmanufacturingbusinessesltd/ZMBL</t>
+          <t>https://www.moneycontrol.com/ipo/zetwerkmanufacturingbusinesses/ZMBL</t>
         </is>
       </c>
       <c r="R67" t="inlineStr">
         <is>
-          <t>2026-10-16 13:41:40</t>
+          <t>2026-10-17 13:18:36</t>
         </is>
       </c>
     </row>
@@ -5592,12 +5592,12 @@
       <c r="P68" t="inlineStr"/>
       <c r="Q68" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/jioplatformsltd/JPL</t>
+          <t>https://www.moneycontrol.com/ipo/jioplatforms/JPL</t>
         </is>
       </c>
       <c r="R68" t="inlineStr">
         <is>
-          <t>2026-10-16 13:41:40</t>
+          <t>2026-10-17 13:18:36</t>
         </is>
       </c>
     </row>
@@ -5656,12 +5656,12 @@
       <c r="P69" t="inlineStr"/>
       <c r="Q69" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/parashealthcareltd/PHL01</t>
+          <t>https://www.moneycontrol.com/ipo/parashealthcare/PHL01</t>
         </is>
       </c>
       <c r="R69" t="inlineStr">
         <is>
-          <t>2026-10-16 13:41:40</t>
+          <t>2026-10-17 13:18:36</t>
         </is>
       </c>
     </row>

--- a/data/mainboard_ipos.xlsx
+++ b/data/mainboard_ipos.xlsx
@@ -5193,7 +5193,7 @@
       </c>
       <c r="R62" t="inlineStr">
         <is>
-          <t>2026-10-17 13:18:36</t>
+          <t>2026-10-17 23:21:42</t>
         </is>
       </c>
     </row>
@@ -5249,7 +5249,7 @@
       <c r="M63" t="inlineStr"/>
       <c r="N63" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="O63" t="inlineStr"/>
@@ -5261,7 +5261,7 @@
       </c>
       <c r="R63" t="inlineStr">
         <is>
-          <t>2026-10-17 13:18:36</t>
+          <t>2026-10-17 23:21:42</t>
         </is>
       </c>
     </row>
@@ -5329,7 +5329,7 @@
       </c>
       <c r="R64" t="inlineStr">
         <is>
-          <t>2026-10-17 13:18:36</t>
+          <t>2026-10-17 23:21:42</t>
         </is>
       </c>
     </row>
@@ -5385,7 +5385,7 @@
       <c r="M65" t="inlineStr"/>
       <c r="N65" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="O65" t="inlineStr"/>
@@ -5397,7 +5397,7 @@
       </c>
       <c r="R65" t="inlineStr">
         <is>
-          <t>2026-10-17 13:18:36</t>
+          <t>2026-10-17 23:21:42</t>
         </is>
       </c>
     </row>
@@ -5453,7 +5453,7 @@
       <c r="M66" t="inlineStr"/>
       <c r="N66" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8</t>
         </is>
       </c>
       <c r="O66" t="inlineStr"/>
@@ -5465,7 +5465,7 @@
       </c>
       <c r="R66" t="inlineStr">
         <is>
-          <t>2026-10-17 13:18:36</t>
+          <t>2026-10-17 23:21:42</t>
         </is>
       </c>
     </row>
@@ -5533,7 +5533,7 @@
       </c>
       <c r="R67" t="inlineStr">
         <is>
-          <t>2026-10-17 13:18:36</t>
+          <t>2026-10-17 23:21:42</t>
         </is>
       </c>
     </row>
@@ -5597,7 +5597,7 @@
       </c>
       <c r="R68" t="inlineStr">
         <is>
-          <t>2026-10-17 13:18:36</t>
+          <t>2026-10-17 23:21:42</t>
         </is>
       </c>
     </row>
@@ -5661,7 +5661,7 @@
       </c>
       <c r="R69" t="inlineStr">
         <is>
-          <t>2026-10-17 13:18:36</t>
+          <t>2026-10-17 23:21:42</t>
         </is>
       </c>
     </row>

--- a/data/mainboard_ipos.xlsx
+++ b/data/mainboard_ipos.xlsx
@@ -5193,7 +5193,7 @@
       </c>
       <c r="R62" t="inlineStr">
         <is>
-          <t>2026-10-17 23:21:42</t>
+          <t>2026-10-18 13:32:28</t>
         </is>
       </c>
     </row>
@@ -5261,7 +5261,7 @@
       </c>
       <c r="R63" t="inlineStr">
         <is>
-          <t>2026-10-17 23:21:42</t>
+          <t>2026-10-18 13:32:28</t>
         </is>
       </c>
     </row>
@@ -5329,7 +5329,7 @@
       </c>
       <c r="R64" t="inlineStr">
         <is>
-          <t>2026-10-17 23:21:42</t>
+          <t>2026-10-18 13:32:28</t>
         </is>
       </c>
     </row>
@@ -5397,7 +5397,7 @@
       </c>
       <c r="R65" t="inlineStr">
         <is>
-          <t>2026-10-17 23:21:42</t>
+          <t>2026-10-18 13:32:28</t>
         </is>
       </c>
     </row>
@@ -5465,7 +5465,7 @@
       </c>
       <c r="R66" t="inlineStr">
         <is>
-          <t>2026-10-17 23:21:42</t>
+          <t>2026-10-18 13:32:28</t>
         </is>
       </c>
     </row>
@@ -5533,7 +5533,7 @@
       </c>
       <c r="R67" t="inlineStr">
         <is>
-          <t>2026-10-17 23:21:42</t>
+          <t>2026-10-18 13:32:28</t>
         </is>
       </c>
     </row>
@@ -5597,7 +5597,7 @@
       </c>
       <c r="R68" t="inlineStr">
         <is>
-          <t>2026-10-17 23:21:42</t>
+          <t>2026-10-18 13:32:28</t>
         </is>
       </c>
     </row>
@@ -5661,7 +5661,7 @@
       </c>
       <c r="R69" t="inlineStr">
         <is>
-          <t>2026-10-17 23:21:42</t>
+          <t>2026-10-18 13:32:28</t>
         </is>
       </c>
     </row>

--- a/data/mainboard_ipos.xlsx
+++ b/data/mainboard_ipos.xlsx
@@ -5193,7 +5193,7 @@
       </c>
       <c r="R62" t="inlineStr">
         <is>
-          <t>2026-10-18 13:32:28</t>
+          <t>2026-10-18 23:36:23</t>
         </is>
       </c>
     </row>
@@ -5261,7 +5261,7 @@
       </c>
       <c r="R63" t="inlineStr">
         <is>
-          <t>2026-10-18 13:32:28</t>
+          <t>2026-10-18 23:36:23</t>
         </is>
       </c>
     </row>
@@ -5329,7 +5329,7 @@
       </c>
       <c r="R64" t="inlineStr">
         <is>
-          <t>2026-10-18 13:32:28</t>
+          <t>2026-10-18 23:36:23</t>
         </is>
       </c>
     </row>
@@ -5397,7 +5397,7 @@
       </c>
       <c r="R65" t="inlineStr">
         <is>
-          <t>2026-10-18 13:32:28</t>
+          <t>2026-10-18 23:36:23</t>
         </is>
       </c>
     </row>
@@ -5465,7 +5465,7 @@
       </c>
       <c r="R66" t="inlineStr">
         <is>
-          <t>2026-10-18 13:32:28</t>
+          <t>2026-10-18 23:36:23</t>
         </is>
       </c>
     </row>
@@ -5533,7 +5533,7 @@
       </c>
       <c r="R67" t="inlineStr">
         <is>
-          <t>2026-10-18 13:32:28</t>
+          <t>2026-10-18 23:36:23</t>
         </is>
       </c>
     </row>
@@ -5597,7 +5597,7 @@
       </c>
       <c r="R68" t="inlineStr">
         <is>
-          <t>2026-10-18 13:32:28</t>
+          <t>2026-10-18 23:36:23</t>
         </is>
       </c>
     </row>
@@ -5661,7 +5661,7 @@
       </c>
       <c r="R69" t="inlineStr">
         <is>
-          <t>2026-10-18 13:32:28</t>
+          <t>2026-10-18 23:36:23</t>
         </is>
       </c>
     </row>

--- a/data/mainboard_ipos.xlsx
+++ b/data/mainboard_ipos.xlsx
@@ -5193,7 +5193,7 @@
       </c>
       <c r="R62" t="inlineStr">
         <is>
-          <t>2026-10-18 23:36:23</t>
+          <t>2026-10-19 14:23:34</t>
         </is>
       </c>
     </row>
@@ -5261,7 +5261,7 @@
       </c>
       <c r="R63" t="inlineStr">
         <is>
-          <t>2026-10-18 23:36:23</t>
+          <t>2026-10-19 14:23:34</t>
         </is>
       </c>
     </row>
@@ -5329,7 +5329,7 @@
       </c>
       <c r="R64" t="inlineStr">
         <is>
-          <t>2026-10-18 23:36:23</t>
+          <t>2026-10-19 14:23:34</t>
         </is>
       </c>
     </row>
@@ -5397,7 +5397,7 @@
       </c>
       <c r="R65" t="inlineStr">
         <is>
-          <t>2026-10-18 23:36:23</t>
+          <t>2026-10-19 14:23:34</t>
         </is>
       </c>
     </row>
@@ -5465,7 +5465,7 @@
       </c>
       <c r="R66" t="inlineStr">
         <is>
-          <t>2026-10-18 23:36:23</t>
+          <t>2026-10-19 14:23:34</t>
         </is>
       </c>
     </row>
@@ -5533,7 +5533,7 @@
       </c>
       <c r="R67" t="inlineStr">
         <is>
-          <t>2026-10-18 23:36:23</t>
+          <t>2026-10-19 14:23:34</t>
         </is>
       </c>
     </row>
@@ -5597,7 +5597,7 @@
       </c>
       <c r="R68" t="inlineStr">
         <is>
-          <t>2026-10-18 23:36:23</t>
+          <t>2026-10-19 14:23:34</t>
         </is>
       </c>
     </row>
@@ -5661,7 +5661,7 @@
       </c>
       <c r="R69" t="inlineStr">
         <is>
-          <t>2026-10-18 23:36:23</t>
+          <t>2026-10-19 14:23:34</t>
         </is>
       </c>
     </row>

--- a/data/mainboard_ipos.xlsx
+++ b/data/mainboard_ipos.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Mainboard IPOs" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Mainboard IPOs'!$A$1:$R$90</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Mainboard IPOs'!$A$1:$R$92</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -449,7 +449,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R90"/>
+  <dimension ref="A1:R92"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -5193,7 +5193,7 @@
       </c>
       <c r="R62" t="inlineStr">
         <is>
-          <t>2026-10-19 14:23:34</t>
+          <t>2026-10-20 14:03:23</t>
         </is>
       </c>
     </row>
@@ -5261,7 +5261,7 @@
       </c>
       <c r="R63" t="inlineStr">
         <is>
-          <t>2026-10-19 14:23:34</t>
+          <t>2026-10-20 14:03:23</t>
         </is>
       </c>
     </row>
@@ -5273,9 +5273,9 @@
       </c>
       <c r="B64" t="inlineStr"/>
       <c r="C64" t="inlineStr"/>
-      <c r="D64" s="4" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="D64" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -5317,7 +5317,7 @@
       <c r="M64" t="inlineStr"/>
       <c r="N64" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>11</t>
         </is>
       </c>
       <c r="O64" t="inlineStr"/>
@@ -5329,7 +5329,7 @@
       </c>
       <c r="R64" t="inlineStr">
         <is>
-          <t>2026-10-19 14:23:34</t>
+          <t>2026-10-20 14:03:23</t>
         </is>
       </c>
     </row>
@@ -5341,9 +5341,9 @@
       </c>
       <c r="B65" t="inlineStr"/>
       <c r="C65" t="inlineStr"/>
-      <c r="D65" s="4" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="D65" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -5385,7 +5385,7 @@
       <c r="M65" t="inlineStr"/>
       <c r="N65" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O65" t="inlineStr"/>
@@ -5397,7 +5397,7 @@
       </c>
       <c r="R65" t="inlineStr">
         <is>
-          <t>2026-10-19 14:23:34</t>
+          <t>2026-10-20 14:03:23</t>
         </is>
       </c>
     </row>
@@ -5597,7 +5597,7 @@
       </c>
       <c r="R68" t="inlineStr">
         <is>
-          <t>2026-10-19 14:23:34</t>
+          <t>2026-10-20 14:03:23</t>
         </is>
       </c>
     </row>
@@ -5661,14 +5661,14 @@
       </c>
       <c r="R69" t="inlineStr">
         <is>
-          <t>2026-10-19 14:23:34</t>
+          <t>2026-10-20 14:03:23</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Complete Sports and Management India Ltd</t>
+          <t>BLS Polymers Ltd</t>
         </is>
       </c>
       <c r="B70" t="inlineStr"/>
@@ -5680,35 +5680,27 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Aug 28, 2026</t>
+          <t>Oct 27, 2026</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Sep 01, 2026</t>
+          <t>Oct 29, 2026</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Sep 02, 2026</t>
+          <t>Oct 30, 2026</t>
         </is>
       </c>
       <c r="H70" t="inlineStr"/>
-      <c r="I70" t="inlineStr">
-        <is>
-          <t>1000</t>
-        </is>
-      </c>
+      <c r="I70" t="inlineStr"/>
       <c r="J70" t="inlineStr">
         <is>
-          <t>128-135</t>
-        </is>
-      </c>
-      <c r="K70" t="inlineStr">
-        <is>
-          <t>135000</t>
-        </is>
-      </c>
+          <t>142-150</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr"/>
       <c r="L70" t="inlineStr"/>
       <c r="M70" t="inlineStr"/>
       <c r="N70" t="inlineStr"/>
@@ -5716,19 +5708,19 @@
       <c r="P70" t="inlineStr"/>
       <c r="Q70" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/completesportsmanagementindialtd/CSMIL</t>
+          <t>https://www.moneycontrol.com/ipo/blspolymersltd/BPL11</t>
         </is>
       </c>
       <c r="R70" t="inlineStr">
         <is>
-          <t>2026-08-25 09:29:52</t>
+          <t>2026-10-20 14:03:23</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Coreintegra Consulting Services</t>
+          <t>Complete Sports and Management India Ltd</t>
         </is>
       </c>
       <c r="B71" t="inlineStr"/>
@@ -5740,33 +5732,33 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Sep 23, 2026</t>
+          <t>Aug 28, 2026</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Sep 25, 2026</t>
+          <t>Sep 01, 2026</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Sep 28, 2026</t>
+          <t>Sep 02, 2026</t>
         </is>
       </c>
       <c r="H71" t="inlineStr"/>
       <c r="I71" t="inlineStr">
         <is>
-          <t>1600</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>74-78</t>
+          <t>128-135</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>124800</t>
+          <t>135000</t>
         </is>
       </c>
       <c r="L71" t="inlineStr"/>
@@ -5776,19 +5768,19 @@
       <c r="P71" t="inlineStr"/>
       <c r="Q71" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/coreintegraconsultingservices/CCSL</t>
+          <t>https://www.moneycontrol.com/ipo/completesportsmanagementindialtd/CSMIL</t>
         </is>
       </c>
       <c r="R71" t="inlineStr">
         <is>
-          <t>2026-09-22 14:03:25</t>
+          <t>2026-08-25 09:29:52</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Credent Connect N Care Ltd</t>
+          <t>Core4 Engineers Ltd</t>
         </is>
       </c>
       <c r="B72" t="inlineStr"/>
@@ -5800,35 +5792,27 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Aug 13, 2026</t>
+          <t>Oct 23, 2026</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Aug 17, 2026</t>
+          <t>Oct 27, 2026</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Aug 18, 2026</t>
+          <t>Oct 28, 2026</t>
         </is>
       </c>
       <c r="H72" t="inlineStr"/>
-      <c r="I72" t="inlineStr">
-        <is>
-          <t>600</t>
-        </is>
-      </c>
+      <c r="I72" t="inlineStr"/>
       <c r="J72" t="inlineStr">
         <is>
-          <t>179-189</t>
-        </is>
-      </c>
-      <c r="K72" t="inlineStr">
-        <is>
-          <t>113400</t>
-        </is>
-      </c>
+          <t>88-93</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr"/>
       <c r="L72" t="inlineStr"/>
       <c r="M72" t="inlineStr"/>
       <c r="N72" t="inlineStr"/>
@@ -5836,19 +5820,19 @@
       <c r="P72" t="inlineStr"/>
       <c r="Q72" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/credentconnectncareltd/CCC04</t>
+          <t>https://www.moneycontrol.com/ipo/core4engineersltd/CEL05</t>
         </is>
       </c>
       <c r="R72" t="inlineStr">
         <is>
-          <t>2026-08-10 22:43:12</t>
+          <t>2026-10-20 14:03:23</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Dove Soft Ltd</t>
+          <t>Coreintegra Consulting Services</t>
         </is>
       </c>
       <c r="B73" t="inlineStr"/>
@@ -5860,33 +5844,33 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Sep 30, 2026</t>
+          <t>Sep 23, 2026</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Oct 05, 2026</t>
+          <t>Sep 25, 2026</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Oct 06, 2026</t>
+          <t>Sep 28, 2026</t>
         </is>
       </c>
       <c r="H73" t="inlineStr"/>
       <c r="I73" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>1600</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>104-111</t>
+          <t>74-78</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>133200</t>
+          <t>124800</t>
         </is>
       </c>
       <c r="L73" t="inlineStr"/>
@@ -5896,19 +5880,19 @@
       <c r="P73" t="inlineStr"/>
       <c r="Q73" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/dovesoftltd/DSL04</t>
+          <t>https://www.moneycontrol.com/ipo/coreintegraconsultingservices/CCSL</t>
         </is>
       </c>
       <c r="R73" t="inlineStr">
         <is>
-          <t>2026-09-25 14:20:09</t>
+          <t>2026-09-22 14:03:25</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Farm Peace Ltd</t>
+          <t>Credent Connect N Care Ltd</t>
         </is>
       </c>
       <c r="B74" t="inlineStr"/>
@@ -5920,33 +5904,33 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Sep 01, 2026</t>
+          <t>Aug 13, 2026</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Sep 03, 2026</t>
+          <t>Aug 17, 2026</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Sep 04, 2026</t>
+          <t>Aug 18, 2026</t>
         </is>
       </c>
       <c r="H74" t="inlineStr"/>
       <c r="I74" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>600</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>179-189</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>118000</t>
+          <t>113400</t>
         </is>
       </c>
       <c r="L74" t="inlineStr"/>
@@ -5956,19 +5940,19 @@
       <c r="P74" t="inlineStr"/>
       <c r="Q74" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/farmpeaceltd/FPL02</t>
+          <t>https://www.moneycontrol.com/ipo/credentconnectncareltd/CCC04</t>
         </is>
       </c>
       <c r="R74" t="inlineStr">
         <is>
-          <t>2026-08-27 19:43:03</t>
+          <t>2026-08-10 22:43:12</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Green Asia Impex Ltd</t>
+          <t>Dove Soft Ltd</t>
         </is>
       </c>
       <c r="B75" t="inlineStr"/>
@@ -5980,33 +5964,33 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Sep 24, 2026</t>
+          <t>Sep 30, 2026</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Sep 28, 2026</t>
+          <t>Oct 05, 2026</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Sep 29, 2026</t>
+          <t>Oct 06, 2026</t>
         </is>
       </c>
       <c r="H75" t="inlineStr"/>
       <c r="I75" t="inlineStr">
         <is>
-          <t>1600</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>85-90</t>
+          <t>104-111</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>144000</t>
+          <t>133200</t>
         </is>
       </c>
       <c r="L75" t="inlineStr"/>
@@ -6016,19 +6000,19 @@
       <c r="P75" t="inlineStr"/>
       <c r="Q75" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/greenasiaimpexltd/GAIL01</t>
+          <t>https://www.moneycontrol.com/ipo/dovesoftltd/DSL04</t>
         </is>
       </c>
       <c r="R75" t="inlineStr">
         <is>
-          <t>2026-09-22 14:03:25</t>
+          <t>2026-09-25 14:20:09</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Kheria Autocomp Ltd</t>
+          <t>Farm Peace Ltd</t>
         </is>
       </c>
       <c r="B76" t="inlineStr"/>
@@ -6040,33 +6024,33 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Sep 17, 2026</t>
+          <t>Sep 01, 2026</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Sep 21, 2026</t>
+          <t>Sep 03, 2026</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Sep 22, 2026</t>
+          <t>Sep 04, 2026</t>
         </is>
       </c>
       <c r="H76" t="inlineStr"/>
       <c r="I76" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>96-101</t>
+          <t>59</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>121200</t>
+          <t>118000</t>
         </is>
       </c>
       <c r="L76" t="inlineStr"/>
@@ -6076,19 +6060,19 @@
       <c r="P76" t="inlineStr"/>
       <c r="Q76" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/kheriaautocompltd/KAL05</t>
+          <t>https://www.moneycontrol.com/ipo/farmpeaceltd/FPL02</t>
         </is>
       </c>
       <c r="R76" t="inlineStr">
         <is>
-          <t>2026-09-11 13:34:16</t>
+          <t>2026-08-27 19:43:03</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Mopshop Distribution Ltd</t>
+          <t>Green Asia Impex Ltd</t>
         </is>
       </c>
       <c r="B77" t="inlineStr"/>
@@ -6100,33 +6084,33 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Aug 19, 2026</t>
+          <t>Sep 24, 2026</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Aug 21, 2026</t>
+          <t>Sep 28, 2026</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Aug 24, 2026</t>
+          <t>Sep 29, 2026</t>
         </is>
       </c>
       <c r="H77" t="inlineStr"/>
       <c r="I77" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>1600</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>138</t>
+          <t>85-90</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>138000</t>
+          <t>144000</t>
         </is>
       </c>
       <c r="L77" t="inlineStr"/>
@@ -6136,19 +6120,19 @@
       <c r="P77" t="inlineStr"/>
       <c r="Q77" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/mopshopdistributionltd/MDL03</t>
+          <t>https://www.moneycontrol.com/ipo/greenasiaimpexltd/GAIL01</t>
         </is>
       </c>
       <c r="R77" t="inlineStr">
         <is>
-          <t>2026-08-14 21:36:23</t>
+          <t>2026-09-22 14:03:25</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Paluck Technologies Ltd</t>
+          <t>Kheria Autocomp Ltd</t>
         </is>
       </c>
       <c r="B78" t="inlineStr"/>
@@ -6160,33 +6144,33 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Aug 28, 2026</t>
+          <t>Sep 17, 2026</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Sep 01, 2026</t>
+          <t>Sep 21, 2026</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Sep 02, 2026</t>
+          <t>Sep 22, 2026</t>
         </is>
       </c>
       <c r="H78" t="inlineStr"/>
       <c r="I78" t="inlineStr">
         <is>
-          <t>3000</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>46-48</t>
+          <t>96-101</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>144000</t>
+          <t>121200</t>
         </is>
       </c>
       <c r="L78" t="inlineStr"/>
@@ -6196,19 +6180,19 @@
       <c r="P78" t="inlineStr"/>
       <c r="Q78" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/palucktechnologiesltd/PTL08</t>
+          <t>https://www.moneycontrol.com/ipo/kheriaautocompltd/KAL05</t>
         </is>
       </c>
       <c r="R78" t="inlineStr">
         <is>
-          <t>2026-08-25 09:29:52</t>
+          <t>2026-09-11 13:34:16</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Papadmalji Agro Foods Ltd</t>
+          <t>Mopshop Distribution Ltd</t>
         </is>
       </c>
       <c r="B79" t="inlineStr"/>
@@ -6220,33 +6204,33 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Sep 29, 2026</t>
+          <t>Aug 19, 2026</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Oct 01, 2026</t>
+          <t>Aug 21, 2026</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Oct 05, 2026</t>
+          <t>Aug 24, 2026</t>
         </is>
       </c>
       <c r="H79" t="inlineStr"/>
       <c r="I79" t="inlineStr">
         <is>
-          <t>1600</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>69-72</t>
+          <t>138</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>115200</t>
+          <t>138000</t>
         </is>
       </c>
       <c r="L79" t="inlineStr"/>
@@ -6256,19 +6240,19 @@
       <c r="P79" t="inlineStr"/>
       <c r="Q79" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/papadmaljiagrofoodsltd/PAF</t>
+          <t>https://www.moneycontrol.com/ipo/mopshopdistributionltd/MDL03</t>
         </is>
       </c>
       <c r="R79" t="inlineStr">
         <is>
-          <t>2026-09-25 14:20:09</t>
+          <t>2026-08-14 21:36:23</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Paramount Syntex Ltd</t>
+          <t>Paluck Technologies Ltd</t>
         </is>
       </c>
       <c r="B80" t="inlineStr"/>
@@ -6280,33 +6264,33 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Sep 30, 2026</t>
+          <t>Aug 28, 2026</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Oct 06, 2026</t>
+          <t>Sep 01, 2026</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Oct 07, 2026</t>
+          <t>Sep 02, 2026</t>
         </is>
       </c>
       <c r="H80" t="inlineStr"/>
       <c r="I80" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>3000</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>119-127</t>
+          <t>46-48</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>127000</t>
+          <t>144000</t>
         </is>
       </c>
       <c r="L80" t="inlineStr"/>
@@ -6316,19 +6300,19 @@
       <c r="P80" t="inlineStr"/>
       <c r="Q80" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/paramountsyntexltd/PSL06</t>
+          <t>https://www.moneycontrol.com/ipo/palucktechnologiesltd/PTL08</t>
         </is>
       </c>
       <c r="R80" t="inlineStr">
         <is>
-          <t>2026-09-25 14:20:09</t>
+          <t>2026-08-25 09:29:52</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Peshwa Wheat</t>
+          <t>Papadmalji Agro Foods Ltd</t>
         </is>
       </c>
       <c r="B81" t="inlineStr"/>
@@ -6340,33 +6324,33 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Sep 24, 2026</t>
+          <t>Sep 29, 2026</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Sep 28, 2026</t>
+          <t>Oct 01, 2026</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Sep 29, 2026</t>
+          <t>Oct 05, 2026</t>
         </is>
       </c>
       <c r="H81" t="inlineStr"/>
       <c r="I81" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>1600</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>95-101</t>
+          <t>69-72</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>121200</t>
+          <t>115200</t>
         </is>
       </c>
       <c r="L81" t="inlineStr"/>
@@ -6376,75 +6360,79 @@
       <c r="P81" t="inlineStr"/>
       <c r="Q81" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/peshwawheat/PWL01</t>
+          <t>https://www.moneycontrol.com/ipo/papadmaljiagrofoodsltd/PAF</t>
         </is>
       </c>
       <c r="R81" t="inlineStr">
         <is>
-          <t>2026-09-22 14:03:25</t>
+          <t>2026-09-25 14:20:09</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Purple Style Labs Ltd</t>
+          <t>Paramount Syntex Ltd</t>
         </is>
       </c>
       <c r="B82" t="inlineStr"/>
       <c r="C82" t="inlineStr"/>
-      <c r="D82" s="4" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="D82" s="5" t="inlineStr">
+        <is>
+          <t>Upcoming</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Aug 31, 2026</t>
+          <t>Sep 30, 2026</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Sep 02, 2026</t>
+          <t>Oct 06, 2026</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Sep 03, 2026</t>
+          <t>Oct 07, 2026</t>
         </is>
       </c>
       <c r="H82" t="inlineStr"/>
-      <c r="I82" t="inlineStr"/>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>575</t>
-        </is>
-      </c>
-      <c r="K82" t="inlineStr"/>
+          <t>119-127</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>127000</t>
+        </is>
+      </c>
       <c r="L82" t="inlineStr"/>
       <c r="M82" t="inlineStr"/>
-      <c r="N82" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="N82" t="inlineStr"/>
       <c r="O82" t="inlineStr"/>
       <c r="P82" t="inlineStr"/>
       <c r="Q82" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/purplestylelabsltd/PSL05</t>
+          <t>https://www.moneycontrol.com/ipo/paramountsyntexltd/PSL06</t>
         </is>
       </c>
       <c r="R82" t="inlineStr">
         <is>
-          <t>2026-09-02 13:25:30</t>
+          <t>2026-09-25 14:20:09</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Q&amp;T Foods Ltd</t>
+          <t>Peshwa Wheat</t>
         </is>
       </c>
       <c r="B83" t="inlineStr"/>
@@ -6456,17 +6444,17 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Aug 12, 2026</t>
+          <t>Sep 24, 2026</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Aug 14, 2026</t>
+          <t>Sep 28, 2026</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Aug 17, 2026</t>
+          <t>Sep 29, 2026</t>
         </is>
       </c>
       <c r="H83" t="inlineStr"/>
@@ -6477,12 +6465,12 @@
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>115</t>
+          <t>95-101</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>138000</t>
+          <t>121200</t>
         </is>
       </c>
       <c r="L83" t="inlineStr"/>
@@ -6492,79 +6480,75 @@
       <c r="P83" t="inlineStr"/>
       <c r="Q83" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/qtfoodsltd/QFL</t>
+          <t>https://www.moneycontrol.com/ipo/peshwawheat/PWL01</t>
         </is>
       </c>
       <c r="R83" t="inlineStr">
         <is>
-          <t>2026-08-10 10:24:29</t>
+          <t>2026-09-22 14:03:25</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Ravita Engineering Services Ltd</t>
+          <t>Purple Style Labs Ltd</t>
         </is>
       </c>
       <c r="B84" t="inlineStr"/>
       <c r="C84" t="inlineStr"/>
-      <c r="D84" s="5" t="inlineStr">
-        <is>
-          <t>Upcoming</t>
+      <c r="D84" s="4" t="inlineStr">
+        <is>
+          <t>Open</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Oct 13, 2026</t>
+          <t>Aug 31, 2026</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Oct 15, 2026</t>
+          <t>Sep 02, 2026</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Oct 16, 2026</t>
+          <t>Sep 03, 2026</t>
         </is>
       </c>
       <c r="H84" t="inlineStr"/>
-      <c r="I84" t="inlineStr">
-        <is>
-          <t>1200</t>
-        </is>
-      </c>
+      <c r="I84" t="inlineStr"/>
       <c r="J84" t="inlineStr">
         <is>
-          <t>105-112</t>
-        </is>
-      </c>
-      <c r="K84" t="inlineStr">
-        <is>
-          <t>134400</t>
-        </is>
-      </c>
+          <t>575</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr"/>
       <c r="L84" t="inlineStr"/>
       <c r="M84" t="inlineStr"/>
-      <c r="N84" t="inlineStr"/>
+      <c r="N84" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="O84" t="inlineStr"/>
       <c r="P84" t="inlineStr"/>
       <c r="Q84" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/ravitaengineeringservicesltd/RESL</t>
+          <t>https://www.moneycontrol.com/ipo/purplestylelabsltd/PSL05</t>
         </is>
       </c>
       <c r="R84" t="inlineStr">
         <is>
-          <t>2026-10-08 16:06:11</t>
+          <t>2026-09-02 13:25:30</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Shanti Inorganics Ltd</t>
+          <t>Q&amp;T Foods Ltd</t>
         </is>
       </c>
       <c r="B85" t="inlineStr"/>
@@ -6576,33 +6560,33 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Aug 31, 2026</t>
+          <t>Aug 12, 2026</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Sep 02, 2026</t>
+          <t>Aug 14, 2026</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Sep 03, 2026</t>
+          <t>Aug 17, 2026</t>
         </is>
       </c>
       <c r="H85" t="inlineStr"/>
       <c r="I85" t="inlineStr">
         <is>
-          <t>1600</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>79-83</t>
+          <t>115</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>132800</t>
+          <t>138000</t>
         </is>
       </c>
       <c r="L85" t="inlineStr"/>
@@ -6612,19 +6596,19 @@
       <c r="P85" t="inlineStr"/>
       <c r="Q85" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/shantiinorganicsltd/SIL34</t>
+          <t>https://www.moneycontrol.com/ipo/qtfoodsltd/QFL</t>
         </is>
       </c>
       <c r="R85" t="inlineStr">
         <is>
-          <t>2026-08-25 09:29:52</t>
+          <t>2026-08-10 10:24:29</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Technocrats Plasma Systems Ltd</t>
+          <t>Ravita Engineering Services Ltd</t>
         </is>
       </c>
       <c r="B86" t="inlineStr"/>
@@ -6636,33 +6620,33 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Aug 14, 2026</t>
+          <t>Oct 13, 2026</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Aug 18, 2026</t>
+          <t>Oct 15, 2026</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Aug 19, 2026</t>
+          <t>Oct 16, 2026</t>
         </is>
       </c>
       <c r="H86" t="inlineStr"/>
       <c r="I86" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>125-132</t>
+          <t>105-112</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>132000</t>
+          <t>134400</t>
         </is>
       </c>
       <c r="L86" t="inlineStr"/>
@@ -6672,19 +6656,19 @@
       <c r="P86" t="inlineStr"/>
       <c r="Q86" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/technocratsplasmasystemsltd/TPSL</t>
+          <t>https://www.moneycontrol.com/ipo/ravitaengineeringservicesltd/RESL</t>
         </is>
       </c>
       <c r="R86" t="inlineStr">
         <is>
-          <t>2026-08-11 21:41:02</t>
+          <t>2026-10-08 16:06:11</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Unitec Fibres Ltd</t>
+          <t>Shanti Inorganics Ltd</t>
         </is>
       </c>
       <c r="B87" t="inlineStr"/>
@@ -6696,17 +6680,17 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Sep 23, 2026</t>
+          <t>Aug 31, 2026</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Sep 25, 2026</t>
+          <t>Sep 02, 2026</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Sep 28, 2026</t>
+          <t>Sep 03, 2026</t>
         </is>
       </c>
       <c r="H87" t="inlineStr"/>
@@ -6717,12 +6701,12 @@
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>83-88</t>
+          <t>79-83</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>140800</t>
+          <t>132800</t>
         </is>
       </c>
       <c r="L87" t="inlineStr"/>
@@ -6732,19 +6716,19 @@
       <c r="P87" t="inlineStr"/>
       <c r="Q87" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/unitecfibresltd/UFL03</t>
+          <t>https://www.moneycontrol.com/ipo/shantiinorganicsltd/SIL34</t>
         </is>
       </c>
       <c r="R87" t="inlineStr">
         <is>
-          <t>2026-09-18 23:59:33</t>
+          <t>2026-08-25 09:29:52</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>VANS Electroengineerings Ltd</t>
+          <t>Technocrats Plasma Systems Ltd</t>
         </is>
       </c>
       <c r="B88" t="inlineStr"/>
@@ -6756,33 +6740,33 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Sep 29, 2026</t>
+          <t>Aug 14, 2026</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Oct 01, 2026</t>
+          <t>Aug 18, 2026</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Oct 05, 2026</t>
+          <t>Aug 19, 2026</t>
         </is>
       </c>
       <c r="H88" t="inlineStr"/>
       <c r="I88" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>112-118</t>
+          <t>125-132</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>141600</t>
+          <t>132000</t>
         </is>
       </c>
       <c r="L88" t="inlineStr"/>
@@ -6792,19 +6776,19 @@
       <c r="P88" t="inlineStr"/>
       <c r="Q88" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/vanselectroengineeringsltd/VEL03</t>
+          <t>https://www.moneycontrol.com/ipo/technocratsplasmasystemsltd/TPSL</t>
         </is>
       </c>
       <c r="R88" t="inlineStr">
         <is>
-          <t>2026-09-25 14:20:09</t>
+          <t>2026-08-11 21:41:02</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Vaibhav Vyapaar Ltd</t>
+          <t>Unitec Fibres Ltd</t>
         </is>
       </c>
       <c r="B89" t="inlineStr"/>
@@ -6816,33 +6800,33 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Oct 13, 2026</t>
+          <t>Sep 23, 2026</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Oct 15, 2026</t>
+          <t>Sep 25, 2026</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Oct 16, 2026</t>
+          <t>Sep 28, 2026</t>
         </is>
       </c>
       <c r="H89" t="inlineStr"/>
       <c r="I89" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>1600</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>50-52</t>
+          <t>83-88</t>
         </is>
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>104000</t>
+          <t>140800</t>
         </is>
       </c>
       <c r="L89" t="inlineStr"/>
@@ -6852,19 +6836,19 @@
       <c r="P89" t="inlineStr"/>
       <c r="Q89" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/vaibhavvyapaarltd/VVL01</t>
+          <t>https://www.moneycontrol.com/ipo/unitecfibresltd/UFL03</t>
         </is>
       </c>
       <c r="R89" t="inlineStr">
         <is>
-          <t>2026-10-08 16:06:11</t>
+          <t>2026-09-18 23:59:33</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Vama Wovenfab Ltd</t>
+          <t>VANS Electroengineerings Ltd</t>
         </is>
       </c>
       <c r="B90" t="inlineStr"/>
@@ -6876,33 +6860,33 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Sep 15, 2026</t>
+          <t>Sep 29, 2026</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Sep 17, 2026</t>
+          <t>Oct 01, 2026</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Sep 18, 2026</t>
+          <t>Oct 05, 2026</t>
         </is>
       </c>
       <c r="H90" t="inlineStr"/>
       <c r="I90" t="inlineStr">
         <is>
-          <t>400</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>324-341</t>
+          <t>112-118</t>
         </is>
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>136400</t>
+          <t>141600</t>
         </is>
       </c>
       <c r="L90" t="inlineStr"/>
@@ -6912,17 +6896,137 @@
       <c r="P90" t="inlineStr"/>
       <c r="Q90" t="inlineStr">
         <is>
+          <t>https://www.moneycontrol.com/ipo/vanselectroengineeringsltd/VEL03</t>
+        </is>
+      </c>
+      <c r="R90" t="inlineStr">
+        <is>
+          <t>2026-09-25 14:20:09</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Vaibhav Vyapaar Ltd</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr"/>
+      <c r="C91" t="inlineStr"/>
+      <c r="D91" s="5" t="inlineStr">
+        <is>
+          <t>Upcoming</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>Oct 13, 2026</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>Oct 15, 2026</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>Oct 16, 2026</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr"/>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>50-52</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>104000</t>
+        </is>
+      </c>
+      <c r="L91" t="inlineStr"/>
+      <c r="M91" t="inlineStr"/>
+      <c r="N91" t="inlineStr"/>
+      <c r="O91" t="inlineStr"/>
+      <c r="P91" t="inlineStr"/>
+      <c r="Q91" t="inlineStr">
+        <is>
+          <t>https://www.moneycontrol.com/ipo/vaibhavvyapaarltd/VVL01</t>
+        </is>
+      </c>
+      <c r="R91" t="inlineStr">
+        <is>
+          <t>2026-10-08 16:06:11</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Vama Wovenfab Ltd</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr"/>
+      <c r="C92" t="inlineStr"/>
+      <c r="D92" s="5" t="inlineStr">
+        <is>
+          <t>Upcoming</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>Sep 15, 2026</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>Sep 17, 2026</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>Sep 18, 2026</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr"/>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>400</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>324-341</t>
+        </is>
+      </c>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>136400</t>
+        </is>
+      </c>
+      <c r="L92" t="inlineStr"/>
+      <c r="M92" t="inlineStr"/>
+      <c r="N92" t="inlineStr"/>
+      <c r="O92" t="inlineStr"/>
+      <c r="P92" t="inlineStr"/>
+      <c r="Q92" t="inlineStr">
+        <is>
           <t>https://www.moneycontrol.com/ipo/vamawovenfabltd/VWL01</t>
         </is>
       </c>
-      <c r="R90" t="inlineStr">
+      <c r="R92" t="inlineStr">
         <is>
           <t>2026-09-11 13:34:16</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:R90"/>
+  <autoFilter ref="A1:R92"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/mainboard_ipos.xlsx
+++ b/data/mainboard_ipos.xlsx
@@ -5137,9 +5137,9 @@
       </c>
       <c r="B62" t="inlineStr"/>
       <c r="C62" t="inlineStr"/>
-      <c r="D62" s="3" t="inlineStr">
-        <is>
-          <t>Closed</t>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>Listed</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -5188,12 +5188,12 @@
       <c r="P62" t="inlineStr"/>
       <c r="Q62" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/hdfireprotect/HFP</t>
+          <t>https://www.moneycontrol.com/ipo/engineering-industrial-equipments/hdfireprotect/HFP</t>
         </is>
       </c>
       <c r="R62" t="inlineStr">
         <is>
-          <t>2026-10-20 14:03:23</t>
+          <t>2026-10-21 14:05:04</t>
         </is>
       </c>
     </row>
@@ -5261,7 +5261,7 @@
       </c>
       <c r="R63" t="inlineStr">
         <is>
-          <t>2026-10-20 14:03:23</t>
+          <t>2026-10-21 14:05:04</t>
         </is>
       </c>
     </row>
@@ -5317,7 +5317,7 @@
       <c r="M64" t="inlineStr"/>
       <c r="N64" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>46</t>
         </is>
       </c>
       <c r="O64" t="inlineStr"/>
@@ -5329,7 +5329,7 @@
       </c>
       <c r="R64" t="inlineStr">
         <is>
-          <t>2026-10-20 14:03:23</t>
+          <t>2026-10-21 14:05:04</t>
         </is>
       </c>
     </row>
@@ -5385,7 +5385,7 @@
       <c r="M65" t="inlineStr"/>
       <c r="N65" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>14</t>
         </is>
       </c>
       <c r="O65" t="inlineStr"/>
@@ -5397,7 +5397,7 @@
       </c>
       <c r="R65" t="inlineStr">
         <is>
-          <t>2026-10-20 14:03:23</t>
+          <t>2026-10-21 14:05:04</t>
         </is>
       </c>
     </row>
@@ -5409,9 +5409,9 @@
       </c>
       <c r="B66" t="inlineStr"/>
       <c r="C66" t="inlineStr"/>
-      <c r="D66" s="4" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="D66" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -5453,7 +5453,7 @@
       <c r="M66" t="inlineStr"/>
       <c r="N66" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>136</t>
         </is>
       </c>
       <c r="O66" t="inlineStr"/>
@@ -5465,7 +5465,7 @@
       </c>
       <c r="R66" t="inlineStr">
         <is>
-          <t>2026-10-19 14:23:34</t>
+          <t>2026-10-21 14:05:04</t>
         </is>
       </c>
     </row>
@@ -5477,9 +5477,9 @@
       </c>
       <c r="B67" t="inlineStr"/>
       <c r="C67" t="inlineStr"/>
-      <c r="D67" s="4" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="D67" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -5521,7 +5521,7 @@
       <c r="M67" t="inlineStr"/>
       <c r="N67" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="O67" t="inlineStr"/>
@@ -5533,7 +5533,7 @@
       </c>
       <c r="R67" t="inlineStr">
         <is>
-          <t>2026-10-19 14:23:34</t>
+          <t>2026-10-21 14:05:04</t>
         </is>
       </c>
     </row>
@@ -5545,9 +5545,9 @@
       </c>
       <c r="B68" t="inlineStr"/>
       <c r="C68" t="inlineStr"/>
-      <c r="D68" s="5" t="inlineStr">
-        <is>
-          <t>Upcoming</t>
+      <c r="D68" s="4" t="inlineStr">
+        <is>
+          <t>Open</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -5577,7 +5577,7 @@
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>1065-1119</t>
+          <t>1119</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
@@ -5597,7 +5597,7 @@
       </c>
       <c r="R68" t="inlineStr">
         <is>
-          <t>2026-10-20 14:03:23</t>
+          <t>2026-10-21 14:05:04</t>
         </is>
       </c>
     </row>
@@ -5609,9 +5609,9 @@
       </c>
       <c r="B69" t="inlineStr"/>
       <c r="C69" t="inlineStr"/>
-      <c r="D69" s="5" t="inlineStr">
-        <is>
-          <t>Upcoming</t>
+      <c r="D69" s="4" t="inlineStr">
+        <is>
+          <t>Open</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -5641,7 +5641,7 @@
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>660-693</t>
+          <t>693</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
@@ -5661,7 +5661,7 @@
       </c>
       <c r="R69" t="inlineStr">
         <is>
-          <t>2026-10-20 14:03:23</t>
+          <t>2026-10-21 14:05:04</t>
         </is>
       </c>
     </row>
@@ -5693,14 +5693,26 @@
           <t>Oct 30, 2026</t>
         </is>
       </c>
-      <c r="H70" t="inlineStr"/>
-      <c r="I70" t="inlineStr"/>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>Nov 03, 2026</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
       <c r="J70" t="inlineStr">
         <is>
           <t>142-150</t>
         </is>
       </c>
-      <c r="K70" t="inlineStr"/>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>15000</t>
+        </is>
+      </c>
       <c r="L70" t="inlineStr"/>
       <c r="M70" t="inlineStr"/>
       <c r="N70" t="inlineStr"/>
@@ -5713,7 +5725,7 @@
       </c>
       <c r="R70" t="inlineStr">
         <is>
-          <t>2026-10-20 14:03:23</t>
+          <t>2026-10-21 14:05:04</t>
         </is>
       </c>
     </row>
@@ -5806,13 +5818,21 @@
         </is>
       </c>
       <c r="H72" t="inlineStr"/>
-      <c r="I72" t="inlineStr"/>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>1200</t>
+        </is>
+      </c>
       <c r="J72" t="inlineStr">
         <is>
           <t>88-93</t>
         </is>
       </c>
-      <c r="K72" t="inlineStr"/>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>111600</t>
+        </is>
+      </c>
       <c r="L72" t="inlineStr"/>
       <c r="M72" t="inlineStr"/>
       <c r="N72" t="inlineStr"/>

--- a/data/mainboard_ipos.xlsx
+++ b/data/mainboard_ipos.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Mainboard IPOs" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Mainboard IPOs'!$A$1:$R$92</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Mainboard IPOs'!$A$1:$R$94</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -449,7 +449,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R92"/>
+  <dimension ref="A1:R94"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -5177,15 +5177,31 @@
           <t>14905</t>
         </is>
       </c>
-      <c r="L62" t="inlineStr"/>
-      <c r="M62" t="inlineStr"/>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>335</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>18425</t>
+        </is>
+      </c>
       <c r="N62" t="inlineStr">
         <is>
           <t>132</t>
         </is>
       </c>
-      <c r="O62" t="inlineStr"/>
-      <c r="P62" t="inlineStr"/>
+      <c r="O62" t="inlineStr">
+        <is>
+          <t>3520</t>
+        </is>
+      </c>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
       <c r="Q62" t="inlineStr">
         <is>
           <t>https://www.moneycontrol.com/ipo/engineering-industrial-equipments/hdfireprotect/HFP</t>
@@ -5193,7 +5209,7 @@
       </c>
       <c r="R62" t="inlineStr">
         <is>
-          <t>2026-10-21 14:05:04</t>
+          <t>2026-10-22 14:07:33</t>
         </is>
       </c>
     </row>
@@ -5205,9 +5221,9 @@
       </c>
       <c r="B63" t="inlineStr"/>
       <c r="C63" t="inlineStr"/>
-      <c r="D63" s="3" t="inlineStr">
-        <is>
-          <t>Closed</t>
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t>Listed</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -5256,12 +5272,12 @@
       <c r="P63" t="inlineStr"/>
       <c r="Q63" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/fusioncx/FCL02</t>
+          <t>https://www.moneycontrol.com/ipo/bpoites/fusioncx/FCL02</t>
         </is>
       </c>
       <c r="R63" t="inlineStr">
         <is>
-          <t>2026-10-21 14:05:04</t>
+          <t>2026-10-22 14:07:33</t>
         </is>
       </c>
     </row>
@@ -5329,7 +5345,7 @@
       </c>
       <c r="R64" t="inlineStr">
         <is>
-          <t>2026-10-21 14:05:04</t>
+          <t>2026-10-22 14:07:33</t>
         </is>
       </c>
     </row>
@@ -5397,7 +5413,7 @@
       </c>
       <c r="R65" t="inlineStr">
         <is>
-          <t>2026-10-21 14:05:04</t>
+          <t>2026-10-22 14:07:33</t>
         </is>
       </c>
     </row>
@@ -5465,7 +5481,7 @@
       </c>
       <c r="R66" t="inlineStr">
         <is>
-          <t>2026-10-21 14:05:04</t>
+          <t>2026-10-22 14:07:33</t>
         </is>
       </c>
     </row>
@@ -5533,7 +5549,7 @@
       </c>
       <c r="R67" t="inlineStr">
         <is>
-          <t>2026-10-21 14:05:04</t>
+          <t>2026-10-22 14:07:33</t>
         </is>
       </c>
     </row>
@@ -5587,7 +5603,11 @@
       </c>
       <c r="L68" t="inlineStr"/>
       <c r="M68" t="inlineStr"/>
-      <c r="N68" t="inlineStr"/>
+      <c r="N68" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O68" t="inlineStr"/>
       <c r="P68" t="inlineStr"/>
       <c r="Q68" t="inlineStr">
@@ -5597,7 +5617,7 @@
       </c>
       <c r="R68" t="inlineStr">
         <is>
-          <t>2026-10-21 14:05:04</t>
+          <t>2026-10-22 14:07:33</t>
         </is>
       </c>
     </row>
@@ -5651,7 +5671,11 @@
       </c>
       <c r="L69" t="inlineStr"/>
       <c r="M69" t="inlineStr"/>
-      <c r="N69" t="inlineStr"/>
+      <c r="N69" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="O69" t="inlineStr"/>
       <c r="P69" t="inlineStr"/>
       <c r="Q69" t="inlineStr">
@@ -5661,14 +5685,14 @@
       </c>
       <c r="R69" t="inlineStr">
         <is>
-          <t>2026-10-21 14:05:04</t>
+          <t>2026-10-22 14:07:33</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>BLS Polymers Ltd</t>
+          <t>EAAA India Alternatives Ltd</t>
         </is>
       </c>
       <c r="B70" t="inlineStr"/>
@@ -5680,37 +5704,37 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Oct 27, 2026</t>
+          <t>Oct 26, 2026</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
+          <t>Oct 28, 2026</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
           <t>Oct 29, 2026</t>
         </is>
       </c>
-      <c r="G70" t="inlineStr">
-        <is>
-          <t>Oct 30, 2026</t>
-        </is>
-      </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Nov 03, 2026</t>
+          <t>Nov 02, 2026</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>9</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>142-150</t>
+          <t>1585-1665</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>15000</t>
+          <t>14985</t>
         </is>
       </c>
       <c r="L70" t="inlineStr"/>
@@ -5720,19 +5744,19 @@
       <c r="P70" t="inlineStr"/>
       <c r="Q70" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/blspolymersltd/BPL11</t>
+          <t>https://www.moneycontrol.com/ipo/eaaaindiaalternativesltd/EIA</t>
         </is>
       </c>
       <c r="R70" t="inlineStr">
         <is>
-          <t>2026-10-21 14:05:04</t>
+          <t>2026-10-22 14:07:33</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Complete Sports and Management India Ltd</t>
+          <t>BLS Polymers Ltd</t>
         </is>
       </c>
       <c r="B71" t="inlineStr"/>
@@ -5744,33 +5768,37 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Aug 28, 2026</t>
+          <t>Oct 27, 2026</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Sep 01, 2026</t>
+          <t>Oct 29, 2026</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Sep 02, 2026</t>
-        </is>
-      </c>
-      <c r="H71" t="inlineStr"/>
+          <t>Oct 30, 2026</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>Nov 03, 2026</t>
+        </is>
+      </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>128-135</t>
+          <t>142-150</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>135000</t>
+          <t>15000</t>
         </is>
       </c>
       <c r="L71" t="inlineStr"/>
@@ -5780,19 +5808,19 @@
       <c r="P71" t="inlineStr"/>
       <c r="Q71" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/completesportsmanagementindialtd/CSMIL</t>
+          <t>https://www.moneycontrol.com/ipo/blspolymersltd/BPL11</t>
         </is>
       </c>
       <c r="R71" t="inlineStr">
         <is>
-          <t>2026-08-25 09:29:52</t>
+          <t>2026-10-22 14:07:33</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Core4 Engineers Ltd</t>
+          <t>SFC Environmental Technologies Ltd</t>
         </is>
       </c>
       <c r="B72" t="inlineStr"/>
@@ -5804,33 +5832,37 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Oct 23, 2026</t>
+          <t>Oct 27, 2026</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Oct 27, 2026</t>
+          <t>Oct 29, 2026</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Oct 28, 2026</t>
-        </is>
-      </c>
-      <c r="H72" t="inlineStr"/>
+          <t>Oct 30, 2026</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>Nov 03, 2026</t>
+        </is>
+      </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>45</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>88-93</t>
+          <t>313-330</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>111600</t>
+          <t>14850</t>
         </is>
       </c>
       <c r="L72" t="inlineStr"/>
@@ -5840,19 +5872,19 @@
       <c r="P72" t="inlineStr"/>
       <c r="Q72" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/core4engineersltd/CEL05</t>
+          <t>https://www.moneycontrol.com/ipo/sfcenvironmentaltechnologiesltd/SETL</t>
         </is>
       </c>
       <c r="R72" t="inlineStr">
         <is>
-          <t>2026-10-20 14:03:23</t>
+          <t>2026-10-22 14:07:33</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Coreintegra Consulting Services</t>
+          <t>Complete Sports and Management India Ltd</t>
         </is>
       </c>
       <c r="B73" t="inlineStr"/>
@@ -5864,33 +5896,33 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Sep 23, 2026</t>
+          <t>Aug 28, 2026</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Sep 25, 2026</t>
+          <t>Sep 01, 2026</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Sep 28, 2026</t>
+          <t>Sep 02, 2026</t>
         </is>
       </c>
       <c r="H73" t="inlineStr"/>
       <c r="I73" t="inlineStr">
         <is>
-          <t>1600</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>74-78</t>
+          <t>128-135</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>124800</t>
+          <t>135000</t>
         </is>
       </c>
       <c r="L73" t="inlineStr"/>
@@ -5900,19 +5932,19 @@
       <c r="P73" t="inlineStr"/>
       <c r="Q73" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/coreintegraconsultingservices/CCSL</t>
+          <t>https://www.moneycontrol.com/ipo/completesportsmanagementindialtd/CSMIL</t>
         </is>
       </c>
       <c r="R73" t="inlineStr">
         <is>
-          <t>2026-09-22 14:03:25</t>
+          <t>2026-08-25 09:29:52</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Credent Connect N Care Ltd</t>
+          <t>Core4 Engineers Ltd</t>
         </is>
       </c>
       <c r="B74" t="inlineStr"/>
@@ -5924,33 +5956,33 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Aug 13, 2026</t>
+          <t>Oct 23, 2026</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Aug 17, 2026</t>
+          <t>Oct 27, 2026</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Aug 18, 2026</t>
+          <t>Oct 28, 2026</t>
         </is>
       </c>
       <c r="H74" t="inlineStr"/>
       <c r="I74" t="inlineStr">
         <is>
-          <t>600</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>179-189</t>
+          <t>88-93</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>113400</t>
+          <t>111600</t>
         </is>
       </c>
       <c r="L74" t="inlineStr"/>
@@ -5960,19 +5992,19 @@
       <c r="P74" t="inlineStr"/>
       <c r="Q74" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/credentconnectncareltd/CCC04</t>
+          <t>https://www.moneycontrol.com/ipo/core4engineersltd/CEL05</t>
         </is>
       </c>
       <c r="R74" t="inlineStr">
         <is>
-          <t>2026-08-10 22:43:12</t>
+          <t>2026-10-20 14:03:23</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Dove Soft Ltd</t>
+          <t>Coreintegra Consulting Services</t>
         </is>
       </c>
       <c r="B75" t="inlineStr"/>
@@ -5984,33 +6016,33 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Sep 30, 2026</t>
+          <t>Sep 23, 2026</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Oct 05, 2026</t>
+          <t>Sep 25, 2026</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Oct 06, 2026</t>
+          <t>Sep 28, 2026</t>
         </is>
       </c>
       <c r="H75" t="inlineStr"/>
       <c r="I75" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>1600</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>104-111</t>
+          <t>74-78</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>133200</t>
+          <t>124800</t>
         </is>
       </c>
       <c r="L75" t="inlineStr"/>
@@ -6020,19 +6052,19 @@
       <c r="P75" t="inlineStr"/>
       <c r="Q75" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/dovesoftltd/DSL04</t>
+          <t>https://www.moneycontrol.com/ipo/coreintegraconsultingservices/CCSL</t>
         </is>
       </c>
       <c r="R75" t="inlineStr">
         <is>
-          <t>2026-09-25 14:20:09</t>
+          <t>2026-09-22 14:03:25</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Farm Peace Ltd</t>
+          <t>Credent Connect N Care Ltd</t>
         </is>
       </c>
       <c r="B76" t="inlineStr"/>
@@ -6044,33 +6076,33 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Sep 01, 2026</t>
+          <t>Aug 13, 2026</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Sep 03, 2026</t>
+          <t>Aug 17, 2026</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Sep 04, 2026</t>
+          <t>Aug 18, 2026</t>
         </is>
       </c>
       <c r="H76" t="inlineStr"/>
       <c r="I76" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>600</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>179-189</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>118000</t>
+          <t>113400</t>
         </is>
       </c>
       <c r="L76" t="inlineStr"/>
@@ -6080,19 +6112,19 @@
       <c r="P76" t="inlineStr"/>
       <c r="Q76" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/farmpeaceltd/FPL02</t>
+          <t>https://www.moneycontrol.com/ipo/credentconnectncareltd/CCC04</t>
         </is>
       </c>
       <c r="R76" t="inlineStr">
         <is>
-          <t>2026-08-27 19:43:03</t>
+          <t>2026-08-10 22:43:12</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Green Asia Impex Ltd</t>
+          <t>Dove Soft Ltd</t>
         </is>
       </c>
       <c r="B77" t="inlineStr"/>
@@ -6104,33 +6136,33 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Sep 24, 2026</t>
+          <t>Sep 30, 2026</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Sep 28, 2026</t>
+          <t>Oct 05, 2026</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Sep 29, 2026</t>
+          <t>Oct 06, 2026</t>
         </is>
       </c>
       <c r="H77" t="inlineStr"/>
       <c r="I77" t="inlineStr">
         <is>
-          <t>1600</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>85-90</t>
+          <t>104-111</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>144000</t>
+          <t>133200</t>
         </is>
       </c>
       <c r="L77" t="inlineStr"/>
@@ -6140,19 +6172,19 @@
       <c r="P77" t="inlineStr"/>
       <c r="Q77" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/greenasiaimpexltd/GAIL01</t>
+          <t>https://www.moneycontrol.com/ipo/dovesoftltd/DSL04</t>
         </is>
       </c>
       <c r="R77" t="inlineStr">
         <is>
-          <t>2026-09-22 14:03:25</t>
+          <t>2026-09-25 14:20:09</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Kheria Autocomp Ltd</t>
+          <t>Farm Peace Ltd</t>
         </is>
       </c>
       <c r="B78" t="inlineStr"/>
@@ -6164,33 +6196,33 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Sep 17, 2026</t>
+          <t>Sep 01, 2026</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Sep 21, 2026</t>
+          <t>Sep 03, 2026</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Sep 22, 2026</t>
+          <t>Sep 04, 2026</t>
         </is>
       </c>
       <c r="H78" t="inlineStr"/>
       <c r="I78" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>96-101</t>
+          <t>59</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>121200</t>
+          <t>118000</t>
         </is>
       </c>
       <c r="L78" t="inlineStr"/>
@@ -6200,19 +6232,19 @@
       <c r="P78" t="inlineStr"/>
       <c r="Q78" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/kheriaautocompltd/KAL05</t>
+          <t>https://www.moneycontrol.com/ipo/farmpeaceltd/FPL02</t>
         </is>
       </c>
       <c r="R78" t="inlineStr">
         <is>
-          <t>2026-09-11 13:34:16</t>
+          <t>2026-08-27 19:43:03</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Mopshop Distribution Ltd</t>
+          <t>Green Asia Impex Ltd</t>
         </is>
       </c>
       <c r="B79" t="inlineStr"/>
@@ -6224,33 +6256,33 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Aug 19, 2026</t>
+          <t>Sep 24, 2026</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Aug 21, 2026</t>
+          <t>Sep 28, 2026</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Aug 24, 2026</t>
+          <t>Sep 29, 2026</t>
         </is>
       </c>
       <c r="H79" t="inlineStr"/>
       <c r="I79" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>1600</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>138</t>
+          <t>85-90</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>138000</t>
+          <t>144000</t>
         </is>
       </c>
       <c r="L79" t="inlineStr"/>
@@ -6260,19 +6292,19 @@
       <c r="P79" t="inlineStr"/>
       <c r="Q79" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/mopshopdistributionltd/MDL03</t>
+          <t>https://www.moneycontrol.com/ipo/greenasiaimpexltd/GAIL01</t>
         </is>
       </c>
       <c r="R79" t="inlineStr">
         <is>
-          <t>2026-08-14 21:36:23</t>
+          <t>2026-09-22 14:03:25</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Paluck Technologies Ltd</t>
+          <t>Kheria Autocomp Ltd</t>
         </is>
       </c>
       <c r="B80" t="inlineStr"/>
@@ -6284,33 +6316,33 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Aug 28, 2026</t>
+          <t>Sep 17, 2026</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Sep 01, 2026</t>
+          <t>Sep 21, 2026</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Sep 02, 2026</t>
+          <t>Sep 22, 2026</t>
         </is>
       </c>
       <c r="H80" t="inlineStr"/>
       <c r="I80" t="inlineStr">
         <is>
-          <t>3000</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>46-48</t>
+          <t>96-101</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>144000</t>
+          <t>121200</t>
         </is>
       </c>
       <c r="L80" t="inlineStr"/>
@@ -6320,19 +6352,19 @@
       <c r="P80" t="inlineStr"/>
       <c r="Q80" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/palucktechnologiesltd/PTL08</t>
+          <t>https://www.moneycontrol.com/ipo/kheriaautocompltd/KAL05</t>
         </is>
       </c>
       <c r="R80" t="inlineStr">
         <is>
-          <t>2026-08-25 09:29:52</t>
+          <t>2026-09-11 13:34:16</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Papadmalji Agro Foods Ltd</t>
+          <t>Mopshop Distribution Ltd</t>
         </is>
       </c>
       <c r="B81" t="inlineStr"/>
@@ -6344,33 +6376,33 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Sep 29, 2026</t>
+          <t>Aug 19, 2026</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Oct 01, 2026</t>
+          <t>Aug 21, 2026</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Oct 05, 2026</t>
+          <t>Aug 24, 2026</t>
         </is>
       </c>
       <c r="H81" t="inlineStr"/>
       <c r="I81" t="inlineStr">
         <is>
-          <t>1600</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>69-72</t>
+          <t>138</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>115200</t>
+          <t>138000</t>
         </is>
       </c>
       <c r="L81" t="inlineStr"/>
@@ -6380,19 +6412,19 @@
       <c r="P81" t="inlineStr"/>
       <c r="Q81" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/papadmaljiagrofoodsltd/PAF</t>
+          <t>https://www.moneycontrol.com/ipo/mopshopdistributionltd/MDL03</t>
         </is>
       </c>
       <c r="R81" t="inlineStr">
         <is>
-          <t>2026-09-25 14:20:09</t>
+          <t>2026-08-14 21:36:23</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Paramount Syntex Ltd</t>
+          <t>Paluck Technologies Ltd</t>
         </is>
       </c>
       <c r="B82" t="inlineStr"/>
@@ -6404,33 +6436,33 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Sep 30, 2026</t>
+          <t>Aug 28, 2026</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Oct 06, 2026</t>
+          <t>Sep 01, 2026</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Oct 07, 2026</t>
+          <t>Sep 02, 2026</t>
         </is>
       </c>
       <c r="H82" t="inlineStr"/>
       <c r="I82" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>3000</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>119-127</t>
+          <t>46-48</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>127000</t>
+          <t>144000</t>
         </is>
       </c>
       <c r="L82" t="inlineStr"/>
@@ -6440,19 +6472,19 @@
       <c r="P82" t="inlineStr"/>
       <c r="Q82" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/paramountsyntexltd/PSL06</t>
+          <t>https://www.moneycontrol.com/ipo/palucktechnologiesltd/PTL08</t>
         </is>
       </c>
       <c r="R82" t="inlineStr">
         <is>
-          <t>2026-09-25 14:20:09</t>
+          <t>2026-08-25 09:29:52</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Peshwa Wheat</t>
+          <t>Papadmalji Agro Foods Ltd</t>
         </is>
       </c>
       <c r="B83" t="inlineStr"/>
@@ -6464,33 +6496,33 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Sep 24, 2026</t>
+          <t>Sep 29, 2026</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Sep 28, 2026</t>
+          <t>Oct 01, 2026</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Sep 29, 2026</t>
+          <t>Oct 05, 2026</t>
         </is>
       </c>
       <c r="H83" t="inlineStr"/>
       <c r="I83" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>1600</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>95-101</t>
+          <t>69-72</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>121200</t>
+          <t>115200</t>
         </is>
       </c>
       <c r="L83" t="inlineStr"/>
@@ -6500,75 +6532,79 @@
       <c r="P83" t="inlineStr"/>
       <c r="Q83" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/peshwawheat/PWL01</t>
+          <t>https://www.moneycontrol.com/ipo/papadmaljiagrofoodsltd/PAF</t>
         </is>
       </c>
       <c r="R83" t="inlineStr">
         <is>
-          <t>2026-09-22 14:03:25</t>
+          <t>2026-09-25 14:20:09</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Purple Style Labs Ltd</t>
+          <t>Paramount Syntex Ltd</t>
         </is>
       </c>
       <c r="B84" t="inlineStr"/>
       <c r="C84" t="inlineStr"/>
-      <c r="D84" s="4" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="D84" s="5" t="inlineStr">
+        <is>
+          <t>Upcoming</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Aug 31, 2026</t>
+          <t>Sep 30, 2026</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Sep 02, 2026</t>
+          <t>Oct 06, 2026</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Sep 03, 2026</t>
+          <t>Oct 07, 2026</t>
         </is>
       </c>
       <c r="H84" t="inlineStr"/>
-      <c r="I84" t="inlineStr"/>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>575</t>
-        </is>
-      </c>
-      <c r="K84" t="inlineStr"/>
+          <t>119-127</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>127000</t>
+        </is>
+      </c>
       <c r="L84" t="inlineStr"/>
       <c r="M84" t="inlineStr"/>
-      <c r="N84" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="N84" t="inlineStr"/>
       <c r="O84" t="inlineStr"/>
       <c r="P84" t="inlineStr"/>
       <c r="Q84" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/purplestylelabsltd/PSL05</t>
+          <t>https://www.moneycontrol.com/ipo/paramountsyntexltd/PSL06</t>
         </is>
       </c>
       <c r="R84" t="inlineStr">
         <is>
-          <t>2026-09-02 13:25:30</t>
+          <t>2026-09-25 14:20:09</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Q&amp;T Foods Ltd</t>
+          <t>Peshwa Wheat</t>
         </is>
       </c>
       <c r="B85" t="inlineStr"/>
@@ -6580,17 +6616,17 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Aug 12, 2026</t>
+          <t>Sep 24, 2026</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Aug 14, 2026</t>
+          <t>Sep 28, 2026</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Aug 17, 2026</t>
+          <t>Sep 29, 2026</t>
         </is>
       </c>
       <c r="H85" t="inlineStr"/>
@@ -6601,12 +6637,12 @@
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>115</t>
+          <t>95-101</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>138000</t>
+          <t>121200</t>
         </is>
       </c>
       <c r="L85" t="inlineStr"/>
@@ -6616,79 +6652,75 @@
       <c r="P85" t="inlineStr"/>
       <c r="Q85" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/qtfoodsltd/QFL</t>
+          <t>https://www.moneycontrol.com/ipo/peshwawheat/PWL01</t>
         </is>
       </c>
       <c r="R85" t="inlineStr">
         <is>
-          <t>2026-08-10 10:24:29</t>
+          <t>2026-09-22 14:03:25</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Ravita Engineering Services Ltd</t>
+          <t>Purple Style Labs Ltd</t>
         </is>
       </c>
       <c r="B86" t="inlineStr"/>
       <c r="C86" t="inlineStr"/>
-      <c r="D86" s="5" t="inlineStr">
-        <is>
-          <t>Upcoming</t>
+      <c r="D86" s="4" t="inlineStr">
+        <is>
+          <t>Open</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Oct 13, 2026</t>
+          <t>Aug 31, 2026</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Oct 15, 2026</t>
+          <t>Sep 02, 2026</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Oct 16, 2026</t>
+          <t>Sep 03, 2026</t>
         </is>
       </c>
       <c r="H86" t="inlineStr"/>
-      <c r="I86" t="inlineStr">
-        <is>
-          <t>1200</t>
-        </is>
-      </c>
+      <c r="I86" t="inlineStr"/>
       <c r="J86" t="inlineStr">
         <is>
-          <t>105-112</t>
-        </is>
-      </c>
-      <c r="K86" t="inlineStr">
-        <is>
-          <t>134400</t>
-        </is>
-      </c>
+          <t>575</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr"/>
       <c r="L86" t="inlineStr"/>
       <c r="M86" t="inlineStr"/>
-      <c r="N86" t="inlineStr"/>
+      <c r="N86" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="O86" t="inlineStr"/>
       <c r="P86" t="inlineStr"/>
       <c r="Q86" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/ravitaengineeringservicesltd/RESL</t>
+          <t>https://www.moneycontrol.com/ipo/purplestylelabsltd/PSL05</t>
         </is>
       </c>
       <c r="R86" t="inlineStr">
         <is>
-          <t>2026-10-08 16:06:11</t>
+          <t>2026-09-02 13:25:30</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Shanti Inorganics Ltd</t>
+          <t>Q&amp;T Foods Ltd</t>
         </is>
       </c>
       <c r="B87" t="inlineStr"/>
@@ -6700,33 +6732,33 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Aug 31, 2026</t>
+          <t>Aug 12, 2026</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Sep 02, 2026</t>
+          <t>Aug 14, 2026</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Sep 03, 2026</t>
+          <t>Aug 17, 2026</t>
         </is>
       </c>
       <c r="H87" t="inlineStr"/>
       <c r="I87" t="inlineStr">
         <is>
-          <t>1600</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>79-83</t>
+          <t>115</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>132800</t>
+          <t>138000</t>
         </is>
       </c>
       <c r="L87" t="inlineStr"/>
@@ -6736,19 +6768,19 @@
       <c r="P87" t="inlineStr"/>
       <c r="Q87" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/shantiinorganicsltd/SIL34</t>
+          <t>https://www.moneycontrol.com/ipo/qtfoodsltd/QFL</t>
         </is>
       </c>
       <c r="R87" t="inlineStr">
         <is>
-          <t>2026-08-25 09:29:52</t>
+          <t>2026-08-10 10:24:29</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Technocrats Plasma Systems Ltd</t>
+          <t>Ravita Engineering Services Ltd</t>
         </is>
       </c>
       <c r="B88" t="inlineStr"/>
@@ -6760,33 +6792,33 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Aug 14, 2026</t>
+          <t>Oct 13, 2026</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Aug 18, 2026</t>
+          <t>Oct 15, 2026</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Aug 19, 2026</t>
+          <t>Oct 16, 2026</t>
         </is>
       </c>
       <c r="H88" t="inlineStr"/>
       <c r="I88" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>125-132</t>
+          <t>105-112</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>132000</t>
+          <t>134400</t>
         </is>
       </c>
       <c r="L88" t="inlineStr"/>
@@ -6796,19 +6828,19 @@
       <c r="P88" t="inlineStr"/>
       <c r="Q88" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/technocratsplasmasystemsltd/TPSL</t>
+          <t>https://www.moneycontrol.com/ipo/ravitaengineeringservicesltd/RESL</t>
         </is>
       </c>
       <c r="R88" t="inlineStr">
         <is>
-          <t>2026-08-11 21:41:02</t>
+          <t>2026-10-08 16:06:11</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Unitec Fibres Ltd</t>
+          <t>Shanti Inorganics Ltd</t>
         </is>
       </c>
       <c r="B89" t="inlineStr"/>
@@ -6820,17 +6852,17 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Sep 23, 2026</t>
+          <t>Aug 31, 2026</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Sep 25, 2026</t>
+          <t>Sep 02, 2026</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Sep 28, 2026</t>
+          <t>Sep 03, 2026</t>
         </is>
       </c>
       <c r="H89" t="inlineStr"/>
@@ -6841,12 +6873,12 @@
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>83-88</t>
+          <t>79-83</t>
         </is>
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>140800</t>
+          <t>132800</t>
         </is>
       </c>
       <c r="L89" t="inlineStr"/>
@@ -6856,19 +6888,19 @@
       <c r="P89" t="inlineStr"/>
       <c r="Q89" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/unitecfibresltd/UFL03</t>
+          <t>https://www.moneycontrol.com/ipo/shantiinorganicsltd/SIL34</t>
         </is>
       </c>
       <c r="R89" t="inlineStr">
         <is>
-          <t>2026-09-18 23:59:33</t>
+          <t>2026-08-25 09:29:52</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>VANS Electroengineerings Ltd</t>
+          <t>Technocrats Plasma Systems Ltd</t>
         </is>
       </c>
       <c r="B90" t="inlineStr"/>
@@ -6880,33 +6912,33 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Sep 29, 2026</t>
+          <t>Aug 14, 2026</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Oct 01, 2026</t>
+          <t>Aug 18, 2026</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Oct 05, 2026</t>
+          <t>Aug 19, 2026</t>
         </is>
       </c>
       <c r="H90" t="inlineStr"/>
       <c r="I90" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>112-118</t>
+          <t>125-132</t>
         </is>
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>141600</t>
+          <t>132000</t>
         </is>
       </c>
       <c r="L90" t="inlineStr"/>
@@ -6916,19 +6948,19 @@
       <c r="P90" t="inlineStr"/>
       <c r="Q90" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/vanselectroengineeringsltd/VEL03</t>
+          <t>https://www.moneycontrol.com/ipo/technocratsplasmasystemsltd/TPSL</t>
         </is>
       </c>
       <c r="R90" t="inlineStr">
         <is>
-          <t>2026-09-25 14:20:09</t>
+          <t>2026-08-11 21:41:02</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Vaibhav Vyapaar Ltd</t>
+          <t>Unitec Fibres Ltd</t>
         </is>
       </c>
       <c r="B91" t="inlineStr"/>
@@ -6940,33 +6972,33 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Oct 13, 2026</t>
+          <t>Sep 23, 2026</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Oct 15, 2026</t>
+          <t>Sep 25, 2026</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Oct 16, 2026</t>
+          <t>Sep 28, 2026</t>
         </is>
       </c>
       <c r="H91" t="inlineStr"/>
       <c r="I91" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>1600</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>50-52</t>
+          <t>83-88</t>
         </is>
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>104000</t>
+          <t>140800</t>
         </is>
       </c>
       <c r="L91" t="inlineStr"/>
@@ -6976,19 +7008,19 @@
       <c r="P91" t="inlineStr"/>
       <c r="Q91" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/vaibhavvyapaarltd/VVL01</t>
+          <t>https://www.moneycontrol.com/ipo/unitecfibresltd/UFL03</t>
         </is>
       </c>
       <c r="R91" t="inlineStr">
         <is>
-          <t>2026-10-08 16:06:11</t>
+          <t>2026-09-18 23:59:33</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Vama Wovenfab Ltd</t>
+          <t>VANS Electroengineerings Ltd</t>
         </is>
       </c>
       <c r="B92" t="inlineStr"/>
@@ -7000,33 +7032,33 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Sep 15, 2026</t>
+          <t>Sep 29, 2026</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Sep 17, 2026</t>
+          <t>Oct 01, 2026</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Sep 18, 2026</t>
+          <t>Oct 05, 2026</t>
         </is>
       </c>
       <c r="H92" t="inlineStr"/>
       <c r="I92" t="inlineStr">
         <is>
-          <t>400</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>324-341</t>
+          <t>112-118</t>
         </is>
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>136400</t>
+          <t>141600</t>
         </is>
       </c>
       <c r="L92" t="inlineStr"/>
@@ -7036,17 +7068,137 @@
       <c r="P92" t="inlineStr"/>
       <c r="Q92" t="inlineStr">
         <is>
+          <t>https://www.moneycontrol.com/ipo/vanselectroengineeringsltd/VEL03</t>
+        </is>
+      </c>
+      <c r="R92" t="inlineStr">
+        <is>
+          <t>2026-09-25 14:20:09</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>Vaibhav Vyapaar Ltd</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr"/>
+      <c r="C93" t="inlineStr"/>
+      <c r="D93" s="5" t="inlineStr">
+        <is>
+          <t>Upcoming</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>Oct 13, 2026</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>Oct 15, 2026</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>Oct 16, 2026</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr"/>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>50-52</t>
+        </is>
+      </c>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>104000</t>
+        </is>
+      </c>
+      <c r="L93" t="inlineStr"/>
+      <c r="M93" t="inlineStr"/>
+      <c r="N93" t="inlineStr"/>
+      <c r="O93" t="inlineStr"/>
+      <c r="P93" t="inlineStr"/>
+      <c r="Q93" t="inlineStr">
+        <is>
+          <t>https://www.moneycontrol.com/ipo/vaibhavvyapaarltd/VVL01</t>
+        </is>
+      </c>
+      <c r="R93" t="inlineStr">
+        <is>
+          <t>2026-10-08 16:06:11</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>Vama Wovenfab Ltd</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr"/>
+      <c r="C94" t="inlineStr"/>
+      <c r="D94" s="5" t="inlineStr">
+        <is>
+          <t>Upcoming</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>Sep 15, 2026</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>Sep 17, 2026</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>Sep 18, 2026</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr"/>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>400</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>324-341</t>
+        </is>
+      </c>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>136400</t>
+        </is>
+      </c>
+      <c r="L94" t="inlineStr"/>
+      <c r="M94" t="inlineStr"/>
+      <c r="N94" t="inlineStr"/>
+      <c r="O94" t="inlineStr"/>
+      <c r="P94" t="inlineStr"/>
+      <c r="Q94" t="inlineStr">
+        <is>
           <t>https://www.moneycontrol.com/ipo/vamawovenfabltd/VWL01</t>
         </is>
       </c>
-      <c r="R92" t="inlineStr">
+      <c r="R94" t="inlineStr">
         <is>
           <t>2026-09-11 13:34:16</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:R92"/>
+  <autoFilter ref="A1:R94"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/mainboard_ipos.xlsx
+++ b/data/mainboard_ipos.xlsx
@@ -5261,15 +5261,31 @@
           <t>14739</t>
         </is>
       </c>
-      <c r="L63" t="inlineStr"/>
-      <c r="M63" t="inlineStr"/>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>305</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>15555</t>
+        </is>
+      </c>
       <c r="N63" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="O63" t="inlineStr"/>
-      <c r="P63" t="inlineStr"/>
+      <c r="O63" t="inlineStr">
+        <is>
+          <t>816</t>
+        </is>
+      </c>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="Q63" t="inlineStr">
         <is>
           <t>https://www.moneycontrol.com/ipo/bpoites/fusioncx/FCL02</t>
@@ -5277,7 +5293,7 @@
       </c>
       <c r="R63" t="inlineStr">
         <is>
-          <t>2026-10-22 14:07:33</t>
+          <t>2026-10-23 14:03:21</t>
         </is>
       </c>
     </row>
@@ -5289,9 +5305,9 @@
       </c>
       <c r="B64" t="inlineStr"/>
       <c r="C64" t="inlineStr"/>
-      <c r="D64" s="3" t="inlineStr">
-        <is>
-          <t>Closed</t>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>Listed</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -5340,12 +5356,12 @@
       <c r="P64" t="inlineStr"/>
       <c r="Q64" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/bonfigliolitransmissions/BTL04</t>
+          <t>https://www.moneycontrol.com/ipo/engineering-industrial-equipments/bonfigliolitransmissions/BTL04</t>
         </is>
       </c>
       <c r="R64" t="inlineStr">
         <is>
-          <t>2026-10-22 14:07:33</t>
+          <t>2026-10-23 14:03:21</t>
         </is>
       </c>
     </row>
@@ -5357,9 +5373,9 @@
       </c>
       <c r="B65" t="inlineStr"/>
       <c r="C65" t="inlineStr"/>
-      <c r="D65" s="3" t="inlineStr">
-        <is>
-          <t>Closed</t>
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t>Listed</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -5408,12 +5424,12 @@
       <c r="P65" t="inlineStr"/>
       <c r="Q65" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/sahajanandmedicaltechnologies/SMTL</t>
+          <t>https://www.moneycontrol.com/ipo/medical-equipmentsuppliesaccessories/sahajanandmedicaltechnologies/SMTL</t>
         </is>
       </c>
       <c r="R65" t="inlineStr">
         <is>
-          <t>2026-10-22 14:07:33</t>
+          <t>2026-10-23 14:03:21</t>
         </is>
       </c>
     </row>
@@ -5425,9 +5441,9 @@
       </c>
       <c r="B66" t="inlineStr"/>
       <c r="C66" t="inlineStr"/>
-      <c r="D66" s="3" t="inlineStr">
-        <is>
-          <t>Closed</t>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>Listed</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -5476,12 +5492,12 @@
       <c r="P66" t="inlineStr"/>
       <c r="Q66" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/tonboimagingindia/TIIL</t>
+          <t>https://www.moneycontrol.com/ipo/defence/tonboimagingindia/TIIL</t>
         </is>
       </c>
       <c r="R66" t="inlineStr">
         <is>
-          <t>2026-10-22 14:07:33</t>
+          <t>2026-10-23 14:03:21</t>
         </is>
       </c>
     </row>
@@ -5493,9 +5509,9 @@
       </c>
       <c r="B67" t="inlineStr"/>
       <c r="C67" t="inlineStr"/>
-      <c r="D67" s="3" t="inlineStr">
-        <is>
-          <t>Closed</t>
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t>Listed</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -5544,12 +5560,12 @@
       <c r="P67" t="inlineStr"/>
       <c r="Q67" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/zetwerkmanufacturingbusinesses/ZMBL</t>
+          <t>https://www.moneycontrol.com/ipo/engineering-industrial-equipments/zetwerkmanufacturingbusinesses/ZMBL</t>
         </is>
       </c>
       <c r="R67" t="inlineStr">
         <is>
-          <t>2026-10-22 14:07:33</t>
+          <t>2026-10-23 14:03:21</t>
         </is>
       </c>
     </row>
@@ -5605,7 +5621,7 @@
       <c r="M68" t="inlineStr"/>
       <c r="N68" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="O68" t="inlineStr"/>
@@ -5617,7 +5633,7 @@
       </c>
       <c r="R68" t="inlineStr">
         <is>
-          <t>2026-10-22 14:07:33</t>
+          <t>2026-10-23 14:03:21</t>
         </is>
       </c>
     </row>
@@ -5685,7 +5701,7 @@
       </c>
       <c r="R69" t="inlineStr">
         <is>
-          <t>2026-10-22 14:07:33</t>
+          <t>2026-10-23 14:03:21</t>
         </is>
       </c>
     </row>
@@ -5749,7 +5765,7 @@
       </c>
       <c r="R70" t="inlineStr">
         <is>
-          <t>2026-10-22 14:07:33</t>
+          <t>2026-10-23 14:03:21</t>
         </is>
       </c>
     </row>
@@ -5813,7 +5829,7 @@
       </c>
       <c r="R71" t="inlineStr">
         <is>
-          <t>2026-10-22 14:07:33</t>
+          <t>2026-10-23 14:03:21</t>
         </is>
       </c>
     </row>
@@ -5877,7 +5893,7 @@
       </c>
       <c r="R72" t="inlineStr">
         <is>
-          <t>2026-10-22 14:07:33</t>
+          <t>2026-10-23 14:03:21</t>
         </is>
       </c>
     </row>

--- a/data/mainboard_ipos.xlsx
+++ b/data/mainboard_ipos.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Mainboard IPOs" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Mainboard IPOs'!$A$1:$R$94</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Mainboard IPOs'!$A$1:$R$96</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -449,7 +449,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R94"/>
+  <dimension ref="A1:R96"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -5293,7 +5293,7 @@
       </c>
       <c r="R63" t="inlineStr">
         <is>
-          <t>2026-10-23 14:03:21</t>
+          <t>2026-10-24 13:38:31</t>
         </is>
       </c>
     </row>
@@ -5345,15 +5345,31 @@
           <t>14650</t>
         </is>
       </c>
-      <c r="L64" t="inlineStr"/>
-      <c r="M64" t="inlineStr"/>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>586</t>
+        </is>
+      </c>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>14650</t>
+        </is>
+      </c>
       <c r="N64" t="inlineStr">
         <is>
           <t>46</t>
         </is>
       </c>
-      <c r="O64" t="inlineStr"/>
-      <c r="P64" t="inlineStr"/>
+      <c r="O64" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="Q64" t="inlineStr">
         <is>
           <t>https://www.moneycontrol.com/ipo/engineering-industrial-equipments/bonfigliolitransmissions/BTL04</t>
@@ -5361,7 +5377,7 @@
       </c>
       <c r="R64" t="inlineStr">
         <is>
-          <t>2026-10-23 14:03:21</t>
+          <t>2026-10-24 13:38:31</t>
         </is>
       </c>
     </row>
@@ -5413,15 +5429,31 @@
           <t>14792</t>
         </is>
       </c>
-      <c r="L65" t="inlineStr"/>
-      <c r="M65" t="inlineStr"/>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>371</t>
+        </is>
+      </c>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>15953</t>
+        </is>
+      </c>
       <c r="N65" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="O65" t="inlineStr"/>
-      <c r="P65" t="inlineStr"/>
+      <c r="O65" t="inlineStr">
+        <is>
+          <t>1161</t>
+        </is>
+      </c>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
       <c r="Q65" t="inlineStr">
         <is>
           <t>https://www.moneycontrol.com/ipo/medical-equipmentsuppliesaccessories/sahajanandmedicaltechnologies/SMTL</t>
@@ -5429,7 +5461,7 @@
       </c>
       <c r="R65" t="inlineStr">
         <is>
-          <t>2026-10-23 14:03:21</t>
+          <t>2026-10-24 13:38:31</t>
         </is>
       </c>
     </row>
@@ -5481,15 +5513,31 @@
           <t>14700</t>
         </is>
       </c>
-      <c r="L66" t="inlineStr"/>
-      <c r="M66" t="inlineStr"/>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>1160</t>
+        </is>
+      </c>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>24360</t>
+        </is>
+      </c>
       <c r="N66" t="inlineStr">
         <is>
           <t>136</t>
         </is>
       </c>
-      <c r="O66" t="inlineStr"/>
-      <c r="P66" t="inlineStr"/>
+      <c r="O66" t="inlineStr">
+        <is>
+          <t>9660</t>
+        </is>
+      </c>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
       <c r="Q66" t="inlineStr">
         <is>
           <t>https://www.moneycontrol.com/ipo/defence/tonboimagingindia/TIIL</t>
@@ -5497,7 +5545,7 @@
       </c>
       <c r="R66" t="inlineStr">
         <is>
-          <t>2026-10-23 14:03:21</t>
+          <t>2026-10-24 13:38:31</t>
         </is>
       </c>
     </row>
@@ -5549,15 +5597,31 @@
           <t>14949</t>
         </is>
       </c>
-      <c r="L67" t="inlineStr"/>
-      <c r="M67" t="inlineStr"/>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>159</t>
+        </is>
+      </c>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>15741</t>
+        </is>
+      </c>
       <c r="N67" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="O67" t="inlineStr"/>
-      <c r="P67" t="inlineStr"/>
+      <c r="O67" t="inlineStr">
+        <is>
+          <t>792</t>
+        </is>
+      </c>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="Q67" t="inlineStr">
         <is>
           <t>https://www.moneycontrol.com/ipo/engineering-industrial-equipments/zetwerkmanufacturingbusinesses/ZMBL</t>
@@ -5565,7 +5629,7 @@
       </c>
       <c r="R67" t="inlineStr">
         <is>
-          <t>2026-10-23 14:03:21</t>
+          <t>2026-10-24 13:38:31</t>
         </is>
       </c>
     </row>
@@ -5577,9 +5641,9 @@
       </c>
       <c r="B68" t="inlineStr"/>
       <c r="C68" t="inlineStr"/>
-      <c r="D68" s="4" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="D68" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -5621,7 +5685,7 @@
       <c r="M68" t="inlineStr"/>
       <c r="N68" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>22</t>
         </is>
       </c>
       <c r="O68" t="inlineStr"/>
@@ -5633,7 +5697,7 @@
       </c>
       <c r="R68" t="inlineStr">
         <is>
-          <t>2026-10-23 14:03:21</t>
+          <t>2026-10-24 13:38:31</t>
         </is>
       </c>
     </row>
@@ -5645,9 +5709,9 @@
       </c>
       <c r="B69" t="inlineStr"/>
       <c r="C69" t="inlineStr"/>
-      <c r="D69" s="4" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="D69" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -5689,7 +5753,7 @@
       <c r="M69" t="inlineStr"/>
       <c r="N69" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O69" t="inlineStr"/>
@@ -5701,7 +5765,7 @@
       </c>
       <c r="R69" t="inlineStr">
         <is>
-          <t>2026-10-23 14:03:21</t>
+          <t>2026-10-24 13:38:31</t>
         </is>
       </c>
     </row>
@@ -5765,7 +5829,7 @@
       </c>
       <c r="R70" t="inlineStr">
         <is>
-          <t>2026-10-23 14:03:21</t>
+          <t>2026-10-24 13:38:31</t>
         </is>
       </c>
     </row>
@@ -5829,7 +5893,7 @@
       </c>
       <c r="R71" t="inlineStr">
         <is>
-          <t>2026-10-23 14:03:21</t>
+          <t>2026-10-24 13:38:31</t>
         </is>
       </c>
     </row>
@@ -5893,14 +5957,14 @@
       </c>
       <c r="R72" t="inlineStr">
         <is>
-          <t>2026-10-23 14:03:21</t>
+          <t>2026-10-24 13:38:31</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Complete Sports and Management India Ltd</t>
+          <t>M K Sons Fine Jewels Ltd</t>
         </is>
       </c>
       <c r="B73" t="inlineStr"/>
@@ -5912,33 +5976,37 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Aug 28, 2026</t>
+          <t>Oct 28, 2026</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Sep 01, 2026</t>
+          <t>Oct 30, 2026</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Sep 02, 2026</t>
-        </is>
-      </c>
-      <c r="H73" t="inlineStr"/>
+          <t>Nov 02, 2026</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>Nov 04, 2026</t>
+        </is>
+      </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>91</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>128-135</t>
+          <t>153-162</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>135000</t>
+          <t>14742</t>
         </is>
       </c>
       <c r="L73" t="inlineStr"/>
@@ -5948,19 +6016,19 @@
       <c r="P73" t="inlineStr"/>
       <c r="Q73" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/completesportsmanagementindialtd/CSMIL</t>
+          <t>https://www.moneycontrol.com/ipo/mksonsfinejewelsltd/SFJ</t>
         </is>
       </c>
       <c r="R73" t="inlineStr">
         <is>
-          <t>2026-08-25 09:29:52</t>
+          <t>2026-10-24 13:38:31</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Core4 Engineers Ltd</t>
+          <t>Bombay Coated and Special Steels Ltd</t>
         </is>
       </c>
       <c r="B74" t="inlineStr"/>
@@ -5972,33 +6040,37 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Oct 23, 2026</t>
+          <t>Oct 29, 2026</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Oct 27, 2026</t>
+          <t>Nov 02, 2026</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Oct 28, 2026</t>
-        </is>
-      </c>
-      <c r="H74" t="inlineStr"/>
+          <t>Nov 03, 2026</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>Nov 05, 2026</t>
+        </is>
+      </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>182</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>88-93</t>
+          <t>78-82</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>111600</t>
+          <t>14924</t>
         </is>
       </c>
       <c r="L74" t="inlineStr"/>
@@ -6008,19 +6080,19 @@
       <c r="P74" t="inlineStr"/>
       <c r="Q74" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/core4engineersltd/CEL05</t>
+          <t>https://www.moneycontrol.com/ipo/bombaycoatedspecialsteelsltd/BCSSL</t>
         </is>
       </c>
       <c r="R74" t="inlineStr">
         <is>
-          <t>2026-10-20 14:03:23</t>
+          <t>2026-10-24 13:38:31</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Coreintegra Consulting Services</t>
+          <t>Complete Sports and Management India Ltd</t>
         </is>
       </c>
       <c r="B75" t="inlineStr"/>
@@ -6032,33 +6104,33 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Sep 23, 2026</t>
+          <t>Aug 28, 2026</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Sep 25, 2026</t>
+          <t>Sep 01, 2026</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Sep 28, 2026</t>
+          <t>Sep 02, 2026</t>
         </is>
       </c>
       <c r="H75" t="inlineStr"/>
       <c r="I75" t="inlineStr">
         <is>
-          <t>1600</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>74-78</t>
+          <t>128-135</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>124800</t>
+          <t>135000</t>
         </is>
       </c>
       <c r="L75" t="inlineStr"/>
@@ -6068,19 +6140,19 @@
       <c r="P75" t="inlineStr"/>
       <c r="Q75" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/coreintegraconsultingservices/CCSL</t>
+          <t>https://www.moneycontrol.com/ipo/completesportsmanagementindialtd/CSMIL</t>
         </is>
       </c>
       <c r="R75" t="inlineStr">
         <is>
-          <t>2026-09-22 14:03:25</t>
+          <t>2026-08-25 09:29:52</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Credent Connect N Care Ltd</t>
+          <t>Core4 Engineers Ltd</t>
         </is>
       </c>
       <c r="B76" t="inlineStr"/>
@@ -6092,33 +6164,33 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Aug 13, 2026</t>
+          <t>Oct 23, 2026</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Aug 17, 2026</t>
+          <t>Oct 27, 2026</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Aug 18, 2026</t>
+          <t>Oct 28, 2026</t>
         </is>
       </c>
       <c r="H76" t="inlineStr"/>
       <c r="I76" t="inlineStr">
         <is>
-          <t>600</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>179-189</t>
+          <t>88-93</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>113400</t>
+          <t>111600</t>
         </is>
       </c>
       <c r="L76" t="inlineStr"/>
@@ -6128,19 +6200,19 @@
       <c r="P76" t="inlineStr"/>
       <c r="Q76" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/credentconnectncareltd/CCC04</t>
+          <t>https://www.moneycontrol.com/ipo/core4engineersltd/CEL05</t>
         </is>
       </c>
       <c r="R76" t="inlineStr">
         <is>
-          <t>2026-08-10 22:43:12</t>
+          <t>2026-10-20 14:03:23</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Dove Soft Ltd</t>
+          <t>Coreintegra Consulting Services</t>
         </is>
       </c>
       <c r="B77" t="inlineStr"/>
@@ -6152,33 +6224,33 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Sep 30, 2026</t>
+          <t>Sep 23, 2026</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Oct 05, 2026</t>
+          <t>Sep 25, 2026</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Oct 06, 2026</t>
+          <t>Sep 28, 2026</t>
         </is>
       </c>
       <c r="H77" t="inlineStr"/>
       <c r="I77" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>1600</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>104-111</t>
+          <t>74-78</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>133200</t>
+          <t>124800</t>
         </is>
       </c>
       <c r="L77" t="inlineStr"/>
@@ -6188,19 +6260,19 @@
       <c r="P77" t="inlineStr"/>
       <c r="Q77" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/dovesoftltd/DSL04</t>
+          <t>https://www.moneycontrol.com/ipo/coreintegraconsultingservices/CCSL</t>
         </is>
       </c>
       <c r="R77" t="inlineStr">
         <is>
-          <t>2026-09-25 14:20:09</t>
+          <t>2026-09-22 14:03:25</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Farm Peace Ltd</t>
+          <t>Credent Connect N Care Ltd</t>
         </is>
       </c>
       <c r="B78" t="inlineStr"/>
@@ -6212,33 +6284,33 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Sep 01, 2026</t>
+          <t>Aug 13, 2026</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Sep 03, 2026</t>
+          <t>Aug 17, 2026</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Sep 04, 2026</t>
+          <t>Aug 18, 2026</t>
         </is>
       </c>
       <c r="H78" t="inlineStr"/>
       <c r="I78" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>600</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>179-189</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>118000</t>
+          <t>113400</t>
         </is>
       </c>
       <c r="L78" t="inlineStr"/>
@@ -6248,19 +6320,19 @@
       <c r="P78" t="inlineStr"/>
       <c r="Q78" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/farmpeaceltd/FPL02</t>
+          <t>https://www.moneycontrol.com/ipo/credentconnectncareltd/CCC04</t>
         </is>
       </c>
       <c r="R78" t="inlineStr">
         <is>
-          <t>2026-08-27 19:43:03</t>
+          <t>2026-08-10 22:43:12</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Green Asia Impex Ltd</t>
+          <t>Dove Soft Ltd</t>
         </is>
       </c>
       <c r="B79" t="inlineStr"/>
@@ -6272,33 +6344,33 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Sep 24, 2026</t>
+          <t>Sep 30, 2026</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Sep 28, 2026</t>
+          <t>Oct 05, 2026</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Sep 29, 2026</t>
+          <t>Oct 06, 2026</t>
         </is>
       </c>
       <c r="H79" t="inlineStr"/>
       <c r="I79" t="inlineStr">
         <is>
-          <t>1600</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>85-90</t>
+          <t>104-111</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>144000</t>
+          <t>133200</t>
         </is>
       </c>
       <c r="L79" t="inlineStr"/>
@@ -6308,19 +6380,19 @@
       <c r="P79" t="inlineStr"/>
       <c r="Q79" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/greenasiaimpexltd/GAIL01</t>
+          <t>https://www.moneycontrol.com/ipo/dovesoftltd/DSL04</t>
         </is>
       </c>
       <c r="R79" t="inlineStr">
         <is>
-          <t>2026-09-22 14:03:25</t>
+          <t>2026-09-25 14:20:09</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Kheria Autocomp Ltd</t>
+          <t>Farm Peace Ltd</t>
         </is>
       </c>
       <c r="B80" t="inlineStr"/>
@@ -6332,33 +6404,33 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Sep 17, 2026</t>
+          <t>Sep 01, 2026</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Sep 21, 2026</t>
+          <t>Sep 03, 2026</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Sep 22, 2026</t>
+          <t>Sep 04, 2026</t>
         </is>
       </c>
       <c r="H80" t="inlineStr"/>
       <c r="I80" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>96-101</t>
+          <t>59</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>121200</t>
+          <t>118000</t>
         </is>
       </c>
       <c r="L80" t="inlineStr"/>
@@ -6368,19 +6440,19 @@
       <c r="P80" t="inlineStr"/>
       <c r="Q80" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/kheriaautocompltd/KAL05</t>
+          <t>https://www.moneycontrol.com/ipo/farmpeaceltd/FPL02</t>
         </is>
       </c>
       <c r="R80" t="inlineStr">
         <is>
-          <t>2026-09-11 13:34:16</t>
+          <t>2026-08-27 19:43:03</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Mopshop Distribution Ltd</t>
+          <t>Green Asia Impex Ltd</t>
         </is>
       </c>
       <c r="B81" t="inlineStr"/>
@@ -6392,33 +6464,33 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Aug 19, 2026</t>
+          <t>Sep 24, 2026</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Aug 21, 2026</t>
+          <t>Sep 28, 2026</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Aug 24, 2026</t>
+          <t>Sep 29, 2026</t>
         </is>
       </c>
       <c r="H81" t="inlineStr"/>
       <c r="I81" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>1600</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>138</t>
+          <t>85-90</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>138000</t>
+          <t>144000</t>
         </is>
       </c>
       <c r="L81" t="inlineStr"/>
@@ -6428,19 +6500,19 @@
       <c r="P81" t="inlineStr"/>
       <c r="Q81" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/mopshopdistributionltd/MDL03</t>
+          <t>https://www.moneycontrol.com/ipo/greenasiaimpexltd/GAIL01</t>
         </is>
       </c>
       <c r="R81" t="inlineStr">
         <is>
-          <t>2026-08-14 21:36:23</t>
+          <t>2026-09-22 14:03:25</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Paluck Technologies Ltd</t>
+          <t>Kheria Autocomp Ltd</t>
         </is>
       </c>
       <c r="B82" t="inlineStr"/>
@@ -6452,33 +6524,33 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Aug 28, 2026</t>
+          <t>Sep 17, 2026</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Sep 01, 2026</t>
+          <t>Sep 21, 2026</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Sep 02, 2026</t>
+          <t>Sep 22, 2026</t>
         </is>
       </c>
       <c r="H82" t="inlineStr"/>
       <c r="I82" t="inlineStr">
         <is>
-          <t>3000</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>46-48</t>
+          <t>96-101</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>144000</t>
+          <t>121200</t>
         </is>
       </c>
       <c r="L82" t="inlineStr"/>
@@ -6488,19 +6560,19 @@
       <c r="P82" t="inlineStr"/>
       <c r="Q82" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/palucktechnologiesltd/PTL08</t>
+          <t>https://www.moneycontrol.com/ipo/kheriaautocompltd/KAL05</t>
         </is>
       </c>
       <c r="R82" t="inlineStr">
         <is>
-          <t>2026-08-25 09:29:52</t>
+          <t>2026-09-11 13:34:16</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Papadmalji Agro Foods Ltd</t>
+          <t>Mopshop Distribution Ltd</t>
         </is>
       </c>
       <c r="B83" t="inlineStr"/>
@@ -6512,33 +6584,33 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Sep 29, 2026</t>
+          <t>Aug 19, 2026</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Oct 01, 2026</t>
+          <t>Aug 21, 2026</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Oct 05, 2026</t>
+          <t>Aug 24, 2026</t>
         </is>
       </c>
       <c r="H83" t="inlineStr"/>
       <c r="I83" t="inlineStr">
         <is>
-          <t>1600</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>69-72</t>
+          <t>138</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>115200</t>
+          <t>138000</t>
         </is>
       </c>
       <c r="L83" t="inlineStr"/>
@@ -6548,19 +6620,19 @@
       <c r="P83" t="inlineStr"/>
       <c r="Q83" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/papadmaljiagrofoodsltd/PAF</t>
+          <t>https://www.moneycontrol.com/ipo/mopshopdistributionltd/MDL03</t>
         </is>
       </c>
       <c r="R83" t="inlineStr">
         <is>
-          <t>2026-09-25 14:20:09</t>
+          <t>2026-08-14 21:36:23</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Paramount Syntex Ltd</t>
+          <t>Paluck Technologies Ltd</t>
         </is>
       </c>
       <c r="B84" t="inlineStr"/>
@@ -6572,33 +6644,33 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Sep 30, 2026</t>
+          <t>Aug 28, 2026</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Oct 06, 2026</t>
+          <t>Sep 01, 2026</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Oct 07, 2026</t>
+          <t>Sep 02, 2026</t>
         </is>
       </c>
       <c r="H84" t="inlineStr"/>
       <c r="I84" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>3000</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>119-127</t>
+          <t>46-48</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>127000</t>
+          <t>144000</t>
         </is>
       </c>
       <c r="L84" t="inlineStr"/>
@@ -6608,19 +6680,19 @@
       <c r="P84" t="inlineStr"/>
       <c r="Q84" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/paramountsyntexltd/PSL06</t>
+          <t>https://www.moneycontrol.com/ipo/palucktechnologiesltd/PTL08</t>
         </is>
       </c>
       <c r="R84" t="inlineStr">
         <is>
-          <t>2026-09-25 14:20:09</t>
+          <t>2026-08-25 09:29:52</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Peshwa Wheat</t>
+          <t>Papadmalji Agro Foods Ltd</t>
         </is>
       </c>
       <c r="B85" t="inlineStr"/>
@@ -6632,33 +6704,33 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Sep 24, 2026</t>
+          <t>Sep 29, 2026</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Sep 28, 2026</t>
+          <t>Oct 01, 2026</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Sep 29, 2026</t>
+          <t>Oct 05, 2026</t>
         </is>
       </c>
       <c r="H85" t="inlineStr"/>
       <c r="I85" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>1600</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>95-101</t>
+          <t>69-72</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>121200</t>
+          <t>115200</t>
         </is>
       </c>
       <c r="L85" t="inlineStr"/>
@@ -6668,75 +6740,79 @@
       <c r="P85" t="inlineStr"/>
       <c r="Q85" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/peshwawheat/PWL01</t>
+          <t>https://www.moneycontrol.com/ipo/papadmaljiagrofoodsltd/PAF</t>
         </is>
       </c>
       <c r="R85" t="inlineStr">
         <is>
-          <t>2026-09-22 14:03:25</t>
+          <t>2026-09-25 14:20:09</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Purple Style Labs Ltd</t>
+          <t>Paramount Syntex Ltd</t>
         </is>
       </c>
       <c r="B86" t="inlineStr"/>
       <c r="C86" t="inlineStr"/>
-      <c r="D86" s="4" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="D86" s="5" t="inlineStr">
+        <is>
+          <t>Upcoming</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Aug 31, 2026</t>
+          <t>Sep 30, 2026</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Sep 02, 2026</t>
+          <t>Oct 06, 2026</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Sep 03, 2026</t>
+          <t>Oct 07, 2026</t>
         </is>
       </c>
       <c r="H86" t="inlineStr"/>
-      <c r="I86" t="inlineStr"/>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>575</t>
-        </is>
-      </c>
-      <c r="K86" t="inlineStr"/>
+          <t>119-127</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>127000</t>
+        </is>
+      </c>
       <c r="L86" t="inlineStr"/>
       <c r="M86" t="inlineStr"/>
-      <c r="N86" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="N86" t="inlineStr"/>
       <c r="O86" t="inlineStr"/>
       <c r="P86" t="inlineStr"/>
       <c r="Q86" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/purplestylelabsltd/PSL05</t>
+          <t>https://www.moneycontrol.com/ipo/paramountsyntexltd/PSL06</t>
         </is>
       </c>
       <c r="R86" t="inlineStr">
         <is>
-          <t>2026-09-02 13:25:30</t>
+          <t>2026-09-25 14:20:09</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Q&amp;T Foods Ltd</t>
+          <t>Peshwa Wheat</t>
         </is>
       </c>
       <c r="B87" t="inlineStr"/>
@@ -6748,17 +6824,17 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Aug 12, 2026</t>
+          <t>Sep 24, 2026</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Aug 14, 2026</t>
+          <t>Sep 28, 2026</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Aug 17, 2026</t>
+          <t>Sep 29, 2026</t>
         </is>
       </c>
       <c r="H87" t="inlineStr"/>
@@ -6769,12 +6845,12 @@
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>115</t>
+          <t>95-101</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>138000</t>
+          <t>121200</t>
         </is>
       </c>
       <c r="L87" t="inlineStr"/>
@@ -6784,79 +6860,75 @@
       <c r="P87" t="inlineStr"/>
       <c r="Q87" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/qtfoodsltd/QFL</t>
+          <t>https://www.moneycontrol.com/ipo/peshwawheat/PWL01</t>
         </is>
       </c>
       <c r="R87" t="inlineStr">
         <is>
-          <t>2026-08-10 10:24:29</t>
+          <t>2026-09-22 14:03:25</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Ravita Engineering Services Ltd</t>
+          <t>Purple Style Labs Ltd</t>
         </is>
       </c>
       <c r="B88" t="inlineStr"/>
       <c r="C88" t="inlineStr"/>
-      <c r="D88" s="5" t="inlineStr">
-        <is>
-          <t>Upcoming</t>
+      <c r="D88" s="4" t="inlineStr">
+        <is>
+          <t>Open</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Oct 13, 2026</t>
+          <t>Aug 31, 2026</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Oct 15, 2026</t>
+          <t>Sep 02, 2026</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Oct 16, 2026</t>
+          <t>Sep 03, 2026</t>
         </is>
       </c>
       <c r="H88" t="inlineStr"/>
-      <c r="I88" t="inlineStr">
-        <is>
-          <t>1200</t>
-        </is>
-      </c>
+      <c r="I88" t="inlineStr"/>
       <c r="J88" t="inlineStr">
         <is>
-          <t>105-112</t>
-        </is>
-      </c>
-      <c r="K88" t="inlineStr">
-        <is>
-          <t>134400</t>
-        </is>
-      </c>
+          <t>575</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr"/>
       <c r="L88" t="inlineStr"/>
       <c r="M88" t="inlineStr"/>
-      <c r="N88" t="inlineStr"/>
+      <c r="N88" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="O88" t="inlineStr"/>
       <c r="P88" t="inlineStr"/>
       <c r="Q88" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/ravitaengineeringservicesltd/RESL</t>
+          <t>https://www.moneycontrol.com/ipo/purplestylelabsltd/PSL05</t>
         </is>
       </c>
       <c r="R88" t="inlineStr">
         <is>
-          <t>2026-10-08 16:06:11</t>
+          <t>2026-09-02 13:25:30</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Shanti Inorganics Ltd</t>
+          <t>Q&amp;T Foods Ltd</t>
         </is>
       </c>
       <c r="B89" t="inlineStr"/>
@@ -6868,33 +6940,33 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Aug 31, 2026</t>
+          <t>Aug 12, 2026</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Sep 02, 2026</t>
+          <t>Aug 14, 2026</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Sep 03, 2026</t>
+          <t>Aug 17, 2026</t>
         </is>
       </c>
       <c r="H89" t="inlineStr"/>
       <c r="I89" t="inlineStr">
         <is>
-          <t>1600</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>79-83</t>
+          <t>115</t>
         </is>
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>132800</t>
+          <t>138000</t>
         </is>
       </c>
       <c r="L89" t="inlineStr"/>
@@ -6904,19 +6976,19 @@
       <c r="P89" t="inlineStr"/>
       <c r="Q89" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/shantiinorganicsltd/SIL34</t>
+          <t>https://www.moneycontrol.com/ipo/qtfoodsltd/QFL</t>
         </is>
       </c>
       <c r="R89" t="inlineStr">
         <is>
-          <t>2026-08-25 09:29:52</t>
+          <t>2026-08-10 10:24:29</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Technocrats Plasma Systems Ltd</t>
+          <t>Ravita Engineering Services Ltd</t>
         </is>
       </c>
       <c r="B90" t="inlineStr"/>
@@ -6928,33 +7000,33 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Aug 14, 2026</t>
+          <t>Oct 13, 2026</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Aug 18, 2026</t>
+          <t>Oct 15, 2026</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Aug 19, 2026</t>
+          <t>Oct 16, 2026</t>
         </is>
       </c>
       <c r="H90" t="inlineStr"/>
       <c r="I90" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>125-132</t>
+          <t>105-112</t>
         </is>
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>132000</t>
+          <t>134400</t>
         </is>
       </c>
       <c r="L90" t="inlineStr"/>
@@ -6964,19 +7036,19 @@
       <c r="P90" t="inlineStr"/>
       <c r="Q90" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/technocratsplasmasystemsltd/TPSL</t>
+          <t>https://www.moneycontrol.com/ipo/ravitaengineeringservicesltd/RESL</t>
         </is>
       </c>
       <c r="R90" t="inlineStr">
         <is>
-          <t>2026-08-11 21:41:02</t>
+          <t>2026-10-08 16:06:11</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Unitec Fibres Ltd</t>
+          <t>Shanti Inorganics Ltd</t>
         </is>
       </c>
       <c r="B91" t="inlineStr"/>
@@ -6988,17 +7060,17 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Sep 23, 2026</t>
+          <t>Aug 31, 2026</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Sep 25, 2026</t>
+          <t>Sep 02, 2026</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Sep 28, 2026</t>
+          <t>Sep 03, 2026</t>
         </is>
       </c>
       <c r="H91" t="inlineStr"/>
@@ -7009,12 +7081,12 @@
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>83-88</t>
+          <t>79-83</t>
         </is>
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>140800</t>
+          <t>132800</t>
         </is>
       </c>
       <c r="L91" t="inlineStr"/>
@@ -7024,19 +7096,19 @@
       <c r="P91" t="inlineStr"/>
       <c r="Q91" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/unitecfibresltd/UFL03</t>
+          <t>https://www.moneycontrol.com/ipo/shantiinorganicsltd/SIL34</t>
         </is>
       </c>
       <c r="R91" t="inlineStr">
         <is>
-          <t>2026-09-18 23:59:33</t>
+          <t>2026-08-25 09:29:52</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>VANS Electroengineerings Ltd</t>
+          <t>Technocrats Plasma Systems Ltd</t>
         </is>
       </c>
       <c r="B92" t="inlineStr"/>
@@ -7048,33 +7120,33 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Sep 29, 2026</t>
+          <t>Aug 14, 2026</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Oct 01, 2026</t>
+          <t>Aug 18, 2026</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Oct 05, 2026</t>
+          <t>Aug 19, 2026</t>
         </is>
       </c>
       <c r="H92" t="inlineStr"/>
       <c r="I92" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>112-118</t>
+          <t>125-132</t>
         </is>
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>141600</t>
+          <t>132000</t>
         </is>
       </c>
       <c r="L92" t="inlineStr"/>
@@ -7084,19 +7156,19 @@
       <c r="P92" t="inlineStr"/>
       <c r="Q92" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/vanselectroengineeringsltd/VEL03</t>
+          <t>https://www.moneycontrol.com/ipo/technocratsplasmasystemsltd/TPSL</t>
         </is>
       </c>
       <c r="R92" t="inlineStr">
         <is>
-          <t>2026-09-25 14:20:09</t>
+          <t>2026-08-11 21:41:02</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Vaibhav Vyapaar Ltd</t>
+          <t>Unitec Fibres Ltd</t>
         </is>
       </c>
       <c r="B93" t="inlineStr"/>
@@ -7108,33 +7180,33 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Oct 13, 2026</t>
+          <t>Sep 23, 2026</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Oct 15, 2026</t>
+          <t>Sep 25, 2026</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Oct 16, 2026</t>
+          <t>Sep 28, 2026</t>
         </is>
       </c>
       <c r="H93" t="inlineStr"/>
       <c r="I93" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>1600</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>50-52</t>
+          <t>83-88</t>
         </is>
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>104000</t>
+          <t>140800</t>
         </is>
       </c>
       <c r="L93" t="inlineStr"/>
@@ -7144,19 +7216,19 @@
       <c r="P93" t="inlineStr"/>
       <c r="Q93" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/vaibhavvyapaarltd/VVL01</t>
+          <t>https://www.moneycontrol.com/ipo/unitecfibresltd/UFL03</t>
         </is>
       </c>
       <c r="R93" t="inlineStr">
         <is>
-          <t>2026-10-08 16:06:11</t>
+          <t>2026-09-18 23:59:33</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Vama Wovenfab Ltd</t>
+          <t>VANS Electroengineerings Ltd</t>
         </is>
       </c>
       <c r="B94" t="inlineStr"/>
@@ -7168,33 +7240,33 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Sep 15, 2026</t>
+          <t>Sep 29, 2026</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Sep 17, 2026</t>
+          <t>Oct 01, 2026</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Sep 18, 2026</t>
+          <t>Oct 05, 2026</t>
         </is>
       </c>
       <c r="H94" t="inlineStr"/>
       <c r="I94" t="inlineStr">
         <is>
-          <t>400</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>324-341</t>
+          <t>112-118</t>
         </is>
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t>136400</t>
+          <t>141600</t>
         </is>
       </c>
       <c r="L94" t="inlineStr"/>
@@ -7204,17 +7276,137 @@
       <c r="P94" t="inlineStr"/>
       <c r="Q94" t="inlineStr">
         <is>
+          <t>https://www.moneycontrol.com/ipo/vanselectroengineeringsltd/VEL03</t>
+        </is>
+      </c>
+      <c r="R94" t="inlineStr">
+        <is>
+          <t>2026-09-25 14:20:09</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>Vaibhav Vyapaar Ltd</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr"/>
+      <c r="C95" t="inlineStr"/>
+      <c r="D95" s="5" t="inlineStr">
+        <is>
+          <t>Upcoming</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>Oct 13, 2026</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>Oct 15, 2026</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>Oct 16, 2026</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr"/>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>50-52</t>
+        </is>
+      </c>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>104000</t>
+        </is>
+      </c>
+      <c r="L95" t="inlineStr"/>
+      <c r="M95" t="inlineStr"/>
+      <c r="N95" t="inlineStr"/>
+      <c r="O95" t="inlineStr"/>
+      <c r="P95" t="inlineStr"/>
+      <c r="Q95" t="inlineStr">
+        <is>
+          <t>https://www.moneycontrol.com/ipo/vaibhavvyapaarltd/VVL01</t>
+        </is>
+      </c>
+      <c r="R95" t="inlineStr">
+        <is>
+          <t>2026-10-08 16:06:11</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>Vama Wovenfab Ltd</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr"/>
+      <c r="C96" t="inlineStr"/>
+      <c r="D96" s="5" t="inlineStr">
+        <is>
+          <t>Upcoming</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>Sep 15, 2026</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>Sep 17, 2026</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>Sep 18, 2026</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr"/>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>400</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>324-341</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>136400</t>
+        </is>
+      </c>
+      <c r="L96" t="inlineStr"/>
+      <c r="M96" t="inlineStr"/>
+      <c r="N96" t="inlineStr"/>
+      <c r="O96" t="inlineStr"/>
+      <c r="P96" t="inlineStr"/>
+      <c r="Q96" t="inlineStr">
+        <is>
           <t>https://www.moneycontrol.com/ipo/vamawovenfabltd/VWL01</t>
         </is>
       </c>
-      <c r="R94" t="inlineStr">
+      <c r="R96" t="inlineStr">
         <is>
           <t>2026-09-11 13:34:16</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:R94"/>
+  <autoFilter ref="A1:R96"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/mainboard_ipos.xlsx
+++ b/data/mainboard_ipos.xlsx
@@ -5293,7 +5293,7 @@
       </c>
       <c r="R63" t="inlineStr">
         <is>
-          <t>2026-10-24 13:38:31</t>
+          <t>2026-10-24 23:39:52</t>
         </is>
       </c>
     </row>
@@ -5377,7 +5377,7 @@
       </c>
       <c r="R64" t="inlineStr">
         <is>
-          <t>2026-10-24 13:38:31</t>
+          <t>2026-10-24 23:39:52</t>
         </is>
       </c>
     </row>
@@ -5461,7 +5461,7 @@
       </c>
       <c r="R65" t="inlineStr">
         <is>
-          <t>2026-10-24 13:38:31</t>
+          <t>2026-10-24 23:39:52</t>
         </is>
       </c>
     </row>
@@ -5545,7 +5545,7 @@
       </c>
       <c r="R66" t="inlineStr">
         <is>
-          <t>2026-10-24 13:38:31</t>
+          <t>2026-10-24 23:39:52</t>
         </is>
       </c>
     </row>
@@ -5629,7 +5629,7 @@
       </c>
       <c r="R67" t="inlineStr">
         <is>
-          <t>2026-10-24 13:38:31</t>
+          <t>2026-10-24 23:39:52</t>
         </is>
       </c>
     </row>
@@ -5697,7 +5697,7 @@
       </c>
       <c r="R68" t="inlineStr">
         <is>
-          <t>2026-10-24 13:38:31</t>
+          <t>2026-10-24 23:39:52</t>
         </is>
       </c>
     </row>
@@ -5765,7 +5765,7 @@
       </c>
       <c r="R69" t="inlineStr">
         <is>
-          <t>2026-10-24 13:38:31</t>
+          <t>2026-10-24 23:39:52</t>
         </is>
       </c>
     </row>
@@ -5829,7 +5829,7 @@
       </c>
       <c r="R70" t="inlineStr">
         <is>
-          <t>2026-10-24 13:38:31</t>
+          <t>2026-10-24 23:39:52</t>
         </is>
       </c>
     </row>
@@ -5893,7 +5893,7 @@
       </c>
       <c r="R71" t="inlineStr">
         <is>
-          <t>2026-10-24 13:38:31</t>
+          <t>2026-10-24 23:39:52</t>
         </is>
       </c>
     </row>
@@ -5957,7 +5957,7 @@
       </c>
       <c r="R72" t="inlineStr">
         <is>
-          <t>2026-10-24 13:38:31</t>
+          <t>2026-10-24 23:39:52</t>
         </is>
       </c>
     </row>
@@ -6021,7 +6021,7 @@
       </c>
       <c r="R73" t="inlineStr">
         <is>
-          <t>2026-10-24 13:38:31</t>
+          <t>2026-10-24 23:39:52</t>
         </is>
       </c>
     </row>
@@ -6085,7 +6085,7 @@
       </c>
       <c r="R74" t="inlineStr">
         <is>
-          <t>2026-10-24 13:38:31</t>
+          <t>2026-10-24 23:39:52</t>
         </is>
       </c>
     </row>

--- a/data/mainboard_ipos.xlsx
+++ b/data/mainboard_ipos.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Mainboard IPOs" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Mainboard IPOs'!$A$1:$R$96</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Mainboard IPOs'!$A$1:$R$97</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -449,7 +449,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R96"/>
+  <dimension ref="A1:R97"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -5293,7 +5293,7 @@
       </c>
       <c r="R63" t="inlineStr">
         <is>
-          <t>2026-10-24 23:39:52</t>
+          <t>2026-10-25 13:55:51</t>
         </is>
       </c>
     </row>
@@ -5377,7 +5377,7 @@
       </c>
       <c r="R64" t="inlineStr">
         <is>
-          <t>2026-10-24 23:39:52</t>
+          <t>2026-10-25 13:55:51</t>
         </is>
       </c>
     </row>
@@ -5461,7 +5461,7 @@
       </c>
       <c r="R65" t="inlineStr">
         <is>
-          <t>2026-10-24 23:39:52</t>
+          <t>2026-10-25 13:55:51</t>
         </is>
       </c>
     </row>
@@ -5545,7 +5545,7 @@
       </c>
       <c r="R66" t="inlineStr">
         <is>
-          <t>2026-10-24 23:39:52</t>
+          <t>2026-10-25 13:55:51</t>
         </is>
       </c>
     </row>
@@ -5629,7 +5629,7 @@
       </c>
       <c r="R67" t="inlineStr">
         <is>
-          <t>2026-10-24 23:39:52</t>
+          <t>2026-10-25 13:55:51</t>
         </is>
       </c>
     </row>
@@ -5697,7 +5697,7 @@
       </c>
       <c r="R68" t="inlineStr">
         <is>
-          <t>2026-10-24 23:39:52</t>
+          <t>2026-10-25 13:55:51</t>
         </is>
       </c>
     </row>
@@ -5765,7 +5765,7 @@
       </c>
       <c r="R69" t="inlineStr">
         <is>
-          <t>2026-10-24 23:39:52</t>
+          <t>2026-10-25 13:55:51</t>
         </is>
       </c>
     </row>
@@ -5829,7 +5829,7 @@
       </c>
       <c r="R70" t="inlineStr">
         <is>
-          <t>2026-10-24 23:39:52</t>
+          <t>2026-10-25 13:55:51</t>
         </is>
       </c>
     </row>
@@ -5893,7 +5893,7 @@
       </c>
       <c r="R71" t="inlineStr">
         <is>
-          <t>2026-10-24 23:39:52</t>
+          <t>2026-10-25 13:55:51</t>
         </is>
       </c>
     </row>
@@ -5957,7 +5957,7 @@
       </c>
       <c r="R72" t="inlineStr">
         <is>
-          <t>2026-10-24 23:39:52</t>
+          <t>2026-10-25 13:55:51</t>
         </is>
       </c>
     </row>
@@ -6021,7 +6021,7 @@
       </c>
       <c r="R73" t="inlineStr">
         <is>
-          <t>2026-10-24 23:39:52</t>
+          <t>2026-10-25 13:55:51</t>
         </is>
       </c>
     </row>
@@ -6085,14 +6085,14 @@
       </c>
       <c r="R74" t="inlineStr">
         <is>
-          <t>2026-10-24 23:39:52</t>
+          <t>2026-10-25 13:55:51</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Complete Sports and Management India Ltd</t>
+          <t>Antala Industries Ltd</t>
         </is>
       </c>
       <c r="B75" t="inlineStr"/>
@@ -6104,35 +6104,27 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Aug 28, 2026</t>
+          <t>Oct 29, 2026</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Sep 01, 2026</t>
+          <t>Nov 02, 2026</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Sep 02, 2026</t>
+          <t>Nov 03, 2026</t>
         </is>
       </c>
       <c r="H75" t="inlineStr"/>
-      <c r="I75" t="inlineStr">
-        <is>
-          <t>1000</t>
-        </is>
-      </c>
+      <c r="I75" t="inlineStr"/>
       <c r="J75" t="inlineStr">
         <is>
-          <t>128-135</t>
-        </is>
-      </c>
-      <c r="K75" t="inlineStr">
-        <is>
-          <t>135000</t>
-        </is>
-      </c>
+          <t>63-67</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr"/>
       <c r="L75" t="inlineStr"/>
       <c r="M75" t="inlineStr"/>
       <c r="N75" t="inlineStr"/>
@@ -6140,19 +6132,19 @@
       <c r="P75" t="inlineStr"/>
       <c r="Q75" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/completesportsmanagementindialtd/CSMIL</t>
+          <t>https://www.moneycontrol.com/ipo/antalaindustriesltd/AIL13</t>
         </is>
       </c>
       <c r="R75" t="inlineStr">
         <is>
-          <t>2026-08-25 09:29:52</t>
+          <t>2026-10-25 13:55:51</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Core4 Engineers Ltd</t>
+          <t>Complete Sports and Management India Ltd</t>
         </is>
       </c>
       <c r="B76" t="inlineStr"/>
@@ -6164,33 +6156,33 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Oct 23, 2026</t>
+          <t>Aug 28, 2026</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Oct 27, 2026</t>
+          <t>Sep 01, 2026</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Oct 28, 2026</t>
+          <t>Sep 02, 2026</t>
         </is>
       </c>
       <c r="H76" t="inlineStr"/>
       <c r="I76" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>88-93</t>
+          <t>128-135</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>111600</t>
+          <t>135000</t>
         </is>
       </c>
       <c r="L76" t="inlineStr"/>
@@ -6200,19 +6192,19 @@
       <c r="P76" t="inlineStr"/>
       <c r="Q76" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/core4engineersltd/CEL05</t>
+          <t>https://www.moneycontrol.com/ipo/completesportsmanagementindialtd/CSMIL</t>
         </is>
       </c>
       <c r="R76" t="inlineStr">
         <is>
-          <t>2026-10-20 14:03:23</t>
+          <t>2026-08-25 09:29:52</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Coreintegra Consulting Services</t>
+          <t>Core4 Engineers Ltd</t>
         </is>
       </c>
       <c r="B77" t="inlineStr"/>
@@ -6224,33 +6216,33 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Sep 23, 2026</t>
+          <t>Oct 23, 2026</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Sep 25, 2026</t>
+          <t>Oct 27, 2026</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Sep 28, 2026</t>
+          <t>Oct 28, 2026</t>
         </is>
       </c>
       <c r="H77" t="inlineStr"/>
       <c r="I77" t="inlineStr">
         <is>
-          <t>1600</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>74-78</t>
+          <t>88-93</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>124800</t>
+          <t>111600</t>
         </is>
       </c>
       <c r="L77" t="inlineStr"/>
@@ -6260,19 +6252,19 @@
       <c r="P77" t="inlineStr"/>
       <c r="Q77" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/coreintegraconsultingservices/CCSL</t>
+          <t>https://www.moneycontrol.com/ipo/core4engineersltd/CEL05</t>
         </is>
       </c>
       <c r="R77" t="inlineStr">
         <is>
-          <t>2026-09-22 14:03:25</t>
+          <t>2026-10-20 14:03:23</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Credent Connect N Care Ltd</t>
+          <t>Coreintegra Consulting Services</t>
         </is>
       </c>
       <c r="B78" t="inlineStr"/>
@@ -6284,33 +6276,33 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Aug 13, 2026</t>
+          <t>Sep 23, 2026</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Aug 17, 2026</t>
+          <t>Sep 25, 2026</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Aug 18, 2026</t>
+          <t>Sep 28, 2026</t>
         </is>
       </c>
       <c r="H78" t="inlineStr"/>
       <c r="I78" t="inlineStr">
         <is>
-          <t>600</t>
+          <t>1600</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>179-189</t>
+          <t>74-78</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>113400</t>
+          <t>124800</t>
         </is>
       </c>
       <c r="L78" t="inlineStr"/>
@@ -6320,19 +6312,19 @@
       <c r="P78" t="inlineStr"/>
       <c r="Q78" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/credentconnectncareltd/CCC04</t>
+          <t>https://www.moneycontrol.com/ipo/coreintegraconsultingservices/CCSL</t>
         </is>
       </c>
       <c r="R78" t="inlineStr">
         <is>
-          <t>2026-08-10 22:43:12</t>
+          <t>2026-09-22 14:03:25</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Dove Soft Ltd</t>
+          <t>Credent Connect N Care Ltd</t>
         </is>
       </c>
       <c r="B79" t="inlineStr"/>
@@ -6344,33 +6336,33 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Sep 30, 2026</t>
+          <t>Aug 13, 2026</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Oct 05, 2026</t>
+          <t>Aug 17, 2026</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Oct 06, 2026</t>
+          <t>Aug 18, 2026</t>
         </is>
       </c>
       <c r="H79" t="inlineStr"/>
       <c r="I79" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>600</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>104-111</t>
+          <t>179-189</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>133200</t>
+          <t>113400</t>
         </is>
       </c>
       <c r="L79" t="inlineStr"/>
@@ -6380,19 +6372,19 @@
       <c r="P79" t="inlineStr"/>
       <c r="Q79" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/dovesoftltd/DSL04</t>
+          <t>https://www.moneycontrol.com/ipo/credentconnectncareltd/CCC04</t>
         </is>
       </c>
       <c r="R79" t="inlineStr">
         <is>
-          <t>2026-09-25 14:20:09</t>
+          <t>2026-08-10 22:43:12</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Farm Peace Ltd</t>
+          <t>Dove Soft Ltd</t>
         </is>
       </c>
       <c r="B80" t="inlineStr"/>
@@ -6404,33 +6396,33 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Sep 01, 2026</t>
+          <t>Sep 30, 2026</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Sep 03, 2026</t>
+          <t>Oct 05, 2026</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Sep 04, 2026</t>
+          <t>Oct 06, 2026</t>
         </is>
       </c>
       <c r="H80" t="inlineStr"/>
       <c r="I80" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>104-111</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>118000</t>
+          <t>133200</t>
         </is>
       </c>
       <c r="L80" t="inlineStr"/>
@@ -6440,19 +6432,19 @@
       <c r="P80" t="inlineStr"/>
       <c r="Q80" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/farmpeaceltd/FPL02</t>
+          <t>https://www.moneycontrol.com/ipo/dovesoftltd/DSL04</t>
         </is>
       </c>
       <c r="R80" t="inlineStr">
         <is>
-          <t>2026-08-27 19:43:03</t>
+          <t>2026-09-25 14:20:09</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Green Asia Impex Ltd</t>
+          <t>Farm Peace Ltd</t>
         </is>
       </c>
       <c r="B81" t="inlineStr"/>
@@ -6464,33 +6456,33 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Sep 24, 2026</t>
+          <t>Sep 01, 2026</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Sep 28, 2026</t>
+          <t>Sep 03, 2026</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Sep 29, 2026</t>
+          <t>Sep 04, 2026</t>
         </is>
       </c>
       <c r="H81" t="inlineStr"/>
       <c r="I81" t="inlineStr">
         <is>
-          <t>1600</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>85-90</t>
+          <t>59</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>144000</t>
+          <t>118000</t>
         </is>
       </c>
       <c r="L81" t="inlineStr"/>
@@ -6500,19 +6492,19 @@
       <c r="P81" t="inlineStr"/>
       <c r="Q81" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/greenasiaimpexltd/GAIL01</t>
+          <t>https://www.moneycontrol.com/ipo/farmpeaceltd/FPL02</t>
         </is>
       </c>
       <c r="R81" t="inlineStr">
         <is>
-          <t>2026-09-22 14:03:25</t>
+          <t>2026-08-27 19:43:03</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Kheria Autocomp Ltd</t>
+          <t>Green Asia Impex Ltd</t>
         </is>
       </c>
       <c r="B82" t="inlineStr"/>
@@ -6524,33 +6516,33 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Sep 17, 2026</t>
+          <t>Sep 24, 2026</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Sep 21, 2026</t>
+          <t>Sep 28, 2026</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Sep 22, 2026</t>
+          <t>Sep 29, 2026</t>
         </is>
       </c>
       <c r="H82" t="inlineStr"/>
       <c r="I82" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>1600</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>96-101</t>
+          <t>85-90</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>121200</t>
+          <t>144000</t>
         </is>
       </c>
       <c r="L82" t="inlineStr"/>
@@ -6560,19 +6552,19 @@
       <c r="P82" t="inlineStr"/>
       <c r="Q82" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/kheriaautocompltd/KAL05</t>
+          <t>https://www.moneycontrol.com/ipo/greenasiaimpexltd/GAIL01</t>
         </is>
       </c>
       <c r="R82" t="inlineStr">
         <is>
-          <t>2026-09-11 13:34:16</t>
+          <t>2026-09-22 14:03:25</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Mopshop Distribution Ltd</t>
+          <t>Kheria Autocomp Ltd</t>
         </is>
       </c>
       <c r="B83" t="inlineStr"/>
@@ -6584,33 +6576,33 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Aug 19, 2026</t>
+          <t>Sep 17, 2026</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Aug 21, 2026</t>
+          <t>Sep 21, 2026</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Aug 24, 2026</t>
+          <t>Sep 22, 2026</t>
         </is>
       </c>
       <c r="H83" t="inlineStr"/>
       <c r="I83" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>138</t>
+          <t>96-101</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>138000</t>
+          <t>121200</t>
         </is>
       </c>
       <c r="L83" t="inlineStr"/>
@@ -6620,19 +6612,19 @@
       <c r="P83" t="inlineStr"/>
       <c r="Q83" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/mopshopdistributionltd/MDL03</t>
+          <t>https://www.moneycontrol.com/ipo/kheriaautocompltd/KAL05</t>
         </is>
       </c>
       <c r="R83" t="inlineStr">
         <is>
-          <t>2026-08-14 21:36:23</t>
+          <t>2026-09-11 13:34:16</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Paluck Technologies Ltd</t>
+          <t>Mopshop Distribution Ltd</t>
         </is>
       </c>
       <c r="B84" t="inlineStr"/>
@@ -6644,33 +6636,33 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Aug 28, 2026</t>
+          <t>Aug 19, 2026</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Sep 01, 2026</t>
+          <t>Aug 21, 2026</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Sep 02, 2026</t>
+          <t>Aug 24, 2026</t>
         </is>
       </c>
       <c r="H84" t="inlineStr"/>
       <c r="I84" t="inlineStr">
         <is>
-          <t>3000</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>46-48</t>
+          <t>138</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>144000</t>
+          <t>138000</t>
         </is>
       </c>
       <c r="L84" t="inlineStr"/>
@@ -6680,19 +6672,19 @@
       <c r="P84" t="inlineStr"/>
       <c r="Q84" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/palucktechnologiesltd/PTL08</t>
+          <t>https://www.moneycontrol.com/ipo/mopshopdistributionltd/MDL03</t>
         </is>
       </c>
       <c r="R84" t="inlineStr">
         <is>
-          <t>2026-08-25 09:29:52</t>
+          <t>2026-08-14 21:36:23</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Papadmalji Agro Foods Ltd</t>
+          <t>Paluck Technologies Ltd</t>
         </is>
       </c>
       <c r="B85" t="inlineStr"/>
@@ -6704,33 +6696,33 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Sep 29, 2026</t>
+          <t>Aug 28, 2026</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Oct 01, 2026</t>
+          <t>Sep 01, 2026</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Oct 05, 2026</t>
+          <t>Sep 02, 2026</t>
         </is>
       </c>
       <c r="H85" t="inlineStr"/>
       <c r="I85" t="inlineStr">
         <is>
-          <t>1600</t>
+          <t>3000</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>69-72</t>
+          <t>46-48</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>115200</t>
+          <t>144000</t>
         </is>
       </c>
       <c r="L85" t="inlineStr"/>
@@ -6740,19 +6732,19 @@
       <c r="P85" t="inlineStr"/>
       <c r="Q85" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/papadmaljiagrofoodsltd/PAF</t>
+          <t>https://www.moneycontrol.com/ipo/palucktechnologiesltd/PTL08</t>
         </is>
       </c>
       <c r="R85" t="inlineStr">
         <is>
-          <t>2026-09-25 14:20:09</t>
+          <t>2026-08-25 09:29:52</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Paramount Syntex Ltd</t>
+          <t>Papadmalji Agro Foods Ltd</t>
         </is>
       </c>
       <c r="B86" t="inlineStr"/>
@@ -6764,33 +6756,33 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Sep 30, 2026</t>
+          <t>Sep 29, 2026</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Oct 06, 2026</t>
+          <t>Oct 01, 2026</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Oct 07, 2026</t>
+          <t>Oct 05, 2026</t>
         </is>
       </c>
       <c r="H86" t="inlineStr"/>
       <c r="I86" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>1600</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>119-127</t>
+          <t>69-72</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>127000</t>
+          <t>115200</t>
         </is>
       </c>
       <c r="L86" t="inlineStr"/>
@@ -6800,7 +6792,7 @@
       <c r="P86" t="inlineStr"/>
       <c r="Q86" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/paramountsyntexltd/PSL06</t>
+          <t>https://www.moneycontrol.com/ipo/papadmaljiagrofoodsltd/PAF</t>
         </is>
       </c>
       <c r="R86" t="inlineStr">
@@ -6812,7 +6804,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Peshwa Wheat</t>
+          <t>Paramount Syntex Ltd</t>
         </is>
       </c>
       <c r="B87" t="inlineStr"/>
@@ -6824,33 +6816,33 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Sep 24, 2026</t>
+          <t>Sep 30, 2026</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Sep 28, 2026</t>
+          <t>Oct 06, 2026</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Sep 29, 2026</t>
+          <t>Oct 07, 2026</t>
         </is>
       </c>
       <c r="H87" t="inlineStr"/>
       <c r="I87" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>95-101</t>
+          <t>119-127</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>121200</t>
+          <t>127000</t>
         </is>
       </c>
       <c r="L87" t="inlineStr"/>
@@ -6860,135 +6852,135 @@
       <c r="P87" t="inlineStr"/>
       <c r="Q87" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/peshwawheat/PWL01</t>
+          <t>https://www.moneycontrol.com/ipo/paramountsyntexltd/PSL06</t>
         </is>
       </c>
       <c r="R87" t="inlineStr">
         <is>
-          <t>2026-09-22 14:03:25</t>
+          <t>2026-09-25 14:20:09</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Purple Style Labs Ltd</t>
+          <t>Peshwa Wheat</t>
         </is>
       </c>
       <c r="B88" t="inlineStr"/>
       <c r="C88" t="inlineStr"/>
-      <c r="D88" s="4" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="D88" s="5" t="inlineStr">
+        <is>
+          <t>Upcoming</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Aug 31, 2026</t>
+          <t>Sep 24, 2026</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Sep 02, 2026</t>
+          <t>Sep 28, 2026</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Sep 03, 2026</t>
+          <t>Sep 29, 2026</t>
         </is>
       </c>
       <c r="H88" t="inlineStr"/>
-      <c r="I88" t="inlineStr"/>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>1200</t>
+        </is>
+      </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>575</t>
-        </is>
-      </c>
-      <c r="K88" t="inlineStr"/>
+          <t>95-101</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>121200</t>
+        </is>
+      </c>
       <c r="L88" t="inlineStr"/>
       <c r="M88" t="inlineStr"/>
-      <c r="N88" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="N88" t="inlineStr"/>
       <c r="O88" t="inlineStr"/>
       <c r="P88" t="inlineStr"/>
       <c r="Q88" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/purplestylelabsltd/PSL05</t>
+          <t>https://www.moneycontrol.com/ipo/peshwawheat/PWL01</t>
         </is>
       </c>
       <c r="R88" t="inlineStr">
         <is>
-          <t>2026-09-02 13:25:30</t>
+          <t>2026-09-22 14:03:25</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Q&amp;T Foods Ltd</t>
+          <t>Purple Style Labs Ltd</t>
         </is>
       </c>
       <c r="B89" t="inlineStr"/>
       <c r="C89" t="inlineStr"/>
-      <c r="D89" s="5" t="inlineStr">
-        <is>
-          <t>Upcoming</t>
+      <c r="D89" s="4" t="inlineStr">
+        <is>
+          <t>Open</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Aug 12, 2026</t>
+          <t>Aug 31, 2026</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Aug 14, 2026</t>
+          <t>Sep 02, 2026</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Aug 17, 2026</t>
+          <t>Sep 03, 2026</t>
         </is>
       </c>
       <c r="H89" t="inlineStr"/>
-      <c r="I89" t="inlineStr">
-        <is>
-          <t>1200</t>
-        </is>
-      </c>
+      <c r="I89" t="inlineStr"/>
       <c r="J89" t="inlineStr">
         <is>
-          <t>115</t>
-        </is>
-      </c>
-      <c r="K89" t="inlineStr">
-        <is>
-          <t>138000</t>
-        </is>
-      </c>
+          <t>575</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr"/>
       <c r="L89" t="inlineStr"/>
       <c r="M89" t="inlineStr"/>
-      <c r="N89" t="inlineStr"/>
+      <c r="N89" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="O89" t="inlineStr"/>
       <c r="P89" t="inlineStr"/>
       <c r="Q89" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/qtfoodsltd/QFL</t>
+          <t>https://www.moneycontrol.com/ipo/purplestylelabsltd/PSL05</t>
         </is>
       </c>
       <c r="R89" t="inlineStr">
         <is>
-          <t>2026-08-10 10:24:29</t>
+          <t>2026-09-02 13:25:30</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Ravita Engineering Services Ltd</t>
+          <t>Q&amp;T Foods Ltd</t>
         </is>
       </c>
       <c r="B90" t="inlineStr"/>
@@ -7000,17 +6992,17 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Oct 13, 2026</t>
+          <t>Aug 12, 2026</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Oct 15, 2026</t>
+          <t>Aug 14, 2026</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Oct 16, 2026</t>
+          <t>Aug 17, 2026</t>
         </is>
       </c>
       <c r="H90" t="inlineStr"/>
@@ -7021,12 +7013,12 @@
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>105-112</t>
+          <t>115</t>
         </is>
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>134400</t>
+          <t>138000</t>
         </is>
       </c>
       <c r="L90" t="inlineStr"/>
@@ -7036,19 +7028,19 @@
       <c r="P90" t="inlineStr"/>
       <c r="Q90" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/ravitaengineeringservicesltd/RESL</t>
+          <t>https://www.moneycontrol.com/ipo/qtfoodsltd/QFL</t>
         </is>
       </c>
       <c r="R90" t="inlineStr">
         <is>
-          <t>2026-10-08 16:06:11</t>
+          <t>2026-08-10 10:24:29</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Shanti Inorganics Ltd</t>
+          <t>Ravita Engineering Services Ltd</t>
         </is>
       </c>
       <c r="B91" t="inlineStr"/>
@@ -7060,33 +7052,33 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Aug 31, 2026</t>
+          <t>Oct 13, 2026</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Sep 02, 2026</t>
+          <t>Oct 15, 2026</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Sep 03, 2026</t>
+          <t>Oct 16, 2026</t>
         </is>
       </c>
       <c r="H91" t="inlineStr"/>
       <c r="I91" t="inlineStr">
         <is>
-          <t>1600</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>79-83</t>
+          <t>105-112</t>
         </is>
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>132800</t>
+          <t>134400</t>
         </is>
       </c>
       <c r="L91" t="inlineStr"/>
@@ -7096,19 +7088,19 @@
       <c r="P91" t="inlineStr"/>
       <c r="Q91" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/shantiinorganicsltd/SIL34</t>
+          <t>https://www.moneycontrol.com/ipo/ravitaengineeringservicesltd/RESL</t>
         </is>
       </c>
       <c r="R91" t="inlineStr">
         <is>
-          <t>2026-08-25 09:29:52</t>
+          <t>2026-10-08 16:06:11</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Technocrats Plasma Systems Ltd</t>
+          <t>Shanti Inorganics Ltd</t>
         </is>
       </c>
       <c r="B92" t="inlineStr"/>
@@ -7120,33 +7112,33 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Aug 14, 2026</t>
+          <t>Aug 31, 2026</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Aug 18, 2026</t>
+          <t>Sep 02, 2026</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Aug 19, 2026</t>
+          <t>Sep 03, 2026</t>
         </is>
       </c>
       <c r="H92" t="inlineStr"/>
       <c r="I92" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>1600</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>125-132</t>
+          <t>79-83</t>
         </is>
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>132000</t>
+          <t>132800</t>
         </is>
       </c>
       <c r="L92" t="inlineStr"/>
@@ -7156,19 +7148,19 @@
       <c r="P92" t="inlineStr"/>
       <c r="Q92" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/technocratsplasmasystemsltd/TPSL</t>
+          <t>https://www.moneycontrol.com/ipo/shantiinorganicsltd/SIL34</t>
         </is>
       </c>
       <c r="R92" t="inlineStr">
         <is>
-          <t>2026-08-11 21:41:02</t>
+          <t>2026-08-25 09:29:52</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Unitec Fibres Ltd</t>
+          <t>Technocrats Plasma Systems Ltd</t>
         </is>
       </c>
       <c r="B93" t="inlineStr"/>
@@ -7180,33 +7172,33 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Sep 23, 2026</t>
+          <t>Aug 14, 2026</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Sep 25, 2026</t>
+          <t>Aug 18, 2026</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Sep 28, 2026</t>
+          <t>Aug 19, 2026</t>
         </is>
       </c>
       <c r="H93" t="inlineStr"/>
       <c r="I93" t="inlineStr">
         <is>
-          <t>1600</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>83-88</t>
+          <t>125-132</t>
         </is>
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>140800</t>
+          <t>132000</t>
         </is>
       </c>
       <c r="L93" t="inlineStr"/>
@@ -7216,19 +7208,19 @@
       <c r="P93" t="inlineStr"/>
       <c r="Q93" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/unitecfibresltd/UFL03</t>
+          <t>https://www.moneycontrol.com/ipo/technocratsplasmasystemsltd/TPSL</t>
         </is>
       </c>
       <c r="R93" t="inlineStr">
         <is>
-          <t>2026-09-18 23:59:33</t>
+          <t>2026-08-11 21:41:02</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>VANS Electroengineerings Ltd</t>
+          <t>Unitec Fibres Ltd</t>
         </is>
       </c>
       <c r="B94" t="inlineStr"/>
@@ -7240,33 +7232,33 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Sep 29, 2026</t>
+          <t>Sep 23, 2026</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Oct 01, 2026</t>
+          <t>Sep 25, 2026</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Oct 05, 2026</t>
+          <t>Sep 28, 2026</t>
         </is>
       </c>
       <c r="H94" t="inlineStr"/>
       <c r="I94" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>1600</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>112-118</t>
+          <t>83-88</t>
         </is>
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t>141600</t>
+          <t>140800</t>
         </is>
       </c>
       <c r="L94" t="inlineStr"/>
@@ -7276,19 +7268,19 @@
       <c r="P94" t="inlineStr"/>
       <c r="Q94" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/vanselectroengineeringsltd/VEL03</t>
+          <t>https://www.moneycontrol.com/ipo/unitecfibresltd/UFL03</t>
         </is>
       </c>
       <c r="R94" t="inlineStr">
         <is>
-          <t>2026-09-25 14:20:09</t>
+          <t>2026-09-18 23:59:33</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Vaibhav Vyapaar Ltd</t>
+          <t>VANS Electroengineerings Ltd</t>
         </is>
       </c>
       <c r="B95" t="inlineStr"/>
@@ -7300,33 +7292,33 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Oct 13, 2026</t>
+          <t>Sep 29, 2026</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Oct 15, 2026</t>
+          <t>Oct 01, 2026</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Oct 16, 2026</t>
+          <t>Oct 05, 2026</t>
         </is>
       </c>
       <c r="H95" t="inlineStr"/>
       <c r="I95" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>50-52</t>
+          <t>112-118</t>
         </is>
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t>104000</t>
+          <t>141600</t>
         </is>
       </c>
       <c r="L95" t="inlineStr"/>
@@ -7336,19 +7328,19 @@
       <c r="P95" t="inlineStr"/>
       <c r="Q95" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/vaibhavvyapaarltd/VVL01</t>
+          <t>https://www.moneycontrol.com/ipo/vanselectroengineeringsltd/VEL03</t>
         </is>
       </c>
       <c r="R95" t="inlineStr">
         <is>
-          <t>2026-10-08 16:06:11</t>
+          <t>2026-09-25 14:20:09</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Vama Wovenfab Ltd</t>
+          <t>Vaibhav Vyapaar Ltd</t>
         </is>
       </c>
       <c r="B96" t="inlineStr"/>
@@ -7360,33 +7352,33 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Sep 15, 2026</t>
+          <t>Oct 13, 2026</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Sep 17, 2026</t>
+          <t>Oct 15, 2026</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Sep 18, 2026</t>
+          <t>Oct 16, 2026</t>
         </is>
       </c>
       <c r="H96" t="inlineStr"/>
       <c r="I96" t="inlineStr">
         <is>
-          <t>400</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>324-341</t>
+          <t>50-52</t>
         </is>
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t>136400</t>
+          <t>104000</t>
         </is>
       </c>
       <c r="L96" t="inlineStr"/>
@@ -7396,17 +7388,77 @@
       <c r="P96" t="inlineStr"/>
       <c r="Q96" t="inlineStr">
         <is>
+          <t>https://www.moneycontrol.com/ipo/vaibhavvyapaarltd/VVL01</t>
+        </is>
+      </c>
+      <c r="R96" t="inlineStr">
+        <is>
+          <t>2026-10-08 16:06:11</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>Vama Wovenfab Ltd</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr"/>
+      <c r="C97" t="inlineStr"/>
+      <c r="D97" s="5" t="inlineStr">
+        <is>
+          <t>Upcoming</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>Sep 15, 2026</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>Sep 17, 2026</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>Sep 18, 2026</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr"/>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>400</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>324-341</t>
+        </is>
+      </c>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>136400</t>
+        </is>
+      </c>
+      <c r="L97" t="inlineStr"/>
+      <c r="M97" t="inlineStr"/>
+      <c r="N97" t="inlineStr"/>
+      <c r="O97" t="inlineStr"/>
+      <c r="P97" t="inlineStr"/>
+      <c r="Q97" t="inlineStr">
+        <is>
           <t>https://www.moneycontrol.com/ipo/vamawovenfabltd/VWL01</t>
         </is>
       </c>
-      <c r="R96" t="inlineStr">
+      <c r="R97" t="inlineStr">
         <is>
           <t>2026-09-11 13:34:16</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:R96"/>
+  <autoFilter ref="A1:R97"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/mainboard_ipos.xlsx
+++ b/data/mainboard_ipos.xlsx
@@ -5293,7 +5293,7 @@
       </c>
       <c r="R63" t="inlineStr">
         <is>
-          <t>2026-10-25 13:55:51</t>
+          <t>2026-10-25 23:54:20</t>
         </is>
       </c>
     </row>
@@ -5377,7 +5377,7 @@
       </c>
       <c r="R64" t="inlineStr">
         <is>
-          <t>2026-10-25 13:55:51</t>
+          <t>2026-10-25 23:54:20</t>
         </is>
       </c>
     </row>
@@ -5461,7 +5461,7 @@
       </c>
       <c r="R65" t="inlineStr">
         <is>
-          <t>2026-10-25 13:55:51</t>
+          <t>2026-10-25 23:54:20</t>
         </is>
       </c>
     </row>
@@ -5545,7 +5545,7 @@
       </c>
       <c r="R66" t="inlineStr">
         <is>
-          <t>2026-10-25 13:55:51</t>
+          <t>2026-10-25 23:54:20</t>
         </is>
       </c>
     </row>
@@ -5629,7 +5629,7 @@
       </c>
       <c r="R67" t="inlineStr">
         <is>
-          <t>2026-10-25 13:55:51</t>
+          <t>2026-10-25 23:54:20</t>
         </is>
       </c>
     </row>
@@ -5697,7 +5697,7 @@
       </c>
       <c r="R68" t="inlineStr">
         <is>
-          <t>2026-10-25 13:55:51</t>
+          <t>2026-10-25 23:54:20</t>
         </is>
       </c>
     </row>
@@ -5765,7 +5765,7 @@
       </c>
       <c r="R69" t="inlineStr">
         <is>
-          <t>2026-10-25 13:55:51</t>
+          <t>2026-10-25 23:54:20</t>
         </is>
       </c>
     </row>
@@ -5829,7 +5829,7 @@
       </c>
       <c r="R70" t="inlineStr">
         <is>
-          <t>2026-10-25 13:55:51</t>
+          <t>2026-10-25 23:54:20</t>
         </is>
       </c>
     </row>
@@ -5893,7 +5893,7 @@
       </c>
       <c r="R71" t="inlineStr">
         <is>
-          <t>2026-10-25 13:55:51</t>
+          <t>2026-10-25 23:54:20</t>
         </is>
       </c>
     </row>
@@ -5957,7 +5957,7 @@
       </c>
       <c r="R72" t="inlineStr">
         <is>
-          <t>2026-10-25 13:55:51</t>
+          <t>2026-10-25 23:54:20</t>
         </is>
       </c>
     </row>
@@ -6021,7 +6021,7 @@
       </c>
       <c r="R73" t="inlineStr">
         <is>
-          <t>2026-10-25 13:55:51</t>
+          <t>2026-10-25 23:54:20</t>
         </is>
       </c>
     </row>
@@ -6085,7 +6085,7 @@
       </c>
       <c r="R74" t="inlineStr">
         <is>
-          <t>2026-10-25 13:55:51</t>
+          <t>2026-10-25 23:54:20</t>
         </is>
       </c>
     </row>
@@ -6137,7 +6137,7 @@
       </c>
       <c r="R75" t="inlineStr">
         <is>
-          <t>2026-10-25 13:55:51</t>
+          <t>2026-10-25 23:54:20</t>
         </is>
       </c>
     </row>

--- a/data/mainboard_ipos.xlsx
+++ b/data/mainboard_ipos.xlsx
@@ -5293,7 +5293,7 @@
       </c>
       <c r="R63" t="inlineStr">
         <is>
-          <t>2026-10-25 23:54:20</t>
+          <t>2026-10-26 14:26:23</t>
         </is>
       </c>
     </row>
@@ -5377,7 +5377,7 @@
       </c>
       <c r="R64" t="inlineStr">
         <is>
-          <t>2026-10-25 23:54:20</t>
+          <t>2026-10-26 14:26:23</t>
         </is>
       </c>
     </row>
@@ -5461,7 +5461,7 @@
       </c>
       <c r="R65" t="inlineStr">
         <is>
-          <t>2026-10-25 23:54:20</t>
+          <t>2026-10-26 14:26:23</t>
         </is>
       </c>
     </row>
@@ -5545,7 +5545,7 @@
       </c>
       <c r="R66" t="inlineStr">
         <is>
-          <t>2026-10-25 23:54:20</t>
+          <t>2026-10-26 14:26:23</t>
         </is>
       </c>
     </row>
@@ -5629,7 +5629,7 @@
       </c>
       <c r="R67" t="inlineStr">
         <is>
-          <t>2026-10-25 23:54:20</t>
+          <t>2026-10-26 14:26:23</t>
         </is>
       </c>
     </row>
@@ -5697,7 +5697,7 @@
       </c>
       <c r="R68" t="inlineStr">
         <is>
-          <t>2026-10-25 23:54:20</t>
+          <t>2026-10-26 14:26:23</t>
         </is>
       </c>
     </row>
@@ -5765,7 +5765,7 @@
       </c>
       <c r="R69" t="inlineStr">
         <is>
-          <t>2026-10-25 23:54:20</t>
+          <t>2026-10-26 14:26:23</t>
         </is>
       </c>
     </row>
@@ -5777,9 +5777,9 @@
       </c>
       <c r="B70" t="inlineStr"/>
       <c r="C70" t="inlineStr"/>
-      <c r="D70" s="5" t="inlineStr">
-        <is>
-          <t>Upcoming</t>
+      <c r="D70" s="4" t="inlineStr">
+        <is>
+          <t>Open</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -5809,7 +5809,7 @@
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>1585-1665</t>
+          <t>1665</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
@@ -5829,7 +5829,7 @@
       </c>
       <c r="R70" t="inlineStr">
         <is>
-          <t>2026-10-25 23:54:20</t>
+          <t>2026-10-26 14:26:23</t>
         </is>
       </c>
     </row>
@@ -5893,7 +5893,7 @@
       </c>
       <c r="R71" t="inlineStr">
         <is>
-          <t>2026-10-25 23:54:20</t>
+          <t>2026-10-26 14:26:23</t>
         </is>
       </c>
     </row>
@@ -5957,7 +5957,7 @@
       </c>
       <c r="R72" t="inlineStr">
         <is>
-          <t>2026-10-25 23:54:20</t>
+          <t>2026-10-26 14:26:23</t>
         </is>
       </c>
     </row>
@@ -6021,7 +6021,7 @@
       </c>
       <c r="R73" t="inlineStr">
         <is>
-          <t>2026-10-25 23:54:20</t>
+          <t>2026-10-26 14:26:23</t>
         </is>
       </c>
     </row>
@@ -6085,7 +6085,7 @@
       </c>
       <c r="R74" t="inlineStr">
         <is>
-          <t>2026-10-25 23:54:20</t>
+          <t>2026-10-26 14:26:23</t>
         </is>
       </c>
     </row>
@@ -6137,7 +6137,7 @@
       </c>
       <c r="R75" t="inlineStr">
         <is>
-          <t>2026-10-25 23:54:20</t>
+          <t>2026-10-26 14:26:23</t>
         </is>
       </c>
     </row>

--- a/data/mainboard_ipos.xlsx
+++ b/data/mainboard_ipos.xlsx
@@ -5293,7 +5293,7 @@
       </c>
       <c r="R63" t="inlineStr">
         <is>
-          <t>2026-10-26 14:26:23</t>
+          <t>2026-10-27 14:30:33</t>
         </is>
       </c>
     </row>
@@ -5377,7 +5377,7 @@
       </c>
       <c r="R64" t="inlineStr">
         <is>
-          <t>2026-10-26 14:26:23</t>
+          <t>2026-10-27 14:30:33</t>
         </is>
       </c>
     </row>
@@ -5461,7 +5461,7 @@
       </c>
       <c r="R65" t="inlineStr">
         <is>
-          <t>2026-10-26 14:26:23</t>
+          <t>2026-10-27 14:30:33</t>
         </is>
       </c>
     </row>
@@ -5545,7 +5545,7 @@
       </c>
       <c r="R66" t="inlineStr">
         <is>
-          <t>2026-10-26 14:26:23</t>
+          <t>2026-10-27 14:30:33</t>
         </is>
       </c>
     </row>
@@ -5629,7 +5629,7 @@
       </c>
       <c r="R67" t="inlineStr">
         <is>
-          <t>2026-10-26 14:26:23</t>
+          <t>2026-10-27 14:30:33</t>
         </is>
       </c>
     </row>
@@ -5697,7 +5697,7 @@
       </c>
       <c r="R68" t="inlineStr">
         <is>
-          <t>2026-10-26 14:26:23</t>
+          <t>2026-10-27 14:30:33</t>
         </is>
       </c>
     </row>
@@ -5765,7 +5765,7 @@
       </c>
       <c r="R69" t="inlineStr">
         <is>
-          <t>2026-10-26 14:26:23</t>
+          <t>2026-10-27 14:30:33</t>
         </is>
       </c>
     </row>
@@ -5819,7 +5819,11 @@
       </c>
       <c r="L70" t="inlineStr"/>
       <c r="M70" t="inlineStr"/>
-      <c r="N70" t="inlineStr"/>
+      <c r="N70" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="O70" t="inlineStr"/>
       <c r="P70" t="inlineStr"/>
       <c r="Q70" t="inlineStr">
@@ -5829,7 +5833,7 @@
       </c>
       <c r="R70" t="inlineStr">
         <is>
-          <t>2026-10-26 14:26:23</t>
+          <t>2026-10-27 14:30:33</t>
         </is>
       </c>
     </row>
@@ -5841,9 +5845,9 @@
       </c>
       <c r="B71" t="inlineStr"/>
       <c r="C71" t="inlineStr"/>
-      <c r="D71" s="5" t="inlineStr">
-        <is>
-          <t>Upcoming</t>
+      <c r="D71" s="4" t="inlineStr">
+        <is>
+          <t>Open</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -5873,7 +5877,7 @@
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>142-150</t>
+          <t>150</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
@@ -5893,7 +5897,7 @@
       </c>
       <c r="R71" t="inlineStr">
         <is>
-          <t>2026-10-26 14:26:23</t>
+          <t>2026-10-27 14:30:33</t>
         </is>
       </c>
     </row>
@@ -5905,9 +5909,9 @@
       </c>
       <c r="B72" t="inlineStr"/>
       <c r="C72" t="inlineStr"/>
-      <c r="D72" s="5" t="inlineStr">
-        <is>
-          <t>Upcoming</t>
+      <c r="D72" s="4" t="inlineStr">
+        <is>
+          <t>Open</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -5937,7 +5941,7 @@
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>313-330</t>
+          <t>330</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
@@ -5957,7 +5961,7 @@
       </c>
       <c r="R72" t="inlineStr">
         <is>
-          <t>2026-10-26 14:26:23</t>
+          <t>2026-10-27 14:30:33</t>
         </is>
       </c>
     </row>
@@ -6021,7 +6025,7 @@
       </c>
       <c r="R73" t="inlineStr">
         <is>
-          <t>2026-10-26 14:26:23</t>
+          <t>2026-10-27 14:30:33</t>
         </is>
       </c>
     </row>
@@ -6085,7 +6089,7 @@
       </c>
       <c r="R74" t="inlineStr">
         <is>
-          <t>2026-10-26 14:26:23</t>
+          <t>2026-10-27 14:30:33</t>
         </is>
       </c>
     </row>
@@ -6118,13 +6122,21 @@
         </is>
       </c>
       <c r="H75" t="inlineStr"/>
-      <c r="I75" t="inlineStr"/>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
       <c r="J75" t="inlineStr">
         <is>
           <t>63-67</t>
         </is>
       </c>
-      <c r="K75" t="inlineStr"/>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>134000</t>
+        </is>
+      </c>
       <c r="L75" t="inlineStr"/>
       <c r="M75" t="inlineStr"/>
       <c r="N75" t="inlineStr"/>

--- a/data/mainboard_ipos.xlsx
+++ b/data/mainboard_ipos.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Mainboard IPOs" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Mainboard IPOs'!$A$1:$R$97</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Mainboard IPOs'!$A$1:$R$99</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -449,7 +449,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R97"/>
+  <dimension ref="A1:R99"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -5377,7 +5377,7 @@
       </c>
       <c r="R64" t="inlineStr">
         <is>
-          <t>2026-10-27 14:30:33</t>
+          <t>2026-10-28 15:10:36</t>
         </is>
       </c>
     </row>
@@ -5461,7 +5461,7 @@
       </c>
       <c r="R65" t="inlineStr">
         <is>
-          <t>2026-10-27 14:30:33</t>
+          <t>2026-10-28 15:10:36</t>
         </is>
       </c>
     </row>
@@ -5545,7 +5545,7 @@
       </c>
       <c r="R66" t="inlineStr">
         <is>
-          <t>2026-10-27 14:30:33</t>
+          <t>2026-10-28 15:10:36</t>
         </is>
       </c>
     </row>
@@ -5629,7 +5629,7 @@
       </c>
       <c r="R67" t="inlineStr">
         <is>
-          <t>2026-10-27 14:30:33</t>
+          <t>2026-10-28 15:10:36</t>
         </is>
       </c>
     </row>
@@ -5641,9 +5641,9 @@
       </c>
       <c r="B68" t="inlineStr"/>
       <c r="C68" t="inlineStr"/>
-      <c r="D68" s="3" t="inlineStr">
-        <is>
-          <t>Closed</t>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t>Listed</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -5692,12 +5692,12 @@
       <c r="P68" t="inlineStr"/>
       <c r="Q68" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/jioplatforms/JPL</t>
+          <t>https://www.moneycontrol.com/ipo/telecommunication-service-provider/jioplatforms/JPL</t>
         </is>
       </c>
       <c r="R68" t="inlineStr">
         <is>
-          <t>2026-10-27 14:30:33</t>
+          <t>2026-10-28 15:10:36</t>
         </is>
       </c>
     </row>
@@ -5709,9 +5709,9 @@
       </c>
       <c r="B69" t="inlineStr"/>
       <c r="C69" t="inlineStr"/>
-      <c r="D69" s="3" t="inlineStr">
-        <is>
-          <t>Closed</t>
+      <c r="D69" s="2" t="inlineStr">
+        <is>
+          <t>Listed</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -5760,12 +5760,12 @@
       <c r="P69" t="inlineStr"/>
       <c r="Q69" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/parashealthcare/PHL01</t>
+          <t>https://www.moneycontrol.com/ipo/hospitalhealthcare-services/parashealthcare/PHL01</t>
         </is>
       </c>
       <c r="R69" t="inlineStr">
         <is>
-          <t>2026-10-27 14:30:33</t>
+          <t>2026-10-28 15:10:36</t>
         </is>
       </c>
     </row>
@@ -5821,7 +5821,7 @@
       <c r="M70" t="inlineStr"/>
       <c r="N70" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O70" t="inlineStr"/>
@@ -5833,7 +5833,7 @@
       </c>
       <c r="R70" t="inlineStr">
         <is>
-          <t>2026-10-27 14:30:33</t>
+          <t>2026-10-28 15:10:36</t>
         </is>
       </c>
     </row>
@@ -5887,7 +5887,11 @@
       </c>
       <c r="L71" t="inlineStr"/>
       <c r="M71" t="inlineStr"/>
-      <c r="N71" t="inlineStr"/>
+      <c r="N71" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
       <c r="O71" t="inlineStr"/>
       <c r="P71" t="inlineStr"/>
       <c r="Q71" t="inlineStr">
@@ -5897,7 +5901,7 @@
       </c>
       <c r="R71" t="inlineStr">
         <is>
-          <t>2026-10-27 14:30:33</t>
+          <t>2026-10-28 15:10:36</t>
         </is>
       </c>
     </row>
@@ -5951,7 +5955,11 @@
       </c>
       <c r="L72" t="inlineStr"/>
       <c r="M72" t="inlineStr"/>
-      <c r="N72" t="inlineStr"/>
+      <c r="N72" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="O72" t="inlineStr"/>
       <c r="P72" t="inlineStr"/>
       <c r="Q72" t="inlineStr">
@@ -5961,7 +5969,7 @@
       </c>
       <c r="R72" t="inlineStr">
         <is>
-          <t>2026-10-27 14:30:33</t>
+          <t>2026-10-28 15:10:36</t>
         </is>
       </c>
     </row>
@@ -5973,9 +5981,9 @@
       </c>
       <c r="B73" t="inlineStr"/>
       <c r="C73" t="inlineStr"/>
-      <c r="D73" s="5" t="inlineStr">
-        <is>
-          <t>Upcoming</t>
+      <c r="D73" s="4" t="inlineStr">
+        <is>
+          <t>Open</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -6005,7 +6013,7 @@
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>153-162</t>
+          <t>162</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
@@ -6015,7 +6023,11 @@
       </c>
       <c r="L73" t="inlineStr"/>
       <c r="M73" t="inlineStr"/>
-      <c r="N73" t="inlineStr"/>
+      <c r="N73" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="O73" t="inlineStr"/>
       <c r="P73" t="inlineStr"/>
       <c r="Q73" t="inlineStr">
@@ -6025,7 +6037,7 @@
       </c>
       <c r="R73" t="inlineStr">
         <is>
-          <t>2026-10-27 14:30:33</t>
+          <t>2026-10-28 15:10:36</t>
         </is>
       </c>
     </row>
@@ -6089,7 +6101,7 @@
       </c>
       <c r="R74" t="inlineStr">
         <is>
-          <t>2026-10-27 14:30:33</t>
+          <t>2026-10-28 15:10:36</t>
         </is>
       </c>
     </row>
@@ -6636,7 +6648,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Mopshop Distribution Ltd</t>
+          <t>Maxwell Engineering Solutions Ltd</t>
         </is>
       </c>
       <c r="B84" t="inlineStr"/>
@@ -6648,33 +6660,33 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Aug 19, 2026</t>
+          <t>Oct 30, 2026</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Aug 21, 2026</t>
+          <t>Nov 03, 2026</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Aug 24, 2026</t>
+          <t>Nov 04, 2026</t>
         </is>
       </c>
       <c r="H84" t="inlineStr"/>
       <c r="I84" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>800</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>138</t>
+          <t>150-158</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>138000</t>
+          <t>126400</t>
         </is>
       </c>
       <c r="L84" t="inlineStr"/>
@@ -6684,19 +6696,19 @@
       <c r="P84" t="inlineStr"/>
       <c r="Q84" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/mopshopdistributionltd/MDL03</t>
+          <t>https://www.moneycontrol.com/ipo/maxwellengineeringsolutionsltd/MESL</t>
         </is>
       </c>
       <c r="R84" t="inlineStr">
         <is>
-          <t>2026-08-14 21:36:23</t>
+          <t>2026-10-28 15:10:36</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Paluck Technologies Ltd</t>
+          <t>Mopshop Distribution Ltd</t>
         </is>
       </c>
       <c r="B85" t="inlineStr"/>
@@ -6708,33 +6720,33 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Aug 28, 2026</t>
+          <t>Aug 19, 2026</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Sep 01, 2026</t>
+          <t>Aug 21, 2026</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Sep 02, 2026</t>
+          <t>Aug 24, 2026</t>
         </is>
       </c>
       <c r="H85" t="inlineStr"/>
       <c r="I85" t="inlineStr">
         <is>
-          <t>3000</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>46-48</t>
+          <t>138</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>144000</t>
+          <t>138000</t>
         </is>
       </c>
       <c r="L85" t="inlineStr"/>
@@ -6744,19 +6756,19 @@
       <c r="P85" t="inlineStr"/>
       <c r="Q85" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/palucktechnologiesltd/PTL08</t>
+          <t>https://www.moneycontrol.com/ipo/mopshopdistributionltd/MDL03</t>
         </is>
       </c>
       <c r="R85" t="inlineStr">
         <is>
-          <t>2026-08-25 09:29:52</t>
+          <t>2026-08-14 21:36:23</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Papadmalji Agro Foods Ltd</t>
+          <t>Paluck Technologies Ltd</t>
         </is>
       </c>
       <c r="B86" t="inlineStr"/>
@@ -6768,33 +6780,33 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Sep 29, 2026</t>
+          <t>Aug 28, 2026</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Oct 01, 2026</t>
+          <t>Sep 01, 2026</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Oct 05, 2026</t>
+          <t>Sep 02, 2026</t>
         </is>
       </c>
       <c r="H86" t="inlineStr"/>
       <c r="I86" t="inlineStr">
         <is>
-          <t>1600</t>
+          <t>3000</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>69-72</t>
+          <t>46-48</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>115200</t>
+          <t>144000</t>
         </is>
       </c>
       <c r="L86" t="inlineStr"/>
@@ -6804,19 +6816,19 @@
       <c r="P86" t="inlineStr"/>
       <c r="Q86" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/papadmaljiagrofoodsltd/PAF</t>
+          <t>https://www.moneycontrol.com/ipo/palucktechnologiesltd/PTL08</t>
         </is>
       </c>
       <c r="R86" t="inlineStr">
         <is>
-          <t>2026-09-25 14:20:09</t>
+          <t>2026-08-25 09:29:52</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Paramount Syntex Ltd</t>
+          <t>Papadmalji Agro Foods Ltd</t>
         </is>
       </c>
       <c r="B87" t="inlineStr"/>
@@ -6828,33 +6840,33 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Sep 30, 2026</t>
+          <t>Sep 29, 2026</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Oct 06, 2026</t>
+          <t>Oct 01, 2026</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Oct 07, 2026</t>
+          <t>Oct 05, 2026</t>
         </is>
       </c>
       <c r="H87" t="inlineStr"/>
       <c r="I87" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>1600</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>119-127</t>
+          <t>69-72</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>127000</t>
+          <t>115200</t>
         </is>
       </c>
       <c r="L87" t="inlineStr"/>
@@ -6864,7 +6876,7 @@
       <c r="P87" t="inlineStr"/>
       <c r="Q87" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/paramountsyntexltd/PSL06</t>
+          <t>https://www.moneycontrol.com/ipo/papadmaljiagrofoodsltd/PAF</t>
         </is>
       </c>
       <c r="R87" t="inlineStr">
@@ -6876,7 +6888,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Peshwa Wheat</t>
+          <t>Paramount Syntex Ltd</t>
         </is>
       </c>
       <c r="B88" t="inlineStr"/>
@@ -6888,33 +6900,33 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Sep 24, 2026</t>
+          <t>Sep 30, 2026</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Sep 28, 2026</t>
+          <t>Oct 06, 2026</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Sep 29, 2026</t>
+          <t>Oct 07, 2026</t>
         </is>
       </c>
       <c r="H88" t="inlineStr"/>
       <c r="I88" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>95-101</t>
+          <t>119-127</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>121200</t>
+          <t>127000</t>
         </is>
       </c>
       <c r="L88" t="inlineStr"/>
@@ -6924,135 +6936,135 @@
       <c r="P88" t="inlineStr"/>
       <c r="Q88" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/peshwawheat/PWL01</t>
+          <t>https://www.moneycontrol.com/ipo/paramountsyntexltd/PSL06</t>
         </is>
       </c>
       <c r="R88" t="inlineStr">
         <is>
-          <t>2026-09-22 14:03:25</t>
+          <t>2026-09-25 14:20:09</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Purple Style Labs Ltd</t>
+          <t>Peshwa Wheat</t>
         </is>
       </c>
       <c r="B89" t="inlineStr"/>
       <c r="C89" t="inlineStr"/>
-      <c r="D89" s="4" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="D89" s="5" t="inlineStr">
+        <is>
+          <t>Upcoming</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Aug 31, 2026</t>
+          <t>Sep 24, 2026</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Sep 02, 2026</t>
+          <t>Sep 28, 2026</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Sep 03, 2026</t>
+          <t>Sep 29, 2026</t>
         </is>
       </c>
       <c r="H89" t="inlineStr"/>
-      <c r="I89" t="inlineStr"/>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>1200</t>
+        </is>
+      </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>575</t>
-        </is>
-      </c>
-      <c r="K89" t="inlineStr"/>
+          <t>95-101</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>121200</t>
+        </is>
+      </c>
       <c r="L89" t="inlineStr"/>
       <c r="M89" t="inlineStr"/>
-      <c r="N89" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="N89" t="inlineStr"/>
       <c r="O89" t="inlineStr"/>
       <c r="P89" t="inlineStr"/>
       <c r="Q89" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/purplestylelabsltd/PSL05</t>
+          <t>https://www.moneycontrol.com/ipo/peshwawheat/PWL01</t>
         </is>
       </c>
       <c r="R89" t="inlineStr">
         <is>
-          <t>2026-09-02 13:25:30</t>
+          <t>2026-09-22 14:03:25</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Q&amp;T Foods Ltd</t>
+          <t>Purple Style Labs Ltd</t>
         </is>
       </c>
       <c r="B90" t="inlineStr"/>
       <c r="C90" t="inlineStr"/>
-      <c r="D90" s="5" t="inlineStr">
-        <is>
-          <t>Upcoming</t>
+      <c r="D90" s="4" t="inlineStr">
+        <is>
+          <t>Open</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Aug 12, 2026</t>
+          <t>Aug 31, 2026</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Aug 14, 2026</t>
+          <t>Sep 02, 2026</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Aug 17, 2026</t>
+          <t>Sep 03, 2026</t>
         </is>
       </c>
       <c r="H90" t="inlineStr"/>
-      <c r="I90" t="inlineStr">
-        <is>
-          <t>1200</t>
-        </is>
-      </c>
+      <c r="I90" t="inlineStr"/>
       <c r="J90" t="inlineStr">
         <is>
-          <t>115</t>
-        </is>
-      </c>
-      <c r="K90" t="inlineStr">
-        <is>
-          <t>138000</t>
-        </is>
-      </c>
+          <t>575</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr"/>
       <c r="L90" t="inlineStr"/>
       <c r="M90" t="inlineStr"/>
-      <c r="N90" t="inlineStr"/>
+      <c r="N90" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="O90" t="inlineStr"/>
       <c r="P90" t="inlineStr"/>
       <c r="Q90" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/qtfoodsltd/QFL</t>
+          <t>https://www.moneycontrol.com/ipo/purplestylelabsltd/PSL05</t>
         </is>
       </c>
       <c r="R90" t="inlineStr">
         <is>
-          <t>2026-08-10 10:24:29</t>
+          <t>2026-09-02 13:25:30</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Ravita Engineering Services Ltd</t>
+          <t>Q&amp;T Foods Ltd</t>
         </is>
       </c>
       <c r="B91" t="inlineStr"/>
@@ -7064,17 +7076,17 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Oct 13, 2026</t>
+          <t>Aug 12, 2026</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Oct 15, 2026</t>
+          <t>Aug 14, 2026</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Oct 16, 2026</t>
+          <t>Aug 17, 2026</t>
         </is>
       </c>
       <c r="H91" t="inlineStr"/>
@@ -7085,12 +7097,12 @@
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>105-112</t>
+          <t>115</t>
         </is>
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>134400</t>
+          <t>138000</t>
         </is>
       </c>
       <c r="L91" t="inlineStr"/>
@@ -7100,19 +7112,19 @@
       <c r="P91" t="inlineStr"/>
       <c r="Q91" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/ravitaengineeringservicesltd/RESL</t>
+          <t>https://www.moneycontrol.com/ipo/qtfoodsltd/QFL</t>
         </is>
       </c>
       <c r="R91" t="inlineStr">
         <is>
-          <t>2026-10-08 16:06:11</t>
+          <t>2026-08-10 10:24:29</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Shanti Inorganics Ltd</t>
+          <t>Ravita Engineering Services Ltd</t>
         </is>
       </c>
       <c r="B92" t="inlineStr"/>
@@ -7124,33 +7136,33 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Aug 31, 2026</t>
+          <t>Oct 13, 2026</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Sep 02, 2026</t>
+          <t>Oct 15, 2026</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Sep 03, 2026</t>
+          <t>Oct 16, 2026</t>
         </is>
       </c>
       <c r="H92" t="inlineStr"/>
       <c r="I92" t="inlineStr">
         <is>
-          <t>1600</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>79-83</t>
+          <t>105-112</t>
         </is>
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>132800</t>
+          <t>134400</t>
         </is>
       </c>
       <c r="L92" t="inlineStr"/>
@@ -7160,19 +7172,19 @@
       <c r="P92" t="inlineStr"/>
       <c r="Q92" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/shantiinorganicsltd/SIL34</t>
+          <t>https://www.moneycontrol.com/ipo/ravitaengineeringservicesltd/RESL</t>
         </is>
       </c>
       <c r="R92" t="inlineStr">
         <is>
-          <t>2026-08-25 09:29:52</t>
+          <t>2026-10-08 16:06:11</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Technocrats Plasma Systems Ltd</t>
+          <t>Shanti Inorganics Ltd</t>
         </is>
       </c>
       <c r="B93" t="inlineStr"/>
@@ -7184,33 +7196,33 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Aug 14, 2026</t>
+          <t>Aug 31, 2026</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Aug 18, 2026</t>
+          <t>Sep 02, 2026</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Aug 19, 2026</t>
+          <t>Sep 03, 2026</t>
         </is>
       </c>
       <c r="H93" t="inlineStr"/>
       <c r="I93" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>1600</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>125-132</t>
+          <t>79-83</t>
         </is>
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>132000</t>
+          <t>132800</t>
         </is>
       </c>
       <c r="L93" t="inlineStr"/>
@@ -7220,19 +7232,19 @@
       <c r="P93" t="inlineStr"/>
       <c r="Q93" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/technocratsplasmasystemsltd/TPSL</t>
+          <t>https://www.moneycontrol.com/ipo/shantiinorganicsltd/SIL34</t>
         </is>
       </c>
       <c r="R93" t="inlineStr">
         <is>
-          <t>2026-08-11 21:41:02</t>
+          <t>2026-08-25 09:29:52</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Unitec Fibres Ltd</t>
+          <t>Technocrats Plasma Systems Ltd</t>
         </is>
       </c>
       <c r="B94" t="inlineStr"/>
@@ -7244,33 +7256,33 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Sep 23, 2026</t>
+          <t>Aug 14, 2026</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Sep 25, 2026</t>
+          <t>Aug 18, 2026</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Sep 28, 2026</t>
+          <t>Aug 19, 2026</t>
         </is>
       </c>
       <c r="H94" t="inlineStr"/>
       <c r="I94" t="inlineStr">
         <is>
-          <t>1600</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>83-88</t>
+          <t>125-132</t>
         </is>
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t>140800</t>
+          <t>132000</t>
         </is>
       </c>
       <c r="L94" t="inlineStr"/>
@@ -7280,19 +7292,19 @@
       <c r="P94" t="inlineStr"/>
       <c r="Q94" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/unitecfibresltd/UFL03</t>
+          <t>https://www.moneycontrol.com/ipo/technocratsplasmasystemsltd/TPSL</t>
         </is>
       </c>
       <c r="R94" t="inlineStr">
         <is>
-          <t>2026-09-18 23:59:33</t>
+          <t>2026-08-11 21:41:02</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>VANS Electroengineerings Ltd</t>
+          <t>Unitec Fibres Ltd</t>
         </is>
       </c>
       <c r="B95" t="inlineStr"/>
@@ -7304,33 +7316,33 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Sep 29, 2026</t>
+          <t>Sep 23, 2026</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Oct 01, 2026</t>
+          <t>Sep 25, 2026</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Oct 05, 2026</t>
+          <t>Sep 28, 2026</t>
         </is>
       </c>
       <c r="H95" t="inlineStr"/>
       <c r="I95" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>1600</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>112-118</t>
+          <t>83-88</t>
         </is>
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t>141600</t>
+          <t>140800</t>
         </is>
       </c>
       <c r="L95" t="inlineStr"/>
@@ -7340,19 +7352,19 @@
       <c r="P95" t="inlineStr"/>
       <c r="Q95" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/vanselectroengineeringsltd/VEL03</t>
+          <t>https://www.moneycontrol.com/ipo/unitecfibresltd/UFL03</t>
         </is>
       </c>
       <c r="R95" t="inlineStr">
         <is>
-          <t>2026-09-25 14:20:09</t>
+          <t>2026-09-18 23:59:33</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Vaibhav Vyapaar Ltd</t>
+          <t>VANS Electroengineerings Ltd</t>
         </is>
       </c>
       <c r="B96" t="inlineStr"/>
@@ -7364,33 +7376,33 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Oct 13, 2026</t>
+          <t>Sep 29, 2026</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Oct 15, 2026</t>
+          <t>Oct 01, 2026</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Oct 16, 2026</t>
+          <t>Oct 05, 2026</t>
         </is>
       </c>
       <c r="H96" t="inlineStr"/>
       <c r="I96" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>50-52</t>
+          <t>112-118</t>
         </is>
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t>104000</t>
+          <t>141600</t>
         </is>
       </c>
       <c r="L96" t="inlineStr"/>
@@ -7400,19 +7412,19 @@
       <c r="P96" t="inlineStr"/>
       <c r="Q96" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/vaibhavvyapaarltd/VVL01</t>
+          <t>https://www.moneycontrol.com/ipo/vanselectroengineeringsltd/VEL03</t>
         </is>
       </c>
       <c r="R96" t="inlineStr">
         <is>
-          <t>2026-10-08 16:06:11</t>
+          <t>2026-09-25 14:20:09</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Vama Wovenfab Ltd</t>
+          <t>Vaibhav Vyapaar Ltd</t>
         </is>
       </c>
       <c r="B97" t="inlineStr"/>
@@ -7424,33 +7436,33 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Sep 15, 2026</t>
+          <t>Oct 13, 2026</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Sep 17, 2026</t>
+          <t>Oct 15, 2026</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Sep 18, 2026</t>
+          <t>Oct 16, 2026</t>
         </is>
       </c>
       <c r="H97" t="inlineStr"/>
       <c r="I97" t="inlineStr">
         <is>
-          <t>400</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>324-341</t>
+          <t>50-52</t>
         </is>
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t>136400</t>
+          <t>104000</t>
         </is>
       </c>
       <c r="L97" t="inlineStr"/>
@@ -7460,17 +7472,137 @@
       <c r="P97" t="inlineStr"/>
       <c r="Q97" t="inlineStr">
         <is>
+          <t>https://www.moneycontrol.com/ipo/vaibhavvyapaarltd/VVL01</t>
+        </is>
+      </c>
+      <c r="R97" t="inlineStr">
+        <is>
+          <t>2026-10-08 16:06:11</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>Vama Wovenfab Ltd</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr"/>
+      <c r="C98" t="inlineStr"/>
+      <c r="D98" s="5" t="inlineStr">
+        <is>
+          <t>Upcoming</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>Sep 15, 2026</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>Sep 17, 2026</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>Sep 18, 2026</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr"/>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>400</t>
+        </is>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>324-341</t>
+        </is>
+      </c>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>136400</t>
+        </is>
+      </c>
+      <c r="L98" t="inlineStr"/>
+      <c r="M98" t="inlineStr"/>
+      <c r="N98" t="inlineStr"/>
+      <c r="O98" t="inlineStr"/>
+      <c r="P98" t="inlineStr"/>
+      <c r="Q98" t="inlineStr">
+        <is>
           <t>https://www.moneycontrol.com/ipo/vamawovenfabltd/VWL01</t>
         </is>
       </c>
-      <c r="R97" t="inlineStr">
+      <c r="R98" t="inlineStr">
         <is>
           <t>2026-09-11 13:34:16</t>
         </is>
       </c>
     </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>Vectras Enprocon Ltd</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr"/>
+      <c r="C99" t="inlineStr"/>
+      <c r="D99" s="5" t="inlineStr">
+        <is>
+          <t>Upcoming</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>Oct 30, 2026</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>Nov 03, 2026</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>Nov 04, 2026</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr"/>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>1200</t>
+        </is>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>99-105</t>
+        </is>
+      </c>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>126000</t>
+        </is>
+      </c>
+      <c r="L99" t="inlineStr"/>
+      <c r="M99" t="inlineStr"/>
+      <c r="N99" t="inlineStr"/>
+      <c r="O99" t="inlineStr"/>
+      <c r="P99" t="inlineStr"/>
+      <c r="Q99" t="inlineStr">
+        <is>
+          <t>https://www.moneycontrol.com/ipo/vectrasenproconltd/VEL04</t>
+        </is>
+      </c>
+      <c r="R99" t="inlineStr">
+        <is>
+          <t>2026-10-28 15:10:36</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:R97"/>
+  <autoFilter ref="A1:R99"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/mainboard_ipos.xlsx
+++ b/data/mainboard_ipos.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Mainboard IPOs" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Mainboard IPOs'!$A$1:$R$99</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Mainboard IPOs'!$A$1:$R$100</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -449,7 +449,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R99"/>
+  <dimension ref="A1:R100"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -5377,7 +5377,7 @@
       </c>
       <c r="R64" t="inlineStr">
         <is>
-          <t>2026-10-28 15:10:36</t>
+          <t>2026-10-29 15:28:48</t>
         </is>
       </c>
     </row>
@@ -5461,7 +5461,7 @@
       </c>
       <c r="R65" t="inlineStr">
         <is>
-          <t>2026-10-28 15:10:36</t>
+          <t>2026-10-29 15:28:48</t>
         </is>
       </c>
     </row>
@@ -5545,7 +5545,7 @@
       </c>
       <c r="R66" t="inlineStr">
         <is>
-          <t>2026-10-28 15:10:36</t>
+          <t>2026-10-29 15:28:48</t>
         </is>
       </c>
     </row>
@@ -5629,7 +5629,7 @@
       </c>
       <c r="R67" t="inlineStr">
         <is>
-          <t>2026-10-28 15:10:36</t>
+          <t>2026-10-29 15:28:48</t>
         </is>
       </c>
     </row>
@@ -5681,15 +5681,31 @@
           <t>13428</t>
         </is>
       </c>
-      <c r="L68" t="inlineStr"/>
-      <c r="M68" t="inlineStr"/>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>1358</t>
+        </is>
+      </c>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>16296</t>
+        </is>
+      </c>
       <c r="N68" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="O68" t="inlineStr"/>
-      <c r="P68" t="inlineStr"/>
+      <c r="O68" t="inlineStr">
+        <is>
+          <t>2868</t>
+        </is>
+      </c>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
       <c r="Q68" t="inlineStr">
         <is>
           <t>https://www.moneycontrol.com/ipo/telecommunication-service-provider/jioplatforms/JPL</t>
@@ -5697,7 +5713,7 @@
       </c>
       <c r="R68" t="inlineStr">
         <is>
-          <t>2026-10-28 15:10:36</t>
+          <t>2026-10-29 15:28:48</t>
         </is>
       </c>
     </row>
@@ -5749,15 +5765,31 @@
           <t>14553</t>
         </is>
       </c>
-      <c r="L69" t="inlineStr"/>
-      <c r="M69" t="inlineStr"/>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>720</t>
+        </is>
+      </c>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>15120</t>
+        </is>
+      </c>
       <c r="N69" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="O69" t="inlineStr"/>
-      <c r="P69" t="inlineStr"/>
+      <c r="O69" t="inlineStr">
+        <is>
+          <t>567</t>
+        </is>
+      </c>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="Q69" t="inlineStr">
         <is>
           <t>https://www.moneycontrol.com/ipo/hospitalhealthcare-services/parashealthcare/PHL01</t>
@@ -5765,7 +5797,7 @@
       </c>
       <c r="R69" t="inlineStr">
         <is>
-          <t>2026-10-28 15:10:36</t>
+          <t>2026-10-29 15:28:48</t>
         </is>
       </c>
     </row>
@@ -5777,9 +5809,9 @@
       </c>
       <c r="B70" t="inlineStr"/>
       <c r="C70" t="inlineStr"/>
-      <c r="D70" s="4" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="D70" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -5821,7 +5853,7 @@
       <c r="M70" t="inlineStr"/>
       <c r="N70" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="O70" t="inlineStr"/>
@@ -5833,7 +5865,7 @@
       </c>
       <c r="R70" t="inlineStr">
         <is>
-          <t>2026-10-28 15:10:36</t>
+          <t>2026-10-29 15:28:48</t>
         </is>
       </c>
     </row>
@@ -5889,7 +5921,7 @@
       <c r="M71" t="inlineStr"/>
       <c r="N71" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>94</t>
         </is>
       </c>
       <c r="O71" t="inlineStr"/>
@@ -5901,7 +5933,7 @@
       </c>
       <c r="R71" t="inlineStr">
         <is>
-          <t>2026-10-28 15:10:36</t>
+          <t>2026-10-29 15:28:48</t>
         </is>
       </c>
     </row>
@@ -5957,7 +5989,7 @@
       <c r="M72" t="inlineStr"/>
       <c r="N72" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="O72" t="inlineStr"/>
@@ -5969,7 +6001,7 @@
       </c>
       <c r="R72" t="inlineStr">
         <is>
-          <t>2026-10-28 15:10:36</t>
+          <t>2026-10-29 15:28:48</t>
         </is>
       </c>
     </row>
@@ -6025,7 +6057,7 @@
       <c r="M73" t="inlineStr"/>
       <c r="N73" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="O73" t="inlineStr"/>
@@ -6037,7 +6069,7 @@
       </c>
       <c r="R73" t="inlineStr">
         <is>
-          <t>2026-10-28 15:10:36</t>
+          <t>2026-10-29 15:28:48</t>
         </is>
       </c>
     </row>
@@ -6049,9 +6081,9 @@
       </c>
       <c r="B74" t="inlineStr"/>
       <c r="C74" t="inlineStr"/>
-      <c r="D74" s="5" t="inlineStr">
-        <is>
-          <t>Upcoming</t>
+      <c r="D74" s="4" t="inlineStr">
+        <is>
+          <t>Open</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -6081,7 +6113,7 @@
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>78-82</t>
+          <t>82</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
@@ -6091,7 +6123,11 @@
       </c>
       <c r="L74" t="inlineStr"/>
       <c r="M74" t="inlineStr"/>
-      <c r="N74" t="inlineStr"/>
+      <c r="N74" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="O74" t="inlineStr"/>
       <c r="P74" t="inlineStr"/>
       <c r="Q74" t="inlineStr">
@@ -6101,7 +6137,7 @@
       </c>
       <c r="R74" t="inlineStr">
         <is>
-          <t>2026-10-28 15:10:36</t>
+          <t>2026-10-29 15:28:48</t>
         </is>
       </c>
     </row>
@@ -7601,8 +7637,60 @@
         </is>
       </c>
     </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>Vedant Poly Fabs Ltd</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr"/>
+      <c r="C100" t="inlineStr"/>
+      <c r="D100" s="5" t="inlineStr">
+        <is>
+          <t>Upcoming</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>Nov 02, 2026</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>Nov 04, 2026</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>Nov 05, 2026</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr"/>
+      <c r="I100" t="inlineStr"/>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>88-94</t>
+        </is>
+      </c>
+      <c r="K100" t="inlineStr"/>
+      <c r="L100" t="inlineStr"/>
+      <c r="M100" t="inlineStr"/>
+      <c r="N100" t="inlineStr"/>
+      <c r="O100" t="inlineStr"/>
+      <c r="P100" t="inlineStr"/>
+      <c r="Q100" t="inlineStr">
+        <is>
+          <t>https://www.moneycontrol.com/ipo/vedantpolyfabsltd/VPF02</t>
+        </is>
+      </c>
+      <c r="R100" t="inlineStr">
+        <is>
+          <t>2026-10-29 15:28:48</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:R99"/>
+  <autoFilter ref="A1:R100"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/mainboard_ipos.xlsx
+++ b/data/mainboard_ipos.xlsx
@@ -5377,7 +5377,7 @@
       </c>
       <c r="R64" t="inlineStr">
         <is>
-          <t>2026-10-29 15:28:48</t>
+          <t>2026-10-30 15:31:45</t>
         </is>
       </c>
     </row>
@@ -5629,7 +5629,7 @@
       </c>
       <c r="R67" t="inlineStr">
         <is>
-          <t>2026-10-29 15:28:48</t>
+          <t>2026-10-30 15:31:45</t>
         </is>
       </c>
     </row>
@@ -5713,7 +5713,7 @@
       </c>
       <c r="R68" t="inlineStr">
         <is>
-          <t>2026-10-29 15:28:48</t>
+          <t>2026-10-30 15:31:45</t>
         </is>
       </c>
     </row>
@@ -5797,7 +5797,7 @@
       </c>
       <c r="R69" t="inlineStr">
         <is>
-          <t>2026-10-29 15:28:48</t>
+          <t>2026-10-30 15:31:45</t>
         </is>
       </c>
     </row>
@@ -5865,7 +5865,7 @@
       </c>
       <c r="R70" t="inlineStr">
         <is>
-          <t>2026-10-29 15:28:48</t>
+          <t>2026-10-30 15:31:45</t>
         </is>
       </c>
     </row>
@@ -5877,9 +5877,9 @@
       </c>
       <c r="B71" t="inlineStr"/>
       <c r="C71" t="inlineStr"/>
-      <c r="D71" s="4" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="D71" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -5921,7 +5921,7 @@
       <c r="M71" t="inlineStr"/>
       <c r="N71" t="inlineStr">
         <is>
-          <t>94</t>
+          <t>241</t>
         </is>
       </c>
       <c r="O71" t="inlineStr"/>
@@ -5933,7 +5933,7 @@
       </c>
       <c r="R71" t="inlineStr">
         <is>
-          <t>2026-10-29 15:28:48</t>
+          <t>2026-10-30 15:31:45</t>
         </is>
       </c>
     </row>
@@ -5945,9 +5945,9 @@
       </c>
       <c r="B72" t="inlineStr"/>
       <c r="C72" t="inlineStr"/>
-      <c r="D72" s="4" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="D72" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -5989,7 +5989,7 @@
       <c r="M72" t="inlineStr"/>
       <c r="N72" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>9</t>
         </is>
       </c>
       <c r="O72" t="inlineStr"/>
@@ -6001,7 +6001,7 @@
       </c>
       <c r="R72" t="inlineStr">
         <is>
-          <t>2026-10-29 15:28:48</t>
+          <t>2026-10-30 15:31:45</t>
         </is>
       </c>
     </row>
@@ -6069,7 +6069,7 @@
       </c>
       <c r="R73" t="inlineStr">
         <is>
-          <t>2026-10-29 15:28:48</t>
+          <t>2026-10-30 15:31:45</t>
         </is>
       </c>
     </row>
@@ -6125,7 +6125,7 @@
       <c r="M74" t="inlineStr"/>
       <c r="N74" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="O74" t="inlineStr"/>
@@ -6137,7 +6137,7 @@
       </c>
       <c r="R74" t="inlineStr">
         <is>
-          <t>2026-10-29 15:28:48</t>
+          <t>2026-10-30 15:31:45</t>
         </is>
       </c>
     </row>
@@ -7666,13 +7666,21 @@
         </is>
       </c>
       <c r="H100" t="inlineStr"/>
-      <c r="I100" t="inlineStr"/>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>1200</t>
+        </is>
+      </c>
       <c r="J100" t="inlineStr">
         <is>
           <t>88-94</t>
         </is>
       </c>
-      <c r="K100" t="inlineStr"/>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>112800</t>
+        </is>
+      </c>
       <c r="L100" t="inlineStr"/>
       <c r="M100" t="inlineStr"/>
       <c r="N100" t="inlineStr"/>

--- a/data/mainboard_ipos.xlsx
+++ b/data/mainboard_ipos.xlsx
@@ -5377,7 +5377,7 @@
       </c>
       <c r="R64" t="inlineStr">
         <is>
-          <t>2026-10-30 15:31:45</t>
+          <t>2026-10-31 15:09:43</t>
         </is>
       </c>
     </row>
@@ -5629,7 +5629,7 @@
       </c>
       <c r="R67" t="inlineStr">
         <is>
-          <t>2026-10-30 15:31:45</t>
+          <t>2026-10-31 15:09:43</t>
         </is>
       </c>
     </row>
@@ -5713,7 +5713,7 @@
       </c>
       <c r="R68" t="inlineStr">
         <is>
-          <t>2026-10-30 15:31:45</t>
+          <t>2026-10-31 15:09:43</t>
         </is>
       </c>
     </row>
@@ -5797,7 +5797,7 @@
       </c>
       <c r="R69" t="inlineStr">
         <is>
-          <t>2026-10-30 15:31:45</t>
+          <t>2026-10-31 15:09:43</t>
         </is>
       </c>
     </row>
@@ -5860,12 +5860,12 @@
       <c r="P70" t="inlineStr"/>
       <c r="Q70" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/ipo/eaaaindiaalternativesltd/EIA</t>
+          <t>https://www.moneycontrol.com/ipo/eaaaindiaalternatives/EIA</t>
         </is>
       </c>
       <c r="R70" t="inlineStr">
         <is>
-          <t>2026-10-30 15:31:45</t>
+          <t>2026-10-31 15:09:43</t>
         </is>
       </c>
     </row>
@@ -5933,7 +5933,7 @@
       </c>
       <c r="R71" t="inlineStr">
         <is>
-          <t>2026-10-30 15:31:45</t>
+          <t>2026-10-31 15:09:43</t>
         </is>
       </c>
     </row>
@@ -6001,7 +6001,7 @@
       </c>
       <c r="R72" t="inlineStr">
         <is>
-          <t>2026-10-30 15:31:45</t>
+          <t>2026-10-31 15:09:43</t>
         </is>
       </c>
     </row>
@@ -6013,9 +6013,9 @@
       </c>
       <c r="B73" t="inlineStr"/>
       <c r="C73" t="inlineStr"/>
-      <c r="D73" s="4" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="D73" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -6057,7 +6057,7 @@
       <c r="M73" t="inlineStr"/>
       <c r="N73" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="O73" t="inlineStr"/>
@@ -6069,7 +6069,7 @@
       </c>
       <c r="R73" t="inlineStr">
         <is>
-          <t>2026-10-30 15:31:45</t>
+          <t>2026-10-31 15:09:43</t>
         </is>
       </c>
     </row>
@@ -6125,7 +6125,7 @@
       <c r="M74" t="inlineStr"/>
       <c r="N74" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="O74" t="inlineStr"/>
@@ -6137,7 +6137,7 @@
       </c>
       <c r="R74" t="inlineStr">
         <is>
-          <t>2026-10-30 15:31:45</t>
+          <t>2026-10-31 15:09:43</t>
         </is>
       </c>
     </row>
